--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="753">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">Martin BUBER</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Buber"  title=" Wikipedia"&gt;Martin BUBER&lt;/a&gt; était un philosophe juif autrichien surtout célèbre pour sa pensée du dialogue et de la rencontre "Ich und Du" (I and Thou). Sa biographie et son œuvre ont eu une influence durable sur la philosophie politique, la théologie et l’éducation.  Son parcours intellectuel est marqué par une “philosophie du dialogue” qui cherche à rendre l’existence vécue comme  &lt;a href="https://www.youtube.com/watch?v=x2C7AQRu-iw&amp;t=37s" title=" La Solitude Moderne : La Réponse de Martin Buber (Philosophie Pratique) par Philosopheasy en français"&gt;relation authentique &lt;/a&gt; plutôt que comme simple connaissance ou instrumentalisation de l’autre. &lt;/p&gt; &lt;p&gt;  Avec Franz Rosenzweig, il fonde et dirige des institutions d’éducation juive et développe une pédagogie fondée sur le dialogue entre les individus et entre le peuple juif et le monde extérieur. Cette collaboration est centrale dans son développement. Son oeuvre majeure : - &lt;a href="https://www.youtube.com/watch?v=obuZPJirPkE" title=" Martin Buber : Moi et Tu par PhilosophyToons"&gt;" l’essai Ich und Du" &lt;/a&gt; paru en 1923 propose que les relations humaines ne peuvent pas être réduites à des rapports utilitaires ou à des abstractions. Cette pensée s’applique à l’éthique, à la religion, et à l’éducation. Il oppose l’“I–It” (je-tu) à l’“I–Thou” (je-toi), arguant que l’existence humaine se réalise vraiment dans des relations vécues comme présence et écoute réciproque.&lt;/p&gt; &lt;p&gt;  Il a été actif dans l’éducation des adultes juifs en Allemagne et a plaidé pour une pédagogie fondée sur l’engagement personnel et la relation authentique plutôt que sur l’instruction pure. Ses idées inspirent des discussions sur le droit à la différence, le pluralisme religieux et les approches éthiques des conflits, tout en restant critiques des formes de discours essentialistes. &lt;/p&gt;  &lt;audio controls title="Martin Buber, sentinelle de l'humanité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-03.01.2016-ITEMA_20879863-2015C14958E0049-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Buber"  title=" Wikipedia"&gt;Martin BUBER&lt;/a&gt; était un philosophe juif autrichien surtout célèbre pour sa pensée du dialogue et de la rencontre "Ich und Du" (I and Thou). Sa biographie et son œuvre ont eu une influence durable sur la philosophie politique, la théologie et l’éducation.  Son parcours intellectuel est marqué par une “philosophie du dialogue” qui cherche à rendre l’existence vécue comme  &lt;a href="https://www.youtube.com/watch?v=x2C7AQRu-iw" title=" La Solitude Moderne : La Réponse de Martin Buber (Philosophie Pratique) par Philosopheasy en français"&gt;relation authentique &lt;/a&gt; plutôt que comme simple connaissance ou instrumentalisation de l’autre. &lt;/p&gt; &lt;p&gt;  Avec Franz Rosenzweig, il fonde et dirige des institutions d’éducation juive et développe une pédagogie fondée sur le dialogue entre les individus et entre le peuple juif et le monde extérieur. Cette collaboration est centrale dans son développement. Son oeuvre majeure : - &lt;a href="https://www.youtube.com/watch?v=obuZPJirPkE" title=" Martin Buber : Moi et Tu par PhilosophyToons"&gt;" l’essai Ich und Du" &lt;/a&gt; paru en 1923 propose que les relations humaines ne peuvent pas être réduites à des rapports utilitaires ou à des abstractions. Cette pensée s’applique à l’éthique, à la religion, et à l’éducation. Il oppose l’“I–It” (je-tu) à l’“I–Thou” (je-toi), arguant que l’existence humaine se réalise vraiment dans des relations vécues comme présence et écoute réciproque.&lt;/p&gt; &lt;p&gt;  Il a été actif dans l’éducation des adultes juifs en Allemagne et a plaidé pour une pédagogie fondée sur l’engagement personnel et la relation authentique plutôt que sur l’instruction pure. Ses idées inspirent des discussions sur le droit à la différence, le pluralisme religieux et les approches éthiques des conflits, tout en restant critiques des formes de discours essentialistes. &lt;/p&gt;  &lt;audio controls title="Martin Buber, sentinelle de l'humanité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-03.01.2016-ITEMA_20879863-2015C14958E0049-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">x2C7AQRu-iw</t>
@@ -1245,6 +1245,34 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe autrichien érudit de grande renommée en matière de tradition &amp; de littérature juives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1879 – 1934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hans HAHN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hans_Hahn_(math%C3%A9maticien)"  title=" Wikipedia"&gt;Hans HAHN&lt;/a&gt; était un mathématicien autrichien, surtout connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach. Il fut également l’un des principaux fondateurs du Cercle de Vienne, avec Moritz Schlick, Philipp Frank et Otto Neurath. Son intérêt pour la philosophie ne fut donc pas celui d’un philosophe professionnel, mais celui d’un mathématicien qui cherchait à comprendre le rapport entre logique, mathématiques, langage et connaissance scientifique. &lt;/p&gt; &lt;p&gt; Sa philosophie s’inscrit dans l’empirisme logique ou positivisme logique. Comme les &lt;a href="https://www.youtube.com/watch?v=VReApTp5_zg" title=" le cercle de vienne par philosophie analytique"&gt;autres membres du Cercle de Vienne, &lt;/a&gt;  il rejetait la métaphysique traditionnelle lorsqu’elle prétendait produire une connaissance indépendante de toute expérience ou de toute méthode logique. Il contestait notamment l’idée kantienne de vérités « synthétiques a priori » : selon cette orientation, une proposition est soit logique ou mathématique, soit empirique et vérifiable à partir de l’expérience. La philosophie devait ainsi se rapprocher de l’analyse logique des énoncés scientifiques. &lt;/p&gt; &lt;p&gt; Il accordait toutefois aux mathématiques un statut particulier. Il ne pensait pas qu’elles décrivent directement des objets réels, comme le font les sciences expérimentales. Les mathématiques et la logique établissent plutôt des relations formelles entre des propositions ou des symboles. Elles indiquent ce qui découle nécessairement de certaines règles et de certains axiomes. En ce sens, les vérités mathématiques sont analytiques : elles ne tirent pas leur certitude de l’observation, mais de la structure logique du système dans lequel elles sont formulées. &lt;/p&gt; &lt;p&gt; Un aspect important de sa pensée est son refus de fonder les mathématiques sur une intuition particulière. Il se méfiait de l’« intuition » au sens kantien, c’est-à-dire de l’idée que l’esprit aurait un accès immédiat aux structures mathématiques. Il défendait plutôt l’axiomatisation et la rigueur formelle, notamment dans l’arithmétique et l’analyse. Mais il ne réduisait pas nécessairement toute signification à une vérification directe : il soutenait que les hypothèses scientifiques peuvent être significatives même lorsqu’elles ne sont pas définitivement vérifiables, ce qui conduit à assouplir le vérificationnisme strict. &lt;/p&gt; &lt;p&gt; Il concevait la logique non comme une science décrivant les propriétés les plus générales des objets, mais comme un instrument construit par les êtres humains pour parler du monde avec précision. La logique ne serait donc pas une réalité cachée dans les choses : elle apparaît lorsque nous organisons nos énoncés au moyen d’un symbolisme. Sa philosophie défend ainsi une conception scientifique, anti-métaphysique et formaliste de la connaissance, tout en laissant une place aux hypothèses et à la diversité des systèmes logiques. Son œuvre philosophique, moins abondante que son œuvre mathématique, a néanmoins contribué à préparer plusieurs thèmes du positivisme logique et de la philosophie analytique des sciences. &lt;/p&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zlRPxIb2czc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hans HAHN par Wikipedia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hhahn-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positivisme logique ; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mathématicien autrichien connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach.</t>
   </si>
   <si>
     <t xml:space="preserve">1880 – 1903</t>
@@ -1401,6 +1429,25 @@
   </si>
   <si>
     <t xml:space="preserve">éconnomiste qui révolutionna l'économie avec sa macroéconomie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1884 – 1966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philipp FRANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philipp_Frank"  title=" Wikipedia"&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48_Ab-qQzvA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philipp FRANKscien philosopher par Essai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">physicien théoricien, mathématicien et philosophe des sciences austro-américain et l’un des membres fondateurs du Cercle de Vienne.</t>
   </si>
   <si>
     <t xml:space="preserve">1971</t>
@@ -1485,9 +1532,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/lesniewski-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logique</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe polonais spécialiste des fondements de la logique &amp; des mathématiques.</t>
@@ -2497,7 +2541,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2625,6 +2669,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
@@ -2714,7 +2771,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2792,10 +2849,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2804,6 +2857,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3059,7 +3124,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -4503,12 +4568,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>173</v>
+        <v>1879</v>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1934</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>341</v>
@@ -4516,7 +4581,7 @@
       <c r="D39" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="10" t="s">
         <v>343</v>
       </c>
       <c r="F39" s="7" t="s">
@@ -4525,7 +4590,7 @@
       <c r="G39" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="10" t="s">
         <v>346</v>
       </c>
       <c r="I39" s="9"/>
@@ -4533,91 +4598,91 @@
         <v>22</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>151</v>
+        <v>347</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
+      </c>
+      <c r="M39" s="19" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>1931</v>
+        <v>1880</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>355</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>355</v>
+        <v>151</v>
       </c>
       <c r="L40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="M40" s="14" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="41" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>1882</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>1945</v>
+        <v>1931</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="E41" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="F41" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="G41" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="10" t="s">
         <v>362</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>22</v>
+        <v>363</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>180</v>
+        <v>364</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="M41" s="15" t="s">
         <v>365</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4625,44 +4690,46 @@
         <v>1882</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="9"/>
+        <v>369</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>371</v>
+      </c>
       <c r="H42" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>370</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>371</v>
+        <v>180</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M42" s="15" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>374</v>
+        <v>1882</v>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>1937</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>375</v>
@@ -4670,77 +4737,75 @@
       <c r="D43" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="7"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="I43" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="J43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="M43" s="14" t="s">
+      <c r="M43" s="15" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1883</v>
       </c>
-      <c r="B44" s="7" t="n">
-        <v>1946</v>
+      <c r="B44" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="E44" s="12" t="s">
         <v>385</v>
       </c>
+      <c r="E44" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="F44" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="H44" s="10" t="s">
         <v>388</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>389</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="M44" s="2" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M44" s="14" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>1885</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>391</v>
+        <v>1883</v>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>1946</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>392</v>
@@ -4748,7 +4813,7 @@
       <c r="D45" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="12" t="s">
         <v>394</v>
       </c>
       <c r="F45" s="7" t="s">
@@ -4757,1116 +4822,1111 @@
       <c r="G45" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>397</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M45" s="2" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B46" s="7" t="s">
+      <c r="D46" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="E46" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="F46" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="G46" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="H46" s="10"/>
+      <c r="I46" s="9"/>
+      <c r="K46" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="M46" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="G46" s="9" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="2" t="s">
+      <c r="D47" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M46" s="2" t="s">
+      <c r="E47" s="18" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B47" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="G47" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="H47" s="9" t="s">
         <v>412</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>416</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
-        <v>294</v>
+        <v>413</v>
       </c>
       <c r="K47" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M47" s="2" t="s">
+      <c r="D48" s="8" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>1891</v>
-      </c>
-      <c r="B48" s="7" t="s">
+      <c r="E48" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="G48" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="H48" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>425</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>74</v>
+        <v>423</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>171</v>
+        <v>94</v>
       </c>
       <c r="M48" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="F49" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="H49" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="I49" s="9"/>
+      <c r="J49" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="J49" s="2" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L49" s="2" t="s">
+      <c r="C50" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="D50" s="8" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
-        <v>1898</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="E50" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="F50" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="G50" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="H50" s="9" t="s">
         <v>439</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>442</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="K50" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E51" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="G51" s="2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C51" s="7" t="s">
+      <c r="H51" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="J51" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="K51" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="M51" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G51" s="9" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="C52" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M51" s="2" t="s">
+      <c r="D52" s="8" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="E52" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="F52" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="G52" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="H52" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="H52" s="10" t="s">
-        <v>459</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+      <c r="L54" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
         <v>1901</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B55" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>464</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="G53" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="J53" s="2" t="s">
+      <c r="C55" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="L53" s="2" t="s">
+      <c r="K55" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>1967</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="G55" s="9"/>
-      <c r="H55" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
+    <row r="56" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
         <v>1902</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="1" t="n">
+        <v>1967</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="D56" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="E56" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="F56" s="22"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="I56" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G56" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="I56" s="9"/>
       <c r="J56" s="2" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>152</v>
       </c>
       <c r="M56" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B57" s="7" t="n">
-        <v>1993</v>
-      </c>
-      <c r="C57" s="7" t="s">
+      <c r="D57" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="E57" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="F57" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="F57" s="7"/>
       <c r="G57" s="9"/>
       <c r="H57" s="10" t="s">
         <v>494</v>
       </c>
       <c r="I57" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="K57" s="2" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="K59" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>510</v>
-      </c>
-      <c r="F59" s="7" t="s">
+      <c r="L59" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="M59" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="H59" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="I59" s="9"/>
-      <c r="J59" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M59" s="22" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="60" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1907</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E60" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="F60" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="G60" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="H60" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="I60" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L60" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="M60" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="I60" s="9"/>
-      <c r="J60" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="M60" s="2" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="D61" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="E61" s="23" t="s">
         <v>524</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="F61" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="G61" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="H61" s="10" t="s">
         <v>527</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>529</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>160</v>
+        <v>413</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>258</v>
+        <v>364</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="M61" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="M61" s="24" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B62" s="7" t="s">
+      <c r="D62" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="E62" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="F62" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="G62" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="H62" s="10" t="s">
         <v>535</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>537</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L62" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="D63" s="8" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B63" s="7" t="n">
-        <v>2004</v>
-      </c>
-      <c r="C63" s="7" t="s">
+      <c r="E63" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="F63" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="G63" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="H63" s="9" t="s">
         <v>543</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>545</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
         <v>1909</v>
       </c>
-      <c r="B64" s="7" t="n">
-        <v>1996</v>
+      <c r="B64" s="7" t="s">
+        <v>545</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="E64" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="F64" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="G64" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="H64" s="9" t="s">
         <v>551</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>553</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>152</v>
+        <v>552</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B65" s="7" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="E65" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="F65" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="G65" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="H65" s="10" t="s">
         <v>559</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>561</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="K65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M65" s="2" t="s">
+      <c r="D66" s="8" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C66" s="7" t="s">
+      <c r="E66" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="F66" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="G66" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="H66" s="10" t="s">
         <v>567</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>569</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
-        <v>433</v>
+        <v>139</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="L66" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="D67" s="8" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="E67" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="F67" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="G67" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="H67" s="10" t="s">
         <v>575</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>578</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M67" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="D68" s="8" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
-        <v>1914</v>
-      </c>
-      <c r="B68" s="7" t="s">
+      <c r="E68" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="G68" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="H68" s="10" t="s">
         <v>583</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>586</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M68" s="2" t="s">
+      <c r="D69" s="8" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>1919</v>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C69" s="1" t="s">
+      <c r="E69" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="F69" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="G69" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="H69" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>594</v>
-      </c>
+      <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>205</v>
+        <v>576</v>
       </c>
       <c r="L69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="D70" s="8" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="C70" s="7" t="s">
+      <c r="E70" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="F70" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="G70" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="H70" s="9" t="s">
         <v>600</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>602</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
+        <v>1919</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L70" s="2" t="s">
+      <c r="D71" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B71" s="7" t="s">
+      <c r="F71" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="G71" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="H71" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E71" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>94</v>
+        <v>609</v>
       </c>
       <c r="M71" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="E72" s="11" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
-        <v>1923</v>
-      </c>
-      <c r="B72" s="7" t="s">
+      <c r="F72" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="G72" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="H72" s="9" t="s">
         <v>616</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>620</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
-        <v>33</v>
+        <v>617</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>94</v>
+        <v>618</v>
       </c>
       <c r="M72" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B73" s="7" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C73" s="7" t="s">
+      <c r="D73" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="E73" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="F73" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="G73" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="H73" s="9" t="s">
         <v>626</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>627</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M73" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>628</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B74" s="7" t="n">
-        <v>2003</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>629</v>
@@ -5874,346 +5934,349 @@
       <c r="D74" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="10" t="s">
+      <c r="F74" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="I74" s="10" t="s">
+      <c r="G74" s="9" t="s">
         <v>633</v>
       </c>
+      <c r="H74" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>398</v>
+        <v>33</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>634</v>
+        <v>180</v>
       </c>
       <c r="L74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="M74" s="14" t="s">
+    </row>
+    <row r="75" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="C75" s="7" t="s">
+      <c r="D75" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="E75" s="11" t="s">
         <v>638</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="F75" s="7" t="s">
         <v>639</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="G75" s="9" t="s">
         <v>640</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="H75" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="H75" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>643</v>
-      </c>
+      <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M75" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="D76" s="8" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
+      <c r="E76" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="M76" s="14" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>1925</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>648</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="H76" s="9" t="s">
+      <c r="B77" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C77" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="2" t="s">
+      <c r="D77" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="M76" s="14" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+      <c r="L78" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="M78" s="14" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>660</v>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>1926</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L78" s="2" t="s">
+      <c r="B79" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="C79" s="7" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B79" s="7" t="s">
+      <c r="D79" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="E79" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="G79" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="H79" s="9" t="s">
         <v>674</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>676</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>94</v>
+        <v>675</v>
       </c>
       <c r="M79" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B80" s="7" t="s">
+      <c r="E80" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="F80" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="G80" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="H80" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>682</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K80" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="7" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M80" s="2" t="s">
+      <c r="D81" s="8" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="B81" s="7" t="s">
+      <c r="E81" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="F81" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="G81" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="H81" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>693</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M81" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B82" s="7" t="n">
-        <v>2018</v>
+        <v>1929</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>692</v>
       </c>
       <c r="C82" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="E82" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="F82" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="G82" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="H82" s="9" t="s">
         <v>698</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>699</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
-        <v>433</v>
+        <v>33</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>74</v>
+        <v>699</v>
       </c>
       <c r="L82" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="M82" s="14" t="s">
+    </row>
+    <row r="83" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="7" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>701</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B83" s="7" t="n">
-        <v>2026</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>702</v>
@@ -6221,7 +6284,7 @@
       <c r="D83" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="11" t="s">
         <v>704</v>
       </c>
       <c r="F83" s="7" t="s">
@@ -6230,32 +6293,29 @@
       <c r="G83" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="9" t="s">
         <v>707</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="M83" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>708</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>702</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>709</v>
@@ -6274,7 +6334,7 @@
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="2" t="s">
-        <v>496</v>
+        <v>447</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>74</v>
@@ -6286,12 +6346,12 @@
         <v>715</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>716</v>
@@ -6299,7 +6359,7 @@
       <c r="D85" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="E85" s="12" t="s">
         <v>718</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -6316,111 +6376,189 @@
         <v>139</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>94</v>
+        <v>511</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="M86" s="14" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="I87" s="9"/>
+      <c r="J87" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="7" t="n">
         <v>1942</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>645</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>725</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>728</v>
-      </c>
-      <c r="I86" s="10"/>
-      <c r="J86" s="2" t="s">
+      <c r="B88" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="I88" s="10"/>
+      <c r="J88" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
+      <c r="K88" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="n">
         <v>1954</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B89" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>734</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="K87" s="2" t="s">
+      <c r="C89" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K89" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L87" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
+      <c r="L89" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6454,55 +6592,58 @@
     <hyperlink ref="H33" r:id="rId24" display="https://www.laphilo.fr/pho/ktwardowski-mini.webp"/>
     <hyperlink ref="E34" r:id="rId25" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Bertrand_Russell&quot;  title=&quot; Wikipedia&quot;&gt; Bertrand RUSSELL&lt;/a&gt;  était un philosophe, logicien, mathématicien, écrivain et militant britannique empiriste et rationaliste. Ses contributions majeures en mathématiques et en logique ont jeté les bases de la &lt;a href=&quot;https://www.youtube.com/watch?v=I1-6SA1DfRA&amp;ab_channel=HeureBleue&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;pourquoi la philosophie analytique est méconnue en France par Heure Bleue &quot;&gt;philosophie analytique&lt;/a&gt;, un courant dominant de la philosophie anglo-américaine en opposition avec la philosophie continentale romano-germanique. &lt;/p&gt; &lt;p&gt; Il était un philosophe très controversé par les positions qu'il prenait dans le domaine de la religion, de la sexualité et du travail. Son livre paru en 1929 &quot;Le Mariage et la Morale&quot; fera scandale à cette époque car il autorise la femme a pratiqué l'adultère. Concernant le travail, il fera  &lt;a href=&quot;https://www.youtube.com/watch?v=I7dQ5ZES3VI&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;Le travail et l'oisiveté par Alain Bajomée &quot;&gt;l'éloge de l'oisiveté&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;&#10;L'un des ses travaux les plus connus, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Principia_Mathematica&quot;  title=&quot;Principa Mathematica par Wikipédia &quot;&gt;&quot;Principia Mathematica&quot;&lt;/a&gt;, écrit en collaboration avec Alfred North Whitehead. Publié entre 1910 et 1913, cet ouvrage visait à fonder les mathématiques sur une base logique rigoureuse. Bien que le projet n'ait pas atteint tous ses objectifs, il a eu une influence considérable sur le développement ultérieur des mathématiques et de la logique. &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de la connaissance ou &quot;théorie des descriptions&quot; est une contribution majeure de la philosophie analytique. Elle a remis en cause la nature des propositions et la signification des termes définis par description.&lt;/p&gt; &lt;p&gt;&#10;Russell a reçu de nombreux honneurs au cours de sa vie, dont le prix Nobel de littérature en 1950, en reconnaissance de sa contribution exceptionnelle à la &lt;a href=&quot;https://www.youtube.com/watch?v=5IEYW5wuK3Y&amp;ab_channel=PhilosophyOverdose&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Interview on Philosophy par Philosophy Overdose &quot;&gt;pensée philosophique&lt;/a&gt; et à la littérature humaniste.  Il était un penseur engagé sur le plan politique et social ainsi qu'un défenseur passionné du pacifisme et s'est opposé à la participation britannique dans la Première Guerre mondiale. &lt;/p&gt;  &lt;audio controls title=&quot;Autobiographie de Bertrand Russell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-17.01.2017-ITEMA_21199485-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="H37" r:id="rId26" display="https://www.laphilo.fr/pho/cgjung-mini.webp"/>
-    <hyperlink ref="E39" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Weininger&quot;  title=&quot; Wikipedia&quot;&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href=&quot;https://www.youtube.com/watch?v=wetIerJEucU&quot; title=&quot; Otto Weininger Le génie Maudit par Aliouca&quot;&gt;maison de Beethoven à Vienne &lt;/a&gt; . Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=aFZpRoBlMQI&quot; title=&quot; Otto Weininger qui haîssait les femmes par Voyage Endormis&quot;&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href=&quot;https://www.youtube.com/watch?v=vMfEJQVv3VM&quot; title=&quot; Otto Weininger Le mytère du féminin par Philosopheasy en Français&quot;&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits &quot;féminins&quot; vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère &quot;féminine&quot; décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title=&quot;Otto Weininger et la question du genie par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E40" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H40" r:id="rId29" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
-    <hyperlink ref="E41" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H41" r:id="rId31" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
-    <hyperlink ref="H42" r:id="rId32" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
-    <hyperlink ref="I42" r:id="rId33" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
-    <hyperlink ref="E43" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H44" r:id="rId35" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
-    <hyperlink ref="E45" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E47" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
-    <hyperlink ref="E51" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H52" r:id="rId39" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
-    <hyperlink ref="H54" r:id="rId40" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
-    <hyperlink ref="E55" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H55" r:id="rId42" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
-    <hyperlink ref="I55" r:id="rId43" display="https://laphilo.fr/photo/lszabo.webp"/>
-    <hyperlink ref="E56" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
-    <hyperlink ref="E57" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H58" r:id="rId46" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
-    <hyperlink ref="I58" r:id="rId47" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
-    <hyperlink ref="H59" r:id="rId48" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
-    <hyperlink ref="E60" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
-    <hyperlink ref="H60" r:id="rId50" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
-    <hyperlink ref="E61" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E62" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E63" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
-    <hyperlink ref="E64" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
-    <hyperlink ref="H64" r:id="rId55" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
-    <hyperlink ref="H65" r:id="rId56" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
-    <hyperlink ref="H67" r:id="rId57" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
-    <hyperlink ref="H69" r:id="rId58" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
-    <hyperlink ref="E71" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E73" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
-    <hyperlink ref="E74" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H74" r:id="rId62" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
-    <hyperlink ref="I74" r:id="rId63" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="E75" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H75" r:id="rId65" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
-    <hyperlink ref="I75" r:id="rId66" display="https://laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="H78" r:id="rId67" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
-    <hyperlink ref="E80" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
-    <hyperlink ref="E82" r:id="rId69" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H83" r:id="rId70" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
-    <hyperlink ref="E85" r:id="rId71" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H85" r:id="rId72" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
-    <hyperlink ref="H86" r:id="rId73" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
-    <hyperlink ref="E87" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H87" r:id="rId75" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
+    <hyperlink ref="E39" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans_Hahn_(math%C3%A9maticien)&quot;  title=&quot; Wikipedia&quot;&gt;Hans HAHN&lt;/a&gt; était un mathématicien autrichien, surtout connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach. Il fut également l’un des principaux fondateurs du Cercle de Vienne, avec Moritz Schlick, Philipp Frank et Otto Neurath. Son intérêt pour la philosophie ne fut donc pas celui d’un philosophe professionnel, mais celui d’un mathématicien qui cherchait à comprendre le rapport entre logique, mathématiques, langage et connaissance scientifique. &lt;/p&gt; &lt;p&gt; Sa philosophie s’inscrit dans l’empirisme logique ou positivisme logique. Comme les &lt;a href=&quot;https://www.youtube.com/watch?v=VReApTp5_zg&quot; title=&quot; le cercle de vienne par philosophie analytique&quot;&gt;autres membres du Cercle de Vienne, &lt;/a&gt;  il rejetait la métaphysique traditionnelle lorsqu’elle prétendait produire une connaissance indépendante de toute expérience ou de toute méthode logique. Il contestait notamment l’idée kantienne de vérités « synthétiques a priori » : selon cette orientation, une proposition est soit logique ou mathématique, soit empirique et vérifiable à partir de l’expérience. La philosophie devait ainsi se rapprocher de l’analyse logique des énoncés scientifiques. &lt;/p&gt; &lt;p&gt; Il accordait toutefois aux mathématiques un statut particulier. Il ne pensait pas qu’elles décrivent directement des objets réels, comme le font les sciences expérimentales. Les mathématiques et la logique établissent plutôt des relations formelles entre des propositions ou des symboles. Elles indiquent ce qui découle nécessairement de certaines règles et de certains axiomes. En ce sens, les vérités mathématiques sont analytiques : elles ne tirent pas leur certitude de l’observation, mais de la structure logique du système dans lequel elles sont formulées. &lt;/p&gt; &lt;p&gt; Un aspect important de sa pensée est son refus de fonder les mathématiques sur une intuition particulière. Il se méfiait de l’« intuition » au sens kantien, c’est-à-dire de l’idée que l’esprit aurait un accès immédiat aux structures mathématiques. Il défendait plutôt l’axiomatisation et la rigueur formelle, notamment dans l’arithmétique et l’analyse. Mais il ne réduisait pas nécessairement toute signification à une vérification directe : il soutenait que les hypothèses scientifiques peuvent être significatives même lorsqu’elles ne sont pas définitivement vérifiables, ce qui conduit à assouplir le vérificationnisme strict. &lt;/p&gt; &lt;p&gt; Il concevait la logique non comme une science décrivant les propriétés les plus générales des objets, mais comme un instrument construit par les êtres humains pour parler du monde avec précision. La logique ne serait donc pas une réalité cachée dans les choses : elle apparaît lorsque nous organisons nos énoncés au moyen d’un symbolisme. Sa philosophie défend ainsi une conception scientifique, anti-métaphysique et formaliste de la connaissance, tout en laissant une place aux hypothèses et à la diversité des systèmes logiques. Son œuvre philosophique, moins abondante que son œuvre mathématique, a néanmoins contribué à préparer plusieurs thèmes du positivisme logique et de la philosophie analytique des sciences. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H39" r:id="rId28" display="https://www.laphilo.fr/pho/hhahn-mini.webp"/>
+    <hyperlink ref="E40" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Weininger&quot;  title=&quot; Wikipedia&quot;&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href=&quot;https://www.youtube.com/watch?v=wetIerJEucU&quot; title=&quot; Otto Weininger Le génie Maudit par Aliouca&quot;&gt;maison de Beethoven à Vienne &lt;/a&gt; . Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=aFZpRoBlMQI&quot; title=&quot; Otto Weininger qui haîssait les femmes par Voyage Endormis&quot;&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href=&quot;https://www.youtube.com/watch?v=vMfEJQVv3VM&quot; title=&quot; Otto Weininger Le mytère du féminin par Philosopheasy en Français&quot;&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits &quot;féminins&quot; vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère &quot;féminine&quot; décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title=&quot;Otto Weininger et la question du genie par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E41" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H41" r:id="rId31" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H42" r:id="rId33" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
+    <hyperlink ref="H43" r:id="rId34" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
+    <hyperlink ref="I43" r:id="rId35" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
+    <hyperlink ref="E44" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H45" r:id="rId37" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
+    <hyperlink ref="E46" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E47" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E49" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
+    <hyperlink ref="E53" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H54" r:id="rId42" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
+    <hyperlink ref="H56" r:id="rId43" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
+    <hyperlink ref="E57" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H57" r:id="rId45" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
+    <hyperlink ref="I57" r:id="rId46" display="https://laphilo.fr/photo/lszabo.webp"/>
+    <hyperlink ref="E58" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
+    <hyperlink ref="E59" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H60" r:id="rId49" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
+    <hyperlink ref="I60" r:id="rId50" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
+    <hyperlink ref="H61" r:id="rId51" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
+    <hyperlink ref="E62" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
+    <hyperlink ref="H62" r:id="rId53" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
+    <hyperlink ref="E63" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E64" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E65" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
+    <hyperlink ref="E66" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
+    <hyperlink ref="H66" r:id="rId58" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
+    <hyperlink ref="H67" r:id="rId59" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
+    <hyperlink ref="H69" r:id="rId60" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
+    <hyperlink ref="H71" r:id="rId61" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
+    <hyperlink ref="E73" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E75" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
+    <hyperlink ref="E76" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H76" r:id="rId65" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
+    <hyperlink ref="I76" r:id="rId66" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="E77" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H77" r:id="rId68" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
+    <hyperlink ref="I77" r:id="rId69" display="https://laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="H80" r:id="rId70" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
+    <hyperlink ref="E82" r:id="rId71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
+    <hyperlink ref="E84" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H85" r:id="rId73" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
+    <hyperlink ref="E87" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H87" r:id="rId75" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
+    <hyperlink ref="H88" r:id="rId76" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
+    <hyperlink ref="E89" r:id="rId77" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H89" r:id="rId78" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="754">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -1444,7 +1444,10 @@
     <t xml:space="preserve">48_Ab-qQzvA</t>
   </si>
   <si>
-    <t xml:space="preserve">Philipp FRANKscien philosopher par Essai</t>
+    <t xml:space="preserve">Philipp FRANK philosopher par Essai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/pfrank-mini.webp</t>
   </si>
   <si>
     <t xml:space="preserve">physicien théoricien, mathématicien et philosophe des sciences austro-américain et l’un des membres fondateurs du Cercle de Vienne.</t>
@@ -2541,7 +2544,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2669,19 +2672,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
@@ -2771,7 +2761,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2852,23 +2842,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4852,7 +4834,7 @@
       <c r="D46" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="13" t="s">
         <v>402</v>
       </c>
       <c r="F46" s="7" t="s">
@@ -4861,16 +4843,21 @@
       <c r="G46" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="H46" s="10"/>
+      <c r="H46" s="10" t="s">
+        <v>405</v>
+      </c>
       <c r="I46" s="9"/>
+      <c r="J46" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="K46" s="2" t="s">
         <v>347</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="M46" s="21" t="s">
-        <v>405</v>
+      <c r="M46" s="15" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4878,38 +4865,38 @@
         <v>1885</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>171</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4917,38 +4904,38 @@
         <v>1889</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4956,25 +4943,25 @@
         <v>1889</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
@@ -4987,7 +4974,7 @@
         <v>94</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4995,25 +4982,25 @@
         <v>1891</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
@@ -5026,7 +5013,7 @@
         <v>171</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5037,34 +5024,34 @@
         <v>1961</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>104</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5072,38 +5059,38 @@
         <v>1898</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5114,22 +5101,22 @@
         <v>1992</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
@@ -5142,7 +5129,7 @@
         <v>75</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5150,25 +5137,25 @@
         <v>1899</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
@@ -5178,10 +5165,10 @@
         <v>180</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5192,22 +5179,22 @@
         <v>1983</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="F55" s="22" t="s">
         <v>479</v>
       </c>
+      <c r="F55" s="20" t="s">
+        <v>480</v>
+      </c>
       <c r="G55" s="19" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>294</v>
@@ -5219,7 +5206,7 @@
         <v>303</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5230,24 +5217,24 @@
         <v>1967</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="F56" s="22"/>
+        <v>486</v>
+      </c>
+      <c r="F56" s="20"/>
       <c r="G56" s="19"/>
       <c r="H56" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>364</v>
@@ -5256,7 +5243,7 @@
         <v>152</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5264,26 +5251,26 @@
         <v>1902</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>22</v>
@@ -5292,10 +5279,10 @@
         <v>180</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5303,25 +5290,25 @@
         <v>1902</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
@@ -5334,7 +5321,7 @@
         <v>152</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5345,33 +5332,33 @@
         <v>1993</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="9"/>
       <c r="H59" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>258</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5379,28 +5366,28 @@
         <v>1907</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>44</v>
@@ -5409,10 +5396,10 @@
         <v>258</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5423,35 +5410,35 @@
         <v>1992</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="E61" s="23" t="s">
         <v>524</v>
       </c>
+      <c r="E61" s="21" t="s">
+        <v>525</v>
+      </c>
       <c r="F61" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>364</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="M61" s="24" t="s">
         <v>529</v>
+      </c>
+      <c r="M61" s="22" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5459,25 +5446,25 @@
         <v>1907</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
@@ -5487,10 +5474,10 @@
         <v>84</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5498,25 +5485,25 @@
         <v>1908</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
@@ -5526,10 +5513,10 @@
         <v>258</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5537,25 +5524,25 @@
         <v>1909</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
@@ -5565,10 +5552,10 @@
         <v>65</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5579,22 +5566,22 @@
         <v>2004</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
@@ -5604,10 +5591,10 @@
         <v>180</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5618,22 +5605,22 @@
         <v>1996</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
@@ -5646,7 +5633,7 @@
         <v>152</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5654,38 +5641,38 @@
         <v>1911</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5696,35 +5683,35 @@
         <v>1995</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>151</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5732,38 +5719,38 @@
         <v>1913</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5771,29 +5758,29 @@
         <v>1914</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>180</v>
@@ -5802,7 +5789,7 @@
         <v>94</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5813,22 +5800,22 @@
         <v>2001</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>33</v>
@@ -5837,10 +5824,10 @@
         <v>205</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5848,38 +5835,38 @@
         <v>1922</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>170</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5887,25 +5874,25 @@
         <v>1922</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
@@ -5918,7 +5905,7 @@
         <v>94</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5926,25 +5913,25 @@
         <v>1923</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
@@ -5957,7 +5944,7 @@
         <v>94</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5968,22 +5955,22 @@
         <v>2019</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
@@ -5996,7 +5983,7 @@
         <v>94</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6007,33 +5994,33 @@
         <v>2003</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="9"/>
       <c r="H76" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M76" s="14" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6041,28 +6028,28 @@
         <v>1925</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>33</v>
@@ -6074,7 +6061,7 @@
         <v>94</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6082,25 +6069,25 @@
         <v>1925</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
@@ -6110,10 +6097,10 @@
         <v>65</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M78" s="14" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6121,25 +6108,25 @@
         <v>1926</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
@@ -6149,10 +6136,10 @@
         <v>65</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6163,22 +6150,22 @@
         <v>2002</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>33</v>
@@ -6187,10 +6174,10 @@
         <v>74</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6198,25 +6185,25 @@
         <v>1929</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
@@ -6229,7 +6216,7 @@
         <v>94</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6237,38 +6224,38 @@
         <v>1929</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6276,25 +6263,25 @@
         <v>1930</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
@@ -6315,35 +6302,35 @@
         <v>2018</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M84" s="14" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6354,22 +6341,22 @@
         <v>2026</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="2" t="s">
@@ -6379,10 +6366,10 @@
         <v>258</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6393,35 +6380,35 @@
         <v>2026</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M86" s="14" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6432,22 +6419,22 @@
         <v>2019</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="2" t="s">
@@ -6460,7 +6447,7 @@
         <v>94</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6468,38 +6455,38 @@
         <v>1942</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H88" s="10" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6510,34 +6497,34 @@
         <v>2014</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6604,46 +6591,47 @@
     <hyperlink ref="E44" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
     <hyperlink ref="H45" r:id="rId37" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
     <hyperlink ref="E46" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E47" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E49" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
-    <hyperlink ref="E53" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H54" r:id="rId42" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
-    <hyperlink ref="H56" r:id="rId43" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
-    <hyperlink ref="E57" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H57" r:id="rId45" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
-    <hyperlink ref="I57" r:id="rId46" display="https://laphilo.fr/photo/lszabo.webp"/>
-    <hyperlink ref="E58" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
-    <hyperlink ref="E59" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H60" r:id="rId49" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
-    <hyperlink ref="I60" r:id="rId50" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
-    <hyperlink ref="H61" r:id="rId51" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
-    <hyperlink ref="E62" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
-    <hyperlink ref="H62" r:id="rId53" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
-    <hyperlink ref="E63" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E64" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E65" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
-    <hyperlink ref="E66" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
-    <hyperlink ref="H66" r:id="rId58" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
-    <hyperlink ref="H67" r:id="rId59" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
-    <hyperlink ref="H69" r:id="rId60" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
-    <hyperlink ref="H71" r:id="rId61" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
-    <hyperlink ref="E73" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E75" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
-    <hyperlink ref="E76" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H76" r:id="rId65" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
-    <hyperlink ref="I76" r:id="rId66" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="E77" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H77" r:id="rId68" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
-    <hyperlink ref="I77" r:id="rId69" display="https://laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="H80" r:id="rId70" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
-    <hyperlink ref="E82" r:id="rId71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
-    <hyperlink ref="E84" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H85" r:id="rId73" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
-    <hyperlink ref="E87" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H87" r:id="rId75" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
-    <hyperlink ref="H88" r:id="rId76" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
-    <hyperlink ref="E89" r:id="rId77" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H89" r:id="rId78" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
+    <hyperlink ref="H46" r:id="rId39" display="https://www.laphilo.fr/pho/pfrank-mini.webp"/>
+    <hyperlink ref="E47" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E49" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
+    <hyperlink ref="E53" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H54" r:id="rId43" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
+    <hyperlink ref="H56" r:id="rId44" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
+    <hyperlink ref="E57" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H57" r:id="rId46" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
+    <hyperlink ref="I57" r:id="rId47" display="https://laphilo.fr/photo/lszabo.webp"/>
+    <hyperlink ref="E58" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
+    <hyperlink ref="E59" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H60" r:id="rId50" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
+    <hyperlink ref="I60" r:id="rId51" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
+    <hyperlink ref="H61" r:id="rId52" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
+    <hyperlink ref="E62" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
+    <hyperlink ref="H62" r:id="rId54" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
+    <hyperlink ref="E63" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E64" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E65" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
+    <hyperlink ref="E66" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
+    <hyperlink ref="H66" r:id="rId59" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
+    <hyperlink ref="H67" r:id="rId60" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
+    <hyperlink ref="H69" r:id="rId61" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
+    <hyperlink ref="H71" r:id="rId62" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
+    <hyperlink ref="E73" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E75" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
+    <hyperlink ref="E76" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H76" r:id="rId66" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
+    <hyperlink ref="I76" r:id="rId67" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="E77" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H77" r:id="rId69" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
+    <hyperlink ref="I77" r:id="rId70" display="https://laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="H80" r:id="rId71" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
+    <hyperlink ref="E82" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
+    <hyperlink ref="E84" r:id="rId73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H85" r:id="rId74" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
+    <hyperlink ref="E87" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H87" r:id="rId76" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
+    <hyperlink ref="H88" r:id="rId77" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
+    <hyperlink ref="E89" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H89" r:id="rId79" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="763">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -1162,7 +1162,7 @@
     <t xml:space="preserve">ethique ; epistemologie</t>
   </si>
   <si>
-    <t xml:space="preserve">Analytique ; Intuitionnisme</t>
+    <t xml:space="preserve">Analytique ; Intuitionnisme ; Cognitivisme</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe anglais connu pour son parti pris contre le sophisme naturaliste.</t>
@@ -1959,6 +1959,34 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe espagnol intègrant l'agnosticisme dans une réflexion éthique et religieuse évolutive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1910 – 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alfred Jules AYER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer" title=" Wikipedia"&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href="https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html"  title="philosophie analytique par la philosophie"&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href="https://www.youtube.com/watch?v=HG5kIR6iF8g"  title="A,J, Ayer’s Emotivism par philosophy Vibe"&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-XYuh39J-zo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,J, Ayer par ThamesTv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/ajayer-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ethique ; logique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positivisme logique ; Analytique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone.</t>
   </si>
   <si>
     <t xml:space="preserve">1960</t>
@@ -3106,7 +3134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -5597,7 +5625,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
         <v>1909</v>
       </c>
@@ -5636,90 +5664,90 @@
         <v>569</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="351.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B67" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="D67" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="E67" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="F67" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="G67" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="H67" s="10" t="s">
         <v>575</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>576</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M67" s="2" t="s">
+      <c r="M67" s="14" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="306.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
         <v>1911</v>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>1995</v>
+      <c r="B68" s="7" t="s">
+        <v>579</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="E68" s="11" t="s">
         <v>581</v>
       </c>
+      <c r="E68" s="12" t="s">
+        <v>582</v>
+      </c>
       <c r="F68" s="7" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>151</v>
+        <v>586</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>585</v>
+        <v>94</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="255.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>587</v>
+        <v>1911</v>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>1995</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>588</v>
@@ -5727,7 +5755,7 @@
       <c r="D69" s="8" t="s">
         <v>589</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
         <v>590</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -5741,49 +5769,49 @@
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
-        <v>33</v>
+        <v>448</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>577</v>
+        <v>151</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>94</v>
+        <v>594</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="H70" s="9" t="s">
         <v>601</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>602</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
-        <v>602</v>
+        <v>33</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>180</v>
+        <v>586</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>94</v>
@@ -5792,75 +5820,75 @@
         <v>603</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
+    <row r="71" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="I71" s="9"/>
+      <c r="J71" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
         <v>1919</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B72" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="J71" s="2" t="s">
+      <c r="C72" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="J72" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K71" s="2" t="s">
+      <c r="K72" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>619</v>
@@ -5869,69 +5897,69 @@
         <v>620</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
         <v>1922</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="D73" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="E73" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="F73" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="G73" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="H73" s="9" t="s">
         <v>626</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>627</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
-        <v>33</v>
+        <v>627</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>94</v>
+        <v>628</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="E74" s="10" t="s">
         <v>632</v>
       </c>
+      <c r="E74" s="11" t="s">
+        <v>633</v>
+      </c>
       <c r="F74" s="7" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
@@ -5944,132 +5972,130 @@
         <v>94</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B75" s="7" t="n">
-        <v>2019</v>
+        <v>1923</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>638</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>639</v>
+        <v>640</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>641</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>644</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
         <v>1924</v>
       </c>
       <c r="B76" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B77" s="7" t="n">
         <v>2003</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="F76" s="7"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="J76" s="2" t="s">
+      <c r="C77" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="F77" s="7"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="J77" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="M76" s="14" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>654</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>657</v>
-      </c>
-      <c r="I77" s="10" t="s">
+      <c r="K77" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="J77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="L77" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M77" s="2" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M77" s="14" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
         <v>1925</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>661</v>
@@ -6077,7 +6103,7 @@
       <c r="D78" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="11" t="s">
         <v>663</v>
       </c>
       <c r="F78" s="7" t="s">
@@ -6086,26 +6112,28 @@
       <c r="G78" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="H78" s="9" t="s">
+      <c r="H78" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="I78" s="9"/>
+      <c r="I78" s="10" t="s">
+        <v>667</v>
+      </c>
       <c r="J78" s="2" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="M78" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>669</v>
@@ -6116,7 +6144,7 @@
       <c r="D79" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="12" t="s">
         <v>672</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -6130,7 +6158,7 @@
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>65</v>
@@ -6138,118 +6166,118 @@
       <c r="L79" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="M79" s="14" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
+    <row r="80" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="I80" s="9"/>
+      <c r="J80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B81" s="1" t="n">
         <v>2002</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>686</v>
-      </c>
-      <c r="D81" s="8" t="s">
+      <c r="D81" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="E81" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="F81" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H81" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>94</v>
+        <v>692</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
         <v>1929</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>700</v>
+        <v>205</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>94</v>
@@ -6258,9 +6286,9 @@
         <v>701</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>702</v>
@@ -6271,7 +6299,7 @@
       <c r="D83" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="13" t="s">
         <v>705</v>
       </c>
       <c r="F83" s="7" t="s">
@@ -6288,91 +6316,91 @@
         <v>33</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>180</v>
+        <v>709</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M83" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B84" s="7" t="n">
-        <v>2018</v>
+        <v>1930</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>711</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>714</v>
+        <v>716</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>717</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="2" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="M84" s="14" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="E85" s="12" t="s">
         <v>719</v>
       </c>
+      <c r="E85" s="11" t="s">
+        <v>720</v>
+      </c>
       <c r="F85" s="7" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="2" t="s">
-        <v>139</v>
+        <v>448</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>724</v>
+      </c>
+      <c r="M85" s="14" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
         <v>1934</v>
       </c>
@@ -6380,164 +6408,193 @@
         <v>2026</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>728</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H86" s="10" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="I86" s="9"/>
       <c r="J86" s="2" t="s">
-        <v>511</v>
+        <v>139</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="M86" s="14" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>512</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="E87" s="13" t="s">
         <v>733</v>
       </c>
+      <c r="E87" s="11" t="s">
+        <v>734</v>
+      </c>
       <c r="F87" s="7" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="M87" s="14" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="7" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="I88" s="9"/>
+      <c r="J88" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L87" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>740</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
+    <row r="89" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="I89" s="10"/>
+      <c r="J89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="n">
         <v>1954</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B90" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>749</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="J89" s="2" t="s">
+      <c r="C90" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>758</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="J90" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="K89" s="2" t="s">
+      <c r="K90" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L89" s="2" t="s">
+      <c r="L90" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="M89" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M90" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -6546,6 +6603,16 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6612,26 +6679,28 @@
     <hyperlink ref="E65" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
     <hyperlink ref="E66" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
     <hyperlink ref="H66" r:id="rId59" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
-    <hyperlink ref="H67" r:id="rId60" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
-    <hyperlink ref="H69" r:id="rId61" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
-    <hyperlink ref="H71" r:id="rId62" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
-    <hyperlink ref="E73" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E75" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
-    <hyperlink ref="E76" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H76" r:id="rId66" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
-    <hyperlink ref="I76" r:id="rId67" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="E77" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H77" r:id="rId69" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
-    <hyperlink ref="I77" r:id="rId70" display="https://laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="H80" r:id="rId71" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
-    <hyperlink ref="E82" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
-    <hyperlink ref="E84" r:id="rId73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H85" r:id="rId74" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
-    <hyperlink ref="E87" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H87" r:id="rId76" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
-    <hyperlink ref="H88" r:id="rId77" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
-    <hyperlink ref="E89" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H89" r:id="rId79" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
+    <hyperlink ref="E67" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer&quot; title=&quot; Wikipedia&quot;&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href=&quot;https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html&quot;  title=&quot;philosophie analytique par la philosophie&quot;&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href=&quot;https://www.youtube.com/watch?v=HG5kIR6iF8g&quot;  title=&quot;A,J, Ayer’s Emotivism par philosophy Vibe&quot;&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H67" r:id="rId61" display="https://www.laphilo.fr/pho/ajayer-mini.webp"/>
+    <hyperlink ref="H68" r:id="rId62" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
+    <hyperlink ref="H70" r:id="rId63" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
+    <hyperlink ref="H72" r:id="rId64" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
+    <hyperlink ref="E74" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E76" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
+    <hyperlink ref="E77" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H77" r:id="rId68" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
+    <hyperlink ref="I77" r:id="rId69" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="E78" r:id="rId70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H78" r:id="rId71" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
+    <hyperlink ref="I78" r:id="rId72" display="https://laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="H81" r:id="rId73" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
+    <hyperlink ref="E83" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
+    <hyperlink ref="E85" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H86" r:id="rId76" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
+    <hyperlink ref="E88" r:id="rId77" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H88" r:id="rId78" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
+    <hyperlink ref="H89" r:id="rId79" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
+    <hyperlink ref="E90" r:id="rId80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H90" r:id="rId81" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -1269,7 +1269,7 @@
     <t xml:space="preserve">logique</t>
   </si>
   <si>
-    <t xml:space="preserve">Positivisme logique ; </t>
+    <t xml:space="preserve">Positivisme Logique ; </t>
   </si>
   <si>
     <t xml:space="preserve">mathématicien autrichien connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach.</t>
@@ -1983,7 +1983,7 @@
     <t xml:space="preserve">ethique ; logique</t>
   </si>
   <si>
-    <t xml:space="preserve">Positivisme logique ; Analytique</t>
+    <t xml:space="preserve">Positivisme Logique ; Analytique</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone.</t>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="716">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -132,70 +132,6 @@
   </si>
   <si>
     <t xml:space="preserve">femme philosophe anglaise pionnière du féminisme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1767 – 1835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilhelm von HUMBOLDT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wilhelm_von_Humboldt" title=" Wikipedia"&gt;Wilhelm von HUMBOLDT&lt;/a&gt; était un philosophe, linguiste, diplomate et réformateur de l'éducation prussienne, reconnu pour son rôle majeur dans la philosophie du langage, l’anthropologie philosophique, la théorie de l’éducation et la pensée politique libérale. &lt;/p&gt; &lt;p&gt; Il est un des fondateurs de la &lt;a href="https://www.erudit.org/fr/revues/philoso/2006-v33-n2-philoso1428/013888ar/"  title="Langage et pensée chez W. von Humboldt par Erudit"&gt; philosophie du langage&lt;/a&gt; moderne : il conçoit la langue comme une activité créatrice et dynamique, dans laquelle le langage façonne et reflète la pensée, la culture et la perception du monde de chaque peuple. Pour lui, chaque langue exprime la vision du monde singulière de ceux qui la parlent, ce qui implique que les structures grammaticales ne sont pas universelles, mais propres à chaque culture. &lt;/p&gt; &lt;p&gt; Son oeuvre se fonde sur une réflexion anthropologique issue du kantisme : il fait du questionnement « Qu’est-ce que l’homme ? » le cœur de sa philosophie. Cette approche mène à sa célèbre notion de Bildung, la formation ou culture personnelle, qui valorise le développement individuel et la créativité comme objectifs fondamentaux de la vie humaine, avant le &lt;a href="https://www.youtube.com/watch?v=-1SQHJ_pcdQ" title=" Humboldt : pourquoi l’action de l’Etat entrave le développement de l’individualité de l’homme ?  par Ecole de la Liberté"&gt;service de l’État&lt;/a&gt; ou l’utilité économique.&lt;/p&gt; &lt;p&gt;  Dans ses écrits sur les limites de l’action de l’État, il propose un libéralisme original : l’État doit garantir la liberté individuelle, son rôle doit être limité et adapté aux singularités culturelles et personnelles. Paradoxalement, il fut l’architecte du système  &lt;a href="https://www.youtube.com/watch?v=48jB8M8HXJw" title=" Wilhelm von Humboldt’s Education Ideal par Johannes A Niederhauser"&gt;prussien d’éducation&lt;/a&gt;, fondant l’université de Berlin et réformant la pédagogie pour encourager la liberté de l’esprit et le développement holistique de l’élève. &lt;/p&gt; &lt;p&gt; Il était aussi théoricien du &lt;a href="https://www.persee.fr/doc/reval_0035-0974_1993_num_25_3_3664"  title="Wilhelm von Humboldt ou l’humanisme comme idéal de vie et objet de recherches par Persée"&gt;néo-humanisme&lt;/a&gt; allemand, voyant dans l’idéal grec ancien un modèle intemporel pour l’autonomie et l’excellence culturelle. L’esthétique occupe chez lui un rôle central : percevoir la beauté et cultiver la sensibilité sont pour lui indispensables à la réalisation de la "vocation humaine". Il demeure un penseur majeur, à l’origine de la philosophie du langage, d’une anthropologie philosophique profondément humaniste, et d’une conception moderne de l’éducation et de la liberté individuelle. &lt;/p&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">eRUj6NWS1Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"
-Who is Wilhelm von Humboldt" par VIS PHILO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/humboldt-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allemande</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epistemologie ; politique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idéalisme allemand ; Libéralisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe prussien pionnier dans le domaine des sciences de l'éducation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1769 – 1834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedrich SCHLEIERMACHER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Schleiermacher"   title=" Wikipedia"&gt;Friedrich SCHEIERMACHER&lt;/a&gt;  était un philosophe prussien,  souvent considéré comme le "père de la théologie libérale moderne". &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2011_num_91_1_1522"  title="son apport théorique et pratique par persée"&gt;Sa philosophie &lt;/a&gt; intègre des éléments du romantisme, de l'idéalisme allemand et du piétisme, en centrant l'humain sur une conscience intuitive de l'infini. Il édita Platon, prêcha et influença le protestantisme européen sans séparer foi et culture. &lt;/p&gt; &lt;p&gt;  Il pose le sentiment religieux comme une conscience immédiate de la dépendance absolue envers l'infini (Dieu), distincte du savoir ou de la morale kantienne. L'ego est une individualisation de la  &lt;a href="https://www.youtube.com/watch?v=gvpaUR1XceM"  style="color:#88A1E9"  title="Schleiermacher: The Man Behind Protestant Liberalism par Stephen D Morrison"&gt;raison universelle, &lt;/a&gt; un microcosme où univers et individu s'unissent via la conscience de soi. Il articule individualité et communauté via la communication, honorant la finitude humaine et l'invention de soi contre l'absolutisme idéaliste. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures sont "Discours sur la religion" paru en 1799 et "La foi chrétienne"  paru vers 1821, où il réconcilie rationalité et piété. Il a profondément marqué la théologie protestante moderne en introduisant une approche centrée sur le sentiment religieux et l'expérience personnelle, plutôt que sur les dogmes rigides ou la raison pure. Son idée de "dépendance absolue" envers Dieu et la relativisation des doctrines comme expressions humaines de la piété ont pavé la voie au &lt;a href="https://www.youtube.com/watch?v=1FveOtAB86s"  title="L'argument éthique de Schleiermacher en faveur de l'universalisme par Sola Media"&gt;libéralisme théologique. &lt;/a&gt;&lt;/p&gt; &lt;p&gt;  Fondateur de l'herméneutique moderne, art général d'interprétation reliant traduction, littérature et exégèse biblique, il lance l'herméneutique critique de l'Écriture et une théologie pratique pertinente pour la modernité, influençant Ritschl et l'individualisme religieux.&lt;/p&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yta5UpnnLqM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Friedrich Daniel Ernst Schleiermacher: Bridging Enlightenment and Christianity" par VIS PHILO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/schleiermacher-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epistemologie ; spiritualite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herméneutique ; Romantisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe prussien considéré comme le "père de la théologie libérale moderne".</t>
   </si>
   <si>
     <t xml:space="preserve">1858</t>
@@ -426,34 +362,6 @@
     <t xml:space="preserve">femme philosophe féministe britanique à la pensée libérale.</t>
   </si>
   <si>
-    <t xml:space="preserve">1874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1808 – 1874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David STRAUSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Strauss" title=" Wikipedia"&gt;David STRAUSS&lt;/a&gt;  était un philosophe  allemand, né et mort à Ludwigsburg, près de Stuttgart. Disciple de Hegel, il appartient au courant des &lt;a href="https://fr.wikipedia.org/wiki/Jeunes_h%C3%A9g%C3%A9liens"  title=" les jeunes hégéliens par wikipedia"&gt;« jeunes hégéliens » &lt;/a&gt; et marque l'histoire de la théologie par sa critique radicale des Évangiles. Influencé par la philosophie hégélienne, il étudie à Tübingen et devient professeur avant de se consacrer à ses écrits controversés. Sa vie est marquée par des scandales intellectuels qui lui valent révocation et isolement. &lt;/p&gt; &lt;p&gt; Son œuvre majeure, La Vie de Jésus, ou Examen critique de son histoire (1835-1836), applique les principes hégéliens aux récits évangéliques. Il y affirme que les miracles et la naissance surnaturelle du Christ sont des mythes, expressions imaginaires de vérités religieuses plutôt que des faits historiques. Cette thèse, opposée à l'orthodoxie chrétienne, divise l'école hégélienne entre « droite » conservatrice et « gauche » progressiste, dont il est pionnier. &lt;/p&gt; &lt;p&gt; Après le scandale de 1835, il vit comme homme de lettres et publie d'autres ouvrages, comme La Doctrine chrétienne (1840-1841) ou L'Ancienne et la Nouvelle Foi (1872). Ces textes poursuivent sa déconstruction des dogmes, voyant dans l'histoire des doctrines une désintégration progressive. Il critique aussi Schleiermacher et embrasse un &lt;a href="https://www.youtube.com/watch?v=p8r9BYjZ7SQ"  title=" le matérialisme par Culture Philo"&gt;matérialisme scientifique &lt;/a&gt;  tardif, influençant penseurs comme Nietzsche ou Marx. &lt;/p&gt; &lt;p&gt; Son portrait, gravé en 1874, le montre en penseur austère aux favoris sombres, symbole de sa rupture avec la tradition. Il reste une figure clé de la « quête du Jésus historique », révolutionnant l'exégèse biblique par son rationalisme mythique. &lt;/p&gt; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCrGuR0nJ1o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"David Strauss and Historical Criticism" par Nick Nielsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/dstrauss-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herméneutique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe allemand et disciple des Jeunes Hégéliens.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1853</t>
   </si>
   <si>
@@ -551,36 +459,6 @@
     <t xml:space="preserve">Spiritualisme ; Libéralisme</t>
   </si>
   <si>
-    <t xml:space="preserve">1883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1818 - 1883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karl MARX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Karl_Marx"  title=" Wikipedia"&gt;Karl MARX&lt;/a&gt; était un philosophe, économiste et révolutionnaire allemand né à Trèves, est le fondateur  &lt;a href="https://www.youtube.com/watch?v=W_ZwUjnl4W4"  title="La philosophie de Karl Marx par Parole de philosophe"&gt;du marxisme &lt;/a&gt; avec Friedrich Engels. Issu d'une famille juive convertie au protestantisme, il étudie le droit et la philosophie à Bonn, Berlin et Iéna, où il est influencé par Hegel et les jeunes hégéliens comme David Strauss, dont il critique les idées religieuses dans sa jeunesse. Exilé en France puis en Angleterre après les révolutions de 1848, il vit dans la précarité à Londres, soutenu par Engels, et milite au sein de l'Internationale ouvrière. Son portrait de 1875 le montre barbu, pensif, incarnation du penseur engagé.   &lt;/p&gt; &lt;p&gt;    Sa philosophie repose sur le matérialisme historique et dialectique, voyant l'histoire comme une succession de modes de production (esclavagiste, féodal, capitaliste) mue par  &lt;a href="https://www.youtube.com/watch?v=1pYmqDnvTh8"  title="Les classes sociales par DigiSchool Lycee "&gt;la lutte des classes &lt;/a&gt; entre exploiteurs et exploités. Dans  &lt;a href="https://www.youtube.com/watch?v=jb-5oSF2dpU&amp;ab_channel=TanguyLacroix"  title="Le Manifeste du Parti Communiste par Tanguy Lacroix "&gt;"Le Manifeste communiste  &lt;/a&gt; (1848), coécrit avec Engels, il appelle le prolétariat à abolir la propriété privée des moyens de production pour instaurer une société sans classes. Le Capital (1867-1883) analyse le capitalisme comme un système d'exploitation via la plus-value extraite du travail   &lt;a href="https://www.youtube.com/watch?v=rEAxxsX_um0&amp;t=4s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'Aliénation par le Précepteur "&gt;salarié aliéné, &lt;/a&gt;  prédisant sa chute par ses contradictions internes. &lt;/p&gt; &lt;p&gt;  Il rejette la religion comme « opium du peuple », outil d'aliénation masquant l'exploitation réelle, et prône la praxis révolutionnaire : transformer le monde par l'action collective des travailleurs. Critiquant le libéralisme et le socialisme utopique, il envisage une dictature du prolétariat transitoire menant au communisme, où l'État dépérit et les besoins sont satisfaits selon les capacités. Ses idées opposent radicalement celles de Donoso Cortés, qui y voyait un aboutissement satanique du libéralisme. &lt;/p&gt;   &lt;p&gt; Sa contribution la plus importante à la théorie politique est sa conception du  &lt;a href="https://fr.wikipedia.org/wiki/Mat%C3%A9rialisme_dialectique"  title="Le Marxisme Dialectique par Wikipedia "&gt;"matérialisme dialectique"&lt;/a&gt;, qui est l'idée que le changement historique est motivé par des conflits entre des classes sociales opposées et que ces conflits sont finalement résolus par la révolution. &lt;/p&gt; &lt;p&gt; Il a également écrit abondamment sur l'économie, en particulier sur la théorie de la valeur-travail, qui postule que la valeur d'un bien ou d'un service est basée sur la quantité de travail nécessaire pour le produire. &lt;/p&gt; &lt;p&gt;     Son influence sur le XXe siècle est immense : révolutions bolchevique, chinoise, mouvements ouvriers mondiaux, et disciplines comme la sociologie ou l'économie. Malgré les échecs des régimes « marxistes », sa critique du capitalisme reste débattue aujourd'hui. &lt;/p&gt;    &lt;audio controls title="Pour l'avenir par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-26.09.2020-ITEMA_22438423-2020C40092E0005-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fSQgCy_iIcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Karl Marx" par the school of life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/marx-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">politique ; epistemologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marxisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe prussien qui développa l'idéologie Marxiste.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1903</t>
   </si>
   <si>
@@ -627,6 +505,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/spencer-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epistemologie ; politique</t>
   </si>
   <si>
     <t xml:space="preserve">Positivisme</t>
@@ -840,36 +721,6 @@
     <t xml:space="preserve">philosophe et psychologue autrichien, élève de Franz Brentano à Vienne.</t>
   </si>
   <si>
-    <t xml:space="preserve">1918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1858 – 1918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georg SIMMEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georg_Simmel" title=" Wikipedia"&gt;Georg SIMMEL&lt;/a&gt; était un philosophe du royaume de Prusse souvent considéré comme l’un des fondateurs de la sociologie de la modernité et de la   &lt;a href="https://www.youtube.com/watch?v=k2SZfvBp6H8"  title="Georg Simmel , sociologie urbaine . par PHILOVIBE"&gt;"sociologie formelle". &lt;/a&gt;  Il enseigne longtemps en marge de l’université, ce qui explique qu’il ait été moins institutionnalisé que Durkheim ou Weber, mais très influent sur eux et sur la sociologie ultérieure. &lt;/p&gt; &lt;p&gt; Il ne part pas de "la" société comme un grand tout, mais des formes d’interaction entre individus.  Il parle de sociologie formelle : les contenus (amour, travail, politique) varient, mais les formes (conflit, échange) se retrouvent partout et peuvent être étudiées en elles‑mêmes. Pour lui, la modernité se caractérise par une tension entre individu et société, entre culture subjective et culture objective.  La culture est produite par les individus mais devient ensuite une force autonome qui les dépasse, les contraint, et peut les écraser par sa complexité. &lt;/p&gt; &lt;p&gt; Il appartient au courant de la   &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_viel"  title="Philosophie de vie par Wikipedia"&gt;"philosophie de la vie" : &lt;/a&gt;  la vie est pour lui un flux créateur, mouvant, qui déborde toutes les formes fixes.  Les formes (institutions, normes, objets culturels) sont nécessaires pour donner sens au flux de la vie, mais elles se rigidifient et entrent en tension avec ce mouvement vital qui cherche toujours à se dépasser. Il  il insiste sur l’idée que la culture apparaît là où la vie rencontre des valeurs qui la transcendent (art, science, morale), mais ces valeurs finissent par se solidifier en systèmes objectifs qui peuvent aliéner l’individu. &lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Georg Simmel : Les grandes villes / Revue Questions internationales par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12003-25.03.2013-ITEMA_20463123-2013C18006S0084-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9dElPoJYeZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Georg Simmel's Individual and Society | Sociology" par Siciologylearners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/simmel-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epistemologie ; esthetique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Néo-kantisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe prussien co-fondateurs de la sociologie de la modernité "sociologie formelle".</t>
-  </si>
-  <si>
     <t xml:space="preserve">1859 – 1938</t>
   </si>
   <si>
@@ -1480,6 +1331,9 @@
     <t xml:space="preserve">politique ; esthetique</t>
   </si>
   <si>
+    <t xml:space="preserve">Marxisme</t>
+  </si>
+  <si>
     <t xml:space="preserve">philosophe hongrois, l'une des figures les plus importantes du marxisme occidental.</t>
   </si>
   <si>
@@ -2139,6 +1993,9 @@
   </si>
   <si>
     <t xml:space="preserve">Grecque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">politique ; epistemologie</t>
   </si>
   <si>
     <t xml:space="preserve">Constructivisme</t>
@@ -2661,12 +2518,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -2684,6 +2535,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2843,18 +2700,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3134,7 +2991,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -3298,9 +3155,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>37</v>
@@ -3311,7 +3168,7 @@
       <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -3325,180 +3182,180 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="2" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>1769</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="2" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>1771</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="G8" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="H8" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="2" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>1781</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="D9" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>1772</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="E9" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="H9" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L9" s="2" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>1777</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="E10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="H10" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M10" s="2" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>1781</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>1848</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>87</v>
@@ -3506,7 +3363,7 @@
       <c r="D11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>89</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -3515,146 +3372,146 @@
       <c r="G11" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>92</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="2" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>1798</v>
-      </c>
-      <c r="B12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="G12" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="H12" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>102</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="D13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="E13" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="F13" s="7" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="G13" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="H13" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>1807</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="H14" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>1808</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>123</v>
+        <v>1815</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>1895</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>124</v>
@@ -3662,7 +3519,7 @@
       <c r="D15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F15" s="7" t="s">
@@ -3671,3036 +3528,2844 @@
       <c r="G15" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
         <v>129</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
-        <v>1809</v>
+        <v>1818</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="13" t="s">
         <v>135</v>
       </c>
+      <c r="E16" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="F16" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>140</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M16" s="2" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>1813</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="E17" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="H17" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="18" customFormat="false" ht="381.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>1895</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="H18" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="D19" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="E19" s="10" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>1818</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="G19" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="E20" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="F20" s="7" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>1818</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="G20" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="H20" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M20" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>1820</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="H21" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="J21" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="K21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="M21" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="9" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>1853</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L21" s="2" t="s">
+      <c r="D22" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="E22" s="16" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="381.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>1825</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="H22" s="9" t="s">
         <v>192</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="M22" s="14" t="s">
+      <c r="E23" s="17" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>1838</v>
-      </c>
-      <c r="B23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="G23" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="H23" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>1860</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1919</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="F24" s="7"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="I24" s="10" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>1838</v>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>1906</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="J24" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="K24" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="L24" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="M24" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="G24" s="9" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="368.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="C25" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="D25" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M24" s="15" t="s">
+      <c r="E25" s="9" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>1937</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="F25" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="G25" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="H25" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="I25" s="9"/>
+      <c r="J25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H25" s="2" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L25" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="M25" s="15" t="s">
+      <c r="E26" s="10" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>1853</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="G26" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>227</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="322.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="F27" s="7" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
-        <v>1858</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="G27" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="H27" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1866</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>1859</v>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="H28" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="J28" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="K28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F28" s="7" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="C29" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="2" t="s">
+      <c r="E29" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>1860</v>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>1919</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="K29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="10" t="s">
+      <c r="M29" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I29" s="10" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>1873</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="C30" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="D30" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="E30" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="M29" s="15" t="s">
+      <c r="F30" s="7" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="368.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
-        <v>1861</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="G30" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="H30" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="L30" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="E31" s="9" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
-        <v>1861</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="G31" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>276</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>23</v>
+        <v>273</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="E32" s="11" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="322.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
-        <v>1863</v>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="G32" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="H32" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="K32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="D33" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="M32" s="14" t="s">
+      <c r="E33" s="9" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>1866</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>1938</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="F33" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="G33" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="H33" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="I33" s="9"/>
+      <c r="J33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M33" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G33" s="2" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="D34" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="E34" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M33" s="2" t="s">
+      <c r="F34" s="7" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="G34" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="H34" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>302</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>93</v>
+        <v>298</v>
       </c>
       <c r="L34" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="F35" s="7" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
-        <v>1873</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="G35" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="H35" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>311</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1931</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="H36" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
-        <v>1875</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>321</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="K36" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="H37" s="10" t="s">
         <v>323</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
-        <v>1875</v>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>333</v>
+        <v>1882</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1937</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="I38" s="9"/>
+        <v>327</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>330</v>
+      </c>
       <c r="J38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>151</v>
+        <v>331</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M38" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
-        <v>1879</v>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="K39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>1883</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1946</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="H40" s="10" t="s">
         <v>348</v>
-      </c>
-      <c r="M39" s="19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="M40" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>1966</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>356</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>1931</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>362</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G42" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="H42" s="9" t="s">
         <v>364</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B42" s="7" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>372</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
-        <v>22</v>
+        <v>365</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>180</v>
+        <v>366</v>
       </c>
       <c r="L42" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="M42" s="15" t="s">
+      <c r="G43" s="9" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
-        <v>1882</v>
-      </c>
-      <c r="B43" s="7" t="n">
-        <v>1937</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="H43" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>379</v>
-      </c>
+      <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K43" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1889</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="E44" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="M43" s="15" t="s">
+      <c r="F44" s="7" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B44" s="7" t="s">
+      <c r="G44" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="H44" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>386</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>23</v>
+        <v>298</v>
       </c>
       <c r="L44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="M44" s="14" t="s">
+      <c r="G45" s="9" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B45" s="7" t="n">
-        <v>1946</v>
-      </c>
-      <c r="C45" s="7" t="s">
+      <c r="H45" s="9" t="s">
         <v>392</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>397</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="L45" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B46" s="7" t="n">
-        <v>1966</v>
-      </c>
-      <c r="C46" s="7" t="s">
+      <c r="J46" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="K46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="M46" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="F46" s="7" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="D47" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="M46" s="15" t="s">
+      <c r="E47" s="10" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
-        <v>1885</v>
-      </c>
-      <c r="B47" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="G47" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="H47" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="E48" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M47" s="2" t="s">
+      <c r="F48" s="7" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B48" s="7" t="s">
+      <c r="G48" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="H48" s="10" t="s">
         <v>418</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="L48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M48" s="2" t="s">
+      <c r="G49" s="9" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B49" s="7" t="s">
+      <c r="H49" s="10" t="s">
         <v>426</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>432</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
-        <v>294</v>
+        <v>22</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>347</v>
+        <v>140</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>94</v>
+        <v>427</v>
       </c>
       <c r="M49" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="G50" s="19" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
-        <v>1891</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="H50" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="J50" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D50" s="8" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>1967</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="D51" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="E51" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="F51" s="20"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="I51" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M50" s="2" t="s">
+      <c r="J51" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M51" s="2" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C51" s="1" t="s">
+    <row r="52" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="C52" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="D52" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="E52" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="F52" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="G52" s="9"/>
+      <c r="H52" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="I52" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L51" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="M51" s="2" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
-        <v>1898</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="D53" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="E53" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="F53" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="G53" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>456</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>466</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="M53" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B54" s="7" t="s">
+      <c r="D55" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="E55" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="F55" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="G55" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="H55" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="I55" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="M55" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L54" s="2" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="D56" s="8" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>1901</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>1983</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="E56" s="21" t="s">
         <v>477</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="F56" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="G56" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="H56" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="G55" s="19" t="s">
+      <c r="I56" s="9"/>
+      <c r="J56" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="M56" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="J55" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M55" s="2" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="n">
+        <v>1907</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>1967</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="D57" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E57" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="F57" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="2" t="s">
+      <c r="G57" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="H57" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="M56" s="2" t="s">
+      <c r="I57" s="9"/>
+      <c r="J57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B57" s="7" t="s">
+    <row r="58" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E58" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="10" t="s">
+      <c r="G58" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="I57" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="H58" s="9" t="s">
         <v>496</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>504</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>152</v>
+        <v>473</v>
       </c>
       <c r="M58" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L59" s="2" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>1993</v>
-      </c>
-      <c r="C59" s="7" t="s">
+      <c r="M59" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D59" s="8" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="D60" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="10" t="s">
+      <c r="E60" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="F60" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="G60" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L59" s="2" t="s">
+      <c r="H60" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="I60" s="9"/>
+      <c r="J60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L60" s="2" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B60" s="7" t="s">
+      <c r="M60" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C60" s="7" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D61" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E61" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F61" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G61" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="H60" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>520</v>
-      </c>
-      <c r="I60" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B61" s="7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>528</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>414</v>
+        <v>109</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="M61" s="22" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="351.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>490</v>
+        <v>1910</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>1989</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>533</v>
+        <v>523</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>524</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="M62" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M62" s="13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="306.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>537</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>544</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>258</v>
+        <v>538</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>521</v>
+        <v>73</v>
       </c>
       <c r="M63" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="255.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
+        <v>1911</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="H64" s="10" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>552</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
-        <v>33</v>
+        <v>400</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="L64" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="H65" s="10" t="s">
         <v>554</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>2004</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>560</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>180</v>
+        <v>538</v>
       </c>
       <c r="L65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>561</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="H66" s="9" t="s">
         <v>562</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B66" s="7" t="n">
-        <v>1996</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>564</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>568</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
-        <v>139</v>
+        <v>563</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="M66" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
+        <v>1919</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="351.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
-        <v>1910</v>
-      </c>
-      <c r="B67" s="7" t="n">
-        <v>1989</v>
-      </c>
-      <c r="C67" s="7" t="s">
+      <c r="H67" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="F68" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="L67" s="2" t="s">
+      <c r="G68" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="M67" s="14" t="s">
+      <c r="H68" s="9" t="s">
         <v>578</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="306.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>582</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>585</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
-        <v>33</v>
+        <v>579</v>
       </c>
       <c r="K68" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M68" s="2" t="s">
+      <c r="F69" s="7" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="255.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B69" s="7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C69" s="7" t="s">
+      <c r="G69" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="H69" s="9" t="s">
         <v>589</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>593</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
-        <v>448</v>
+        <v>33</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="L69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="F70" s="7" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B70" s="7" t="s">
+      <c r="G70" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="H70" s="9" t="s">
         <v>597</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>602</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>586</v>
+        <v>140</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M70" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
-        <v>1914</v>
-      </c>
-      <c r="B71" s="7" t="s">
+      <c r="H71" s="10" t="s">
         <v>604</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>610</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="F72" s="7"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M71" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>1919</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="M72" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="D72" s="1" t="s">
+    </row>
+    <row r="73" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="D73" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="E73" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="F73" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="G73" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="H73" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="J73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="C73" s="7" t="s">
+      <c r="K73" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D73" s="8" t="s">
+    </row>
+    <row r="74" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="C74" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="D74" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="E74" s="16" t="s">
         <v>625</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="F74" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="2" t="s">
+      <c r="G74" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L73" s="2" t="s">
+      <c r="H74" s="9" t="s">
         <v>628</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>630</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>634</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>636</v>
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M74" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="M74" s="13" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>637</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
-        <v>1923</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>641</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>644</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>94</v>
+        <v>638</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B76" s="7" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="I76" s="9"/>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>644</v>
+      </c>
       <c r="J76" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>312</v>
+        <v>53</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>94</v>
+        <v>645</v>
       </c>
       <c r="M76" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B77" s="7" t="n">
-        <v>2003</v>
-      </c>
-      <c r="C77" s="7" t="s">
+      <c r="H77" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="I77" s="9"/>
+      <c r="J77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E77" s="11" t="s">
+    </row>
+    <row r="78" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="10" t="s">
+      <c r="C78" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="I77" s="10" t="s">
+      <c r="D78" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="J77" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K77" s="2" t="s">
+      <c r="E78" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="L77" s="2" t="s">
+      <c r="F78" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="M77" s="14" t="s">
+      <c r="G78" s="9" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="C78" s="7" t="s">
+      <c r="H78" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="D78" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="I78" s="10" t="s">
-        <v>667</v>
-      </c>
+      <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>84</v>
+        <v>662</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M78" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B79" s="7" t="s">
+      <c r="G79" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="H79" s="9" t="s">
         <v>670</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>672</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>673</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>675</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="2" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="L79" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7" t="n">
+        <v>1933</v>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="H80" s="10" t="s">
         <v>676</v>
-      </c>
-      <c r="M79" s="14" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
-        <v>1926</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>682</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>684</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
-        <v>22</v>
+        <v>400</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L80" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="M80" s="13" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="I81" s="9"/>
+      <c r="J81" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="M81" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="M80" s="2" t="s">
+    </row>
+    <row r="82" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>1926</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="E82" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="F82" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="G82" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="H82" s="10" t="s">
         <v>690</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>694</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>697</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>698</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>700</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
-        <v>33</v>
+        <v>463</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>205</v>
+        <v>53</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>691</v>
+      </c>
+      <c r="M82" s="13" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>702</v>
+        <v>1936</v>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>2019</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>705</v>
+        <v>694</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>695</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>708</v>
+        <v>697</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>698</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>709</v>
+        <v>34</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1930</v>
+        <v>1942</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>711</v>
+        <v>622</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>714</v>
+        <v>701</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>702</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="I84" s="9"/>
+        <v>704</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="I84" s="10"/>
       <c r="J84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>180</v>
+        <v>706</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B85" s="7" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>720</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>723</v>
-      </c>
-      <c r="I85" s="9"/>
+        <v>707</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>711</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>714</v>
+      </c>
       <c r="J85" s="2" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="M85" s="14" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B86" s="7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>728</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B87" s="7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>735</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>737</v>
-      </c>
-      <c r="I87" s="9"/>
-      <c r="J87" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="M87" s="14" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
-        <v>1936</v>
-      </c>
-      <c r="B88" s="7" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>740</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>742</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>745</v>
-      </c>
-      <c r="I88" s="9"/>
-      <c r="J88" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>747</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>749</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>752</v>
-      </c>
-      <c r="I89" s="10"/>
-      <c r="J89" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>758</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-    </row>
+        <v>427</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Schleiermacher&quot;   title=&quot; Wikipedia&quot;&gt;Friedrich SCHEIERMACHER&lt;/a&gt;  était un philosophe prussien,  souvent considéré comme le &quot;père de la théologie libérale moderne&quot;. &lt;a href=&quot;https://www.persee.fr/doc/rhpr_0035-2403_2011_num_91_1_1522&quot;  title=&quot;son apport théorique et pratique par persée&quot;&gt;Sa philosophie &lt;/a&gt; intègre des éléments du romantisme, de l'idéalisme allemand et du piétisme, en centrant l'humain sur une conscience intuitive de l'infini. Il édita Platon, prêcha et influença le protestantisme européen sans séparer foi et culture. &lt;/p&gt; &lt;p&gt;  Il pose le sentiment religieux comme une conscience immédiate de la dépendance absolue envers l'infini (Dieu), distincte du savoir ou de la morale kantienne. L'ego est une individualisation de la  &lt;a href=&quot;https://www.youtube.com/watch?v=gvpaUR1XceM&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Schleiermacher: The Man Behind Protestant Liberalism par Stephen D Morrison&quot;&gt;raison universelle, &lt;/a&gt; un microcosme où univers et individu s'unissent via la conscience de soi. Il articule individualité et communauté via la communication, honorant la finitude humaine et l'invention de soi contre l'absolutisme idéaliste. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures sont &quot;Discours sur la religion&quot; paru en 1799 et &quot;La foi chrétienne&quot;  paru vers 1821, où il réconcilie rationalité et piété. Il a profondément marqué la théologie protestante moderne en introduisant une approche centrée sur le sentiment religieux et l'expérience personnelle, plutôt que sur les dogmes rigides ou la raison pure. Son idée de &quot;dépendance absolue&quot; envers Dieu et la relativisation des doctrines comme expressions humaines de la piété ont pavé la voie au &lt;a href=&quot;https://www.youtube.com/watch?v=1FveOtAB86s&quot;  title=&quot;L'argument éthique de Schleiermacher en faveur de l'universalisme par Sola Media&quot;&gt;libéralisme théologique. &lt;/a&gt;&lt;/p&gt; &lt;p&gt;  Fondateur de l'herméneutique moderne, art général d'interprétation reliant traduction, littérature et exégèse biblique, il lance l'herméneutique critique de l'Écriture et une théologie pratique pertinente pour la modernité, influençant Ritschl et l'individualisme religieux.&lt;/p&gt; "/>
-    <hyperlink ref="E8" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Owen&quot;  title=&quot; Wikipedia&quot;&gt;Robert OWEN&lt;/a&gt; était un industriel gallois devenu philosophe social, figure majeure du &lt;a href=&quot;https://laviedesidees.fr/Robert-Owen-pere-du-socialisme-britannique&quot; style=&quot;color:#88A1E9&quot; title=&quot;Robert Owen, père du socialisme britannique ? par idées de la vie&quot;&gt;&quot;socialisme utopique&quot;&lt;/a&gt; et l’un des pères du mouvement coopératif et de l’urbanisme social. Il défend une thèse matérialiste du caractère humain : pour lui, le caractère n’est pas inné mais entièrement façonné par les &quot;circonstances&quot; physiques, morales et sociales auxquelles l’individu est exposé dès l’enfance. Il en conclut que l’on ne doit ni louer ni blâmer moralement les individus, mais transformer les institutions et l’environnement pour produire des caractères meilleurs, ce qui fait de l’éducation et de l’organisation sociale les leviers principaux de la réforme morale. &lt;/p&gt; &lt;p&gt; À &lt;a href=&quot;https://www.youtube.com/watch?v=QHWn6aPxKtQ&quot; title=&quot;New Lanark: Robert Owen's Utopianism and the Latter Day Saints par Centre Place&quot;&gt;New Lanark&lt;/a&gt;, il crée des écoles modèles, dont l’&quot;Institute for the Formation of Character&quot;, qui proposent une éducation gratuite, non répressive, axée sur le jeu, la musique et la formation morale plutôt que sur la simple préparation au travail. À partir de 1817, il promeut des communautés coopératives auto-suffisantes, comme New Harmony aux États-Unis, conçues comme des petites villes idéales où la propriété est collective et où l’organisation rationnelle du travail permet de supprimer la misère et la concurrence&lt;/p&gt; &lt;p&gt;  Il critique vigoureusement les religions instituées, auxquelles il reproche d’entretenir le sectarisme et la division, et propose une &quot;religion rationnelle&quot; fondée sur la bienveillance, la coopération et l’éducation. Il devient un  &lt;a href=&quot;https://www.youtube.com/watch?v=VmDDCsdQNAY&quot;  title=&quot;The Reformer Who Dreamed Of A Utopia | Robert Owen par History's forgotten people&quot;&gt;inspirateur important &lt;/a&gt; du mouvement ouvrier britannique, soutient les premières lois sur le travail des enfants, participe aux débuts du syndicalisme et contribue à développer le mouvement coopératif, dont il est souvent présenté comme un fondateur. &lt;/p&gt; &lt;p&gt; Son texte majeur est &lt;a href=&quot;https://www.youtube.com/watch?v=rY9ic8AC2VU&quot;  title=&quot;&quot;A New View of Society and Other Writings&quot; By Robert Owen par Novelzilla&quot;&gt;&quot;A New View of Society&quot; &lt;/a&gt; , où il expose sa théorie de la formation du caractère et ses projets de réforme sociale globale, complété plus tard par &quot;The Book of the New Moral World&quot;. Marx et Engels le rangeront parmi les &quot;socialistes utopiques&quot; : ils critiquent son manque d’analyse du capitalisme, mais reconnaissent en lui un précurseur dont les expériences concrètes ont nourri le socialisme et l’idée moderne de réforme par les institutions. &lt;/p&gt; "/>
-    <hyperlink ref="E10" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Shepherd&quot;  title=&quot; Wikipedia&quot;&gt;Mary SHEPHERD&lt;/a&gt; était une philosophe écossaise connue surtout pour sa défense d’une métaphysique réaliste et sa critique approfondie de la conception de &lt;a href=&quot;https://www.youtube.com/watch?v=HNfw1g_omaM&quot; style=&quot;color:#88A1E9&quot; title=&quot;Mary Shepherd's Philosophy: Causation, Perception, and Mind  par Philosopher Friends&quot;&gt;la causalité &lt;/a&gt; chez Hume et les philosophes écossais de son époque. &lt;/p&gt; &lt;p&gt; Elle soutient des principes comme &quot;un être ne peut pas commencer à exister de lui-même&quot; et &quot;des causes semblables produisent nécessairement des effets semblables&quot;, cherchant à montrer qu’il y a une nécessité dans le lien causal, et non une simple habitude psychologique comme chez Hume.&lt;/p&gt; &lt;p&gt;  Elle défend l’idée que nos croyances existentielles peuvent être rationnellement justifiées par des arguments causaux, et ne reposent ni sur un simple scepticisme ni seulement sur l’instinct. Dans ses essais sur la perception, elle critique l’idéalisme de Berkeley et certaines positions de Reid, mais reste réaliste : pour elle, la perception et la causalité permettent de conclure à l’existence d’un univers externe. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - &quot;An Essay upon the Relation of Cause and Effect&quot; paru en 1824 : livre où elle critique la théorie humienne de la causalité et discute aussi Thomas Brown et William Lawrence et - &quot;Essays on the Perception of an External Universe, and other Subjects Connected with the Doctrine of Causation&quot; paru en 1827 : recueil de textes sur la perception du monde extérieur, la causalité, l’existence de Dieu, l’esprit et le corps, discutant notamment Berkeley et Thomas Reid. &lt;/p&gt; &lt;p&gt; Depuis la fin du XXᵉ siècle, des historiennes et historiens de la philosophie, ainsi que des éditions critiques de ses œuvres, contribuent à la réhabiliter comme une figure importante de la philosophie moderne, en particulier dans les études féministes de la philosophie. On note son influence sur la philosophie écossaise, et des contemporains la citent comme une interlocutrice de poids dans les débats sur la causalité et la connaissance. &lt;/p&gt; "/>
-    <hyperlink ref="E11" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Bolzano&quot;  title=&quot; Wikipedia&quot;&gt;Bernard BOLZANO&lt;/a&gt; était un philosophe, logicien et mathématicien tchèque d'origine italienne, prêtre catholique et professeur à Prague, connu pour son œuvre monumentale Wissenschaftslehre (1837), une théorie de la science visant à fonder toutes les disciplines sur une logique rigoureuse. Il distingue trois domaines : le langage (mots, phrases), la pensée subjective (idées et jugements humains) et le domaine logique objectif (idées &quot;en soi&quot; et propositions &quot;en soi&quot;), qui existent indépendamment de l'esprit humain, anticipant la sémantique moderne. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=q3B51UxE2Eo&quot; title=&quot;b Bolzano logic truth philosophy par  philosopher friends&quot;&gt;Sa philosophie &lt;/a&gt;  exposée principalement dans sa Wissenschaftslehre (1837), vise à établir une théorie universelle de la science reposant sur des fondements logiques indubitables. Il distingue trois domaines distincts : le langage (mots et phrases), la pensée subjective (idées et jugements humains) et le domaine objectif de la logique (idées &quot;en soi&quot; et propositions &quot;en soi&quot;), ces dernières existant indépendamment de tout esprit, comme des entités abstraites atemporelles et accessibles par la raison pure. &lt;/p&gt; &lt;p&gt; Il  révolutionne la logique en introduisant les &quot;propositions en soi&quot; (Sätze an sich), vérités objectives analysables par leurs parties constitutives (représentations objectives). La relation clé est celle de &quot;fonction&quot; ou &quot;fondation&quot; (Abfolge), où une vérité se justifie par des vérités plus fondamentales, formant une hiérarchie architectonique des sciences : chaque discipline est un sous-ensemble cohérent du domaine total des vérités, organisé déductivement mais aussi objectivement. &lt;/p&gt; &lt;p&gt; Il rejette l'idéalisme subjectif de Kant ou Hegel : les vérités mathématiques et logiques ne dépendent pas de la constitution humaine, mais préexistent comme réalités objectives. Sa sémantique propositionnelle anticipe Frege et la logique moderne, avec une déduction stricte (degré 1 de validité) opposée aux contradictions (degré 0) et aux probabilités. &lt;/p&gt; &lt;p&gt; Il applique cette rigueur à une éthique et une métaphysique objectivistes : le bien et le mal sont des propriétés objectives des actions, fondées sur des impératifs catégoriques logiques. &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1977_num_75_27_5948_t1_0542_0000_3&quot; title=&quot;qu’est ce que la philosophie par  Persée&quot;&gt;Sa pensée, &lt;/a&gt; anti-sceptique, cherche à ancrer toute connaissance dans des bases irréfutables pour éviter le doute radical. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H11" r:id="rId5" display="https://laphilo.fr/pho/bbolzano-mini.webp"/>
-    <hyperlink ref="E12" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Giacomo_Leopardi&quot;  title=&quot; Wikipedia&quot;&gt;Giacomo LEOPARDI&lt;/a&gt;  était un poète &amp; philosophe italien souvent présenté comme l’un des plus profonds représentants du pessimisme moderne. À partir de 1819, il vit ce qu’il appelle une &quot;conversion philosophique&quot; : il quitte l’illusion d’un monde harmonieux pour la recherche du &quot;vrai&quot;, au prix d’une vision très sombre de la condition humaine. &lt;/p&gt; &lt;p&gt; Il i résume   &lt;a href=&quot;https://www.youtube.com/watch?v=2IQ7BUruaMk&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Giacomo Léopardi : Pensées par Ina Culture&quot;&gt;&quot;sa pensée &lt;/a&gt; par l’idée d’&quot;infelicità&quot;, un malheur constitutif de la condition humaine, et non pas seulement accidentel. Il se méfie de l’idée de progrès moral ou spirituel de l’humanité, qu’il voit comme un récit optimiste sans fondement réel.  La nature n’est pas non plus bonne ni providentielle, elle produit la vie mais aussi la souffrance, sans finalité morale ; l’existence est &quot;un mal pour tous les éléments qui composent l’univers&quot;. &lt;/p&gt; &lt;p&gt; Pour lui, la raison dévoile la vérité, mais cette vérité est désespérante et détruit les illusions qui rendaient la vie supportable.  Il valorise les illusions (espoirs, rêves, mythes) comme un rempart contre le nihilisme et l’égoïsme ; la &quot;pure raison&quot;, en les dissipant, isole les individus et dissout les liens sociaux. Son pessimisme n’est pas une complaisance à la tristesse ; c’est une lucidité douloureuse sur la finitude et la souffrance, qu’il assume jusqu’au bout. : Il ne cherche pas à &quot;propager&quot; une doctrine du désespoir, mais à chanter,  &lt;a href=&quot;https://www.youtube.com/watch?v=MbXrKkikvpg&quot;  title=&quot;Dialogue du Tasse et de son démon familier, Giacomo Leopardi par Poème&quot;&gt;en poète,&lt;/a&gt;  le mal de vivre et à en tirer une vision lucide de l’humain. &lt;/p&gt; &lt;p&gt;  Il écrit qu’une philosophie séparée de toute religion (comprise comme morale générale) devient une &quot;doctrine de la scélératesse raisonnée&quot;, c’est‑à‑dire une pensée qui peut justifier l’absence de vertu.  Pour atteindre sa vraie perfection, la philosophie doit, selon lui, rencontrer la poésie, c’est‑à‑dire l’imagination, la sensibilité, la capacité de faire sentir ce qu’elle pense. &lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le Zibaldone de Giacomo Leopardi par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11991-13.04.2014-ITEMA_20614026-2014C18021E0014-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E13" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Stuart_Mill&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href=&quot;https://www.youtube.com/watch?v=kDfp2afvj28&quot; style=&quot;color:#88A1E9&quot; title=&quot;John Stuart Mill - Synthèse par El Khader&quot;&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=yCDOVcvNYpY&quot; title=&quot; L'utilitarisme par Culture Philo&quot;&gt;&quot;  l’Utilitarisme&quot;&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href=&quot;https://www.youtube.com/watch?v=DVG_FL8jKe0&quot; title=&quot;John Stuart Mill - De La Liberté par Let's make liberalism great again&quot;&gt;&quot; De la liberté&quot;&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href=&quot;https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s&quot; title=&quot;JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques&quot;&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;John Stuart Mill par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;"/>
-    <hyperlink ref="E16" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Juan_Donoso_Cort%C3%A9s&quot;  title=&quot; Wikipedia&quot;&gt;Juan Donoso CORTÉS&lt;/a&gt;  était un marquis, philosophe, écrivain et homme politique espagnol né à Valle de la Serena en Estrémadure, est une figure majeure du contre-révolutionnarisme catholique. Issu d'une famille noble liée à Hernán Cortés, il étudie le droit à Salamanque et Séville, influencé initialement par les Lumières (Rousseau, Voltaire). Il commence comme libéral modéré, soutenant la régente Marie-Christine et la Constitution de 1812, et occupe des postes diplomatiques comme ambassadeur à Berlin. Son portrait par Federico de Madrazo en 1849 le montre en homme sérieux, décoré, symbole de son ascension politique. &lt;/p&gt; &lt;p&gt;  Marqué par le Printemps des peuples de 1848, il rompt avec le libéralisme pour embrasser un traditionalisme radical inspiré de Joseph de Maistre, Louis de Bonald et Vico. Dans son &lt;a href=&quot;https://www.persee.fr/doc/mcm_1146-1225_1991_num_9_1_1035&quot;  title=&quot; une interpretation apocalyptique de l’ère des masses par Persée&quot;&gt;Discours sur la dictature &lt;/a&gt;  (1848) aux Cortes espagnols, il défend la dictature comme rempart contre la révolution, opposant la répression intérieure (morale, religieuse) à la répression extérieure (politique). Pour lui, plus une société est catholique, moins elle a besoin &lt;a href=&quot;https://www.youtube.com/watch?v=TVfxMGiUJqE&quot;  title=&quot; Donoso Cortès – Discours sur la dictature par La Sapinière&quot;&gt;d'État autoritaire &lt;/a&gt; ; l'inverse mène à l'anarchie ou au despotisme. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Essai sur le catholicisme, le libéralisme et le socialisme (1851), est une théologie de l'histoire providentialiste et pessimiste. Il y dénonce le libéralisme comme &quot;théorie de l'anarchie&quot; issue de la raison humaine faillible, et le socialisme comme son aboutissement satanique, prônant la souveraineté divine et l'infaillibilité de l'autorité (papale). Influencé par saint Augustin et Bossuet, il voit le catholicisme comme seul antidote à la décadence moderne. &lt;/p&gt; &lt;p&gt; Penseur précurseur de Carl Schmitt et de l'ultramontanisme, il meurt à Paris en 1853, sa tombe à Madrid témoignant de son legs conservateur. Sa critique prophétique du rationalisme et du progrès libéral résonne encore dans les débats sur l'ordre moral face à la modernité. &lt;/p&gt; "/>
-    <hyperlink ref="H18" r:id="rId9" display="https://www.laphilo.fr/pho/csecretan-mini.webp"/>
-    <hyperlink ref="E19" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Marx&quot;  title=&quot; Wikipedia&quot;&gt;Karl MARX&lt;/a&gt; était un philosophe, économiste et révolutionnaire allemand né à Trèves, est le fondateur  &lt;a href=&quot;https://www.youtube.com/watch?v=W_ZwUjnl4W4&quot;  title=&quot;La philosophie de Karl Marx par Parole de philosophe&quot;&gt;du marxisme &lt;/a&gt; avec Friedrich Engels. Issu d'une famille juive convertie au protestantisme, il étudie le droit et la philosophie à Bonn, Berlin et Iéna, où il est influencé par Hegel et les jeunes hégéliens comme David Strauss, dont il critique les idées religieuses dans sa jeunesse. Exilé en France puis en Angleterre après les révolutions de 1848, il vit dans la précarité à Londres, soutenu par Engels, et milite au sein de l'Internationale ouvrière. Son portrait de 1875 le montre barbu, pensif, incarnation du penseur engagé.   &lt;/p&gt; &lt;p&gt;    Sa philosophie repose sur le matérialisme historique et dialectique, voyant l'histoire comme une succession de modes de production (esclavagiste, féodal, capitaliste) mue par  &lt;a href=&quot;https://www.youtube.com/watch?v=1pYmqDnvTh8&quot;  title=&quot;Les classes sociales par DigiSchool Lycee &quot;&gt;la lutte des classes &lt;/a&gt; entre exploiteurs et exploités. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=jb-5oSF2dpU&amp;ab_channel=TanguyLacroix&quot;  title=&quot;Le Manifeste du Parti Communiste par Tanguy Lacroix &quot;&gt;&quot;Le Manifeste communiste  &lt;/a&gt; (1848), coécrit avec Engels, il appelle le prolétariat à abolir la propriété privée des moyens de production pour instaurer une société sans classes. Le Capital (1867-1883) analyse le capitalisme comme un système d'exploitation via la plus-value extraite du travail   &lt;a href=&quot;https://www.youtube.com/watch?v=rEAxxsX_um0&amp;t=4s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'Aliénation par le Précepteur &quot;&gt;salarié aliéné, &lt;/a&gt;  prédisant sa chute par ses contradictions internes. &lt;/p&gt; &lt;p&gt;  Il rejette la religion comme « opium du peuple », outil d'aliénation masquant l'exploitation réelle, et prône la praxis révolutionnaire : transformer le monde par l'action collective des travailleurs. Critiquant le libéralisme et le socialisme utopique, il envisage une dictature du prolétariat transitoire menant au communisme, où l'État dépérit et les besoins sont satisfaits selon les capacités. Ses idées opposent radicalement celles de Donoso Cortés, qui y voyait un aboutissement satanique du libéralisme. &lt;/p&gt;   &lt;p&gt; Sa contribution la plus importante à la théorie politique est sa conception du  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Mat%C3%A9rialisme_dialectique&quot;  title=&quot;Le Marxisme Dialectique par Wikipedia &quot;&gt;&quot;matérialisme dialectique&quot;&lt;/a&gt;, qui est l'idée que le changement historique est motivé par des conflits entre des classes sociales opposées et que ces conflits sont finalement résolus par la révolution. &lt;/p&gt; &lt;p&gt; Il a également écrit abondamment sur l'économie, en particulier sur la théorie de la valeur-travail, qui postule que la valeur d'un bien ou d'un service est basée sur la quantité de travail nécessaire pour le produire. &lt;/p&gt; &lt;p&gt;     Son influence sur le XXe siècle est immense : révolutions bolchevique, chinoise, mouvements ouvriers mondiaux, et disciplines comme la sociologie ou l'économie. Malgré les échecs des régimes « marxistes », sa critique du capitalisme reste débattue aujourd'hui. &lt;/p&gt;    &lt;audio controls title=&quot;Pour l'avenir par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-26.09.2020-ITEMA_22438423-2020C40092E0005-1779455909.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E21" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Spencer&quot;  title=&quot; Wikipedia&quot;&gt;Herbert SPENCER&lt;/a&gt; était un philosophe, sociologue et anthropologue britanique et un parfait exemple d'autodidacte. Ingénieur de formation, il devient journaliste et se consacre entièrement à l'écriture. Son œuvre est immense, culminant avec son Système de &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-5541_1904_num_11_41_1823&quot; title=&quot; La philosophie d'Herbert Spencer  par Persée&quot;&gt; philosophie synthétique&lt;/a&gt;, une série de volumes visant à unifier toutes les connaissances humaines (biologie, psychologie, sociologie, éthique) sous un seul principe directeur : l'évolution. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre (et la plus controversée) est son application de la théorie de l'évolution à la société humaine, une idée souvent résumée par l'expression qu'il a popularisée : la &quot;survie du plus apte&quot;. Il a développé une théorie de l'évolution avant même la publication de &quot;L'Origine des espèces de Charles Darwin&quot;. Cependant, alors que Darwin se concentrait sur le mécanisme biologique de la sélection naturelle, Spencer voyait &lt;a href=&quot;https://www.youtube.com/watch?v=pBbr4mBO3kA&quot; style=&quot;color:#88A1E9&quot; title=&quot; &#10;Social Darwinism | Herbert Spencer par Sociologylearners&quot;&gt;l'évolution&lt;/a&gt;  comme une loi universelle s'appliquant à tous les phénomènes : l'univers, les organismes biologiques, l'esprit humain, les cultures et les sociétés progressent tous du simple au complexe, de l'homogène à l'hétérogène. &lt;/p&gt; &lt;p&gt; Il  a appliqué le principe de la &quot;survie du plus apte&quot; aux sociétés humaines. Il estimait que la compétition entre les individus et entre les sociétés était un moteur naturel et bénéfique du progrès. Elle permettait d'éliminer les &quot;inaptes&quot; et de favoriser les &quot;plus aptes&quot; (les plus talentueux, les plus travailleurs, les plus adaptés), conduisant ainsi à l'amélioration de l'espèce humaine.&lt;/p&gt; &lt;p&gt;  Il était un farouche partisan du libéralisme intégral et de l'État minimal (laissez-faire). Il s'opposait catégoriquement à toute intervention de l'État dans la vie sociale, comme l'aide aux pauvres, les lois sociales, l'éducation publique ou la santé publique. Pour lui, ces interventions artificielles perturbaient le processus naturel de sélection en maintenant en vie les &quot;inaptes&quot;, ce qui affaiblissait la société à long terme. Il n'a pas simplement &quot;appliqué&quot; &lt;a href=&quot;https://www.youtube.com/watch?v=MfsLeQOZfEA&quot;  title=&quot; Le DARWINISME SOCIAL en 6 minutes !  par Culture Philo&quot;&gt;Darwin aux sociétés&lt;/a&gt; . Il avait sa propre théorie évolutionniste, et c'est Darwin qui a ensuite emprunté l'expression &quot;survie du plus apte&quot; à Spencer. &lt;/p&gt; &lt;p&gt; Il était un penseur complexe qui a tenté de bâtir un système philosophique total. Bien que sa réputation soit aujourd'hui entachée par les usages politiques terribles qui ont été faits de ses idées, son influence sur la pensée moderne est indéniable. Il reste une figure essentielle pour comprendre l'optimisme scientiste et la foi dans le progrès qui caractérisent le XIXe siècle, ainsi que les dérives possibles lorsqu'on tente d'appliquer des lois naturelles au domaine social et moral. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H22" r:id="rId12" display="https://www.laphilo.fr/pho/thhuxley-mini.webp"/>
-    <hyperlink ref="E23" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Henry_Sidgwick&quot;   title=&quot; Wikipedia&quot;&gt;Henry SIDGWICK&lt;/a&gt; était un philosophe anglais majeur de l'utilitarisme classique, influencé par Jeremy Bentham et John Stuart Mill. Il excella en mathématiques et sciences humaines à Cambridge, obtenant un poste de maître de conférences en 1859 au Trinity College. Il promut l'éducation des femmes en cofondant le Newnham College en 1875 et œuvra pour des cours du soir et l'enseignement par correspondance, rendant l'université accessible aux travailleurs.  &lt;/p&gt; &lt;p&gt; Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/The_Methods_of_Ethics&quot;  title=&quot;The methods of ethics  par Wikipedia&quot;&gt;&quot;The Methods of Ethics&quot;&lt;/a&gt;, il analyse trois méthodes éthiques du sens commun : l'intuitionnisme, , &lt;a href=&quot;https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=3s&quot;  title=&quot;L'UTILITARISME en 4 minutes par Culture Philo&quot;&gt;l'utilitarisme&lt;/a&gt; et l'égoïsme éthique, les ramenant à des principes rationnels comme l'universalité, la prudence et la bienveillance pour le plus grand bonheur. Il rejette l'empirisme et l'égoïsme psychologique de Bentham, défendant un intuitionnisme philosophique avec des critères de vérité basés sur la clarté, la cohérence et le consensus. Il introduit le paradoxe de l'hédonisme, où la poursuite directe du plaisir peut l'éloigner, et soutient un réalisme moral non naturaliste, où les vérités éthiques sont cognitives et non réductibles à des propriétés naturelles. &lt;/p&gt; &lt;p&gt; Il contribua à l'économie politique et à l'épistémologie, critiquant les inconsistances de la &lt;a href=&quot;https://www.youtube.com/watch?v=45WGS8b6Xd8&quot;  title=&quot;Henry Sidgwick | Ethics, Utilitarianism, and Beyond par Philosopher Friends&quot;&gt;morale commune&lt;/a&gt; pour les résoudre via l'utilitarisme. Athée agnostique après un éloignement du christianisme, il fonda en 1888 la &quot;Cambridge Ethical Society&quot;, une organisation humaniste précoce. Son travail sur la parapsychologie visait à examiner scientifiquement des phénomènes comme la télépathie, motivé par des implications éthiques sur l'au-delà. &lt;/p&gt; "/>
-    <hyperlink ref="E24" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Auberon_Edward_Herbert&quot;  title=&quot; Wikipedia&quot;&gt;Auberon Edward HERBERT&lt;/a&gt; était un aristocrate, politicien, écrivain et philosophe politique britannique. Il est surtout connu comme le créateur et le principal popularisateur  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Volontarisme_(courant_politique)&quot;  title=&quot;volontarisme politique   par Wikipedia&quot;&gt;du volontarisme, &lt;/a&gt; une doctrine politique fondée sur un gouvernement financé exclusivement par des cotisations volontaires. &lt;/p&gt; &lt;p&gt; Son principe fondamental était que l'usage de la force, même par une majorité parlementaire, contre des individus pacifiques est toujours immoral. De ce postulat, il considérait l'impôt obligatoire comme une forme de contrainte légalisée.  &lt;a href=&quot;https://www.youtube.com/watch?v=6gHkEBGmevc&quot;  title=&quot;auberon herbert unknown hero par the daily objective&quot;&gt;Sa conception &lt;/a&gt; prônait un État financé uniquement par des cotisations volontaires des citoyens. Il ne rejetait cependant pas totalement l'État. Il pensait que un appareil centralisé de justice (incluant tribunaux, police et armée) est nécessaire pour défendre les droits individuels contre l'agression extérieure et la criminalité. Il exigeait simplement que cet appareil ne force personne à financer ses actions. &lt;/p&gt; &lt;p&gt; Il  était un disciple ardent mais indépendant de la philosophie de Herbert Spencer. Il a développé une variante du  &lt;a href=&quot;https://www.libertarianism.org/publications/essays/auberon-herbert-voluntaryist&quot;  title=&quot;volontarisme par libertarianism&quot;&gt;spencérien individualisme &lt;/a&gt; qu'il décrivait comme « volontarisme ». Il fut actif dans des organisations comme la Personal Rights and Self-Help Association et la Liberty and Property Defense League. &lt;/p&gt; &lt;p&gt;  Bien que le volontarisme soit parfois associé à l'anarcho-capitalisme au XXᵉ siècle, il rejetait l'anarchie et défendait l'existence d'un État pouvant faire respecter la loi. Il a écrit pendant plus de 20 ans, produisant des pamphlets et des centaines de lettres dans des journaux.  &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H24" r:id="rId15" display="https://laphilo.fr/pho/aeherbert-mini.webp"/>
-    <hyperlink ref="H25" r:id="rId16" display="https://www.laphilo.fr/pho/tgmasaryk-mini.webp"/>
-    <hyperlink ref="H28" r:id="rId17" display="https://www.laphilo.fr/pho/salexander-mini.webp"/>
-    <hyperlink ref="E29" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis&quot;  title=&quot; Wikipedia&quot;&gt;Jacob OSSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H29" r:id="rId19" display="https://www.laphilo.fr/pho/jossis-mini.webp"/>
-    <hyperlink ref="I29" r:id="rId20" display="https://www.laphilo.fr/photo/jossis.webp"/>
-    <hyperlink ref="E31" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alfred_North_Whitehead&quot;  title=&quot; Wikipedia&quot;&gt;Alfred North WHITEHEAD&lt;/a&gt; était un philosophe et mathématicien britannique, surtout connu pour avoir élaboré une &quot;philosophie du processus&quot;, où la réalité est pensée comme un flux d’événements plutôt que comme un ensemble de choses fixes.&lt;/p&gt; &lt;p&gt;  Il commence sa carrière comme mathématicien à Cambridge et coécrit avec Bertrand Russell les célèbres Principia Mathematica, œuvre majeure de logique et de fondements des mathématiques puis il se tourne vers la philosophie de la nature et la métaphysique, avant d’enseigner à Harvard où il écrit ses ouvrages philosophiques les plus importants.&lt;/p&gt; &lt;p&gt; Dans son livre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proc%C3%A8s_et_r%C3%A9alit%C3%A9&quot; title=&quot;Procès et réalité par Wikipedia&quot;&gt; &quot;Process and Reality&quot;&lt;/a&gt; paru en 1929, souvent considéré comme son grand ouvrage systématique, fondateur de la &quot;philosophie du processus&quot;. Il soutient que la réalité est faite  &lt;a href=&quot;https://www.youtube.com/watch?v=oH23HsQ58zA&amp;list=PL29llNJMc6MFgVRFBs83lA83DGLvfuqGF&quot; title=&quot; &quot;Importance&quot; - 'Modes of Thought' by Alfred North Whitehead par Culture Footnotes2Plato&quot;&gt;d’événements&lt;/a&gt; ou de &quot;occasions actuelles&quot; plutôt que d’objets matériels immuables.​ Chaque entité est un processus de devenir, lié aux autres par un réseau de relations, et non un &quot;bloc&quot; isolé.​ Il parle de &quot;philosophie de l’organisme&quot; ou le réel est un tissu vivant de processus interdépendants, où les prétendues essences stables (comme la matière) ne sont que des abstractions. &lt;/p&gt; &lt;p&gt;   Il propose une conception originale de Dieu, souvent qualifiée de &quot;dipolaire&quot;.​ D’un côté, la &quot;nature primordiale&quot; de Dieu contient l’ensemble  &lt;a href=&quot;https://www.youtube.com/watch?v=lhAdwvZx5yA&quot; title=&quot; Why The Future Is Never Fixed | Alfred North Whitehead par Purduit Of Truth&quot;&gt;des possibles &lt;/a&gt;ou des valeurs potentielles ; de l’autre, la &quot; nature conséquente&quot; désigne la manière dont Dieu intègre et valorise effectivement ce qui se passe dans le monde.​ &lt;/p&gt;  &lt;audio controls title=&quot; Alfred North Whitehead (1861 - 1947) par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10199-22.08.2007-ITEMA_20082691-2007C3330E0021-ITE_00007383_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H32" r:id="rId22" display="https://www.laphilo.fr/pho/gsantayana-mini.webp"/>
-    <hyperlink ref="E33" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Kazimierz_Twardowski&quot;  title=&quot; Wikipedia&quot;&gt;Kazimierz TWARDOWSKI&lt;/a&gt; était un philosophe polonais, fondateur de l'École philosophique de &lt;a href=&quot;https://www.youtube.com/watch?v=0jq5XLDyh3M&quot;  title=&quot;ivov-warsaw school par stay curious radio&quot;&gt;Lvov-Varsovie, &lt;/a&gt; l'un des mouvements philosophiques les plus importants et les plus originaux de l'Europe du XXe siècle. Élève de Franz Brentano à Vienne, il s'établit à Lvov en 1895 où il enseigna jusqu'à sa mort, formant une génération extraordinaire de philosophes, logiciens et mathématiciens polonais. Son influence sur la philosophie polonaise est comparable à celle de Brentano sur la philosophie autrichienne. &lt;/p&gt; &lt;p&gt; Sa contribution &lt;a href=&quot;https://www.youtube.com/watch?v=kGQU8Fw53BE&quot;  title=&quot;kazimierz twardowski par stay curious radio&quot;&gt;philosophique principale, &lt;/a&gt;  exposée dans &lt;em&gt;Zur Lehre vom Inhalt und Gegenstand der Vorstellungen&lt;/em&gt; (1894), est la distinction rigoureuse entre le contenu d'un acte mental (l'image mentale) et son objet (ce à quoi l'acte se réfère). Cette distinction, qui s'inscrit dans la tradition brentanienne de la psychologie descriptive, contribua à clarifier les fondements de la &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_2017_num_115_4_8628&quot;  title=&quot;twarddowski sur la vérité par persée&quot;&gt;théorie de la connaissance &lt;/a&gt; et prépara le terrain pour le développement de la phénoménologie et de la philosophie analytique. &lt;/p&gt; &lt;p&gt; Comme fondateur de l'École de Lvov-Varsovie, il forma des penseurs aussi importants que Jan Łukasiewicz (inventeur de la logique à trois valeurs et de la notation polonaise), Stanisław Leśniewski, Tadeusz Kotarbiński et Alfred Tarski. Cette école, caractérisée par sa rigueur logique, sa clarté analytique et son antipsychologisme, eut une influence considérable sur la logique et la philosophie du langage mondiales. Il incarne l'idéal du philosophe-professeur qui forme des disciples, invente des méthodes et fonde une tradition. &lt;/p&gt;"/>
-    <hyperlink ref="H33" r:id="rId24" display="https://www.laphilo.fr/pho/ktwardowski-mini.webp"/>
-    <hyperlink ref="E34" r:id="rId25" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Bertrand_Russell&quot;  title=&quot; Wikipedia&quot;&gt; Bertrand RUSSELL&lt;/a&gt;  était un philosophe, logicien, mathématicien, écrivain et militant britannique empiriste et rationaliste. Ses contributions majeures en mathématiques et en logique ont jeté les bases de la &lt;a href=&quot;https://www.youtube.com/watch?v=I1-6SA1DfRA&amp;ab_channel=HeureBleue&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;pourquoi la philosophie analytique est méconnue en France par Heure Bleue &quot;&gt;philosophie analytique&lt;/a&gt;, un courant dominant de la philosophie anglo-américaine en opposition avec la philosophie continentale romano-germanique. &lt;/p&gt; &lt;p&gt; Il était un philosophe très controversé par les positions qu'il prenait dans le domaine de la religion, de la sexualité et du travail. Son livre paru en 1929 &quot;Le Mariage et la Morale&quot; fera scandale à cette époque car il autorise la femme a pratiqué l'adultère. Concernant le travail, il fera  &lt;a href=&quot;https://www.youtube.com/watch?v=I7dQ5ZES3VI&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;Le travail et l'oisiveté par Alain Bajomée &quot;&gt;l'éloge de l'oisiveté&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;&#10;L'un des ses travaux les plus connus, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Principia_Mathematica&quot;  title=&quot;Principa Mathematica par Wikipédia &quot;&gt;&quot;Principia Mathematica&quot;&lt;/a&gt;, écrit en collaboration avec Alfred North Whitehead. Publié entre 1910 et 1913, cet ouvrage visait à fonder les mathématiques sur une base logique rigoureuse. Bien que le projet n'ait pas atteint tous ses objectifs, il a eu une influence considérable sur le développement ultérieur des mathématiques et de la logique. &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de la connaissance ou &quot;théorie des descriptions&quot; est une contribution majeure de la philosophie analytique. Elle a remis en cause la nature des propositions et la signification des termes définis par description.&lt;/p&gt; &lt;p&gt;&#10;Russell a reçu de nombreux honneurs au cours de sa vie, dont le prix Nobel de littérature en 1950, en reconnaissance de sa contribution exceptionnelle à la &lt;a href=&quot;https://www.youtube.com/watch?v=5IEYW5wuK3Y&amp;ab_channel=PhilosophyOverdose&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Interview on Philosophy par Philosophy Overdose &quot;&gt;pensée philosophique&lt;/a&gt; et à la littérature humaniste.  Il était un penseur engagé sur le plan politique et social ainsi qu'un défenseur passionné du pacifisme et s'est opposé à la participation britannique dans la Première Guerre mondiale. &lt;/p&gt;  &lt;audio controls title=&quot;Autobiographie de Bertrand Russell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-17.01.2017-ITEMA_21199485-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H37" r:id="rId26" display="https://www.laphilo.fr/pho/cgjung-mini.webp"/>
-    <hyperlink ref="E39" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans_Hahn_(math%C3%A9maticien)&quot;  title=&quot; Wikipedia&quot;&gt;Hans HAHN&lt;/a&gt; était un mathématicien autrichien, surtout connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach. Il fut également l’un des principaux fondateurs du Cercle de Vienne, avec Moritz Schlick, Philipp Frank et Otto Neurath. Son intérêt pour la philosophie ne fut donc pas celui d’un philosophe professionnel, mais celui d’un mathématicien qui cherchait à comprendre le rapport entre logique, mathématiques, langage et connaissance scientifique. &lt;/p&gt; &lt;p&gt; Sa philosophie s’inscrit dans l’empirisme logique ou positivisme logique. Comme les &lt;a href=&quot;https://www.youtube.com/watch?v=VReApTp5_zg&quot; title=&quot; le cercle de vienne par philosophie analytique&quot;&gt;autres membres du Cercle de Vienne, &lt;/a&gt;  il rejetait la métaphysique traditionnelle lorsqu’elle prétendait produire une connaissance indépendante de toute expérience ou de toute méthode logique. Il contestait notamment l’idée kantienne de vérités « synthétiques a priori » : selon cette orientation, une proposition est soit logique ou mathématique, soit empirique et vérifiable à partir de l’expérience. La philosophie devait ainsi se rapprocher de l’analyse logique des énoncés scientifiques. &lt;/p&gt; &lt;p&gt; Il accordait toutefois aux mathématiques un statut particulier. Il ne pensait pas qu’elles décrivent directement des objets réels, comme le font les sciences expérimentales. Les mathématiques et la logique établissent plutôt des relations formelles entre des propositions ou des symboles. Elles indiquent ce qui découle nécessairement de certaines règles et de certains axiomes. En ce sens, les vérités mathématiques sont analytiques : elles ne tirent pas leur certitude de l’observation, mais de la structure logique du système dans lequel elles sont formulées. &lt;/p&gt; &lt;p&gt; Un aspect important de sa pensée est son refus de fonder les mathématiques sur une intuition particulière. Il se méfiait de l’« intuition » au sens kantien, c’est-à-dire de l’idée que l’esprit aurait un accès immédiat aux structures mathématiques. Il défendait plutôt l’axiomatisation et la rigueur formelle, notamment dans l’arithmétique et l’analyse. Mais il ne réduisait pas nécessairement toute signification à une vérification directe : il soutenait que les hypothèses scientifiques peuvent être significatives même lorsqu’elles ne sont pas définitivement vérifiables, ce qui conduit à assouplir le vérificationnisme strict. &lt;/p&gt; &lt;p&gt; Il concevait la logique non comme une science décrivant les propriétés les plus générales des objets, mais comme un instrument construit par les êtres humains pour parler du monde avec précision. La logique ne serait donc pas une réalité cachée dans les choses : elle apparaît lorsque nous organisons nos énoncés au moyen d’un symbolisme. Sa philosophie défend ainsi une conception scientifique, anti-métaphysique et formaliste de la connaissance, tout en laissant une place aux hypothèses et à la diversité des systèmes logiques. Son œuvre philosophique, moins abondante que son œuvre mathématique, a néanmoins contribué à préparer plusieurs thèmes du positivisme logique et de la philosophie analytique des sciences. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H39" r:id="rId28" display="https://www.laphilo.fr/pho/hhahn-mini.webp"/>
-    <hyperlink ref="E40" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Weininger&quot;  title=&quot; Wikipedia&quot;&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href=&quot;https://www.youtube.com/watch?v=wetIerJEucU&quot; title=&quot; Otto Weininger Le génie Maudit par Aliouca&quot;&gt;maison de Beethoven à Vienne &lt;/a&gt; . Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=aFZpRoBlMQI&quot; title=&quot; Otto Weininger qui haîssait les femmes par Voyage Endormis&quot;&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href=&quot;https://www.youtube.com/watch?v=vMfEJQVv3VM&quot; title=&quot; Otto Weininger Le mytère du féminin par Philosopheasy en Français&quot;&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits &quot;féminins&quot; vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère &quot;féminine&quot; décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title=&quot;Otto Weininger et la question du genie par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E41" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H41" r:id="rId31" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
-    <hyperlink ref="E42" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H42" r:id="rId33" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
-    <hyperlink ref="H43" r:id="rId34" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
-    <hyperlink ref="I43" r:id="rId35" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
-    <hyperlink ref="E44" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H45" r:id="rId37" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
-    <hyperlink ref="E46" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H46" r:id="rId39" display="https://www.laphilo.fr/pho/pfrank-mini.webp"/>
-    <hyperlink ref="E47" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E49" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
-    <hyperlink ref="E53" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H54" r:id="rId43" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
-    <hyperlink ref="H56" r:id="rId44" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
-    <hyperlink ref="E57" r:id="rId45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H57" r:id="rId46" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
-    <hyperlink ref="I57" r:id="rId47" display="https://laphilo.fr/photo/lszabo.webp"/>
-    <hyperlink ref="E58" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
-    <hyperlink ref="E59" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H60" r:id="rId50" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
-    <hyperlink ref="I60" r:id="rId51" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
-    <hyperlink ref="H61" r:id="rId52" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
-    <hyperlink ref="E62" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
-    <hyperlink ref="H62" r:id="rId54" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
-    <hyperlink ref="E63" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E64" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E65" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
-    <hyperlink ref="E66" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
-    <hyperlink ref="H66" r:id="rId59" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
-    <hyperlink ref="E67" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer&quot; title=&quot; Wikipedia&quot;&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href=&quot;https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html&quot;  title=&quot;philosophie analytique par la philosophie&quot;&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href=&quot;https://www.youtube.com/watch?v=HG5kIR6iF8g&quot;  title=&quot;A,J, Ayer’s Emotivism par philosophy Vibe&quot;&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H67" r:id="rId61" display="https://www.laphilo.fr/pho/ajayer-mini.webp"/>
-    <hyperlink ref="H68" r:id="rId62" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
-    <hyperlink ref="H70" r:id="rId63" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
-    <hyperlink ref="H72" r:id="rId64" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
-    <hyperlink ref="E74" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E76" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
-    <hyperlink ref="E77" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H77" r:id="rId68" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
-    <hyperlink ref="I77" r:id="rId69" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="E78" r:id="rId70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H78" r:id="rId71" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
-    <hyperlink ref="I78" r:id="rId72" display="https://laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="H81" r:id="rId73" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
-    <hyperlink ref="E83" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
-    <hyperlink ref="E85" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H86" r:id="rId76" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
-    <hyperlink ref="E88" r:id="rId77" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H88" r:id="rId78" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
-    <hyperlink ref="H89" r:id="rId79" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
-    <hyperlink ref="E90" r:id="rId80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H90" r:id="rId81" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
+    <hyperlink ref="E6" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Robert_Owen&quot;  title=&quot; Wikipedia&quot;&gt;Robert OWEN&lt;/a&gt; était un industriel gallois devenu philosophe social, figure majeure du &lt;a href=&quot;https://laviedesidees.fr/Robert-Owen-pere-du-socialisme-britannique&quot; style=&quot;color:#88A1E9&quot; title=&quot;Robert Owen, père du socialisme britannique ? par idées de la vie&quot;&gt;&quot;socialisme utopique&quot;&lt;/a&gt; et l’un des pères du mouvement coopératif et de l’urbanisme social. Il défend une thèse matérialiste du caractère humain : pour lui, le caractère n’est pas inné mais entièrement façonné par les &quot;circonstances&quot; physiques, morales et sociales auxquelles l’individu est exposé dès l’enfance. Il en conclut que l’on ne doit ni louer ni blâmer moralement les individus, mais transformer les institutions et l’environnement pour produire des caractères meilleurs, ce qui fait de l’éducation et de l’organisation sociale les leviers principaux de la réforme morale. &lt;/p&gt; &lt;p&gt; À &lt;a href=&quot;https://www.youtube.com/watch?v=QHWn6aPxKtQ&quot; title=&quot;New Lanark: Robert Owen's Utopianism and the Latter Day Saints par Centre Place&quot;&gt;New Lanark&lt;/a&gt;, il crée des écoles modèles, dont l’&quot;Institute for the Formation of Character&quot;, qui proposent une éducation gratuite, non répressive, axée sur le jeu, la musique et la formation morale plutôt que sur la simple préparation au travail. À partir de 1817, il promeut des communautés coopératives auto-suffisantes, comme New Harmony aux États-Unis, conçues comme des petites villes idéales où la propriété est collective et où l’organisation rationnelle du travail permet de supprimer la misère et la concurrence&lt;/p&gt; &lt;p&gt;  Il critique vigoureusement les religions instituées, auxquelles il reproche d’entretenir le sectarisme et la division, et propose une &quot;religion rationnelle&quot; fondée sur la bienveillance, la coopération et l’éducation. Il devient un  &lt;a href=&quot;https://www.youtube.com/watch?v=VmDDCsdQNAY&quot;  title=&quot;The Reformer Who Dreamed Of A Utopia | Robert Owen par History's forgotten people&quot;&gt;inspirateur important &lt;/a&gt; du mouvement ouvrier britannique, soutient les premières lois sur le travail des enfants, participe aux débuts du syndicalisme et contribue à développer le mouvement coopératif, dont il est souvent présenté comme un fondateur. &lt;/p&gt; &lt;p&gt; Son texte majeur est &lt;a href=&quot;https://www.youtube.com/watch?v=rY9ic8AC2VU&quot;  title=&quot;&quot;A New View of Society and Other Writings&quot; By Robert Owen par Novelzilla&quot;&gt;&quot;A New View of Society&quot; &lt;/a&gt; , où il expose sa théorie de la formation du caractère et ses projets de réforme sociale globale, complété plus tard par &quot;The Book of the New Moral World&quot;. Marx et Engels le rangeront parmi les &quot;socialistes utopiques&quot; : ils critiquent son manque d’analyse du capitalisme, mais reconnaissent en lui un précurseur dont les expériences concrètes ont nourri le socialisme et l’idée moderne de réforme par les institutions. &lt;/p&gt; "/>
+    <hyperlink ref="E8" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Shepherd&quot;  title=&quot; Wikipedia&quot;&gt;Mary SHEPHERD&lt;/a&gt; était une philosophe écossaise connue surtout pour sa défense d’une métaphysique réaliste et sa critique approfondie de la conception de &lt;a href=&quot;https://www.youtube.com/watch?v=HNfw1g_omaM&quot; style=&quot;color:#88A1E9&quot; title=&quot;Mary Shepherd's Philosophy: Causation, Perception, and Mind  par Philosopher Friends&quot;&gt;la causalité &lt;/a&gt; chez Hume et les philosophes écossais de son époque. &lt;/p&gt; &lt;p&gt; Elle soutient des principes comme &quot;un être ne peut pas commencer à exister de lui-même&quot; et &quot;des causes semblables produisent nécessairement des effets semblables&quot;, cherchant à montrer qu’il y a une nécessité dans le lien causal, et non une simple habitude psychologique comme chez Hume.&lt;/p&gt; &lt;p&gt;  Elle défend l’idée que nos croyances existentielles peuvent être rationnellement justifiées par des arguments causaux, et ne reposent ni sur un simple scepticisme ni seulement sur l’instinct. Dans ses essais sur la perception, elle critique l’idéalisme de Berkeley et certaines positions de Reid, mais reste réaliste : pour elle, la perception et la causalité permettent de conclure à l’existence d’un univers externe. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - &quot;An Essay upon the Relation of Cause and Effect&quot; paru en 1824 : livre où elle critique la théorie humienne de la causalité et discute aussi Thomas Brown et William Lawrence et - &quot;Essays on the Perception of an External Universe, and other Subjects Connected with the Doctrine of Causation&quot; paru en 1827 : recueil de textes sur la perception du monde extérieur, la causalité, l’existence de Dieu, l’esprit et le corps, discutant notamment Berkeley et Thomas Reid. &lt;/p&gt; &lt;p&gt; Depuis la fin du XXᵉ siècle, des historiennes et historiens de la philosophie, ainsi que des éditions critiques de ses œuvres, contribuent à la réhabiliter comme une figure importante de la philosophie moderne, en particulier dans les études féministes de la philosophie. On note son influence sur la philosophie écossaise, et des contemporains la citent comme une interlocutrice de poids dans les débats sur la causalité et la connaissance. &lt;/p&gt; "/>
+    <hyperlink ref="E9" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_Bolzano&quot;  title=&quot; Wikipedia&quot;&gt;Bernard BOLZANO&lt;/a&gt; était un philosophe, logicien et mathématicien tchèque d'origine italienne, prêtre catholique et professeur à Prague, connu pour son œuvre monumentale Wissenschaftslehre (1837), une théorie de la science visant à fonder toutes les disciplines sur une logique rigoureuse. Il distingue trois domaines : le langage (mots, phrases), la pensée subjective (idées et jugements humains) et le domaine logique objectif (idées &quot;en soi&quot; et propositions &quot;en soi&quot;), qui existent indépendamment de l'esprit humain, anticipant la sémantique moderne. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=q3B51UxE2Eo&quot; title=&quot;b Bolzano logic truth philosophy par  philosopher friends&quot;&gt;Sa philosophie &lt;/a&gt;  exposée principalement dans sa Wissenschaftslehre (1837), vise à établir une théorie universelle de la science reposant sur des fondements logiques indubitables. Il distingue trois domaines distincts : le langage (mots et phrases), la pensée subjective (idées et jugements humains) et le domaine objectif de la logique (idées &quot;en soi&quot; et propositions &quot;en soi&quot;), ces dernières existant indépendamment de tout esprit, comme des entités abstraites atemporelles et accessibles par la raison pure. &lt;/p&gt; &lt;p&gt; Il  révolutionne la logique en introduisant les &quot;propositions en soi&quot; (Sätze an sich), vérités objectives analysables par leurs parties constitutives (représentations objectives). La relation clé est celle de &quot;fonction&quot; ou &quot;fondation&quot; (Abfolge), où une vérité se justifie par des vérités plus fondamentales, formant une hiérarchie architectonique des sciences : chaque discipline est un sous-ensemble cohérent du domaine total des vérités, organisé déductivement mais aussi objectivement. &lt;/p&gt; &lt;p&gt; Il rejette l'idéalisme subjectif de Kant ou Hegel : les vérités mathématiques et logiques ne dépendent pas de la constitution humaine, mais préexistent comme réalités objectives. Sa sémantique propositionnelle anticipe Frege et la logique moderne, avec une déduction stricte (degré 1 de validité) opposée aux contradictions (degré 0) et aux probabilités. &lt;/p&gt; &lt;p&gt; Il applique cette rigueur à une éthique et une métaphysique objectivistes : le bien et le mal sont des propriétés objectives des actions, fondées sur des impératifs catégoriques logiques. &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1977_num_75_27_5948_t1_0542_0000_3&quot; title=&quot;qu’est ce que la philosophie par  Persée&quot;&gt;Sa pensée, &lt;/a&gt; anti-sceptique, cherche à ancrer toute connaissance dans des bases irréfutables pour éviter le doute radical. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H9" r:id="rId4" display="https://laphilo.fr/pho/bbolzano-mini.webp"/>
+    <hyperlink ref="E10" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Giacomo_Leopardi&quot;  title=&quot; Wikipedia&quot;&gt;Giacomo LEOPARDI&lt;/a&gt;  était un poète &amp; philosophe italien souvent présenté comme l’un des plus profonds représentants du pessimisme moderne. À partir de 1819, il vit ce qu’il appelle une &quot;conversion philosophique&quot; : il quitte l’illusion d’un monde harmonieux pour la recherche du &quot;vrai&quot;, au prix d’une vision très sombre de la condition humaine. &lt;/p&gt; &lt;p&gt; Il i résume   &lt;a href=&quot;https://www.youtube.com/watch?v=2IQ7BUruaMk&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Giacomo Léopardi : Pensées par Ina Culture&quot;&gt;&quot;sa pensée &lt;/a&gt; par l’idée d’&quot;infelicità&quot;, un malheur constitutif de la condition humaine, et non pas seulement accidentel. Il se méfie de l’idée de progrès moral ou spirituel de l’humanité, qu’il voit comme un récit optimiste sans fondement réel.  La nature n’est pas non plus bonne ni providentielle, elle produit la vie mais aussi la souffrance, sans finalité morale ; l’existence est &quot;un mal pour tous les éléments qui composent l’univers&quot;. &lt;/p&gt; &lt;p&gt; Pour lui, la raison dévoile la vérité, mais cette vérité est désespérante et détruit les illusions qui rendaient la vie supportable.  Il valorise les illusions (espoirs, rêves, mythes) comme un rempart contre le nihilisme et l’égoïsme ; la &quot;pure raison&quot;, en les dissipant, isole les individus et dissout les liens sociaux. Son pessimisme n’est pas une complaisance à la tristesse ; c’est une lucidité douloureuse sur la finitude et la souffrance, qu’il assume jusqu’au bout. : Il ne cherche pas à &quot;propager&quot; une doctrine du désespoir, mais à chanter,  &lt;a href=&quot;https://www.youtube.com/watch?v=MbXrKkikvpg&quot;  title=&quot;Dialogue du Tasse et de son démon familier, Giacomo Leopardi par Poème&quot;&gt;en poète,&lt;/a&gt;  le mal de vivre et à en tirer une vision lucide de l’humain. &lt;/p&gt; &lt;p&gt;  Il écrit qu’une philosophie séparée de toute religion (comprise comme morale générale) devient une &quot;doctrine de la scélératesse raisonnée&quot;, c’est‑à‑dire une pensée qui peut justifier l’absence de vertu.  Pour atteindre sa vraie perfection, la philosophie doit, selon lui, rencontrer la poésie, c’est‑à‑dire l’imagination, la sensibilité, la capacité de faire sentir ce qu’elle pense. &lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le Zibaldone de Giacomo Leopardi par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11991-13.04.2014-ITEMA_20614026-2014C18021E0014-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E11" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/John_Stuart_Mill&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href=&quot;https://www.youtube.com/watch?v=kDfp2afvj28&quot; style=&quot;color:#88A1E9&quot; title=&quot;John Stuart Mill - Synthèse par El Khader&quot;&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=yCDOVcvNYpY&quot; title=&quot; L'utilitarisme par Culture Philo&quot;&gt;&quot;  l’Utilitarisme&quot;&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href=&quot;https://www.youtube.com/watch?v=DVG_FL8jKe0&quot; title=&quot;John Stuart Mill - De La Liberté par Let's make liberalism great again&quot;&gt;&quot; De la liberté&quot;&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href=&quot;https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s&quot; title=&quot;JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques&quot;&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;John Stuart Mill par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;&#10;"/>
+    <hyperlink ref="E13" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Juan_Donoso_Cort%C3%A9s&quot;  title=&quot; Wikipedia&quot;&gt;Juan Donoso CORTÉS&lt;/a&gt;  était un marquis, philosophe, écrivain et homme politique espagnol né à Valle de la Serena en Estrémadure, est une figure majeure du contre-révolutionnarisme catholique. Issu d'une famille noble liée à Hernán Cortés, il étudie le droit à Salamanque et Séville, influencé initialement par les Lumières (Rousseau, Voltaire). Il commence comme libéral modéré, soutenant la régente Marie-Christine et la Constitution de 1812, et occupe des postes diplomatiques comme ambassadeur à Berlin. Son portrait par Federico de Madrazo en 1849 le montre en homme sérieux, décoré, symbole de son ascension politique. &lt;/p&gt; &lt;p&gt;  Marqué par le Printemps des peuples de 1848, il rompt avec le libéralisme pour embrasser un traditionalisme radical inspiré de Joseph de Maistre, Louis de Bonald et Vico. Dans son &lt;a href=&quot;https://www.persee.fr/doc/mcm_1146-1225_1991_num_9_1_1035&quot;  title=&quot; une interpretation apocalyptique de l’ère des masses par Persée&quot;&gt;Discours sur la dictature &lt;/a&gt;  (1848) aux Cortes espagnols, il défend la dictature comme rempart contre la révolution, opposant la répression intérieure (morale, religieuse) à la répression extérieure (politique). Pour lui, plus une société est catholique, moins elle a besoin &lt;a href=&quot;https://www.youtube.com/watch?v=TVfxMGiUJqE&quot;  title=&quot; Donoso Cortès – Discours sur la dictature par La Sapinière&quot;&gt;d'État autoritaire &lt;/a&gt; ; l'inverse mène à l'anarchie ou au despotisme. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse, Essai sur le catholicisme, le libéralisme et le socialisme (1851), est une théologie de l'histoire providentialiste et pessimiste. Il y dénonce le libéralisme comme &quot;théorie de l'anarchie&quot; issue de la raison humaine faillible, et le socialisme comme son aboutissement satanique, prônant la souveraineté divine et l'infaillibilité de l'autorité (papale). Influencé par saint Augustin et Bossuet, il voit le catholicisme comme seul antidote à la décadence moderne. &lt;/p&gt; &lt;p&gt; Penseur précurseur de Carl Schmitt et de l'ultramontanisme, il meurt à Paris en 1853, sa tombe à Madrid témoignant de son legs conservateur. Sa critique prophétique du rationalisme et du progrès libéral résonne encore dans les débats sur l'ordre moral face à la modernité. &lt;/p&gt; "/>
+    <hyperlink ref="H15" r:id="rId8" display="https://www.laphilo.fr/pho/csecretan-mini.webp"/>
+    <hyperlink ref="E17" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Herbert_Spencer&quot;  title=&quot; Wikipedia&quot;&gt;Herbert SPENCER&lt;/a&gt; était un philosophe, sociologue et anthropologue britanique et un parfait exemple d'autodidacte. Ingénieur de formation, il devient journaliste et se consacre entièrement à l'écriture. Son œuvre est immense, culminant avec son Système de &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-5541_1904_num_11_41_1823&quot; title=&quot; La philosophie d'Herbert Spencer  par Persée&quot;&gt; philosophie synthétique&lt;/a&gt;, une série de volumes visant à unifier toutes les connaissances humaines (biologie, psychologie, sociologie, éthique) sous un seul principe directeur : l'évolution. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre (et la plus controversée) est son application de la théorie de l'évolution à la société humaine, une idée souvent résumée par l'expression qu'il a popularisée : la &quot;survie du plus apte&quot;. Il a développé une théorie de l'évolution avant même la publication de &quot;L'Origine des espèces de Charles Darwin&quot;. Cependant, alors que Darwin se concentrait sur le mécanisme biologique de la sélection naturelle, Spencer voyait &lt;a href=&quot;https://www.youtube.com/watch?v=pBbr4mBO3kA&quot; style=&quot;color:#88A1E9&quot; title=&quot; &#10;Social Darwinism | Herbert Spencer par Sociologylearners&quot;&gt;l'évolution&lt;/a&gt;  comme une loi universelle s'appliquant à tous les phénomènes : l'univers, les organismes biologiques, l'esprit humain, les cultures et les sociétés progressent tous du simple au complexe, de l'homogène à l'hétérogène. &lt;/p&gt; &lt;p&gt; Il  a appliqué le principe de la &quot;survie du plus apte&quot; aux sociétés humaines. Il estimait que la compétition entre les individus et entre les sociétés était un moteur naturel et bénéfique du progrès. Elle permettait d'éliminer les &quot;inaptes&quot; et de favoriser les &quot;plus aptes&quot; (les plus talentueux, les plus travailleurs, les plus adaptés), conduisant ainsi à l'amélioration de l'espèce humaine.&lt;/p&gt; &lt;p&gt;  Il était un farouche partisan du libéralisme intégral et de l'État minimal (laissez-faire). Il s'opposait catégoriquement à toute intervention de l'État dans la vie sociale, comme l'aide aux pauvres, les lois sociales, l'éducation publique ou la santé publique. Pour lui, ces interventions artificielles perturbaient le processus naturel de sélection en maintenant en vie les &quot;inaptes&quot;, ce qui affaiblissait la société à long terme. Il n'a pas simplement &quot;appliqué&quot; &lt;a href=&quot;https://www.youtube.com/watch?v=MfsLeQOZfEA&quot;  title=&quot; Le DARWINISME SOCIAL en 6 minutes !  par Culture Philo&quot;&gt;Darwin aux sociétés&lt;/a&gt; . Il avait sa propre théorie évolutionniste, et c'est Darwin qui a ensuite emprunté l'expression &quot;survie du plus apte&quot; à Spencer. &lt;/p&gt; &lt;p&gt; Il était un penseur complexe qui a tenté de bâtir un système philosophique total. Bien que sa réputation soit aujourd'hui entachée par les usages politiques terribles qui ont été faits de ses idées, son influence sur la pensée moderne est indéniable. Il reste une figure essentielle pour comprendre l'optimisme scientiste et la foi dans le progrès qui caractérisent le XIXe siècle, ainsi que les dérives possibles lorsqu'on tente d'appliquer des lois naturelles au domaine social et moral. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H18" r:id="rId10" display="https://www.laphilo.fr/pho/thhuxley-mini.webp"/>
+    <hyperlink ref="E19" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Henry_Sidgwick&quot;   title=&quot; Wikipedia&quot;&gt;Henry SIDGWICK&lt;/a&gt; était un philosophe anglais majeur de l'utilitarisme classique, influencé par Jeremy Bentham et John Stuart Mill. Il excella en mathématiques et sciences humaines à Cambridge, obtenant un poste de maître de conférences en 1859 au Trinity College. Il promut l'éducation des femmes en cofondant le Newnham College en 1875 et œuvra pour des cours du soir et l'enseignement par correspondance, rendant l'université accessible aux travailleurs.  &lt;/p&gt; &lt;p&gt; Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/The_Methods_of_Ethics&quot;  title=&quot;The methods of ethics  par Wikipedia&quot;&gt;&quot;The Methods of Ethics&quot;&lt;/a&gt;, il analyse trois méthodes éthiques du sens commun : l'intuitionnisme, , &lt;a href=&quot;https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=3s&quot;  title=&quot;L'UTILITARISME en 4 minutes par Culture Philo&quot;&gt;l'utilitarisme&lt;/a&gt; et l'égoïsme éthique, les ramenant à des principes rationnels comme l'universalité, la prudence et la bienveillance pour le plus grand bonheur. Il rejette l'empirisme et l'égoïsme psychologique de Bentham, défendant un intuitionnisme philosophique avec des critères de vérité basés sur la clarté, la cohérence et le consensus. Il introduit le paradoxe de l'hédonisme, où la poursuite directe du plaisir peut l'éloigner, et soutient un réalisme moral non naturaliste, où les vérités éthiques sont cognitives et non réductibles à des propriétés naturelles. &lt;/p&gt; &lt;p&gt; Il contribua à l'économie politique et à l'épistémologie, critiquant les inconsistances de la &lt;a href=&quot;https://www.youtube.com/watch?v=45WGS8b6Xd8&quot;  title=&quot;Henry Sidgwick | Ethics, Utilitarianism, and Beyond par Philosopher Friends&quot;&gt;morale commune&lt;/a&gt; pour les résoudre via l'utilitarisme. Athée agnostique après un éloignement du christianisme, il fonda en 1888 la &quot;Cambridge Ethical Society&quot;, une organisation humaniste précoce. Son travail sur la parapsychologie visait à examiner scientifiquement des phénomènes comme la télépathie, motivé par des implications éthiques sur l'au-delà. &lt;/p&gt; "/>
+    <hyperlink ref="E20" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Auberon_Edward_Herbert&quot;  title=&quot; Wikipedia&quot;&gt;Auberon Edward HERBERT&lt;/a&gt; était un aristocrate, politicien, écrivain et philosophe politique britannique. Il est surtout connu comme le créateur et le principal popularisateur  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Volontarisme_(courant_politique)&quot;  title=&quot;volontarisme politique   par Wikipedia&quot;&gt;du volontarisme, &lt;/a&gt; une doctrine politique fondée sur un gouvernement financé exclusivement par des cotisations volontaires. &lt;/p&gt; &lt;p&gt; Son principe fondamental était que l'usage de la force, même par une majorité parlementaire, contre des individus pacifiques est toujours immoral. De ce postulat, il considérait l'impôt obligatoire comme une forme de contrainte légalisée.  &lt;a href=&quot;https://www.youtube.com/watch?v=6gHkEBGmevc&quot;  title=&quot;auberon herbert unknown hero par the daily objective&quot;&gt;Sa conception &lt;/a&gt; prônait un État financé uniquement par des cotisations volontaires des citoyens. Il ne rejetait cependant pas totalement l'État. Il pensait que un appareil centralisé de justice (incluant tribunaux, police et armée) est nécessaire pour défendre les droits individuels contre l'agression extérieure et la criminalité. Il exigeait simplement que cet appareil ne force personne à financer ses actions. &lt;/p&gt; &lt;p&gt; Il  était un disciple ardent mais indépendant de la philosophie de Herbert Spencer. Il a développé une variante du  &lt;a href=&quot;https://www.libertarianism.org/publications/essays/auberon-herbert-voluntaryist&quot;  title=&quot;volontarisme par libertarianism&quot;&gt;spencérien individualisme &lt;/a&gt; qu'il décrivait comme « volontarisme ». Il fut actif dans des organisations comme la Personal Rights and Self-Help Association et la Liberty and Property Defense League. &lt;/p&gt; &lt;p&gt;  Bien que le volontarisme soit parfois associé à l'anarcho-capitalisme au XXᵉ siècle, il rejetait l'anarchie et défendait l'existence d'un État pouvant faire respecter la loi. Il a écrit pendant plus de 20 ans, produisant des pamphlets et des centaines de lettres dans des journaux.  &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H20" r:id="rId13" display="https://laphilo.fr/pho/aeherbert-mini.webp"/>
+    <hyperlink ref="H21" r:id="rId14" display="https://www.laphilo.fr/pho/tgmasaryk-mini.webp"/>
+    <hyperlink ref="H23" r:id="rId15" display="https://www.laphilo.fr/pho/salexander-mini.webp"/>
+    <hyperlink ref="E24" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis&quot;  title=&quot; Wikipedia&quot;&gt;Jacob OSSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H24" r:id="rId17" display="https://www.laphilo.fr/pho/jossis-mini.webp"/>
+    <hyperlink ref="I24" r:id="rId18" display="https://www.laphilo.fr/photo/jossis.webp"/>
+    <hyperlink ref="E26" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Alfred_North_Whitehead&quot;  title=&quot; Wikipedia&quot;&gt;Alfred North WHITEHEAD&lt;/a&gt; était un philosophe et mathématicien britannique, surtout connu pour avoir élaboré une &quot;philosophie du processus&quot;, où la réalité est pensée comme un flux d’événements plutôt que comme un ensemble de choses fixes.&lt;/p&gt; &lt;p&gt;  Il commence sa carrière comme mathématicien à Cambridge et coécrit avec Bertrand Russell les célèbres Principia Mathematica, œuvre majeure de logique et de fondements des mathématiques puis il se tourne vers la philosophie de la nature et la métaphysique, avant d’enseigner à Harvard où il écrit ses ouvrages philosophiques les plus importants.&lt;/p&gt; &lt;p&gt; Dans son livre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Proc%C3%A8s_et_r%C3%A9alit%C3%A9&quot; title=&quot;Procès et réalité par Wikipedia&quot;&gt; &quot;Process and Reality&quot;&lt;/a&gt; paru en 1929, souvent considéré comme son grand ouvrage systématique, fondateur de la &quot;philosophie du processus&quot;. Il soutient que la réalité est faite  &lt;a href=&quot;https://www.youtube.com/watch?v=oH23HsQ58zA&amp;list=PL29llNJMc6MFgVRFBs83lA83DGLvfuqGF&quot; title=&quot; &quot;Importance&quot; - 'Modes of Thought' by Alfred North Whitehead par Culture Footnotes2Plato&quot;&gt;d’événements&lt;/a&gt; ou de &quot;occasions actuelles&quot; plutôt que d’objets matériels immuables.​ Chaque entité est un processus de devenir, lié aux autres par un réseau de relations, et non un &quot;bloc&quot; isolé.​ Il parle de &quot;philosophie de l’organisme&quot; ou le réel est un tissu vivant de processus interdépendants, où les prétendues essences stables (comme la matière) ne sont que des abstractions. &lt;/p&gt; &lt;p&gt;   Il propose une conception originale de Dieu, souvent qualifiée de &quot;dipolaire&quot;.​ D’un côté, la &quot;nature primordiale&quot; de Dieu contient l’ensemble  &lt;a href=&quot;https://www.youtube.com/watch?v=lhAdwvZx5yA&quot; title=&quot; Why The Future Is Never Fixed | Alfred North Whitehead par Purduit Of Truth&quot;&gt;des possibles &lt;/a&gt;ou des valeurs potentielles ; de l’autre, la &quot; nature conséquente&quot; désigne la manière dont Dieu intègre et valorise effectivement ce qui se passe dans le monde.​ &lt;/p&gt;  &lt;audio controls title=&quot; Alfred North Whitehead (1861 - 1947) par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10199-22.08.2007-ITEMA_20082691-2007C3330E0021-ITE_00007383_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="H27" r:id="rId20" display="https://www.laphilo.fr/pho/gsantayana-mini.webp"/>
+    <hyperlink ref="E28" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Kazimierz_Twardowski&quot;  title=&quot; Wikipedia&quot;&gt;Kazimierz TWARDOWSKI&lt;/a&gt; était un philosophe polonais, fondateur de l'École philosophique de &lt;a href=&quot;https://www.youtube.com/watch?v=0jq5XLDyh3M&quot;  title=&quot;ivov-warsaw school par stay curious radio&quot;&gt;Lvov-Varsovie, &lt;/a&gt; l'un des mouvements philosophiques les plus importants et les plus originaux de l'Europe du XXe siècle. Élève de Franz Brentano à Vienne, il s'établit à Lvov en 1895 où il enseigna jusqu'à sa mort, formant une génération extraordinaire de philosophes, logiciens et mathématiciens polonais. Son influence sur la philosophie polonaise est comparable à celle de Brentano sur la philosophie autrichienne. &lt;/p&gt; &lt;p&gt; Sa contribution &lt;a href=&quot;https://www.youtube.com/watch?v=kGQU8Fw53BE&quot;  title=&quot;kazimierz twardowski par stay curious radio&quot;&gt;philosophique principale, &lt;/a&gt;  exposée dans &lt;em&gt;Zur Lehre vom Inhalt und Gegenstand der Vorstellungen&lt;/em&gt; (1894), est la distinction rigoureuse entre le contenu d'un acte mental (l'image mentale) et son objet (ce à quoi l'acte se réfère). Cette distinction, qui s'inscrit dans la tradition brentanienne de la psychologie descriptive, contribua à clarifier les fondements de la &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_2017_num_115_4_8628&quot;  title=&quot;twarddowski sur la vérité par persée&quot;&gt;théorie de la connaissance &lt;/a&gt; et prépara le terrain pour le développement de la phénoménologie et de la philosophie analytique. &lt;/p&gt; &lt;p&gt; Comme fondateur de l'École de Lvov-Varsovie, il forma des penseurs aussi importants que Jan Łukasiewicz (inventeur de la logique à trois valeurs et de la notation polonaise), Stanisław Leśniewski, Tadeusz Kotarbiński et Alfred Tarski. Cette école, caractérisée par sa rigueur logique, sa clarté analytique et son antipsychologisme, eut une influence considérable sur la logique et la philosophie du langage mondiales. Il incarne l'idéal du philosophe-professeur qui forme des disciples, invente des méthodes et fonde une tradition. &lt;/p&gt;"/>
+    <hyperlink ref="H28" r:id="rId22" display="https://www.laphilo.fr/pho/ktwardowski-mini.webp"/>
+    <hyperlink ref="E29" r:id="rId23" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Bertrand_Russell&quot;  title=&quot; Wikipedia&quot;&gt; Bertrand RUSSELL&lt;/a&gt;  était un philosophe, logicien, mathématicien, écrivain et militant britannique empiriste et rationaliste. Ses contributions majeures en mathématiques et en logique ont jeté les bases de la &lt;a href=&quot;https://www.youtube.com/watch?v=I1-6SA1DfRA&amp;ab_channel=HeureBleue&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;pourquoi la philosophie analytique est méconnue en France par Heure Bleue &quot;&gt;philosophie analytique&lt;/a&gt;, un courant dominant de la philosophie anglo-américaine en opposition avec la philosophie continentale romano-germanique. &lt;/p&gt; &lt;p&gt; Il était un philosophe très controversé par les positions qu'il prenait dans le domaine de la religion, de la sexualité et du travail. Son livre paru en 1929 &quot;Le Mariage et la Morale&quot; fera scandale à cette époque car il autorise la femme a pratiqué l'adultère. Concernant le travail, il fera  &lt;a href=&quot;https://www.youtube.com/watch?v=I7dQ5ZES3VI&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;Le travail et l'oisiveté par Alain Bajomée &quot;&gt;l'éloge de l'oisiveté&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;&#10;L'un des ses travaux les plus connus, &lt;a href=&quot;https://fr.wikipedia.org/wiki/Principia_Mathematica&quot;  title=&quot;Principa Mathematica par Wikipédia &quot;&gt;&quot;Principia Mathematica&quot;&lt;/a&gt;, écrit en collaboration avec Alfred North Whitehead. Publié entre 1910 et 1913, cet ouvrage visait à fonder les mathématiques sur une base logique rigoureuse. Bien que le projet n'ait pas atteint tous ses objectifs, il a eu une influence considérable sur le développement ultérieur des mathématiques et de la logique. &lt;/p&gt; &lt;p&gt;&#10;Sa théorie de la connaissance ou &quot;théorie des descriptions&quot; est une contribution majeure de la philosophie analytique. Elle a remis en cause la nature des propositions et la signification des termes définis par description.&lt;/p&gt; &lt;p&gt;&#10;Russell a reçu de nombreux honneurs au cours de sa vie, dont le prix Nobel de littérature en 1950, en reconnaissance de sa contribution exceptionnelle à la &lt;a href=&quot;https://www.youtube.com/watch?v=5IEYW5wuK3Y&amp;ab_channel=PhilosophyOverdose&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Interview on Philosophy par Philosophy Overdose &quot;&gt;pensée philosophique&lt;/a&gt; et à la littérature humaniste.  Il était un penseur engagé sur le plan politique et social ainsi qu'un défenseur passionné du pacifisme et s'est opposé à la participation britannique dans la Première Guerre mondiale. &lt;/p&gt;  &lt;audio controls title=&quot;Autobiographie de Bertrand Russell par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-17.01.2017-ITEMA_21199485-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H32" r:id="rId24" display="https://www.laphilo.fr/pho/cgjung-mini.webp"/>
+    <hyperlink ref="E34" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans_Hahn_(math%C3%A9maticien)&quot;  title=&quot; Wikipedia&quot;&gt;Hans HAHN&lt;/a&gt; était un mathématicien autrichien, surtout connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach. Il fut également l’un des principaux fondateurs du Cercle de Vienne, avec Moritz Schlick, Philipp Frank et Otto Neurath. Son intérêt pour la philosophie ne fut donc pas celui d’un philosophe professionnel, mais celui d’un mathématicien qui cherchait à comprendre le rapport entre logique, mathématiques, langage et connaissance scientifique. &lt;/p&gt; &lt;p&gt; Sa philosophie s’inscrit dans l’empirisme logique ou positivisme logique. Comme les &lt;a href=&quot;https://www.youtube.com/watch?v=VReApTp5_zg&quot; title=&quot; le cercle de vienne par philosophie analytique&quot;&gt;autres membres du Cercle de Vienne, &lt;/a&gt;  il rejetait la métaphysique traditionnelle lorsqu’elle prétendait produire une connaissance indépendante de toute expérience ou de toute méthode logique. Il contestait notamment l’idée kantienne de vérités « synthétiques a priori » : selon cette orientation, une proposition est soit logique ou mathématique, soit empirique et vérifiable à partir de l’expérience. La philosophie devait ainsi se rapprocher de l’analyse logique des énoncés scientifiques. &lt;/p&gt; &lt;p&gt; Il accordait toutefois aux mathématiques un statut particulier. Il ne pensait pas qu’elles décrivent directement des objets réels, comme le font les sciences expérimentales. Les mathématiques et la logique établissent plutôt des relations formelles entre des propositions ou des symboles. Elles indiquent ce qui découle nécessairement de certaines règles et de certains axiomes. En ce sens, les vérités mathématiques sont analytiques : elles ne tirent pas leur certitude de l’observation, mais de la structure logique du système dans lequel elles sont formulées. &lt;/p&gt; &lt;p&gt; Un aspect important de sa pensée est son refus de fonder les mathématiques sur une intuition particulière. Il se méfiait de l’« intuition » au sens kantien, c’est-à-dire de l’idée que l’esprit aurait un accès immédiat aux structures mathématiques. Il défendait plutôt l’axiomatisation et la rigueur formelle, notamment dans l’arithmétique et l’analyse. Mais il ne réduisait pas nécessairement toute signification à une vérification directe : il soutenait que les hypothèses scientifiques peuvent être significatives même lorsqu’elles ne sont pas définitivement vérifiables, ce qui conduit à assouplir le vérificationnisme strict. &lt;/p&gt; &lt;p&gt; Il concevait la logique non comme une science décrivant les propriétés les plus générales des objets, mais comme un instrument construit par les êtres humains pour parler du monde avec précision. La logique ne serait donc pas une réalité cachée dans les choses : elle apparaît lorsque nous organisons nos énoncés au moyen d’un symbolisme. Sa philosophie défend ainsi une conception scientifique, anti-métaphysique et formaliste de la connaissance, tout en laissant une place aux hypothèses et à la diversité des systèmes logiques. Son œuvre philosophique, moins abondante que son œuvre mathématique, a néanmoins contribué à préparer plusieurs thèmes du positivisme logique et de la philosophie analytique des sciences. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H34" r:id="rId26" display="https://www.laphilo.fr/pho/hhahn-mini.webp"/>
+    <hyperlink ref="E35" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Weininger&quot;  title=&quot; Wikipedia&quot;&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href=&quot;https://www.youtube.com/watch?v=wetIerJEucU&quot; title=&quot; Otto Weininger Le génie Maudit par Aliouca&quot;&gt;maison de Beethoven à Vienne &lt;/a&gt; . Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=aFZpRoBlMQI&quot; title=&quot; Otto Weininger qui haîssait les femmes par Voyage Endormis&quot;&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href=&quot;https://www.youtube.com/watch?v=vMfEJQVv3VM&quot; title=&quot; Otto Weininger Le mytère du féminin par Philosopheasy en Français&quot;&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits &quot;féminins&quot; vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère &quot;féminine&quot; décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title=&quot;Otto Weininger et la question du genie par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E36" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H36" r:id="rId29" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
+    <hyperlink ref="E37" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H37" r:id="rId31" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
+    <hyperlink ref="H38" r:id="rId32" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
+    <hyperlink ref="I38" r:id="rId33" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
+    <hyperlink ref="E39" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H40" r:id="rId35" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
+    <hyperlink ref="E41" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H41" r:id="rId37" display="https://www.laphilo.fr/pho/pfrank-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E44" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
+    <hyperlink ref="E48" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H49" r:id="rId41" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
+    <hyperlink ref="H51" r:id="rId42" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
+    <hyperlink ref="E52" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H52" r:id="rId44" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
+    <hyperlink ref="I52" r:id="rId45" display="https://laphilo.fr/photo/lszabo.webp"/>
+    <hyperlink ref="E53" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
+    <hyperlink ref="E54" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H55" r:id="rId48" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
+    <hyperlink ref="I55" r:id="rId49" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
+    <hyperlink ref="H56" r:id="rId50" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
+    <hyperlink ref="E57" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
+    <hyperlink ref="H57" r:id="rId52" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
+    <hyperlink ref="E58" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E59" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E60" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
+    <hyperlink ref="E61" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
+    <hyperlink ref="H61" r:id="rId57" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
+    <hyperlink ref="E62" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer&quot; title=&quot; Wikipedia&quot;&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href=&quot;https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html&quot;  title=&quot;philosophie analytique par la philosophie&quot;&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href=&quot;https://www.youtube.com/watch?v=HG5kIR6iF8g&quot;  title=&quot;A,J, Ayer’s Emotivism par philosophy Vibe&quot;&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H62" r:id="rId59" display="https://www.laphilo.fr/pho/ajayer-mini.webp"/>
+    <hyperlink ref="H63" r:id="rId60" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
+    <hyperlink ref="H65" r:id="rId61" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
+    <hyperlink ref="H67" r:id="rId62" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
+    <hyperlink ref="E69" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E71" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
+    <hyperlink ref="E72" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H72" r:id="rId66" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
+    <hyperlink ref="I72" r:id="rId67" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="E73" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H73" r:id="rId69" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
+    <hyperlink ref="I73" r:id="rId70" display="https://laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="H76" r:id="rId71" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
+    <hyperlink ref="E78" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
+    <hyperlink ref="E80" r:id="rId73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H81" r:id="rId74" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
+    <hyperlink ref="E83" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H83" r:id="rId76" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
+    <hyperlink ref="H84" r:id="rId77" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
+    <hyperlink ref="E85" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H85" r:id="rId79" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="716">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -457,6 +457,9 @@
   </si>
   <si>
     <t xml:space="preserve">Spiritualisme ; Libéralisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe suisse protestant, généralement rangé dans une forme de spiritualisme chrétien.</t>
   </si>
   <si>
     <t xml:space="preserve">1903</t>
@@ -1167,9 +1170,6 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/febner-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">poli</t>
-  </si>
-  <si>
     <t xml:space="preserve">langage</t>
   </si>
   <si>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/anders-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">philosophe allemand ponnier du mouvement antinucléaire et critique de la technique moderne.</t>
+    <t xml:space="preserve">philosophe autrichien pionnier du mouvement antinucléaire et critique de la technique moderne.</t>
   </si>
   <si>
     <t xml:space="preserve">1904 – 1993</t>
@@ -2524,6 +2524,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2547,13 +2554,6 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2707,11 +2707,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2719,15 +2719,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3541,44 +3541,47 @@
       <c r="L15" s="2" t="s">
         <v>132</v>
       </c>
+      <c r="M15" s="13" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
         <v>1818</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3586,38 +3589,38 @@
         <v>1820</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="381.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3628,35 +3631,35 @@
         <v>1895</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M18" s="13" t="s">
         <v>158</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3664,38 +3667,38 @@
         <v>1838</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3706,22 +3709,22 @@
         <v>1906</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
@@ -3731,10 +3734,10 @@
         <v>53</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M20" s="14" t="s">
         <v>176</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3745,34 +3748,34 @@
         <v>1937</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" s="15" t="s">
         <v>179</v>
       </c>
+      <c r="E21" s="16" t="s">
+        <v>180</v>
+      </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="M21" s="14" t="s">
         <v>185</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3780,25 +3783,25 @@
         <v>1853</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E22" s="16" t="s">
         <v>189</v>
       </c>
+      <c r="E22" s="17" t="s">
+        <v>190</v>
+      </c>
       <c r="F22" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="2" t="s">
@@ -3808,10 +3811,10 @@
         <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3822,22 +3825,22 @@
         <v>1938</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E23" s="17" t="s">
         <v>197</v>
       </c>
+      <c r="E23" s="18" t="s">
+        <v>198</v>
+      </c>
       <c r="F23" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
@@ -3847,10 +3850,10 @@
         <v>121</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M23" s="14" t="s">
         <v>202</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3861,33 +3864,33 @@
         <v>1919</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="9"/>
       <c r="H24" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="M24" s="14" t="s">
         <v>211</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="368.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3895,38 +3898,38 @@
         <v>1861</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3934,25 +3937,25 @@
         <v>1861</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
@@ -3962,10 +3965,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="322.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3976,35 +3979,35 @@
         <v>1952</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E27" s="15" t="s">
         <v>232</v>
       </c>
+      <c r="E27" s="16" t="s">
+        <v>233</v>
+      </c>
       <c r="F27" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
         <v>109</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="M27" s="13" t="s">
         <v>238</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4015,25 +4018,25 @@
         <v>1938</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E28" s="18" t="s">
         <v>241</v>
       </c>
+      <c r="E28" s="19" t="s">
+        <v>242</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>72</v>
@@ -4042,7 +4045,7 @@
         <v>73</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4050,25 +4053,25 @@
         <v>1872</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="2" t="s">
@@ -4078,10 +4081,10 @@
         <v>72</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4089,38 +4092,38 @@
         <v>1873</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4128,38 +4131,38 @@
         <v>1875</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
         <v>82</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4170,22 +4173,22 @@
         <v>1961</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
@@ -4195,10 +4198,10 @@
         <v>63</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4206,25 +4209,25 @@
         <v>1878</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
@@ -4237,7 +4240,7 @@
         <v>122</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4248,35 +4251,35 @@
         <v>1934</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="M34" s="19" t="s">
         <v>300</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4284,25 +4287,25 @@
         <v>1880</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
@@ -4315,7 +4318,7 @@
         <v>84</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4326,26 +4329,26 @@
         <v>1931</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>314</v>
+        <v>22</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>315</v>
@@ -4353,7 +4356,7 @@
       <c r="L36" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M36" s="13" t="s">
+      <c r="M36" s="14" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4387,12 +4390,12 @@
         <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="M37" s="14" t="s">
+      <c r="M37" s="15" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4429,7 +4432,7 @@
       <c r="L38" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="M38" s="14" t="s">
+      <c r="M38" s="15" t="s">
         <v>333</v>
       </c>
     </row>
@@ -4468,7 +4471,7 @@
       <c r="L39" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="M39" s="13" t="s">
+      <c r="M39" s="14" t="s">
         <v>342</v>
       </c>
     </row>
@@ -4485,7 +4488,7 @@
       <c r="D40" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="17" t="s">
         <v>345</v>
       </c>
       <c r="F40" s="7" t="s">
@@ -4541,12 +4544,12 @@
         <v>22</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="M41" s="14" t="s">
+      <c r="M41" s="15" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4563,7 +4566,7 @@
       <c r="D42" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="19" t="s">
         <v>361</v>
       </c>
       <c r="F42" s="7" t="s">
@@ -4655,10 +4658,10 @@
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>73</v>
@@ -4680,7 +4683,7 @@
       <c r="D45" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="E45" s="17" t="s">
         <v>389</v>
       </c>
       <c r="F45" s="7" t="s">
@@ -4719,7 +4722,7 @@
       <c r="D46" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="19" t="s">
         <v>396</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -4835,7 +4838,7 @@
       <c r="D49" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="17" t="s">
         <v>423</v>
       </c>
       <c r="F49" s="7" t="s">
@@ -4852,7 +4855,7 @@
         <v>22</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>427</v>
@@ -4874,26 +4877,26 @@
       <c r="D50" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>431</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="G50" s="13" t="s">
         <v>433</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>434</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>435</v>
@@ -4912,11 +4915,11 @@
       <c r="D51" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>438</v>
       </c>
       <c r="F51" s="20"/>
-      <c r="G51" s="19"/>
+      <c r="G51" s="13"/>
       <c r="H51" s="2" t="s">
         <v>439</v>
       </c>
@@ -4966,7 +4969,7 @@
         <v>22</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>448</v>
@@ -5042,7 +5045,7 @@
         <v>463</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>464</v>
@@ -5083,7 +5086,7 @@
         <v>130</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>473</v>
@@ -5200,7 +5203,7 @@
         <v>130</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>473</v>
@@ -5278,7 +5281,7 @@
         <v>82</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>513</v>
@@ -5361,7 +5364,7 @@
       <c r="L62" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M62" s="13" t="s">
+      <c r="M62" s="14" t="s">
         <v>530</v>
       </c>
     </row>
@@ -5378,7 +5381,7 @@
       <c r="D63" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="E63" s="17" t="s">
         <v>534</v>
       </c>
       <c r="F63" s="7" t="s">
@@ -5456,7 +5459,7 @@
       <c r="D65" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="17" t="s">
         <v>551</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -5495,7 +5498,7 @@
       <c r="D66" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E66" s="17" t="s">
         <v>559</v>
       </c>
       <c r="F66" s="7" t="s">
@@ -5512,7 +5515,7 @@
         <v>563</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>73</v>
@@ -5550,7 +5553,7 @@
         <v>33</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>571</v>
@@ -5628,7 +5631,7 @@
         <v>33</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>73</v>
@@ -5667,7 +5670,7 @@
         <v>33</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>73</v>
@@ -5706,7 +5709,7 @@
         <v>33</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>73</v>
@@ -5748,7 +5751,7 @@
       <c r="L72" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="M72" s="13" t="s">
+      <c r="M72" s="14" t="s">
         <v>613</v>
       </c>
     </row>
@@ -5806,7 +5809,7 @@
       <c r="D74" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E74" s="17" t="s">
         <v>625</v>
       </c>
       <c r="F74" s="7" t="s">
@@ -5820,7 +5823,7 @@
       </c>
       <c r="I74" s="9"/>
       <c r="J74" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>44</v>
@@ -5828,7 +5831,7 @@
       <c r="L74" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="M74" s="13" t="s">
+      <c r="M74" s="14" t="s">
         <v>630</v>
       </c>
     </row>
@@ -5939,7 +5942,7 @@
         <v>33</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>73</v>
@@ -6017,7 +6020,7 @@
         <v>33</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>73</v>
@@ -6058,7 +6061,7 @@
       <c r="L80" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="M80" s="13" t="s">
+      <c r="M80" s="14" t="s">
         <v>678</v>
       </c>
     </row>
@@ -6075,7 +6078,7 @@
       <c r="D81" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="E81" s="16" t="s">
+      <c r="E81" s="17" t="s">
         <v>681</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -6092,7 +6095,7 @@
         <v>109</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>464</v>
@@ -6136,7 +6139,7 @@
       <c r="L82" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="M82" s="13" t="s">
+      <c r="M82" s="14" t="s">
         <v>692</v>
       </c>
     </row>
@@ -6231,7 +6234,7 @@
       <c r="D85" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="E85" s="14" t="s">
         <v>711</v>
       </c>
       <c r="F85" s="1" t="s">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="725">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES MODERNES (AUTRES) — Données source</t>
   </si>
@@ -1151,6 +1151,59 @@
     <t xml:space="preserve">philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans "Sexe et caractère".</t>
   </si>
   <si>
+    <t xml:space="preserve">1881 – 1966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luitzen Egbertus Jan BROUWER</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Luitzen_Egbertus_Jan_Brouwer"  title=" Wikipedia"&gt;Luitzen Egbertus Jan BROUWER/a&gt; était un mathématicien et philosophe néerlandais, surtout connu comme le fondateur de l’intuitionnisme mathématique. Il a également joué un rôle majeur dans la naissance de la topologie moderne, mais son ambition philosophique était plus vaste : il voulait repenser les fondements des mathématiques à partir de l’activité de l’esprit, plutôt que de les faire reposer uniquement sur la logique formelle ou sur l’existence d’un monde abstrait d’objets mathématiques. &lt;/p&gt; &lt;p&gt; Pour lui,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">:   &lt;a href="http://serge.mehl.free.fr/chrono/Brouwer.html" title="Brouwer par mehl"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> les mathématiques &lt;/a&gt; ne décrivent pas un univers objectif indépendant de l’homme ; elles sont d’abord une construction mentale. Le mathématicien produit les nombres, les figures et les relations par une activité intérieure fondée sur l’intuition du temps. Il subit ici l’influence de Kant et de Schopenhauer : le temps constitue une forme fondamentale de l’expérience, tandis que le langage et les systèmes logiques ne sont que des moyens secondaires pour communiquer des constructions déjà réalisées par la pensée. &lt;/p&gt; &lt;p&gt; Cette conception le conduit à défendre une mathématique constructive. Une proposition mathématique ne doit être considérée comme vraie que si l’on possède une méthode permettant effectivement de la construire ou d’en démontrer la validité. Il critique donc certains raisonnements classiques, notamment le principe du tiers exclu — selon lequel toute proposition est vraie ou fausse — lorsqu’ils affirment l’existence d’un objet sans fournir de construction concrète. Ainsi, démontrer qu’un objet ne peut pas ne pas exister ne suffit pas toujours : il faut encore savoir comment le construire. &lt;/p&gt; &lt;p&gt; Sa philosophie générale est ainsi proche d’un idéalisme radical, voire d’un certain solipsisme : la vérité mathématique dépend de l’activité du sujet qui construit et comprend. Sa pensée dépasse cependant la seule technique mathématique, car il se méfiait également du langage, de la logique et de la vie sociale lorsqu’ils prétendent remplacer l’expérience intérieure. Ses réflexions sur la vie, l’art et le mysticisme, notamment dans Leven, Kunst en Mystiek publié en 1905, montrent qu’il concevait la pensée comme une recherche de simplicité et d’authenticité, opposée aux illusions produites par les conventions collectives. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">OSAeoMe7T70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L E J Brouwer par See Hear Say Learn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/lejbrouwer-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Néerlandaise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solipsisme ; Intuitionnisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mathématicien et philosophe néerlandais  connu comme le fondateur de l’intuitionnisme mathématique26/09/26</t>
+  </si>
+  <si>
     <t xml:space="preserve">1882 – 1931</t>
   </si>
   <si>
@@ -2429,7 +2482,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2557,6 +2610,31 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Times New Roman"/>
@@ -2646,7 +2724,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2727,15 +2805,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2997,7 +3087,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="94.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="24.62"/>
@@ -4321,12 +4411,12 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="314.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>1931</v>
+        <v>1966</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>309</v>
@@ -4334,7 +4424,7 @@
       <c r="D36" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="20" t="s">
         <v>311</v>
       </c>
       <c r="F36" s="7" t="s">
@@ -4343,29 +4433,29 @@
       <c r="G36" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="21" t="s">
         <v>314</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>22</v>
+        <v>315</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="M36" s="14" t="s">
+      <c r="M36" s="22" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>1882</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>1945</v>
+        <v>1931</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>318</v>
@@ -4373,7 +4463,7 @@
       <c r="D37" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>320</v>
       </c>
       <c r="F37" s="7" t="s">
@@ -4390,13 +4480,13 @@
         <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>141</v>
+        <v>324</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="M37" s="15" t="s">
         <v>325</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4404,44 +4494,46 @@
         <v>1882</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="9"/>
+        <v>329</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>331</v>
+      </c>
       <c r="H38" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>330</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>331</v>
+        <v>141</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" s="15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="361.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>334</v>
+        <v>1882</v>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1937</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>335</v>
@@ -4449,189 +4541,187 @@
       <c r="D39" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="7"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="I39" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="J39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="M39" s="14" t="s">
+      <c r="M39" s="15" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
         <v>1883</v>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>1946</v>
+      <c r="B40" s="7" t="s">
+        <v>343</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E40" s="17" t="s">
         <v>345</v>
       </c>
+      <c r="E40" s="11" t="s">
+        <v>346</v>
+      </c>
       <c r="F40" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="H40" s="10" t="s">
         <v>348</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>349</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M40" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M40" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>1966</v>
+        <v>1946</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E41" s="12" t="s">
         <v>353</v>
       </c>
+      <c r="E41" s="17" t="s">
+        <v>354</v>
+      </c>
       <c r="F41" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>299</v>
+        <v>53</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="M41" s="15" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>358</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>1885</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>358</v>
+        <v>1884</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>1966</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="E42" s="19" t="s">
         <v>361</v>
       </c>
+      <c r="E42" s="12" t="s">
+        <v>362</v>
+      </c>
       <c r="F42" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="H42" s="9" t="s">
         <v>364</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>365</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
-        <v>365</v>
+        <v>22</v>
       </c>
       <c r="K42" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M42" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="L42" s="2" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="C43" s="7" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B43" s="7" t="s">
+      <c r="D43" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="E43" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="G43" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="H43" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>375</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
-        <v>22</v>
+        <v>374</v>
       </c>
       <c r="K43" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
         <v>1889</v>
       </c>
@@ -4644,7 +4734,7 @@
       <c r="D44" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="9" t="s">
         <v>381</v>
       </c>
       <c r="F44" s="7" t="s">
@@ -4658,140 +4748,140 @@
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>299</v>
+        <v>385</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>73</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="E45" s="17" t="s">
         <v>389</v>
       </c>
+      <c r="E45" s="10" t="s">
+        <v>390</v>
+      </c>
       <c r="F45" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="I46" s="9"/>
+      <c r="J46" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="L46" s="2" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+    <row r="47" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
         <v>1898</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="M47" s="2" t="s">
+      <c r="B48" s="7" t="s">
         <v>412</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>1992</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>413</v>
@@ -4799,7 +4889,7 @@
       <c r="D48" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="10" t="s">
         <v>415</v>
       </c>
       <c r="F48" s="7" t="s">
@@ -4808,258 +4898,260 @@
       <c r="G48" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="9" t="s">
         <v>418</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>53</v>
+        <v>419</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>54</v>
+        <v>420</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>1899</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>420</v>
+      <c r="B49" s="7" t="n">
+        <v>1992</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E49" s="17" t="s">
         <v>423</v>
       </c>
+      <c r="E49" s="11" t="s">
+        <v>424</v>
+      </c>
       <c r="F49" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>427</v>
+        <v>54</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+    <row r="50" customFormat="false" ht="211.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="I50" s="9"/>
+      <c r="J50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
         <v>1901</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B51" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="C51" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="J51" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L51" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="M51" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
         <v>1902</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B52" s="1" t="n">
         <v>1967</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="L51" s="2" t="s">
+      <c r="C52" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="F52" s="23"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="G52" s="9"/>
-      <c r="H52" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="M52" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
         <v>1902</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="E53" s="10" t="s">
         <v>453</v>
       </c>
+      <c r="E53" s="11" t="s">
+        <v>454</v>
+      </c>
       <c r="F53" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="G53" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="G53" s="9"/>
+      <c r="H53" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="I53" s="9"/>
+      <c r="I53" s="10" t="s">
+        <v>449</v>
+      </c>
       <c r="J53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L53" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M53" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
+      <c r="M54" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
         <v>1904</v>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B55" s="7" t="n">
         <v>1993</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>467</v>
@@ -5067,23 +5159,19 @@
       <c r="D55" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="7"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="I55" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="J55" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>210</v>
@@ -5095,363 +5183,365 @@
         <v>474</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
         <v>1907</v>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>1992</v>
+      <c r="B56" s="7" t="s">
+        <v>475</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="E56" s="21" t="s">
         <v>477</v>
       </c>
+      <c r="E56" s="9" t="s">
+        <v>478</v>
+      </c>
       <c r="F56" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I56" s="9"/>
+        <v>481</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>471</v>
+      </c>
       <c r="J56" s="2" t="s">
-        <v>365</v>
+        <v>130</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>315</v>
+        <v>210</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="M56" s="22" t="s">
         <v>482</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
         <v>1907</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>442</v>
+      <c r="B57" s="7" t="n">
+        <v>1992</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="E57" s="12" t="s">
         <v>485</v>
       </c>
+      <c r="E57" s="24" t="s">
+        <v>486</v>
+      </c>
       <c r="F57" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="2" t="s">
-        <v>33</v>
+        <v>374</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>490</v>
+      </c>
+      <c r="M57" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="E58" s="11" t="s">
         <v>493</v>
       </c>
+      <c r="E58" s="12" t="s">
+        <v>494</v>
+      </c>
       <c r="F58" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="H58" s="9" t="s">
         <v>496</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>497</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>210</v>
+        <v>63</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>473</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="E59" s="10" t="s">
         <v>501</v>
       </c>
+      <c r="E59" s="11" t="s">
+        <v>502</v>
+      </c>
       <c r="F59" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
         <v>1909</v>
       </c>
-      <c r="B60" s="7" t="n">
-        <v>2004</v>
+      <c r="B60" s="7" t="s">
+        <v>507</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="E60" s="12" t="s">
         <v>509</v>
       </c>
+      <c r="E60" s="10" t="s">
+        <v>510</v>
+      </c>
       <c r="F60" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="H60" s="10" t="s">
         <v>512</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>513</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
         <v>1909</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>1996</v>
+        <v>2004</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="E61" s="11" t="s">
         <v>517</v>
       </c>
+      <c r="E61" s="12" t="s">
+        <v>518</v>
+      </c>
       <c r="F61" s="7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>122</v>
+        <v>522</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="351.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="173.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>528</v>
+        <v>34</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="M62" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="306.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="351.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B63" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>1989</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="D63" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="E63" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="F63" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="G63" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="10" t="s">
         <v>536</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>537</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K63" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M63" s="2" t="s">
+      <c r="M63" s="14" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="255.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="306.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
         <v>1911</v>
       </c>
-      <c r="B64" s="7" t="n">
-        <v>1995</v>
+      <c r="B64" s="7" t="s">
+        <v>540</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="E64" s="11" t="s">
         <v>542</v>
       </c>
+      <c r="E64" s="17" t="s">
+        <v>543</v>
+      </c>
       <c r="F64" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
-        <v>400</v>
+        <v>33</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>121</v>
+        <v>547</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>546</v>
+        <v>73</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="255.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>548</v>
+        <v>1911</v>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1995</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>549</v>
@@ -5459,7 +5549,7 @@
       <c r="D65" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="11" t="s">
         <v>551</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -5473,49 +5563,49 @@
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="2" t="s">
-        <v>33</v>
+        <v>409</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>538</v>
+        <v>121</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>73</v>
+        <v>555</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="H66" s="9" t="s">
         <v>562</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>563</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
-        <v>563</v>
+        <v>33</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>141</v>
+        <v>547</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>73</v>
@@ -5524,146 +5614,146 @@
         <v>564</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
+    <row r="67" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="I67" s="9"/>
+      <c r="J67" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
         <v>1919</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B68" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="J67" s="2" t="s">
+      <c r="C68" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="J68" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="K68" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="M68" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="69" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
         <v>1922</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D69" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="E69" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="F69" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="G69" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="H69" s="9" t="s">
         <v>587</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>589</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
-        <v>33</v>
+        <v>588</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>141</v>
+        <v>589</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>73</v>
+        <v>590</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="E70" s="10" t="s">
         <v>594</v>
       </c>
+      <c r="E70" s="11" t="s">
+        <v>595</v>
+      </c>
       <c r="F70" s="7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="2" t="s">
@@ -5676,132 +5766,130 @@
         <v>73</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B71" s="7" t="n">
-        <v>2019</v>
+        <v>1923</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>600</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>603</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>604</v>
+        <v>605</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>606</v>
       </c>
       <c r="I71" s="9"/>
       <c r="J71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>264</v>
+        <v>141</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>73</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
         <v>1924</v>
       </c>
       <c r="B72" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="I72" s="9"/>
+      <c r="J72" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B73" s="7" t="n">
         <v>2003</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="F72" s="7"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="M72" s="14" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>591</v>
-      </c>
       <c r="C73" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>616</v>
-      </c>
-      <c r="F73" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="F73" s="7"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="I73" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="I73" s="10" t="s">
+      <c r="J73" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K73" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="L73" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M73" s="2" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M73" s="14" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
         <v>1925</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>623</v>
@@ -5809,7 +5897,7 @@
       <c r="D74" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="11" t="s">
         <v>625</v>
       </c>
       <c r="F74" s="7" t="s">
@@ -5818,26 +5906,28 @@
       <c r="G74" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="H74" s="9" t="s">
+      <c r="H74" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="I74" s="9"/>
+      <c r="I74" s="10" t="s">
+        <v>629</v>
+      </c>
       <c r="J74" s="2" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="M74" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>631</v>
@@ -5848,7 +5938,7 @@
       <c r="D75" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="17" t="s">
         <v>634</v>
       </c>
       <c r="F75" s="7" t="s">
@@ -5862,7 +5952,7 @@
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="2" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>44</v>
@@ -5870,118 +5960,118 @@
       <c r="L75" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="M75" s="14" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
+    <row r="76" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="358.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B77" s="1" t="n">
         <v>2002</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="G77" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="H77" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="I77" s="9"/>
       <c r="J77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>73</v>
+        <v>654</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
         <v>1929</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>662</v>
+        <v>167</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>73</v>
@@ -5990,9 +6080,9 @@
         <v>663</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>664</v>
@@ -6003,7 +6093,7 @@
       <c r="D79" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12" t="s">
         <v>667</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -6020,91 +6110,91 @@
         <v>33</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>141</v>
+        <v>671</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M79" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B80" s="7" t="n">
-        <v>2018</v>
+        <v>1930</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>673</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>676</v>
+        <v>678</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>679</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
-        <v>400</v>
+        <v>33</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="M80" s="14" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="E81" s="17" t="s">
         <v>681</v>
       </c>
+      <c r="E81" s="11" t="s">
+        <v>682</v>
+      </c>
       <c r="F81" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>686</v>
+      </c>
+      <c r="M81" s="14" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
         <v>1934</v>
       </c>
@@ -6112,164 +6202,193 @@
         <v>2026</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>687</v>
+        <v>689</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>690</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
-        <v>463</v>
+        <v>109</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="M82" s="14" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>473</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="E83" s="12" t="s">
         <v>695</v>
       </c>
+      <c r="E83" s="11" t="s">
+        <v>696</v>
+      </c>
       <c r="F83" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="M83" s="14" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="217.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L83" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="I84" s="10"/>
-      <c r="J84" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
+    <row r="85" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="I85" s="10"/>
+      <c r="J85" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
         <v>1954</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B86" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>711</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K85" s="2" t="s">
+      <c r="C86" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>720</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L86" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -6279,7 +6398,16 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
     </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+    </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6317,58 +6445,59 @@
     <hyperlink ref="E34" r:id="rId25" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Hans_Hahn_(math%C3%A9maticien)&quot;  title=&quot; Wikipedia&quot;&gt;Hans HAHN&lt;/a&gt; était un mathématicien autrichien, surtout connu pour ses travaux en analyse fonctionnelle et pour le théorème de Hahn-Banach. Il fut également l’un des principaux fondateurs du Cercle de Vienne, avec Moritz Schlick, Philipp Frank et Otto Neurath. Son intérêt pour la philosophie ne fut donc pas celui d’un philosophe professionnel, mais celui d’un mathématicien qui cherchait à comprendre le rapport entre logique, mathématiques, langage et connaissance scientifique. &lt;/p&gt; &lt;p&gt; Sa philosophie s’inscrit dans l’empirisme logique ou positivisme logique. Comme les &lt;a href=&quot;https://www.youtube.com/watch?v=VReApTp5_zg&quot; title=&quot; le cercle de vienne par philosophie analytique&quot;&gt;autres membres du Cercle de Vienne, &lt;/a&gt;  il rejetait la métaphysique traditionnelle lorsqu’elle prétendait produire une connaissance indépendante de toute expérience ou de toute méthode logique. Il contestait notamment l’idée kantienne de vérités « synthétiques a priori » : selon cette orientation, une proposition est soit logique ou mathématique, soit empirique et vérifiable à partir de l’expérience. La philosophie devait ainsi se rapprocher de l’analyse logique des énoncés scientifiques. &lt;/p&gt; &lt;p&gt; Il accordait toutefois aux mathématiques un statut particulier. Il ne pensait pas qu’elles décrivent directement des objets réels, comme le font les sciences expérimentales. Les mathématiques et la logique établissent plutôt des relations formelles entre des propositions ou des symboles. Elles indiquent ce qui découle nécessairement de certaines règles et de certains axiomes. En ce sens, les vérités mathématiques sont analytiques : elles ne tirent pas leur certitude de l’observation, mais de la structure logique du système dans lequel elles sont formulées. &lt;/p&gt; &lt;p&gt; Un aspect important de sa pensée est son refus de fonder les mathématiques sur une intuition particulière. Il se méfiait de l’« intuition » au sens kantien, c’est-à-dire de l’idée que l’esprit aurait un accès immédiat aux structures mathématiques. Il défendait plutôt l’axiomatisation et la rigueur formelle, notamment dans l’arithmétique et l’analyse. Mais il ne réduisait pas nécessairement toute signification à une vérification directe : il soutenait que les hypothèses scientifiques peuvent être significatives même lorsqu’elles ne sont pas définitivement vérifiables, ce qui conduit à assouplir le vérificationnisme strict. &lt;/p&gt; &lt;p&gt; Il concevait la logique non comme une science décrivant les propriétés les plus générales des objets, mais comme un instrument construit par les êtres humains pour parler du monde avec précision. La logique ne serait donc pas une réalité cachée dans les choses : elle apparaît lorsque nous organisons nos énoncés au moyen d’un symbolisme. Sa philosophie défend ainsi une conception scientifique, anti-métaphysique et formaliste de la connaissance, tout en laissant une place aux hypothèses et à la diversité des systèmes logiques. Son œuvre philosophique, moins abondante que son œuvre mathématique, a néanmoins contribué à préparer plusieurs thèmes du positivisme logique et de la philosophie analytique des sciences. &lt;/p&gt; &#10;&#10;&#10;"/>
     <hyperlink ref="H34" r:id="rId26" display="https://www.laphilo.fr/pho/hhahn-mini.webp"/>
     <hyperlink ref="E35" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Weininger&quot;  title=&quot; Wikipedia&quot;&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href=&quot;https://www.youtube.com/watch?v=wetIerJEucU&quot; title=&quot; Otto Weininger Le génie Maudit par Aliouca&quot;&gt;maison de Beethoven à Vienne &lt;/a&gt; . Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href=&quot;https://www.youtube.com/watch?v=aFZpRoBlMQI&quot; title=&quot; Otto Weininger qui haîssait les femmes par Voyage Endormis&quot;&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href=&quot;https://www.youtube.com/watch?v=vMfEJQVv3VM&quot; title=&quot; Otto Weininger Le mytère du féminin par Philosopheasy en Français&quot;&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits &quot;féminins&quot; vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère &quot;féminine&quot; décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title=&quot;Otto Weininger et la question du genie par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E36" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H36" r:id="rId29" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
-    <hyperlink ref="E37" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H37" r:id="rId31" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
-    <hyperlink ref="H38" r:id="rId32" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
-    <hyperlink ref="I38" r:id="rId33" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
-    <hyperlink ref="E39" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="H40" r:id="rId35" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
-    <hyperlink ref="E41" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H41" r:id="rId37" display="https://www.laphilo.fr/pho/pfrank-mini.webp"/>
-    <hyperlink ref="E42" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E44" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
-    <hyperlink ref="E48" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H49" r:id="rId41" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
-    <hyperlink ref="H51" r:id="rId42" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
-    <hyperlink ref="E52" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H52" r:id="rId44" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
-    <hyperlink ref="I52" r:id="rId45" display="https://laphilo.fr/photo/lszabo.webp"/>
-    <hyperlink ref="E53" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
-    <hyperlink ref="E54" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H55" r:id="rId48" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
-    <hyperlink ref="I55" r:id="rId49" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
-    <hyperlink ref="H56" r:id="rId50" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
-    <hyperlink ref="E57" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
-    <hyperlink ref="H57" r:id="rId52" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
-    <hyperlink ref="E58" r:id="rId53" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E59" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E60" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
-    <hyperlink ref="E61" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
-    <hyperlink ref="H61" r:id="rId57" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
-    <hyperlink ref="E62" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer&quot; title=&quot; Wikipedia&quot;&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href=&quot;https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html&quot;  title=&quot;philosophie analytique par la philosophie&quot;&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href=&quot;https://www.youtube.com/watch?v=HG5kIR6iF8g&quot;  title=&quot;A,J, Ayer’s Emotivism par philosophy Vibe&quot;&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H62" r:id="rId59" display="https://www.laphilo.fr/pho/ajayer-mini.webp"/>
-    <hyperlink ref="H63" r:id="rId60" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
-    <hyperlink ref="H65" r:id="rId61" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
-    <hyperlink ref="H67" r:id="rId62" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
-    <hyperlink ref="E69" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E71" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
-    <hyperlink ref="E72" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H72" r:id="rId66" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
-    <hyperlink ref="I72" r:id="rId67" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="E73" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H73" r:id="rId69" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
-    <hyperlink ref="I73" r:id="rId70" display="https://laphilo.fr/photo/akotanyi.webp"/>
-    <hyperlink ref="H76" r:id="rId71" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
-    <hyperlink ref="E78" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
-    <hyperlink ref="E80" r:id="rId73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
-    <hyperlink ref="H81" r:id="rId74" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
-    <hyperlink ref="E83" r:id="rId75" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="H83" r:id="rId76" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
-    <hyperlink ref="H84" r:id="rId77" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
-    <hyperlink ref="E85" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="H85" r:id="rId79" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
+    <hyperlink ref="H36" r:id="rId28" display="https://www.laphilo.fr/pho/lejbrouwer-mini.webp"/>
+    <hyperlink ref="E37" r:id="rId29" display="&lt;p&gt;&lt;a href=&quot;https://en.wikipedia.org/wiki/Ferdinand_Ebner&quot;  title=&quot; Wikipedia&quot;&gt;Ferdinand EBNER&lt;/a&gt; était un philosophe autrichien, également instituteur, qui a vécu relativement à l’écart du monde universitaire. Avec Martin Buber et Franz Rosenzweig, il est considéré comme l’un des fondateurs de la philosophie dialogique, courant qui place la relation entre les personnes au centre de la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Sa thèse fondamentale est que l’être humain n’existe véritablement que dans la relation entre un « je » et un « tu ». Le « je » isolé, enfermé dans sa propre conscience, ne suffit pas à définir la personne : celle-ci devient pleinement elle-même lorsqu’elle rencontre un autre sujet et entre avec lui dans une relation vivante. Il oppose ainsi la relation personnelle à l’enfermement dans le   &lt;a href=&quot;https://fr.wikipedia.org/wiki/Solipsisme&quot;  title=&quot;solipsisme par wikipedia&quot;&gt;solipsisme.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Chez lui, le langage n’est pas seulement un moyen de communiquer des informations. La parole est ce qui rend possible la rencontre entre les personnes et constitue l’espace spirituel du dialogue. Le mot véritable ne transmet donc pas uniquement un contenu intellectuel : il établit une relation, engage celui qui parle et peut devenir une expression de l’amour. &lt;/p&gt; &lt;p&gt; Il a exercé une influence importante sur les penseurs dialogiques ultérieurs, notamment sur Lajos Szabó et Béla Tábor qui prolongent son intuition selon laquelle la personne, le langage et la vérité ne peuvent être compris indépendamment du dialogue ; cependant, ils la développent dans des directions différentes, plus liées à la théorie des signes, à la critique sociale et à la question juive.  &lt;a href=&quot;https://www.persee.fr/doc/austr_0396-4590_1982_num_14_1_1978&quot;  title=&quot;congrès à la mémoire de Ferdinand Ebner par persée&quot;&gt;En résumé,&lt;/a&gt;  il est avant tout un philosophe du dialogue, du langage et de la relation personnelle, à la frontière entre philosophie de l’existence, personnalisme et pensée chrétienne. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H37" r:id="rId30" display="https://www.laphilo.fr/pho/febner-mini.webp"/>
+    <hyperlink ref="E38" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Otto_Neurath&quot;  title=&quot; Wikipedia&quot;&gt;Otto NEURATH&lt;/a&gt; était un philosophe, sociologue et économiste autrichien, figure centrale et « leader atypique » du Cercle de Vienne et de l’empirisme logique. Né à Vienne, formé aux sciences sociales et à l’économie, il combine très tôt engagement politique socialiste, activité militante et réflexion épistémologique, ce qui le distingue de plusieurs de ses collègues plus académiques. Son projet global est de promouvoir une « conception scientifique du monde », opposée à la métaphysique spéculative, et d’orienter la philosophie vers une attitude scientifique au service de l’émancipation sociale. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour avoir formulé et défendu une version originale du physicalisme au début des années 1930. Contre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme&quot;  title=&quot;phénoménisme par wikipedia&quot;&gt;le phénoménalisme de Carnap, &lt;/a&gt;  qui partait de l’expérience privée, il propose un langage de « choses, événements et processus publics » situés dans l’espace et le temps, incluant les comportements et les événements physiologiques. Pour lui, l’unité, l’intelligibilité et l’objectivité de la science reposent sur cette base physicaliste : tous les énoncés scientifiques doivent pouvoir s’exprimer dans un vocabulaire intersubjectif, accessible à tous, et non dans un langage privé d’états de conscience. &lt;/p&gt; &lt;p&gt;Son  physicalisme n’est pas un réductionnisme étroit à la physique théorique, mais une orientation méthodologique et politique visant à unifier les sciences naturelles et sociales. Il s’inscrit dans un compromis entre empirisme (héritage de Mach) et matérialisme (influence de Marx), en insistant sur le caractère social et pratique de la connaissance scientifique. Cette position le conduit à rejeter les reconstructions logiques trop abstraites de la connaissance (modèle « pyramidal » de Russell ou Carnap) et à défendre un modèle « encyclopédiste » : une science collective, incomplète, toujours révisable, proche de la manière dont les scientifiques travaillent réellement. &lt;/p&gt; &lt;p&gt; Il joue également un rôle majeur dans le mouvement pour l’« unité de la science », en éditant l’Encyclopaedia of Unified Science et en organisant des congrès internationaux autour de ce projet. Il cherche à intégrer les sciences sociales dans ce cadre unifié, en montrant que les phénomènes sociaux et économiques peuvent être traités selon la même attitude scientifique que les phénomènes naturels, sans pour autant les réduire de façon simpliste. Son approche combine ainsi rigueur épistémologique, souci d’accessibilité (y compris par ses célèbres diagrammes statistiques, les Isotypes) et volonté de démocratisation du savoir. &lt;/p&gt; &lt;p&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=dh31H4dJEhY&quot;  title=&quot;otto Neurath par see hear say learn&quot;&gt;Sa philosophie &lt;/a&gt; est indissociable de son engagement politique et de sa trajectoire d’exilé : contraint de fuir le nazisme et laissant une œuvre à la fois technique et profondément humaniste. Sa conception de la philosophie comme clarification des méthodes scientifiques, son refus de la métaphysique dogmatique et son insistance sur le caractère collectif et fallible du savoir en font un penseur clé pour comprendre les dimensions sociales et politiques de l’empirisme logique. Son héritage se retrouve aujourd’hui dans les débats sur le naturalisme, la philosophie des sciences sociales et les projets d’unification des savoirs. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H38" r:id="rId32" display="https://www.laphilo.fr/pho/oneurath-mini.webp"/>
+    <hyperlink ref="H39" r:id="rId33" display="https://www.laphilo.fr/pho/ohneurath-mini.webp"/>
+    <hyperlink ref="I39" r:id="rId34" display="https://www.laphilo.fr/photo/ohneurath.webp"/>
+    <hyperlink ref="E40" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset&quot;  title=&quot; Wikipedia&quot;&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href=&quot;https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/&quot;  title=&quot;José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ&quot;&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, La révolte des masses, analyse la montée de  &lt;a href=&quot;https://www.youtube.com/watch?v=bse3ho0Hk7U&quot;  title=&quot;José Ortéga y Gasset : le règne de l’homme masse par Ego Non&quot;&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la monarchie autoritaire de Primo de Rivera, puis en faveur de la République.  &lt;a href=&quot;https://www.youtube.com/watch?v=jdB0729NoPg&quot;  title=&quot;José Ortéga y Gasset : méditation sur la technique par Edition Allia&quot;&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. &lt;/p&gt;   &lt;audio controls title=&quot; José ORTEGA y GASSET, penser la diversité culturelle par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="H41" r:id="rId36" display="https://laphilo.fr/pho/jmkeynes-mini.webp"/>
+    <hyperlink ref="E42" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Philipp_Frank&quot;  title=&quot; Wikipedia&quot;&gt;Philipp FRANK&lt;/a&gt; était un physicien théoricien, mathématicien et philosophe des sciences austro-américain. Il fut l’un des membres fondateurs du Cercle de Vienne et participa, avec Hans Hahn et Otto Neurath, à la formation de ce qui allait devenir l’empirisme logique. Il enseigna notamment à Prague, où il succéda à Albert Einstein, avec lequel il entretint une longue relation intellectuelle et personnelle. &lt;/p&gt; &lt;p&gt; Sa philosophie  appartient donc au positivisme logique, mais elle possède une orientation très empiriste, pragmatiste et historique. Il cherche à comprendre comment les théories scientifiques se construisent, comment elles sont confrontées à l’expérience et comment elles dépendent aussi de choix conceptuels. La science n’est pas, selon lui, une simple accumulation de faits : elle élabore des systèmes théoriques qui permettent d’organiser, de prévoir et d’interpréter les phénomènes. &lt;/p&gt; &lt;p&gt; Un thème important chez Frank est la critique de la causalité conçue comme une loi métaphysique absolue. Dans ses premiers travaux, il soutient que le principe de causalité ne peut être confirmé ou réfuté directement par l’expérience ; il fonctionne plutôt comme une convention ou une règle d’organisation des phénomènes. Cela ne signifie pas que la science soit arbitraire, car les théories doivent rester confrontées aux faits, mais que la forme générale de nos théories n’est pas imposée mécaniquement par l’expérience. &lt;/p&gt; &lt;p&gt; Il s’intéresse particulièrement à la théorie de la relativité d’Einstein. Il estime que la physique moderne montre le rôle conjoint de l’expérience et de la construction intellectuelle : une théorie scientifique est une création conceptuelle, mais elle doit être contrôlée par l’observation et l’expérimentation. Dans cette perspective, il défend une forme de relativisme méthodologique : le sens et la vérité d’un énoncé doivent être rapportés au cadre théorique, aux méthodes et aux conditions dans lesquels cet énoncé est formulé. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H42" r:id="rId38" display="https://www.laphilo.fr/pho/pfrank-mini.webp"/>
+    <hyperlink ref="E43" r:id="rId39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gy%C3%B6rgy_Luk%C3%A1cs&quot;  title=&quot; Wikipedia&quot;&gt;György LUKÁCS&lt;/a&gt; était un philosophe et critique littéraire hongrois, l'une des figures les plus importantes du marxisme occidental et de la  &lt;a href=&quot;https://www.youtube.com/watch?v=7xZ2dErDlhA&quot;  title=&quot;l’’esthétique de Georg LUKACS par Editions Critiques&quot;&gt;  théorie esthétique &lt;/a&gt; du XXe siècle. Né à Budapest dans une famille de banquiers juifs aisée, il étudia à Berlin et à Heidelberg auprès de Simmel et de Weber, avant d'adhérer au Parti communiste hongrois en 1918 et de participer à la République des Conseils hongroise. Exilé après son échec, il vécut à Vienne, Berlin, Moscou et revint en Hongrie en 1945. &lt;/p&gt; &lt;p&gt; Ses deux œuvres de jeunesse — &lt;em&gt;L'Âme et les formes&lt;/em&gt; (1911) et &lt;em&gt;La Théorie du roman&lt;/em&gt; (1916) — sont des contributions majeures à la philosophie de la culture et à l'esthétique. Dans &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=WA4AajumLHY&quot;  title=&quot;Histoire de conscience de classe Georg LUKACS par Detour théorique&quot;&gt;Histoire et conscience de classe &lt;/a&gt; &lt;/em&gt; (1923), son œuvre marxiste fondamentale, il développe les concepts de réification et de conscience de classe : le capitalisme produit une « réification » qui transforme les relations humaines en relations entre choses, et la conscience de classe du prolétariat est le seul sujet capable de saisir la totalité sociale et de surmonter cette aliénation. Ce texte fut l'un des fondements du marxisme occidental. &lt;/p&gt; &lt;p&gt; Dans ses œuvres tardives — &lt;em&gt;L'Esthétique&lt;/em&gt; (1963) et &lt;em&gt;Ontologie de l'être social&lt;/em&gt; (1971) — il tenta une synthèse marxiste de l'esthétique et de l'ontologie d'une ampleur encyclopédique. Ses travaux sur le réalisme littéraire, ses études sur Goethe, Balzac et Thomas Mann constituent des références importantes de la critique &lt;a href=&quot;https://www.persee.fr/doc/homso_0018-4306_1971_num_20_1_1405&quot;  title=&quot;l’évolution de la pensée de Georg LUKACS par Persée&quot;&gt;  littéraire marxiste. &lt;/a&gt;  Figure ambiguë par sa fidélité au communisme malgré les crimes staliniens, il reste l'un des philosophes les plus influents et les plus discutés du marxisme occidental. &lt;/p&gt;  &lt;audio controls title=&quot; Georg LUKACS, un penseur dans le feu de l’esprit par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-05.09.2025-ITEMA_24200841-2025C3372E0434-NET_MFC_22DB0A1A-8C49-4DD7-A53D-AC71F4115752-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E45" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski&quot;   title=&quot; Wikipedia&quot;&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href=&quot;https://www.youtube.com/watch?v=Vvt7ns_jZvY&quot;  title=&quot;The logic of reality  par TroughtLab&quot;&gt;la logique et des mathématiques &lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique &quot;vraie&quot; modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; "/>
+    <hyperlink ref="E49" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Hayek&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; , il en fait un fondement de sa critique du &lt;a href=&quot;https://fr.wikipedia.org/wiki/Constructivisme_(politique)&quot;  title=&quot; Constructivisme  par Wikipedia&quot;&gt;&quot;constructivisme rationnel&quot; :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'&quot;ordre spontané&quot; des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique . &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une &quot;prétention au savoir&quot; illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href=&quot;https://www.youtube.com/watch?v=TiGv4YcFieQ&quot;  title=&quot;La route de la servitude  par Capsio&quot;&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H50" r:id="rId42" display="https://www.laphilo.fr/pho/aschutz-mini.webp"/>
+    <hyperlink ref="H52" r:id="rId43" display="https://www.laphilo.fr/pho/lszabo-mini.webp"/>
+    <hyperlink ref="E53" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Karl_Popper&quot;  title=&quot; Wikipedia&quot;&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href=&quot;https://www.youtube.com/watch?v=AENUk4f6Ftg&quot; title=&quot;K Popper la logique et la découverte scientifique par Philosophie Analytique&quot;&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href=&quot;https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9&quot; title=&quot;Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté&quot;&gt; critère de falsifiabilité &lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href=&quot;https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde&quot; title=&quot;sciences et  pseudosciences par François Jourde&quot;&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href=&quot;https://www.youtube.com/watch?v=WheeYYBtSMA&quot; title=&quot;la société ouverte et ses ennemis par GORVS S&quot;&gt;  &quot;La Société Ouverte et ses ennemis &quot;,&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de &quot;société ouverte&quot; où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href=&quot;https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;Le paradoxe de la tolérance par le Précepteur&quot;&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Introduction à la philosophe de Karl Popper par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H53" r:id="rId45" display="https://www.laphilo.fr/pho/popper-mini.webp"/>
+    <hyperlink ref="I53" r:id="rId46" display="https://laphilo.fr/photo/lszabo.webp"/>
+    <hyperlink ref="E54" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders&quot;  title=&quot; Wikipedia&quot;&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href=&quot;https://www.youtube.com/watch?v=r4eq7EoRtTQ&quot;  title=&quot; Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope&quot;&gt;&quot;l'obsolescence de l'homme&quot;&lt;/a&gt; . Selon lui, l'homme moderne est   &lt;a href=&quot;https://books.openedition.org/pur/52513?lang=fr&quot; title=&quot;La notion de « supraliminaire » chez Günther Anders par OpenEdition&quot;&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression &quot;prométhée honteux&quot;  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href=&quot;https://www.youtube.com/watch?v=8xIiiYQJymQ&quot;  title=&quot;L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée&quot;&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href=&quot;https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde&quot; title=&quot;l'être jetable Günther Anders par La vie des idées&quot;&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title=&quot;Avoir raison avec... Günther Anders par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;"/>
+    <hyperlink ref="E55" r:id="rId48" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen&quot;  title=&quot; Wikipedia&quot;&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011&quot;  title=&quot; In memory of Fernand van steenberghen  par Persée&quot;&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H56" r:id="rId49" display="https://www.laphilo.fr/pho/schuon-mini.webp"/>
+    <hyperlink ref="I56" r:id="rId50" display="https://laphilo.fr/photo/fsteenberghen.webp"/>
+    <hyperlink ref="H57" r:id="rId51" display="https://www.laphilo.fr/pho/btabor-mini.webp"/>
+    <hyperlink ref="E58" r:id="rId52" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frederick_Copleston&quot;   title=&quot; Wikipedia&quot;&gt;Frederick COPLESTON&lt;/a&gt;  était un prêtre jésuite anglais, philosophe et historien de la philosophie, est surtout célèbre pour son monumental History of Philosophy en neuf volumes (1946-1975), qui retrace l'évolution de la pensée occidentale de l'Antiquité à l'époque contemporaine. Né près de Taunton, il étudie les classiques et la philosophie à Oxford avant de se convertir au catholicisme en 1925 et d'entrer dans la Compagnie de Jésus. &lt;/p&gt; &lt;p&gt; Son œuvre maîtresse offre une &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1953_num_51_29_7900_t1_0138_0000_3&quot; title=&quot;A history of philosophy by frederick Copleston par Persée&quot;&gt;synthèse équilibrée &lt;/a&gt; et accessible, couvrant les présocratiques, Platon, Aristote, les scolastiques comme Thomas d'Aquin, jusqu'aux modernes (Descartes, Kant, Hegel) et contemporains (Russell, Wittgenstein). Il distingue les causes in fieri (en devenir) des causes in esse (en être) pour clarifier les preuves de l'existence de Dieu chez Aquinas, soulignant un Dieu omniprésent plutôt qu'un simple déclencheur cosmique. Cette approche &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomisme&quot; title=&quot;le Tomisme par Wikipedia&quot;&gt;thomiste,&lt;/a&gt;  influencée par sa formation jésuite, respecte les auteurs sans parti pris apologétique. &lt;/p&gt; &lt;p&gt; Il gagne une popularité médiatique grâce à son débat radiodiffusé de 1948 avec Bertrand Russell sur l'existence de Dieu, où il défend la métaphysique contre l'athéisme analytique. L'année suivante, il affronte A.J. Ayer sur le positivisme logique et le sens du langage religieux, montrant la pertinence de la philosophie thomiste face aux courants dominants. Ces échanges illustrent sa capacité à dialoguer avec l'adversaire dans un esprit de rationalité ouverte. &lt;/p&gt; &lt;p&gt; Son héritage perdure comme référence pour étudiants et chercheurs, loué pour sa rigueur et sa complétude, malgré l'émergence de perspectives globales sur la philosophie non occidentale. Nommé Fellow de la British Academy en 1970 et Commandeur de l'Ordre de l'Empire britannique, il incarne un pont entre tradition scolastique et modernité, influençant les débats sur foi, raison et histoire intellectuelle. &lt;/p&gt;"/>
+    <hyperlink ref="H58" r:id="rId53" display="https://www.laphilo.fr/pho/copleston-mini.webp"/>
+    <hyperlink ref="E59" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Titus_Burckhardt&quot;  title=&quot; Wikipedia&quot;&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href=&quot;https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)&quot; title=&quot; Le Pérennialisme par Wikipedia&quot;&gt;pérennialisme &lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href=&quot;https://www.youtube.com/watch?v=Thok9so1Zik&quot; title=&quot; Introdustion aux doctrines ésothériques de l’Islam par Red Draco&quot;&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href=&quot;https://www.youtube.com/watch?v=Mx6E82Mt-v4&quot; title=&quot; Etre conservateur par Agar Hagar&quot;&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E60" r:id="rId55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Isaiah_Berlin&quot; title=&quot; Wikipedia&quot;&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href=&quot;https://www.youtube.com/watch?v=zSCS0toL5wc&quot; title=&quot;Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français&quot;&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot;  title=&quot;Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français&quot;&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=s-SVrbkJE5M&quot; title=&quot; Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français&quot;&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant &quot;décence humaine&quot; face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : - &quot;Karl Marx: His Life and Environment&quot; paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. - &quot;The Hedgehog and the Fox&quot; paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. - &quot;Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E61" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Eugenio_Garin&quot; title=&quot; Wikipedia&quot;&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; On peut donc dire que Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; "/>
+    <hyperlink ref="E62" r:id="rId57" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren&quot; title=&quot; Wikipedia&quot;&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une &quot;perplexité&quot; ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;, il développe une &quot;éthique de la perplexité&quot; : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href=&quot;https://www.youtube.com/watch?v=L3sJ7AvOT08&quot;  title=&quot; José Luis Aranguren  par Lecturas Fragmentadas&quot;&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique &quot;progressiste&quot; puis laïc engagé, il valorise la dissidence intellectuelle et une &quot;justice sociale&quot; cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;&#10;"/>
+    <hyperlink ref="H62" r:id="rId58" display="https://laphilo.fr/pho/jlaranguren-mini.webp"/>
+    <hyperlink ref="E63" r:id="rId59" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alfred_Jules_Ayer&quot; title=&quot; Wikipedia&quot;&gt;Alfred Jules AYER&lt;/a&gt; souvent surnommé « Freddie », était un philosophe britannique qui a joué un rôle central dans la diffusion du positivisme logique dans le monde anglophone. Né à Londres dans une famille d’origine suisse et néerlandaise, il fait ses études à Eton puis à Oxford, où il devient rapidement  &lt;a href=&quot;https://www.la-philosophie.fr/philosophie-analytique/alfred-jules-ayer-8.html&quot;  title=&quot;philosophie analytique par la philosophie&quot;&gt; une figure majeure &lt;/a&gt; de la philosophie analytique. C’est à seulement 24 ans qu’il publie son ouvrage le plus célèbre, Language, Truth, and Logic (1936), qui expose avec clarté et rigueur les thèses fondamentales du Cercle de Vienne et établit sa réputation internationale. &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve le principe de vérification, selon lequel une proposition n’a de sens cognitif que si elle est soit analytique (vraie en vertu de la signification des termes, comme en logique ou en mathématiques), soit empiriquement vérifiable (c’est-à-dire susceptible d’être confirmée ou infirmée par l’expérience). Ce critère lui permet de rejeter comme dénuées de sens littéral la plupart des affirmations de la métaphysique traditionnelle, de la théologie spéculative et de certaines formes d’éthique normative : elles ne sont pas fausses, mais simplement non vérifiables, donc dépourvues de contenu factuel. Il distingue ainsi strictement la philosophie, conçue comme analyse logique du langage, des sciences empiriques, seules habilitées à produire des connaissances sur le monde. &lt;/p&gt; &lt;p&gt; En éthique, il défend une position connue sous  &lt;a href=&quot;https://www.youtube.com/watch?v=HG5kIR6iF8g&quot;  title=&quot;A,J, Ayer’s Emotivism par philosophy Vibe&quot;&gt;le nom d’émotivisme. &lt;/a&gt;  Selon lui, les jugements moraux (« Le vol est mal », « La générosité est bonne ») n’expriment pas des faits objectifs, car il n’existe pas de « faits moraux » vérifiables empiriquement. Ils sont plutôt l’expression d’attitudes émotionnelles ou de prescriptions destinées à influencer les comportements d’autrui. Cette thèse s’inscrit dans une distinction radicale entre faits et valeurs : la science et la logique peuvent traiter des premiers, mais les secondes relèvent de la subjectivité et ne peuvent fonder aucune connaissance objective. &lt;/p&gt; &lt;p&gt; Au fil de sa carrière, il a nuancé certaines de ses positions initiales, notamment en reformulant le principe de vérification pour répondre aux objections (par exemple, en distinguant vérification directe et indirecte). Il a aussi évolué sur des questions de perception, de causalité et de liberté, tout en restant fidèle à un empirisme rigoureux et à une méfiance envers toute forme de métaphysique spéculative. Malgré les critiques ultérieures adressées au positivisme logique — notamment sur le statut même du principe de vérification —, son influence sur la philosophie analytique du XXᵉ siècle reste profonde, en particulier dans les débats sur le sens, la connaissance et l’éthique. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H63" r:id="rId60" display="https://www.laphilo.fr/pho/ajayer-mini.webp"/>
+    <hyperlink ref="H64" r:id="rId61" display="https://www.laphilo.fr/pho/jlaustin-mini.webp"/>
+    <hyperlink ref="H66" r:id="rId62" display="https://www.laphilo.fr/pho/pgrice-mini.webp"/>
+    <hyperlink ref="H68" r:id="rId63" display="https://www.laphilo.fr/pho/eanscombe-mini.webp"/>
+    <hyperlink ref="E70" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Stephen_Toulmin&quot;  title=&quot; Wikipedia&quot;&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href=&quot;https://www.youtube.com/watch?v=J1WDW2F-KBs&quot;  title=&quot; le modèle de Toulmin  par Mooc Cyu&quot;&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme &quot;probablement&quot;), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects &quot;field-dependent&quot; (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique.https://www.youtube.com/watch?v=HALSBMQlSqUhttps://en.wikipedia.org/wiki/Stephen_Toulmin &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un &quot;champ stable&quot; partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href=&quot;https://www.youtube.com/watch?v=hv7BUYzRiiU&quot;  title=&quot; le cartesian theatre de Toulmin  par Edwin gardner&quot;&gt;&quot;pluralistic conceptual relativism&quot; &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E72" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mary_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href=&quot;https://fr.wikipedia.org/wiki/Existentialisme&quot;  title=&quot; l’existentialisme Wikipedia&quot;&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href=&quot;https://en.wikipedia.org/wiki/Ethics_Since_1900&quot;  title=&quot; Ethics Since 1900 Wikipedia&quot;&gt;Ethics Since 1900 &lt;/a&gt; , elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de &quot;statementing&quot;, qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  &#10;&#10;"/>
+    <hyperlink ref="E73" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Attila_Kot%C3%A1nyi&quot;  title=&quot; Wikipedia&quot;&gt;Attila KOTANYI&lt;/a&gt; était un poète, philosophe, écrivain et architecte-urbaniste hongrois, membre de l’Internationale situationniste entre 1960 et 1963, avant d’être exclu pour « mysticisme chrétien » et de poursuivre une pensée très originale, marquée par la critique radicale du capitalisme et par des références à la mystique juive et au bouddhisme. Il développe très tôt un marxisme non dogmatique, éloigné des partis communistes officiels, et centré sur l’idée d’un humanisme régulateur qui place l’humain créateur au centre de toutes les activités. Pour lui, &lt;a href=&quot;https://situationnisteblog.com/2022/10/31/attila-kotanyi-larchitecture-du-silence-2022/&quot;  title=&quot;attila kotanyi architecture du silence par situationniste blog&quot;&gt;l’architecture, la poésie, la peinture ou la musique &lt;/a&gt; ne sont pas des domaines séparés par leur utilité, mais des expressions d’une même activité créatrice dont le produit final est le créateur lui-même. Cette vision s’inscrit dans une volonté de dépasser la division du travail et la séparation des disciplines, en phase avec le projet marxien d’émancipation totale de l’être humain. &lt;/p&gt; &lt;p&gt; Avec Raoul Vaneigem, il cofonde le Bureau d’urbanisme unitaire, qui propose de penser l’urbanisme non comme une technique de gestion, mais comme un art des relations et de la connexion, englobant tous les autres arts. Leur « Programme élémentaire du bureau d’urbanisme unitaire » vise à créer des « espaces de ravissement » et des « châteaux situationnistes » : des environnements favorisant la rencontre, le jeu, la dérive et la construction de situations libératrices. L’idée est de transformer l’espace urbain en un terrain d’expérimentation permanente où la vie quotidienne peut devenir une œuvre collective, joyeuse et non aliénée. &lt;/p&gt; &lt;p&gt; En 1963, il est exclu de &lt;a href=&quot;https://www.youtube.com/watch?v=2IaFG-HWBms&quot;  title=&quot;150ans de la commune thèse situationniste par libradio genève&quot;&gt;l’Internationale situationniste &lt;/a&gt; pour son « mysticisme chrétien », car il défend la thèse de l’impossibilité d’un art non corrompu et s’intéresse aux traditions mystiques, notamment chrétiennes, mais aussi juives et bouddhistes. Dans les années 1990, de retour à Budapest, il anime un cercle de jeunes intellectuels lors de rencontres hebdomadaires où il élabore sa théorie du Shabbat, conçue comme une suspension radicale de l’activité productive et un temps de résistance au capitalisme. Cette « théorie du Shabbat » prolonge sa critique de la société du spectacle en proposant un temps sacré, non marchand, où l’être humain peut échapper à la logique du travail et de la performance. &lt;/p&gt; &lt;p&gt; Sa  philosophie de se caractérise par une radicalité fondée sur la subjectivité, nourrie aussi bien par le marxisme que par la mystique juive, le bouddhisme et diverses traditions spirituelles. Sa pensée articule critique sociale et quête existentielle : il ne s’agit pas seulement de transformer les structures économiques et urbaines, mais aussi de libérer la vie intérieure, la créativité et la capacité de jouir sans entraves. En ce sens, il apparaît comme un penseur de la résistance intérieure et de la création d’espaces (concrets et symboliques) où l’humain peut redevenir sujet de sa propre existence. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H73" r:id="rId67" display="https://www.laphilo.fr/pho/akotanyi-mini.webp"/>
+    <hyperlink ref="I73" r:id="rId68" display="https://www.laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="E74" r:id="rId69" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anthony_Quinton&quot;  title=&quot; Wikipedia&quot;&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href=&quot;https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3&quot;  title=&quot; Anthony Quinton Hume 2000  par Persée&quot;&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions.https://www.youtube.com/watch?v=-qV2YFhKES8https://www.reddit.com/r/PoliticalPhilosophy/comments/15vj8do/foundational_texts_on_conservativism/ &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nominalisme&quot;  title=&quot; nominalisme par Wikipedia&quot;&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Conservatisme&quot;  title=&quot; conservatisme par Wikipedia&quot;&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H74" r:id="rId70" display="https://www.laphilo.fr/pho/quinton-mini.webp"/>
+    <hyperlink ref="I74" r:id="rId71" display="https://laphilo.fr/photo/akotanyi.webp"/>
+    <hyperlink ref="H77" r:id="rId72" display="https://www.laphilo.fr/pho/sbeer-mini.webp"/>
+    <hyperlink ref="E79" r:id="rId73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Geoffrey_Warnock&quot;  title=&quot; Wikipedia&quot;&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J.L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href=&quot;https://fr.wikipedia.org/wiki/Intuitionnisme_social&quot;   title=&quot;L’intuitionnisme par Kikipedia&quot;&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; "/>
+    <hyperlink ref="E81" r:id="rId74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Hassner&quot;  title=&quot; Wikipedia&quot;&gt;Pierre HASNER&lt;/a&gt; était un philosophe politique français d’origine roumaine, figure de la pensée européenne sur la guerre, le totalitarisme et la politique mondiale. Formé à la philosophie (École normale supérieure, agrégation en 1952) et proche de Raymond Aron, il a fait de la philosophie le socle de son analyse des relations internationales, cherchant à éclairer les problèmes géopolitiques par la pensée politique et morale. &lt;/p&gt; &lt;p&gt; Il se distingue par une approche qui combine philosophie politique et sociologie historique des relations internationales. Il est considéré comme inclassable, étant décrit comme « réaliste » (car il prend toujours en compte les contraintes du politique), « libéral » (car il insiste sur les normes et les droits de l’homme) et même « constructiviste » (par son intérêt pour le rôle des idées dans les RI). Sa pensée a marqué l’étude de la guerre froide, puis  &lt;a href=&quot;https://lediplomate.media/portrait-pierre-hassner-philosophe-interprete-inclassable-monde-desordonne/&quot;  title=&quot;pierre hassner philosophe fracture d’un monde desordonné par lediplomate&quot;&gt;celle des conflits de l’après-guerre &lt;/a&gt;  froide, notamment terrorisme, guerres hybrides et « nettoyage ethnique ». &lt;/p&gt; &lt;p&gt; Parmi ses œuvres majeures, on trouve La Violence et la Paix, La Terreur et l’Empire (2003), Washington et le Monde. Dilemmes d’une superpuissance (2003, avec Justin Vaïsse) et La Revanche des passions. Métamorphoses de la violence et crises du politique (2015). Il développe une réflexion sur la géopolitique des passions, soulignant que la guerre n’est pas un état « clair et distinct », mais une réalité diffuse et graduelle, marquée par les conflits hybrides, le terrorisme islamiste et la montée des violences politiques et identitaires. Pour lui, le totalitarisme et la guerre sont deux fléaux qu’il tente de comprendre pour essayer de surmonter leurs causes. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un disciple de Raymond Aron, reprenant sa tradition de philosophie politique appliquée aux grandes questions internationales : guerre, paix, puissance, valeurs. Il n’est pas rattaché à un courant strict (réaliste, libéral, constructiviste) mais incarne une  &lt;a href=&quot;https://www.youtube.com/watch?v=9XnlKLbbm2Q&quot;  title=&quot;pierre hassner par smolar web of stories&quot;&gt;forme de pensée politique &lt;/a&gt; ouverte, qui refuse les catégories rigides et cherche à comprendre la complexité du monde à partir de la philosophie. Il reste une référence incontournable pour ceux qui veulent penser la guerre, la paix et la politique mondiale sans se limiter à des schémas académiques fermés, et son héritage est considéré comme plus urgent que jamais dans un monde marqué par les crises géopolitiques contemporaines. &lt;/p&gt; &#10; &lt;audio controls title=&quot;pierre Hassner par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11189-26.11.2015-ITEMA_20849989-2015C15000E0181-ITE_00077318_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;"/>
+    <hyperlink ref="H82" r:id="rId75" display="https://www.laphilo.fr/pho/lluisifont-mini.webp"/>
+    <hyperlink ref="E84" r:id="rId76" display="&lt;p&gt;&lt;a href=&quot;https://es.wikipedia.org/wiki/Javier_Muguerza&quot;   title=&quot; Wikipedia&quot;&gt;Javier MURGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la &quot;perplexité&quot; comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses &quot;trois Critiques&quot; (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="H84" r:id="rId77" display="https://laphilo.fr/pho/jmuguerza-mini.webp"/>
+    <hyperlink ref="H85" r:id="rId78" display="https://www.laphilo.fr/pho/parfit-mini.webp"/>
+    <hyperlink ref="E86" r:id="rId79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A1szl%C3%B3_Tengelyi&quot;   title=&quot; Wikipedia&quot;&gt;Laszlo TENGELYI&lt;/a&gt;  était un philosophe hongrois renommé, spécialiste de phénoménologie, qui n'est pas directement associé à l'agnosticisme dans ses travaux principaux, mais dont la réflexion philosophique touche aux limites de la connaissance humaine, un thème proche. Né à Budapest, il a étudié à l'université Eötvös Loránd avant de poursuivre une carrière académique en Allemagne, notamment comme professeur à l'université de Wuppertal à partir de 2001, succédant à Klaus Held sur la chaire de phénoménologie et philosophie théorétique. &lt;/p&gt; &lt;p&gt; Ses recherches se concentraient sur la phénoménologie husserlienne, le kantisme et la &quot;nouvelle phénoménologie&quot; française, comme chez Levinas ou Marion, explorant l'expérience de la singularité, l'affectivité et les rapports entre monde fini et infini. Dans des ouvrages tels que Neue Phänomenologie in Frankreich (2012) ou Welt und Unendlichkeit (posthume, 2014), il questionne les fondements de la métaphysique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_(philosophie)&quot;  title=&quot; Phénoménologie  par Wikipedia&quot;&gt;phénoménologique, &lt;/a&gt; sans aborder explicitement l'agnosticisme, mais en soulignant les horizons inconnaissables de l'expérience. &lt;/p&gt; &lt;p&gt; Bien qu'aucun lien direct n'apparaisse avec l'origine de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Agnosticisme&quot;  title=&quot; Agnosticisme  par Wikipedia&quot;&gt;l'agnosticisme &lt;/a&gt;  – forgé par Thomas Huxley en 1869 et remontant à Protagoras –, Tengelyi a contribué à des débats sur la connaissance et l'absolu via son engagement dans des revues comme Annales de phénoménologie. Un document mentionne &quot;di-agnostique Henry&quot; près de son nom, peut-être une référence contextuelle à des discussions philosophiques sur le doute épistémologique, mais cela reste marginal. &lt;/p&gt; &lt;p&gt; Il i reste une figure clé de la phénoménologie contemporaine européenne, avec des publications en hongrois, allemand et français, et un engagement public, comme sa lettre ouverte en 2011 défendant des intellectuels hongrois face à des attaques médiatiques. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="H86" r:id="rId80" display="https://laphilo.fr/pho/ltengelyi-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1048576"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -2957,6 +2957,11 @@
       <c r="M3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -3735,6 +3740,11 @@
       </c>
       <c r="M23" s="15" t="s">
         <v>203</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="24" customFormat="false" ht="279" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4123,6 +4133,11 @@
       <c r="M33" s="2" t="s">
         <v>292</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
@@ -4201,6 +4216,11 @@
       <c r="M35" s="2" t="s">
         <v>308</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="313.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
@@ -4317,6 +4337,11 @@
       </c>
       <c r="M38" s="15" t="s">
         <v>334</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="39" customFormat="false" ht="361.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4472,6 +4497,11 @@
       <c r="M42" s="15" t="s">
         <v>366</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
@@ -4511,6 +4541,11 @@
       <c r="M43" s="2" t="s">
         <v>377</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
@@ -4550,6 +4585,11 @@
       <c r="M44" s="2" t="s">
         <v>386</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
@@ -4783,6 +4823,11 @@
       <c r="M50" s="2" t="s">
         <v>437</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
@@ -4820,6 +4865,11 @@
       </c>
       <c r="M51" s="2" t="s">
         <v>444</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4897,6 +4947,11 @@
       <c r="M53" s="2" t="s">
         <v>458</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
@@ -4935,6 +4990,11 @@
       </c>
       <c r="M54" s="2" t="s">
         <v>466</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="55" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5053,6 +5113,11 @@
       <c r="M57" s="22" t="s">
         <v>491</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
@@ -5169,6 +5234,11 @@
       </c>
       <c r="M60" s="2" t="s">
         <v>515</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5754,6 +5824,11 @@
       <c r="M75" s="14" t="s">
         <v>639</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -5983,6 +6058,11 @@
       </c>
       <c r="M81" s="14" t="s">
         <v>687</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
     </row>
     <row r="82" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2962,6 +2962,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="207" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -3001,6 +3011,11 @@
       <c r="M4" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="300" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -3040,6 +3055,11 @@
       <c r="M5" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -3079,6 +3099,11 @@
       <c r="M6" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="231" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -3118,6 +3143,11 @@
       <c r="M7" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
@@ -3157,6 +3187,11 @@
       <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="166.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -3196,6 +3231,11 @@
       <c r="M9" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -3235,6 +3275,11 @@
       <c r="M10" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -3274,6 +3319,11 @@
       <c r="M11" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="148.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -3313,6 +3363,11 @@
       <c r="M12" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
@@ -3352,6 +3407,11 @@
       <c r="M13" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
@@ -3391,6 +3451,14 @@
       <c r="M14" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -3430,6 +3498,11 @@
       <c r="M15" s="13" t="s">
         <v>133</v>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
@@ -3469,6 +3542,11 @@
       <c r="M16" s="2" t="s">
         <v>142</v>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
@@ -3508,6 +3586,14 @@
       <c r="M17" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P17">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="381" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
@@ -3547,6 +3633,11 @@
       <c r="M18" s="14" t="s">
         <v>159</v>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -3586,6 +3677,11 @@
       <c r="M19" s="2" t="s">
         <v>169</v>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
@@ -3625,6 +3721,11 @@
       <c r="M20" s="15" t="s">
         <v>177</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -3663,6 +3764,11 @@
       <c r="M21" s="15" t="s">
         <v>186</v>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
@@ -3702,6 +3808,11 @@
       <c r="M22" s="2" t="s">
         <v>195</v>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="279" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
@@ -3744,6 +3855,11 @@
       <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3783,6 +3899,11 @@
       <c r="M24" s="15" t="s">
         <v>212</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="368.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
@@ -3822,6 +3943,11 @@
       <c r="M25" s="2" t="s">
         <v>221</v>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
@@ -3861,6 +3987,14 @@
       <c r="M26" s="2" t="s">
         <v>230</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P26">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="321.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
@@ -3900,6 +4034,11 @@
       <c r="M27" s="14" t="s">
         <v>239</v>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -3938,6 +4077,11 @@
       <c r="M28" s="2" t="s">
         <v>247</v>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
@@ -3977,6 +4121,14 @@
       <c r="M29" s="2" t="s">
         <v>256</v>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
@@ -4016,6 +4168,11 @@
       <c r="M30" s="2" t="s">
         <v>266</v>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
@@ -4055,6 +4212,11 @@
       <c r="M31" s="2" t="s">
         <v>276</v>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
@@ -4094,6 +4256,11 @@
       <c r="M32" s="2" t="s">
         <v>284</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
@@ -4138,6 +4305,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
@@ -4177,6 +4349,11 @@
       <c r="M34" s="13" t="s">
         <v>301</v>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
@@ -4221,6 +4398,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="313.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
@@ -4260,6 +4442,11 @@
       <c r="M36" s="15" t="s">
         <v>317</v>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
@@ -4299,6 +4486,11 @@
       <c r="M37" s="14" t="s">
         <v>326</v>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="361.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
@@ -4341,6 +4533,11 @@
       <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4380,6 +4577,11 @@
       <c r="M39" s="15" t="s">
         <v>342</v>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
@@ -4419,6 +4621,11 @@
       <c r="M40" s="14" t="s">
         <v>351</v>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="223.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
@@ -4458,6 +4665,11 @@
       <c r="M41" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
@@ -4502,6 +4714,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
@@ -4546,6 +4763,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
@@ -4590,6 +4812,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
@@ -4629,6 +4859,11 @@
       <c r="M45" s="2" t="s">
         <v>394</v>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
@@ -4668,6 +4903,11 @@
       <c r="M46" s="2" t="s">
         <v>402</v>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
@@ -4706,6 +4946,11 @@
       <c r="M47" s="2" t="s">
         <v>411</v>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
@@ -4745,6 +4990,11 @@
       <c r="M48" s="2" t="s">
         <v>421</v>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
@@ -4784,6 +5034,11 @@
       <c r="M49" s="2" t="s">
         <v>428</v>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
@@ -4828,6 +5083,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
@@ -4869,6 +5129,11 @@
       <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4908,6 +5173,11 @@
       <c r="M52" s="2" t="s">
         <v>450</v>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
@@ -4952,6 +5222,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
@@ -4994,6 +5269,11 @@
       <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -5033,6 +5313,11 @@
       <c r="M55" s="2" t="s">
         <v>474</v>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
@@ -5074,6 +5359,11 @@
       <c r="M56" s="2" t="s">
         <v>483</v>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
@@ -5118,6 +5408,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
@@ -5157,6 +5452,11 @@
       <c r="M58" s="2" t="s">
         <v>498</v>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
@@ -5196,6 +5496,11 @@
       <c r="M59" s="2" t="s">
         <v>506</v>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
@@ -5237,7 +5542,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;russe</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -5279,6 +5589,11 @@
       <c r="M61" s="2" t="s">
         <v>523</v>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
@@ -5318,6 +5633,11 @@
       <c r="M62" s="2" t="s">
         <v>530</v>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="351" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
@@ -5357,6 +5677,11 @@
       <c r="M63" s="14" t="s">
         <v>539</v>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="306" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
@@ -5396,6 +5721,11 @@
       <c r="M64" s="2" t="s">
         <v>548</v>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
@@ -5435,6 +5765,11 @@
       <c r="M65" s="2" t="s">
         <v>556</v>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
@@ -5474,6 +5809,11 @@
       <c r="M66" s="2" t="s">
         <v>564</v>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
@@ -5513,6 +5853,11 @@
       <c r="M67" s="2" t="s">
         <v>573</v>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
@@ -5551,6 +5896,11 @@
       <c r="M68" s="2" t="s">
         <v>581</v>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
@@ -5590,6 +5940,11 @@
       <c r="M69" s="2" t="s">
         <v>591</v>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
@@ -5629,6 +5984,11 @@
       <c r="M70" s="2" t="s">
         <v>599</v>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
@@ -5668,6 +6028,11 @@
       <c r="M71" s="2" t="s">
         <v>607</v>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
@@ -5706,6 +6071,11 @@
       </c>
       <c r="M72" s="2" t="s">
         <v>614</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5744,6 +6114,11 @@
       <c r="M73" s="14" t="s">
         <v>622</v>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
@@ -5785,6 +6160,11 @@
       <c r="M74" s="2" t="s">
         <v>630</v>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
@@ -5829,6 +6209,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -5868,6 +6253,11 @@
       <c r="M76" s="2" t="s">
         <v>648</v>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="358.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
@@ -5906,6 +6296,11 @@
       <c r="M77" s="2" t="s">
         <v>655</v>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
@@ -5945,6 +6340,11 @@
       <c r="M78" s="2" t="s">
         <v>663</v>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
@@ -5984,6 +6384,11 @@
       <c r="M79" s="2" t="s">
         <v>672</v>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
@@ -6020,6 +6425,11 @@
       <c r="L80" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
@@ -6064,6 +6474,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
@@ -6103,6 +6518,11 @@
       <c r="M82" s="2" t="s">
         <v>694</v>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
@@ -6142,6 +6562,11 @@
       <c r="M83" s="14" t="s">
         <v>701</v>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="217.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
@@ -6181,6 +6606,11 @@
       <c r="M84" s="2" t="s">
         <v>708</v>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
@@ -6220,6 +6650,11 @@
       <c r="M85" s="2" t="s">
         <v>717</v>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
@@ -6257,6 +6692,11 @@
       </c>
       <c r="M86" s="2" t="s">
         <v>724</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
     </row>
     <row r="87" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -3055,6 +3055,11 @@
       <c r="M5" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3187,6 +3192,11 @@
       <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3362,6 +3372,11 @@
       </c>
       <c r="M12" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -4577,6 +4592,11 @@
       <c r="M39" s="15" t="s">
         <v>342</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -5896,6 +5916,11 @@
       <c r="M68" s="2" t="s">
         <v>581</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -6071,6 +6096,11 @@
       </c>
       <c r="M72" s="2" t="s">
         <v>614</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6700,24 +6730,175 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E87" s="1"/>
+      <c r="A87" s="1">
+        <v>1904</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1904 - 1991</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">María ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/María_Zambrano"  title=" Wikipedia"&gt;María ZAMBRANO&lt;/a&gt; (1904-1991) est une philosophe et essayiste espagnole, disciple de José Ortega y Gasset. Engagée du côté de la République pendant la guerre civile, elle dut s'exiler en 1939 et vécut près de quarante-cinq ans loin de son pays, au Mexique, à Cuba, à Porto Rico, en Italie, en France et en Suisse, avant de revenir en Espagne en 1984.&lt;/p&gt; &lt;p&gt;Sa pensée s'éloigne de celle de son maître. Elle reproche à la philosophie occidentale d'avoir séparé la raison de la vie, de l'émotion et du sacré. Elle propose une « raison poétique », une manière de penser qui ne cherche pas à dominer la réalité par des concepts, mais à l'accueillir, à l'écouter et à la laisser apparaître, comme le fait la poésie.&lt;/p&gt; &lt;p&gt;L'exil occupe une place centrale dans sa pensée : loin d'être seulement une perte, il devient pour elle une condition philosophique, une manière de vivre dépouillée qui ouvre à une vérité plus profonde. Elle voyait dans la figure d'Antigone, à laquelle elle consacra une pièce, &lt;em&gt;La Tombe d'Antigone&lt;/em&gt;, le symbole de toutes les victimes de l'histoire et de la conscience qui refuse l'injustice.&lt;/p&gt; &lt;p&gt;Dans des livres comme &lt;em&gt;Philosophie et poésie&lt;/em&gt; (1939), &lt;em&gt;L'Homme et le divin&lt;/em&gt; (1955) ou &lt;em&gt;Les Clairières du bois&lt;/em&gt; (1977), elle explore le rêve, la mémoire, l'exil et le sacré, dans un style qui mêle philosophie et littérature. Longtemps méconnue, elle reçut en 1988 le prix Cervantès, la plus haute distinction littéraire du monde hispanique, et elle est aujourd'hui considérée comme l'une des grandes voix de la pensée espagnole du XXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="1"/>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espagnole</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe espagnole, disciple d'Ortega y Gasset, penseuse de la « raison poétique ».</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E88" s="1"/>
+      <c r="A88" s="1">
+        <v>1919</v>
+      </c>
+      <c r="B88" s="1">
+        <v>1999</v>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1919 - 1999</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iris MURDOCH</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Murdoch"  title=" Wikipedia"&gt;Iris MURDOCH&lt;/a&gt; (1919-1999) est une philosophe et romancière britannique, née à Dublin. Elle enseigna la philosophie à Oxford, où elle fut, avec Elizabeth Anscombe, Philippa Foot et Mary Midgley, l'une des figures d'un groupe de femmes philosophes qui renouvelèrent la réflexion morale après la Seconde Guerre mondiale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Souveraineté du bien&lt;/em&gt; (1970), elle critique à la fois l'existentialisme et la philosophie analytique de son temps, qui réduisaient la morale à des choix de la volonté. Pour elle, la vie morale se joue d'abord dans la manière de voir : être bon, c'est porter sur les autres et sur le monde une « attention » juste et aimante, qui nous arrache à notre égoïsme. Elle reprend l'idée platonicienne du Bien comme réalité supérieure qui attire l'âme vers la vérité.&lt;/p&gt; &lt;p&gt;Murdoch donne l'exemple d'une belle-mère qui méprise sa belle-fille, mais qui, sans rien changer à son comportement extérieur, s'efforce de la regarder autrement, avec justice et bienveillance, jusqu'à la voir telle qu'elle est vraiment. Ce travail intérieur, invisible, est pour Murdoch l'essentiel de la vie morale. Elle voyait aussi dans l'art et la beauté, et notamment dans la contemplation de la nature, un moyen de se détacher de soi.&lt;/p&gt; &lt;p&gt;Elle est aussi l'autrice de vingt-six romans, dont &lt;em&gt;La Mer, la mer&lt;/em&gt;, qui reçut le Booker Prize en 1978, où elle met en scène les illusions et les passions de personnages en quête de sens. Atteinte de la maladie d'Alzheimer à la fin de sa vie, elle a inspiré le film &lt;em&gt;Iris&lt;/em&gt; (2001). Sa philosophie morale connaît aujourd'hui un grand regain d'intérêt.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="M88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et romancière britannique, penseuse d'une morale de l'attention inspirée de Platon.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1">
+        <v>1920</v>
+      </c>
+      <c r="B89" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920 - 2010</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippa FOOT</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippa_Foot"  title=" Wikipedia"&gt;Philippa FOOT&lt;/a&gt; (1920-2010) est une philosophe britannique qui enseigna à Oxford puis aux États-Unis. Avec Elizabeth Anscombe et Iris Murdoch, elle contribua à faire revivre l'éthique de la vertu, inspirée d'Aristote, face aux morales du devoir et aux morales de l'utilité qui dominaient la philosophie anglo-saxonne.&lt;/p&gt; &lt;p&gt;Elle est connue du grand public pour avoir inventé en 1967 le célèbre « dilemme du tramway » : un tramway fou va tuer cinq personnes, mais on peut le détourner vers une voie où il n'en tuera qu'une. Faut-il le faire ? Cette expérience de pensée, discutée depuis par des milliers de philosophes, sert aujourd'hui aussi à réfléchir aux choix des voitures autonomes.&lt;/p&gt; &lt;p&gt;Philippa Foot fut aussi l'une des fondatrices d'Oxfam, grande organisation de lutte contre la pauvreté, ce qui montre son souci de relier la philosophie morale à l'action. Au début de sa carrière, elle critiqua vivement l'idée, alors dominante, que les jugements moraux ne sont que l'expression de nos sentiments ou de nos choix, en montrant que des mots comme « grossier » ou « courageux » décrivent des faits autant qu'ils expriment des valeurs.&lt;/p&gt; &lt;p&gt;Dans son livre &lt;em&gt;Le Bien naturel&lt;/em&gt; (2001), elle défend l'idée que le bien et le mal moraux ne sont pas de simples préférences : comme une plante ou un animal peut être en bonne ou en mauvaise santé selon sa nature, un être humain peut être bon ou défectueux selon ce qui est nécessaire à une vie humaine réussie. Les vertus comme le courage, la justice ou la tempérance sont ainsi ancrées dans notre nature d'êtres vivants et sociaux.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éthique de la vertu</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe britannique, refondatrice de l'éthique de la vertu et inventrice du « dilemme du tramway ».</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P89">
+        <v>2</v>
+      </c>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -6897,6 +6897,359 @@
         </is>
       </c>
       <c r="P89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1">
+        <v>1912</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2009</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912 – 2009</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arne NÆSS</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arne_N%C3%A6ss" title=" Wikipedia"&gt;Arne NÆSS&lt;/a&gt; est un philosophe norvégien, fondateur de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologie_profonde" title=" Wikipedia"&gt;écologie profonde&lt;/a&gt;. Né à Oslo, il participe dans les années 1930 aux discussions du Cercle de Vienne, puis devient à vingt-sept ans professeur à l’université d’Oslo, où il enseigne de 1939 à 1969. Longtemps seul professeur de philosophie de Norvège, il marque durablement l’enseignement du pays. Résistant pendant l’occupation allemande, il est aussi un alpiniste de haut niveau, qui dirige en 1950 la première ascension du Tirich Mir, dans l’Hindou Kouch.&lt;/p&gt; &lt;p&gt;D’abord spécialiste de logique et de philosophie du langage, il étudie ensuite Spinoza et Gandhi, et s’engage dans la défense de la nature après la lecture du &lt;em&gt;Printemps silencieux&lt;/em&gt; de Rachel Carson. En 1973, il distingue une écologie « superficielle », qui lutte contre la pollution pour préserver la santé et le confort des pays riches, et une écologie « profonde », qui reconnaît une valeur propre à tous les êtres vivants, indépendamment de leur utilité pour l’homme. Il en tire une plate-forme en huit points, qui appelle à réduire la pression humaine sur la nature.&lt;/p&gt; &lt;p&gt;Sa philosophie personnelle, qu’il appelle « écosophie T », du nom de son refuge de montagne, Tvergastein, repose sur la « réalisation de soi » : plus on s’identifie aux autres êtres, plus le soi s’élargit, et la protection de la nature devient l’expression même de ce soi élargi. Il est aussi le premier président norvégien du parti écologiste et pratique la désobéissance civile, en s’enchaînant en 1970 avec d’autres militants pour empêcher la construction d’un barrage. Il meurt à Oslo en 2009.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/naess-mini.webp</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Norvégienne</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecologisme</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe norvégien, alpiniste et fondateur de l’écologie profonde.</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1">
+        <v>1916</v>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2003</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1916 – 2003</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georg Henrik VON WRIGHT</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georg_Henrik_von_Wright" title=" Wikipedia"&gt;Georg Henrik VON WRIGHT&lt;/a&gt; est un philosophe et logicien finlandais de langue suédoise. Né à Helsinki, élève d’Eino Kaila, il part à Cambridge en 1939, où il devient l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein" title=" Wikipedia"&gt;Ludwig Wittgenstein&lt;/a&gt;, auquel il succède en 1948 à la chaire de philosophie, avant de rentrer en Finlande en 1951. Nommé en 1961 membre de l’Académie de Finlande, il est l’un des intellectuels les plus respectés des pays nordiques. À la mort de Wittgenstein, il est l’un des trois exécuteurs testamentaires chargés de publier ses manuscrits, dont les &lt;em&gt;Recherches philosophiques&lt;/em&gt; et &lt;em&gt;De la certitude&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Logicien, il étudie l’induction et les probabilités, puis la logique modale. En 1951, il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_d%C3%A9ontique" title=" Wikipedia"&gt;logique déontique&lt;/a&gt;, la logique des normes : elle étudie les rapports entre ce qui est obligatoire, permis et interdit, comme la logique modale étudie le nécessaire et le possible. Il développe aussi une logique de l’action et du changement. Dans &lt;em&gt;Explication et compréhension&lt;/em&gt; (1971), il défend l’idée que les actions humaines ne s’expliquent pas comme des phénomènes naturels, par des causes, mais se comprennent à partir des intentions et des raisons des personnes qui agissent.&lt;/p&gt; &lt;p&gt;Dans les dernières décennies de sa vie, il devient un critique inquiet de la civilisation technique. Dans &lt;em&gt;Le Mythe du progrès&lt;/em&gt; (1993), il se demande si le développement des sciences et des techniques, qui menace l’environnement et la diversité des cultures, constitue vraiment un progrès pour l’humanité. Il défend un humanisme fondé sur la raison et la mesure. Il meurt à Helsinki en 2003.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vonwright-mini.webp</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finlandaise</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; ethique</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Humanisme</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et logicien finlandais, successeur de Wittgenstein à Cambridge, fondateur de la logique déontique.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1">
+        <v>1929</v>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2015</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1929 – 2015</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaakko HINTIKKA</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaakko_Hintikka" title=" Wikipedia"&gt;Jaakko HINTIKKA&lt;/a&gt; est un logicien et philosophe finlandais, l’un des penseurs les plus inventifs de la philosophie analytique. Né à Vantaa, près d’Helsinki, élève de Georg Henrik von Wright, il enseigne à Helsinki, puis aux États-Unis, à Stanford, en Floride et à Boston. Auteur de plus de cinquante livres et de plus de quatre cent cinquante articles, il a reçu en 2005 le prix Rolf Schock, l’une des plus hautes distinctions en logique et en philosophie.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Knowledge and Belief&lt;/em&gt; (1962), il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_%C3%A9pist%C3%A9mique" title=" Wikipedia"&gt;logique épistémique&lt;/a&gt;, qui étudie avec précision les notions de connaissance et de croyance : que signifie « je sais que », « je crois que », ou « il sait que je sais » ? Pour cela, il utilise l’idée de « mondes possibles », les différentes façons dont le monde pourrait être compatibles avec ce que l’on sait. Ces travaux sont aujourd’hui utilisés en informatique, en intelligence artificielle et en théorie des jeux.&lt;/p&gt; &lt;p&gt;Il propose aussi une « sémantique des jeux » : comprendre une phrase logique, c’est comprendre un jeu entre deux joueurs, l’un qui cherche à la vérifier, l’autre à la réfuter. Avec Gabriel Sandu, il en tire une nouvelle logique, dite « logique IF », plus expressive que la logique classique, dont il pensait qu’elle devrait servir de fondement aux mathématiques. Historien de la philosophie, il a aussi écrit sur Aristote, Descartes, Kant et Wittgenstein, notamment une lecture célèbre du « Je pense, donc je suis » comme acte plutôt que comme raisonnement. Il meurt en 2015.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hintikka-mini.webp</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finlandaise</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logicien et philosophe finlandais, fondateur de la logique épistémique et de la sémantique des jeux.</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1">
+        <v>1923</v>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2010</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1923 – 2010</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mihailo MARKOVIĆ</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mihailo_Markovi%C4%87" title=" Wikipedia (en)"&gt;Mihailo MARKOVIĆ&lt;/a&gt; est un philosophe serbe, l’une des figures majeures de l’école Praxis, puis un acteur controversé du nationalisme serbe. Né à Belgrade, il rejoint jeune le Parti communiste et combat dans la résistance des partisans pendant la Seconde Guerre mondiale. Il soutient deux thèses de doctorat, à Belgrade puis à Londres, où il étudie la logique auprès d’A. J. Ayer, et devient professeur à l’université de Belgrade.&lt;/p&gt; &lt;p&gt;Après la rupture entre Tito et Staline en 1948, il publie en 1952 la première grande critique de la philosophie stalinienne en Yougoslavie. Dans les années 1960, il devient l’un des principaux théoriciens de l’école Praxis, qui défend un marxisme humaniste inspiré des écrits du jeune Marx, centré sur la liberté créatrice de l’homme et la critique de l’aliénation, à l’Ouest comme à l’Est. Il collabore à la revue &lt;em&gt;Praxis&lt;/em&gt; et à l’école d’été de Korčula, où se rencontrent des penseurs marxistes du monde entier. Ses critiques de la bureaucratie lui valent d’être suspendu de l’université en 1975 avec sept collègues.&lt;/p&gt; &lt;p&gt;Son parcours prend ensuite un tour très différent : membre de l’Académie serbe des sciences et des arts, il est l’un des auteurs du Mémorandum de 1986, texte qui formule les revendications du nationalisme serbe, puis devient l’un des idéologues du parti de &lt;a href="https://fr.wikipedia.org/wiki/Slobodan_Milo%C5%A1evi%C4%87" title=" Wikipedia"&gt;Slobodan Milošević&lt;/a&gt;. Ce soutien, pendant les guerres de Yougoslavie, lui a été vivement reproché, notamment par ses anciens compagnons de l’école Praxis. Il meurt à Belgrade en 2010.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/markovic-mini.webp</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serbe</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme ; Humanisme</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe serbe de l’école Praxis, critique du stalinisme, devenu ensuite idéologue du nationalisme serbe.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1">
+        <v>1927</v>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1993</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1927 – 1993</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gajo PETROVIĆ</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Gajo_Petrovi%C4%87" title=" Wikipedia (en)"&gt;Gajo PETROVIĆ&lt;/a&gt; est un philosophe croate, principal fondateur de l’école Praxis, le grand courant du marxisme humaniste yougoslave. Né à Karlovac, il étudie la philosophie à Zagreb, puis, en 1946-1948, en Union soviétique, où il découvre l’étouffement de la pensée sous Staline. Dès 1949, sa critique d’un dirigeant de la ligne officielle lui vaut d’être exclu du Parti communiste. Réintégré à l’université, il y enseigne la logique et la philosophie jusqu’à sa retraite.&lt;/p&gt; &lt;p&gt;Il fonde en 1964 avec d’autres philosophes de Zagreb la revue &lt;em&gt;Praxis&lt;/em&gt;, publiée jusqu’en 1974 et connue dans le monde entier, ainsi que l’école d’été de Korčula, qui réunit dans une île de l’Adriatique des penseurs de l’Est et de l’Ouest, d’&lt;a href="https://fr.wikipedia.org/wiki/Ernst_Bloch" title=" Wikipedia"&gt;Ernst Bloch&lt;/a&gt; à &lt;a href="https://fr.wikipedia.org/wiki/Herbert_Marcuse" title=" Wikipedia"&gt;Herbert Marcuse&lt;/a&gt; et Jürgen Habermas. Il préside aussi l’Association yougoslave de philosophie. Contre le marxisme dogmatique des partis, il revient aux écrits du jeune Marx : l’homme est un être de « praxis », c’est-à-dire d’activité libre et créatrice, qui se fait lui-même en transformant le monde.&lt;/p&gt; &lt;p&gt;Pour Petrović, la philosophie doit être une « critique impitoyable de tout ce qui existe », y compris du socialisme réel et de ses bureaucraties. En 1968, il soutient ouvertement les manifestations étudiantes, ce qui lui vaut une nouvelle exclusion du parti, et la revue est contrainte de cesser de paraître en 1974. Ses livres, comme &lt;em&gt;Marx au milieu du XXe siècle&lt;/em&gt; (1967), ont été traduits dans de nombreuses langues. Il meurt à Zagreb en 1993, à soixante-six ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/petrovic-mini.webp</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croate</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme ; Humanisme</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe croate, fondateur de la revue Praxis, penseur d’un marxisme humaniste et critique.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1">
+        <v>1936</v>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1936 – 2026</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ioanna KUÇURADI</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C4%B0oanna_Ku%C3%A7uradi" title=" Wikipedia"&gt;Ioanna KUÇURADI&lt;/a&gt; est une philosophe turque d’origine grecque, l’une des grandes figures internationales de la philosophie des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_l%27homme" title=" Wikipedia"&gt;droits de l’homme&lt;/a&gt;. Née à Istanbul dans une famille de la communauté grecque, elle étudie la philosophie à l’université d’Istanbul, où elle soutient son doctorat en 1965. En 1968, elle fonde le département de philosophie de l’université Hacettepe, à Ankara, qu’elle dirige jusqu’en 2005.&lt;/p&gt; &lt;p&gt;Spécialiste de l’éthique, elle étudie la nature des valeurs et défend l’idée qu’une connaissance éthique est possible : on peut connaître, et pas seulement ressentir, la valeur de l’être humain et ce qu’exige le respect de sa dignité. Les droits de l’homme ne sont pas pour elle de simples conventions juridiques, mais des exigences éthiques qui découlent de cette valeur, et qui doivent guider les lois et les politiques. Elle insiste sur l’importance de l’éducation aux droits de l’homme et sur la responsabilité des philosophes dans la vie publique.&lt;/p&gt; &lt;p&gt;Elle crée à Hacettepe un centre de recherche sur la philosophie des droits de l’homme, préside en Turquie le Haut Conseil consultatif des droits de l’homme et occupe une chaire de philosophie de l’UNESCO. Présidente de la Société turque de philosophie, puis de la Fédération internationale des sociétés de philosophie de 1998 à 2003 et de l’Institut international de philosophie, elle a beaucoup œuvré au dialogue entre les philosophies du monde. Elle meurt à Istanbul le 2 octobre 2026, deux jours avant ses quatre-vingt-dix ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kucuradi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turque</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe turque, penseuse des valeurs et de la philosophie des droits de l’homme.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P95">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P95"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -7250,6 +7250,185 @@
         </is>
       </c>
       <c r="P95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1">
+        <v>1864</v>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1936</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1864 – 1936</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miguel de UNAMUNO</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Miguel_de_Unamuno" title=" Wikipedia"&gt;Miguel de UNAMUNO&lt;/a&gt; est un écrivain et philosophe espagnol, figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9n%C3%A9ration_de_1898" title=" Wikipedia"&gt;génération de 1898&lt;/a&gt;, qui s’interroge sur l’âme de l’Espagne après la perte de ses dernières colonies. Né à Bilbao, professeur de grec puis recteur de l’université de Salamanque à partir de 1900, il écrit des romans, des poèmes, du théâtre et des essais. Ses critiques contre la monarchie et la dictature de Primo de Rivera lui valent d’être exilé en 1924 aux Canaries, puis il vit à Paris et à Hendaye jusqu’en 1930. Dans &lt;em&gt;Vie de Don Quichotte et de Sancho&lt;/em&gt; (1905), il fait du chevalier errant un héros de la foi contre le bon sens.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Sentiment_tragique_de_la_vie" title=" Wikipedia"&gt;&lt;em&gt;Le Sentiment tragique de la vie&lt;/em&gt;&lt;/a&gt; (1913), il part de « l’homme de chair et d’os », qui veut ne pas mourir. La raison lui dit que rien ne survit à la mort ; le cœur réclame l’immortalité. Unamuno refuse de trancher : la vie authentique consiste à vivre ce combat sans le résoudre, dans une foi qui doute. Lecteur passionné de Kierkegaard, il annonce l’existentialisme. Dans &lt;em&gt;L’Agonie du christianisme&lt;/em&gt; (1925), « agonie » est prise au sens grec de lutte. Dans son roman &lt;em&gt;Brouillard&lt;/em&gt; (1914), le héros vient discuter de son sort avec l’auteur lui-même.&lt;/p&gt; &lt;p&gt;Le 12 octobre 1936, au début de la guerre civile, il affronte publiquement dans l’université de Salamanque le général franquiste Millán Astray, qui vient de crier « Vive la mort ! », et lui oppose, selon le récit devenu célèbre : « Vous vaincrez, mais vous ne convaincrez pas. » Destitué et assigné à résidence, il meurt le 31 décembre 1936. Il reste l’une des grandes voix de la conscience européenne face au fanatisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/unamuno-mini.webp</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espagnole</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et philosophe espagnol, auteur du Sentiment tragique de la vie, penseur de l’angoisse et de la foi.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1">
+        <v>1903</v>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1994</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1903 – 1994</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yeshayahou LEIBOWITZ</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yeshayahou_Leibowitz" title=" Wikipedia"&gt;Yeshayahou LEIBOWITZ&lt;/a&gt; est un scientifique, philosophe et moraliste israélien, l’un des intellectuels les plus marquants et les plus controversés de son pays. Né à Riga dans une famille juive orthodoxe, il étudie la chimie et la philosophie à Berlin, puis la médecine à Bâle. Installé en 1934 en Palestine, il enseigne pendant près de soixante ans la chimie, la biochimie, la neurophysiologie et la philosophie à l’Université hébraïque de Jérusalem, et dirige l’&lt;a href="https://fr.wikipedia.org/wiki/Encyclop%C3%A9die_h%C3%A9bra%C3%AFque" title=" Wikipedia"&gt;Encyclopédie hébraïque&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Juif pratiquant rigoureux, il défend une conception austère de la foi. Le judaïsme n’est pas pour lui une sagesse, une morale ou une identité nationale, mais le service de Dieu par l’accomplissement des commandements, pour lui-même et sans rien attendre en retour : la religion n’est pas là pour satisfaire les besoins de l’homme. Il refuse donc d’attribuer une valeur religieuse à l’État, à la terre ou à l’histoire, et réclame la séparation de la religion et de l’État, qui selon lui corrompt la religion en la mettant au service de la politique.&lt;/p&gt; &lt;p&gt;Dès la guerre de 1967, il met en garde contre l’occupation des territoires palestiniens, qui détruirait selon lui la société israélienne elle-même, et appelle les soldats à refuser de servir dans les territoires. Ses critiques, parfois formulées en termes d’une extrême dureté, provoquent de vives polémiques. Lorsque le prix Israël lui est attribué, peu avant sa mort, le Premier ministre Yitzhak Rabin menace de boycotter la cérémonie, et Leibowitz renonce au prix. Il meurt à Jérusalem en 1994.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/leibowitz-mini.webp</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israélienne</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monothéisme</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scientifique et philosophe israélien, penseur d’une foi sans illusions, critique de l’occupation.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1">
+        <v>1923</v>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1923 – 2020</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eduardo LOURENÇO</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eduardo_Louren%C3%A7o" title=" Wikipedia"&gt;Eduardo LOURENÇO&lt;/a&gt; est un essayiste, philosophe et critique portugais, l’un des grands intellectuels européens du XXe siècle. Né dans un village de la Beira, près de la frontière espagnole, il étudie l’histoire et la philosophie à l’université de Coimbra. Son premier livre, &lt;em&gt;Hétérodoxie&lt;/em&gt; (1949), revendique le droit de penser librement, contre les orthodoxies religieuses et politiques, dans le Portugal de la dictature de Salazar.&lt;/p&gt; &lt;p&gt;Il enseigne ensuite en Allemagne, à Hambourg et Heidelberg, puis au Brésil, avant de s’installer en France en 1960, à Grenoble puis à Nice, où il passe l’essentiel de sa carrière. De ce long exil, il observe son pays avec distance et tendresse. Dans &lt;em&gt;Le Labyrinthe de la saudade&lt;/em&gt; (1978), il analyse la « mythologie » que les Portugais se font d’eux-mêmes : un peuple qui, après avoir dominé un empire, oscille entre le sentiment d’être exceptionnel et celui d’être insignifiant, et se réfugie dans la &lt;a href="https://fr.wikipedia.org/wiki/Saudade" title=" Wikipedia"&gt;&lt;em&gt;saudade&lt;/em&gt;&lt;/a&gt;, cette nostalgie de ce qui n’est plus ou n’a jamais été.&lt;/p&gt; &lt;p&gt;Grand lecteur de Fernando Pessoa, dont il est l’un des meilleurs interprètes, et de toute la littérature portugaise depuis Camões, il réfléchit aussi à l’Europe, à la place de la culture dans un monde dominé par la technique, et au sens de la fin des empires coloniaux. Conseiller culturel à Rome, administrateur de la Fondation Gulbenkian à Lisbonne, il reçoit le prix Pessoa en 1996. Considéré comme un sage par ses compatriotes, il meurt à Lisbonne en 2020, à quatre-vingt-dix-sept ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lourenco-mini.webp</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugaise</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Existentialisme</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">essayiste et philosophe portugais, penseur de l’identité portugaise et de la saudade.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P98">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -7429,6 +7429,354 @@
         </is>
       </c>
       <c r="P98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1">
+        <v>1883</v>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1957</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1883 – 1957</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Níkos KAZANTZÁKIS</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%ADkos_Kazantz%C3%A1kis" title=" Wikipedia"&gt;Níkos KAZANTZÁKIS&lt;/a&gt; est un écrivain et penseur grec, l’un des grands auteurs européens du XXe siècle. Né à Héraklion, en Crète, alors encore sous domination ottomane, il étudie le droit à Athènes puis la philosophie à Paris, où il suit les cours d’&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson" title=" Wikipedia"&gt;Henri Bergson&lt;/a&gt;. Il traduit Nietzsche, Bergson et Dante en grec, voyage dans toute l’Europe, en Russie, au Japon et en Chine, et passe sa vie à chercher une réponse aux grandes questions, à travers le christianisme, le bouddhisme, le nationalisme puis le communisme, sans jamais s’arrêter à aucune.&lt;/p&gt; &lt;p&gt;Dans son court traité &lt;em&gt;Ascèse&lt;/em&gt; (1927), il expose sa philosophie : le monde est traversé par un élan vital qui lutte pour se libérer de la matière et s’élever, et l’homme doit collaborer à cet effort, sans espoir de récompense ni certitude de salut. « Je n’espère rien. Je ne crains rien. Je suis libre » : cette phrase, gravée sur sa tombe à Héraklion, résume l’idéal d’un homme qui accepte l’angoisse et le combat comme le cœur même de la vie.&lt;/p&gt; &lt;p&gt;Ses romans ont rendu cette pensée célèbre dans le monde entier : &lt;a href="https://fr.wikipedia.org/wiki/Alexis_Zorba" title=" Wikipedia"&gt;&lt;em&gt;Alexis Zorba&lt;/em&gt;&lt;/a&gt; (1946) oppose un intellectuel timide à un homme qui vit pleinement chaque instant, et &lt;em&gt;La Dernière Tentation du Christ&lt;/em&gt; (1955) montre un Christ déchiré entre l’esprit et la chair, ce qui lui vaut d’être condamné par les Églises orthodoxe et catholique. Il compose aussi une immense &lt;em&gt;Odyssée&lt;/em&gt; de 33 333 vers, qui prolonge le poème d’Homère. Il meurt en Allemagne en 1957, après avoir manqué de peu le prix Nobel de littérature.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kazantzakis-mini.webp</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecque</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vitalisme ; Mysticisme</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et penseur grec, auteur d’Alexis Zorba et d’Ascèse, chercheur inquiet de la liberté et du sens.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1">
+        <v>1893</v>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1893 – 1970</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roman INGARDEN</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roman_Ingarden" title=" Wikipedia"&gt;Roman INGARDEN&lt;/a&gt; est un philosophe polonais, l’un des principaux représentants de la phénoménologie et le fondateur de l’esthétique phénoménologique. Né à Cracovie, il étudie à Göttingen auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Husserl" title=" Wikipedia"&gt;Edmund Husserl&lt;/a&gt;, sous la direction duquel il soutient en 1918 une thèse sur Bergson. Il y rencontre &lt;a href="https://fr.wikipedia.org/wiki/Edith_Stein" title=" Wikipedia"&gt;Edith Stein&lt;/a&gt;, avec qui il entretient pendant des années une correspondance et une amitié intellectuelle. Enseignant longtemps dans des lycées, il n’obtient une chaire à l’université de Lwów que dans les années 1930.&lt;/p&gt; &lt;p&gt;Fidèle à la méthode de Husserl, il refuse pourtant le tournant de son maître vers l’idéalisme, qui fait dépendre le monde de la conscience. Dans &lt;em&gt;La Controverse sur l’existence du monde&lt;/em&gt;, il défend une phénoménologie réaliste : le monde existe indépendamment de nous, et la philosophie doit décrire avec précision les différents modes d’être des choses. Il s’intéresse particulièrement aux objets « purement intentionnels », qui n’existent que par la conscience qui les vise.&lt;/p&gt; &lt;p&gt;L’œuvre d’art en est l’exemple : dans &lt;em&gt;L’Œuvre d’art littéraire&lt;/em&gt; (1931), il montre qu’un roman est composé de plusieurs couches, les sons des mots, leurs significations, les objets représentés et les aspects sous lesquels ils apparaissent. Il comporte aussi des « lieux d’indétermination » que le lecteur doit remplir par son imagination. Écarté de l’enseignement pendant plusieurs années par le régime communiste, qui lui reproche son « idéalisme », il continue d’écrire, notamment sur la responsabilité morale, qu’il enracine dans la structure même de l’être humain. Il meurt à Cracovie en 1970.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ingarden-mini.webp</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polonaise</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie ; Réalisme</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe polonais, élève de Husserl, phénoménologue réaliste et grand théoricien de l’œuvre d’art.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1">
+        <v>1907</v>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1977</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1907 – 1977</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan PATOČKA</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Pato%C4%8Dka" title=" Wikipedia"&gt;Jan PATOČKA&lt;/a&gt; est le plus grand philosophe tchèque du XXe siècle. Né à Turnov, il étudie à Prague, à Paris et à Fribourg-en-Brisgau, où il est l’un des derniers élèves d’Edmund Husserl et suit aussi les cours de Heidegger. Il consacre sa thèse d’habilitation au « monde naturel », le monde de l’expérience quotidienne, que les sciences tendent à faire oublier. Mais l’occupation nazie, puis le régime communiste, l’écartent presque constamment de l’université, et il doit enseigner dans des séminaires privés, chez lui ou chez ses élèves.&lt;/p&gt; &lt;p&gt;Pour Patočka, l’Europe est née d’une idée grecque : le « soin de l’âme », formulé par &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt;. Il s’agit de vivre dans la vérité et de s’interroger sans cesse sur le sens de son existence, plutôt que de se contenter d’une vie confortable et sans questions. Dans ses &lt;em&gt;Essais hérétiques sur la philosophie de l’histoire&lt;/em&gt; (1975), il décrit l’histoire comme ce moment où l’homme ose vivre sans certitude, dans une existence « ébranlée », et propose la « solidarité des ébranlés » : ceux qui ont compris la fragilité du sens peuvent s’unir contre la violence et le mensonge.&lt;/p&gt; &lt;p&gt;En 1977, il devient l’un des trois porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, qui réclame au régime le respect des droits de l’homme. Interrogé pendant des heures par la police, il meurt d’une hémorragie cérébrale le 13 mars 1977. Grand spécialiste de Comenius, dont il a édité les œuvres, il a formé dans la clandestinité toute une génération. Ses élèves et ses proches, comme Václav Havel, ont fait vivre sa pensée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/patocka-mini.webp</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tchèque</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe tchèque, phénoménologue, penseur du « soin de l’âme » et porte-parole de la Charte 77.</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1">
+        <v>1907</v>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1986</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1907 – 1986</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mircea ELIADE</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mircea_Eliade" title=" Wikipedia"&gt;Mircea ELIADE&lt;/a&gt; est un historien des religions, philosophe et romancier roumain, l’un des fondateurs de l’histoire moderne des religions. Né à Bucarest, il part à vingt et un ans pour l’Inde, où il étudie le sanskrit et le yoga à Calcutta, puis séjourne dans un ermitage de l’Himalaya. Revenu en Roumanie, il devient une figure brillante de la jeune génération. Mais dans les années 1930, il soutient publiquement la &lt;a href="https://fr.wikipedia.org/wiki/Garde_de_fer" title=" Wikipedia"&gt;Garde de fer&lt;/a&gt;, mouvement fasciste et antisémite, un engagement qui reste la part sombre de sa biographie.&lt;/p&gt; &lt;p&gt;Après la guerre, il s’installe à Paris, puis enseigne à partir de 1957 à l’université de Chicago. Dans &lt;em&gt;Le Sacré et le Profane&lt;/em&gt; (1957), il montre que l’homme religieux vit dans un monde où certains lieux, certains temps et certains objets sont chargés d’une puissance qui les distingue de l’ordinaire : une « hiérophanie », manifestation du &lt;a href="https://fr.wikipedia.org/wiki/Sacr%C3%A9" title=" Wikipedia"&gt;sacré&lt;/a&gt;. Le temple, la fête ou le rite rejoignent le « centre du monde » et le temps des origines.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Mythe de l’éternel retour&lt;/em&gt; (1949), il explique que les sociétés traditionnelles cherchent à abolir le temps historique en répétant sans cesse les gestes exemplaires des dieux et des ancêtres, alors que le monde moderne vit dans une histoire irréversible, source d’angoisse. Il voit dans les mythes, les symboles et les rêves une manière universelle de donner sens au monde. Il consacre aussi un grand livre au &lt;a href="https://fr.wikipedia.org/wiki/Yoga" title=" Wikipedia"&gt;yoga&lt;/a&gt;, fruit de son séjour en Inde. Romancier, il écrit enfin une grande &lt;em&gt;Histoire des croyances et des idées religieuses&lt;/em&gt;. Il meurt à Chicago en 1986.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eliade-mini.webp</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roumaine</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien des religions roumain, penseur du sacré, du mythe et de l’éternel retour.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1">
+        <v>1927</v>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2009</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1927 – 2009</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leszek KOŁAKOWSKI</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leszek_Ko%C5%82akowski" title=" Wikipedia"&gt;Leszek KOŁAKOWSKI&lt;/a&gt; est un philosophe et historien des idées polonais. Né à Radom, il adhère jeune au Parti communiste et devient, au début des années 1950, un philosophe marxiste en vue, auteur d’une thèse sur &lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza" title=" Wikipedia"&gt;Spinoza&lt;/a&gt;. Mais après la mort de Staline, il dénonce le dogmatisme du parti et devient l’une des voix du « révisionnisme » : il défend un marxisme humaniste, attaché à la liberté de pensée. Professeur à l’université de Varsovie, il est exclu du parti en 1966, puis chassé de son poste en 1968.&lt;/p&gt; &lt;p&gt;Il s’exile alors en Occident et enseigne à Oxford, où il passe le reste de sa vie. Son œuvre majeure, &lt;em&gt;Les Principaux Courants du marxisme&lt;/em&gt; (1976-1978), retrace en trois volumes l’histoire de cette pensée, de ses origines à son déclin. Il y soutient que le stalinisme n’était pas une trahison du marxisme mais l’une de ses conséquences possibles : la promesse d’une humanité parfaitement unifiée et réconciliée conduit, quand on veut la réaliser par la force, à la tyrannie.&lt;/p&gt; &lt;p&gt;Penseur de la religion, il s’intéresse aussi aux mystiques et aux « chrétiens sans Église » du XVIIe siècle, et défend l’idée que les questions religieuses, sur le mal, la mort ou le sens, ne disparaissent pas avec la modernité. Il soutient le syndicat &lt;a href="https://fr.wikipedia.org/wiki/Solidarno%C5%9B%C4%87" title=" Wikipedia"&gt;Solidarność&lt;/a&gt; dans les années 1980. Esprit ironique et sceptique, il se méfie de toutes les promesses de salut politique. Il reçoit en 2003 le prix Kluge, l’une des plus hautes distinctions en sciences humaines. Il meurt à Oxford en 2009, à quatre-vingt-un ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kolakowski-mini.webp</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polonaise</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe polonais, marxiste devenu critique du communisme, auteur des Principaux courants du marxisme.</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1">
+        <v>1936</v>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2011</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1936 – 2011</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Václav HAVEL</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A1clav_Havel" title=" Wikipedia"&gt;Václav HAVEL&lt;/a&gt; est un dramaturge, essayiste et homme d’État tchèque, l’une des grandes figures de la dissidence contre le communisme. Né à Prague dans une famille bourgeoise, il est écarté des études supérieures par le régime à cause de son origine. Il travaille au théâtre, où ses pièces absurdes et satiriques, comme &lt;em&gt;La Fête en plein air&lt;/em&gt; (1963), se moquent du langage creux de la bureaucratie. Après l’écrasement du &lt;a href="https://fr.wikipedia.org/wiki/Printemps_de_Prague" title=" Wikipedia"&gt;Printemps de Prague&lt;/a&gt; en 1968, ses œuvres sont interdites.&lt;/p&gt; &lt;p&gt;En 1977, il est l’un des fondateurs et porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, avec Jan Patočka, dont il se veut l’héritier. Dans &lt;em&gt;Le Pouvoir des sans-pouvoir&lt;/em&gt; (1978), il prend l’exemple d’un marchand de légumes qui place dans sa vitrine l’affiche « Prolétaires de tous les pays, unissez-vous ! » sans y croire, simplement pour être tranquille. Le régime ne tient que grâce à ces petits mensonges consentis par chacun. Refuser d’y participer, « vivre dans la vérité », est donc un acte politique : c’est le pouvoir de ceux qui n’en ont pas.&lt;/p&gt; &lt;p&gt;Emprisonné à plusieurs reprises, au total près de cinq ans, il écrit à sa femme des lettres publiées sous le titre &lt;em&gt;Lettres à Olga&lt;/em&gt;, méditation sur la responsabilité et l’espérance. Il devient en 1989 le chef de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_de_Velours" title=" Wikipedia"&gt;révolution de Velours&lt;/a&gt;, qui renverse pacifiquement le régime. Il est élu président de la Tchécoslovaquie, puis de la République tchèque jusqu’en 2003, en défendant une politique fondée sur la conscience et la responsabilité morale. Il meurt en 2011, à soixante-quinze ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/havel-mini.webp</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tchèque</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Existentialisme</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dramaturge, dissident et président tchèque, penseur de la « vie dans la vérité » face au totalitarisme.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P104">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -7777,6 +7777,470 @@
         </is>
       </c>
       <c r="P104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1">
+        <v>1866</v>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1952</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1866 – 1952</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benedetto CROCE</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Benedetto_Croce" title=" Wikipedia"&gt;Benedetto CROCE&lt;/a&gt; est un philosophe, historien et homme politique italien, la grande figure intellectuelle de l’Italie de la première moitié du XXe siècle. Né dans les Abruzzes dans une famille aisée, il perd ses parents et sa sœur dans un tremblement de terre en 1883, dont il réchappe lui-même blessé. Installé à Naples, il fonde en 1903 la revue &lt;em&gt;La Critica&lt;/em&gt;, qu’il dirige pendant plus de quarante ans, et développe une « philosophie de l’esprit » héritière de Hegel et de Vico.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Esthétique&lt;/em&gt; (1902), il définit l’art comme « intuition-expression » : l’artiste ne copie pas la réalité, il donne forme à une intuition singulière, et l’œuvre n’existe vraiment que dans cette expression. L’art est ainsi une forme de connaissance à part entière, distincte de la connaissance logique. Pour Croce, toute histoire est « histoire contemporaine », parce qu’elle répond aux questions du présent, et l’histoire humaine est au fond l’histoire de la liberté qui se conquiert.&lt;/p&gt; &lt;p&gt;D’abord ministre de l’Instruction publique, il rompt avec le &lt;a href="https://fr.wikipedia.org/wiki/Fascisme" title=" Wikipedia"&gt;fascisme&lt;/a&gt; et rédige en 1925 le &lt;em&gt;Manifeste des intellectuels antifascistes&lt;/em&gt;, en réponse à celui de Giovanni Gentile. Pendant tout le régime de Mussolini, il reste une voix libre, tolérée mais surveillée. Après la chute du fascisme, il refonde le Parti libéral italien et devient sénateur de la République. Il meurt à Naples en 1952. Son influence a été immense en Italie, jusque chez ses adversaires comme Antonio Gramsci. Sa longue amitié avec &lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile" title=" Wikipedia"&gt;Giovanni Gentile&lt;/a&gt;, son ancien collaborateur, s’était brisée sur la question du fascisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/croce-mini.webp</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idéalisme ; Libéralisme</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe italien, penseur de l’esthétique comme intuition et de l’histoire comme histoire de la liberté.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1976</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900 – 1976</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gilbert RYLE</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_Ryle" title=" Wikipedia"&gt;Gilbert RYLE&lt;/a&gt; est un philosophe britannique, l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_du_langage_ordinaire" title=" Wikipedia"&gt;philosophie du langage ordinaire&lt;/a&gt; qui domine Oxford au milieu du XXe siècle. Né à Brighton, il étudie et enseigne toute sa vie à Oxford, à part la Seconde Guerre mondiale, qu’il passe dans le renseignement. Il dirige pendant près de vingt-cinq ans la grande revue philosophique &lt;em&gt;Mind&lt;/em&gt; et forme toute une génération de philosophes.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;La Notion d’esprit&lt;/em&gt; (1949) s’attaque à ce qu’il appelle avec ironie le « mythe de Descartes », ou le « dogme du fantôme dans la machine » : l’idée que l’être humain serait composé d’un corps mécanique et d’un esprit invisible qui le piloterait de l’intérieur. Selon Ryle, cette conception repose sur une « erreur de catégorie ». C’est comme un visiteur qui, après avoir vu les collèges, les bibliothèques et les laboratoires d’Oxford, demanderait : « Mais où est l’université ? » L’université n’est pas un bâtiment de plus, c’est la manière dont tout cela est organisé.&lt;/p&gt; &lt;p&gt;De même, l’esprit n’est pas une chose cachée derrière nos actes : dire de quelqu’un qu’il est intelligent, c’est dire comment il agit et comment il agirait dans diverses situations. Ryle distingue aussi « savoir que », connaître des faits, et « savoir comment », posséder un savoir-faire. Ses analyses ont profondément influencé la philosophie de l’esprit, même si beaucoup jugent aujourd’hui son approche trop proche du béhaviorisme. Il a aussi consacré un livre à Platon, &lt;em&gt;Plato’s Progress&lt;/em&gt; (1966). Il meurt en 1976.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ryle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Béhaviorisme</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe britannique d’Oxford, critique du « fantôme dans la machine » cartésien.</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1">
+        <v>1919</v>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2006</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1919 – 2006</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peter STRAWSON</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Peter_Frederick_Strawson" title=" Wikipedia"&gt;Peter STRAWSON&lt;/a&gt; est un philosophe britannique de l’école d’Oxford, qui a renouvelé la métaphysique au sein de la philosophie analytique. Né à Londres, il étudie à Oxford, où il enseigne ensuite pendant toute sa carrière, jusqu’à occuper la chaire de métaphysique. Il se fait connaître en 1950 par un article célèbre, « De l’acte de référence », où il critique la théorie des descriptions de &lt;a href="https://fr.wikipedia.org/wiki/Bertrand_Russell" title=" Wikipedia"&gt;Bertrand Russell&lt;/a&gt;. Il est anobli en 1977 et devient Sir Peter Strawson.&lt;/p&gt; &lt;p&gt;Pour Russell, la phrase « L’actuel roi de France est chauve » est simplement fausse, puisqu’il n’y a pas de roi de France. Strawson répond que ce ne sont pas les phrases mais les personnes qui, en les utilisant, font référence ou affirment quelque chose : ici, la question de la vérité ne se pose même pas, car la phrase présuppose l’existence d’un roi. Il défend ainsi une analyse du langage tel qu’on l’utilise réellement, contre la seule logique formelle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Individus&lt;/em&gt; (1959), il propose une « métaphysique descriptive » : au lieu d’inventer une image nouvelle du monde, elle décrit la structure de pensée que nous partageons tous, où les corps et les personnes sont les éléments de base. Dans &lt;em&gt;Les Limites du sens&lt;/em&gt; (1966), il relit &lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant" title=" Wikipedia"&gt;Kant&lt;/a&gt; dans cet esprit. Dans « Liberté et ressentiment » (1962), il montre que nos réactions morales, comme la gratitude ou l’indignation, font partie de notre nature et ne dépendent pas de la question du déterminisme. Il meurt à Londres en 2006 ; son fils Galen Strawson est lui aussi philosophe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/strawson-mini.webp</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; langage</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe britannique d’Oxford, fondateur d’une « métaphysique descriptive » des cadres de notre pensée.</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1">
+        <v>1922</v>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1974</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1922 – 1974</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imre LAKATOS</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Imre_Lakatos" title=" Wikipedia"&gt;Imre LAKATOS&lt;/a&gt; est un philosophe des mathématiques et des sciences d’origine hongroise. Né à Debrecen dans une famille juive, il échappe à la Shoah, où meurent sa mère et sa grand-mère, en changeant de nom ; il prend celui de Lakatos. Militant communiste après la guerre, il est pourtant emprisonné pendant trois ans sous le régime stalinien. Après l’insurrection de Budapest en 1956, il s’enfuit en Angleterre, où il étudie à Cambridge, puis enseigne à la London School of Economics, auprès de &lt;a href="https://fr.wikipedia.org/wiki/Karl_Popper" title=" Wikipedia"&gt;Karl Popper&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Preuves et réfutations&lt;/em&gt;, il montre, sous la forme d’un dialogue entre un professeur et ses élèves, que les mathématiques ne progressent pas par une simple accumulation de vérités démontrées, mais par une succession de conjectures, de contre-exemples et de corrections des définitions. Même les mathématiques ont une histoire faite d’essais et d’erreurs.&lt;/p&gt; &lt;p&gt;En philosophie des sciences, il cherche une voie entre Popper, pour qui une théorie doit être abandonnée dès qu’elle est réfutée, et Thomas Kuhn, qui décrit les révolutions scientifiques comme des changements presque irrationnels de paradigme. Selon Lakatos, les scientifiques travaillent dans des « &lt;a href="https://fr.wikipedia.org/wiki/Programme_de_recherche" title=" Wikipedia"&gt;programmes de recherche&lt;/a&gt; » : un noyau dur de principes que l’on protège, entouré d’hypothèses que l’on ajuste. Un programme est « progressif » s’il prédit des faits nouveaux, « dégénérescent » s’il ne fait que se défendre. Son séminaire de la London School of Economics attire les meilleurs philosophes des sciences, et son débat avec son ami et adversaire Paul Feyerabend est resté célèbre. Il meurt subitement à Londres en 1974, à cinquante et un ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lakatos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hongroise</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; logique</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsificationnisme ; Rationalisme</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe des sciences hongrois, penseur des « programmes de recherche » et de la logique de la découverte mathématique.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1">
+        <v>1924</v>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1994</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1924 – 1994</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paul FEYERABEND</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Feyerabend" title=" Wikipedia"&gt;Paul FEYERABEND&lt;/a&gt; est un philosophe des sciences autrichien, l’un des plus provocateurs du XXe siècle. Né à Vienne, il est grièvement blessé pendant la Seconde Guerre mondiale, alors qu’il sert dans l’armée allemande, et en garde un handicap toute sa vie. Il étudie la physique, l’histoire et le théâtre, puis la philosophie auprès de Karl Popper à Londres. Il enseigne ensuite à Bristol, puis pendant de longues années à Berkeley, en Californie, et à Zurich.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Contre_la_m%C3%A9thode" title=" Wikipedia"&gt;&lt;em&gt;Contre la méthode&lt;/em&gt;&lt;/a&gt; (1975), il soutient qu’il n’existe pas de méthode scientifique unique et universelle. L’étude de l’histoire des sciences, et notamment de Galilée, montre que les grands savants ont souvent progressé en violant les règles qu’on prétend leur imposer : en défendant des idées contre les faits établis, en usant de propagande et de rhétorique. D’où sa formule provocante : en matière de méthode, « tout est bon » (&lt;em&gt;anything goes&lt;/em&gt;). Il appelle cette position un « anarchisme épistémologique ».&lt;/p&gt; &lt;p&gt;Feyerabend ne rejette pas la science, mais son statut de vérité officielle. Dans une société libre, dit-il, la science devrait être séparée de l’État comme l’Église l’a été, et les citoyens devraient pouvoir juger eux-mêmes des savoirs, y compris des médecines traditionnelles ou des savoirs non occidentaux. Ses positions ont suscité de vives polémiques. Avec son ami Imre Lakatos, il projetait d’écrire un livre à deux voix, « pour et contre la méthode ». Son autobiographie, &lt;em&gt;Tuer le temps&lt;/em&gt;, paraît après sa mort, survenue en Suisse en 1994.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/feyerabend-mini.webp</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autrichienne</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relativisme</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe des sciences autrichien, auteur de Contre la méthode, défenseur d’un « anarchisme épistémologique ».</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1">
+        <v>1929</v>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1929 – 2025</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alasdair MACINTYRE</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alasdair_MacIntyre" title=" Wikipedia"&gt;Alasdair MACINTYRE&lt;/a&gt; est un philosophe écossais, l’un des penseurs de la morale les plus influents de la fin du XXe siècle. Né à Glasgow en 1929, il est d’abord marxiste et proche de la nouvelle gauche britannique, avant de s’éloigner du marxisme. Il s’installe aux États-Unis en 1970 et enseigne dans plusieurs universités, notamment à l’université Notre-Dame, dans l’Indiana. Converti au catholicisme dans les années 1980, il se rattache à la tradition d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt; et de Thomas d’Aquin.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Après la vertu&lt;/em&gt; (1981) part d’un constat : les débats moraux d’aujourd’hui, sur la guerre, l’avortement ou la justice, sont interminables, car chacun utilise des fragments de traditions anciennes dont on a perdu le cadre commun. Les Lumières ont voulu fonder la morale sur la seule raison individuelle ; cet échec a conduit à l’« émotivisme », l’idée que les jugements moraux ne sont que l’expression de préférences personnelles.&lt;/p&gt; &lt;p&gt;Contre cette impasse, MacIntyre propose de revenir à l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89thique_de_la_vertu" title=" Wikipedia"&gt;éthique des vertus&lt;/a&gt; : la vie bonne se comprend comme un récit unifié, inscrit dans des « pratiques » partagées, comme un métier ou un art, et dans une tradition vivante, au sein d’une communauté. Les vertus sont les qualités qui nous permettent d’atteindre les biens propres à ces pratiques. &lt;em&gt;Après la vertu&lt;/em&gt; se termine par un appel à construire des communautés locales où les vertus puissent survivre, en attendant « un autre saint Benoît ». Il prolonge cette réflexion dans &lt;em&gt;Quelle justice ? Quelle rationalité ?&lt;/em&gt; (1988). Il meurt dans l’Indiana en mai 2025, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/macintyre-mini.webp</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éthique de la vertu ; Communautarisme</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe écossais, auteur d’Après la vertu, grand rénovateur de l’éthique aristotélicienne des vertus.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1">
+        <v>1932</v>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2016</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1932 – 2016</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umberto ECO</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Umberto_Eco" title=" Wikipedia"&gt;Umberto ECO&lt;/a&gt; est un philosophe, sémioticien et romancier italien, l’un des intellectuels les plus célèbres de son temps. Né à Alexandrie, dans le Piémont, il consacre sa thèse à l’esthétique de &lt;a href="https://fr.wikipedia.org/wiki/Thomas_d%27Aquin" title=" Wikipedia"&gt;Thomas d’Aquin&lt;/a&gt; et devient un grand connaisseur du Moyen Âge. Il travaille d’abord à la télévision italienne, puis enseigne à l’université de Bologne, où il occupe la première chaire de &lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9miotique" title=" Wikipedia"&gt;sémiotique&lt;/a&gt; en Italie, la science des signes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Œuvre ouverte&lt;/em&gt; (1962), il montre que les œuvres d’art modernes, de Joyce à la musique contemporaine, ne délivrent pas un message unique : elles laissent au lecteur ou à l’auditeur une part de liberté pour construire leur sens. Mais dans &lt;em&gt;Les Limites de l’interprétation&lt;/em&gt; (1990), il met en garde contre l’excès inverse : un texte autorise de nombreuses lectures, mais pas n’importe lesquelles. Il étudie aussi la culture de masse, la publicité, les bandes dessinées et les romans populaires avec le même sérieux que les classiques.&lt;/p&gt; &lt;p&gt;Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/Le_Nom_de_la_rose_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Le Nom de la rose&lt;/em&gt;&lt;/a&gt; (1980), enquête policière dans une abbaye du XIVe siècle, est un succès mondial ; il y met en scène la peur du rire et le pouvoir des livres. Il publie ensuite d’autres romans et de nombreux essais. Dans un texte célèbre, il décrit aussi les traits de ce qu’il appelle le « fascisme éternel », toujours prêt à renaître. Il écrit aussi sur &lt;em&gt;La Recherche de la langue parfaite&lt;/em&gt; (1994) dans la culture européenne. Grand bibliophile, il possédait une bibliothèque de plusieurs dizaines de milliers de volumes. Il meurt à Milan en 2016.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eco-mini.webp</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; langage</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structuralisme ; Herméneutique</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sémioticien, philosophe et romancier italien, auteur de L’Œuvre ouverte et du Nom de la rose.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1">
+        <v>1933</v>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1933 – 2023</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antonio NEGRI</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Toni_Negri" title=" Wikipedia"&gt;Antonio NEGRI&lt;/a&gt; (dit Toni Negri) est un philosophe italien, figure majeure de la pensée marxiste radicale de la fin du XXe siècle. Né à Padoue, professeur de philosophie politique dans l’université de cette ville, il est dans les années 1960 et 1970 l’un des animateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;, un courant qui part des luttes concrètes des ouvriers d’usine plutôt que des directives des partis, puis du mouvement de l’Autonomie ouvrière.&lt;/p&gt; &lt;p&gt;En 1979, il est arrêté et accusé d’être le cerveau des Brigades rouges, accusation dont il est finalement lavé, mais il est condamné pour d’autres faits liés à la violence politique de ces années. Élu député en 1983, il profite de son immunité pour s’exiler en France, où il enseigne pendant quatorze ans, notamment à l’université Paris-VIII et au Collège international de philosophie, et se rapproche de Deleuze et de Guattari. Il rentre en Italie en 1997 pour purger sa peine. Parallèlement, il écrit sur Spinoza, dont il fait le penseur d’une puissance collective et créatrice.&lt;/p&gt; &lt;p&gt;Avec le philosophe américain Michael Hardt, il publie en 2000 &lt;em&gt;Empire&lt;/em&gt;, qui décrit la mondialisation comme une nouvelle forme de souveraineté sans centre ni frontières, réseau des États, des firmes et des institutions internationales. Face à elle se dresse la « multitude », l’ensemble des singularités qui produisent la richesse commune et peuvent s’organiser sans chef. Ce livre devient une référence du mouvement altermondialiste ; ils le prolongent dans &lt;em&gt;Multitude&lt;/em&gt; (2004) et &lt;em&gt;Commonwealth&lt;/em&gt; (2009). Il meurt à Villejuif, près de Paris, en 2023, à quatre-vingt-dix ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/negri-mini.webp</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe italien de l’opéraïsme, coauteur d’Empire, penseur de la « multitude ».</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P112">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -4309,8 +4309,10 @@
       <c r="K33" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>122</v>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme ; Hassidisme</t>
+        </is>
       </c>
       <c r="M33" s="2" t="s">
         <v>292</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -3049,8 +3049,10 @@
       <c r="K5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>35</v>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Féminisme ; Lumières</t>
+        </is>
       </c>
       <c r="M5" s="2" t="s">
         <v>36</v>
@@ -3595,8 +3597,10 @@
       <c r="K17" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>150</v>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Darwinisme social</t>
+        </is>
       </c>
       <c r="M17" s="2" t="s">
         <v>151</v>
@@ -8229,7 +8233,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme</t>
+          <t xml:space="preserve">Marxisme ; Opéraïsme</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -8245,6 +8249,62 @@
       <c r="P112">
         <v>2</v>
       </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1">
+        <v>1931</v>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931 – 2023</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mario TRONTI</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mario_Tronti" title=" Wikipedia"&gt;Mario TRONTI&lt;/a&gt; est un philosophe et homme politique italien, l’un des fondateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;. Né à Rome en 1931, il milite dans les années 1950 au Parti communiste italien et se forme à la philosophie auprès de Galvano Della Volpe, un marxiste qui s’opposait à la lecture humaniste de Gramsci. En 1961, il participe avec Raniero Panzieri à la fondation de la revue &lt;em&gt;Quaderni rossi&lt;/em&gt;, puis fonde en 1964 sa propre revue, &lt;em&gt;Classe operaia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Ouvriers et capital&lt;/em&gt; (1966) est le texte fondateur du courant. Il y propose une « révolution copernicienne » dans le marxisme : on a toujours pensé que le capital menait le jeu et que les ouvriers réagissaient ; il faut renverser la perspective et voir que ce sont les luttes ouvrières qui obligent le capital à se transformer, à innover, à mécaniser, à se réorganiser. La classe ouvrière n’est pas un simple rouage du système, mais la force active de l’histoire. Son but n’est pas d’être reconnue comme force de travail, mais de refuser le travail salarié lui-même. Ces idées inspirent la « nouvelle gauche » italienne et les grèves de l’« automne chaud » de 1969.&lt;/p&gt; &lt;p&gt;Pourtant, Tronti fait le choix inverse de ses camarades : il revient au Parti communiste, et défend dans les années 1970 l’« autonomie du politique », la nécessité pour les ouvriers de conquérir les institutions plutôt que de les fuir. Professeur de philosophie politique à l’université de Sienne pendant trente ans, il est deux fois sénateur. Il revient sur cette histoire dans &lt;em&gt;Nous, opéraïstes&lt;/em&gt; (2009). Il meurt en 2023, à quatre-vingt-douze ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tronti-mini.webp</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opéraïsme ; Marxisme</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe italien, fondateur de l’opéraïsme, penseur de la « révolution copernicienne » des luttes ouvrières.</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P113"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2992,8 +2992,10 @@
       <c r="F4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>20</v>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Karl Leonhard Reinhold , Everything Philosophers " par See Hear Say Learn</t>
+        </is>
       </c>
       <c r="H4" s="9" t="s">
         <v>21</v>
@@ -3496,8 +3498,10 @@
       <c r="F15" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>128</v>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">charles secretan par VIS PHILO</t>
+        </is>
       </c>
       <c r="H15" s="10" t="s">
         <v>129</v>
@@ -3765,8 +3769,10 @@
       <c r="F21" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>182</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thomas masaryk par Slavier</t>
+        </is>
       </c>
       <c r="H21" s="2" t="s">
         <v>183</v>
@@ -5273,8 +5279,10 @@
       <c r="F54" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>464</v>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"GÜNTHER ANDERS : L'obsolescence de l'homme" par Parole de Philosophe</t>
+        </is>
       </c>
       <c r="H54" s="9" t="s">
         <v>465</v>
@@ -5904,8 +5912,10 @@
       <c r="F68" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>578</v>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le consequentialisme par Noé Jacomet</t>
+        </is>
       </c>
       <c r="H68" s="2" t="s">
         <v>579</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -6449,8 +6449,11 @@
       <c r="D80" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="E80" s="11" t="s">
-        <v>676</v>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bryan_Magee"  title=" Wikipedia"&gt;Bryan MAGEE&lt;/a&gt; était un philosophe britannique , auteur, homme politique et célèbre vulgarisateur de la philosophie. Né à Londres dans une famille modeste, il étudie à Oxford puis à Yale grâce à une bourse Rhodes. Député travailliste (1974-1983) pour Leyton avant de rejoindre le SDP, il est surtout connu pour ses émissions BBC : Men of Ideas (1978) et The Great Philosophers (1987), où il interroge des géants comme Popper, Wittgenstein ou Habermas avec clarté et profondeur. &lt;/p&gt; &lt;p&gt; Il  excelle dans la philosophie de Schopenhauer, dont il publie une étude majeure (The Philosophy of Schopenhauer, 1983, révisée 1997), soulignant son influence sur Wagner, Wittgenstein et le bouddhisme.  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" "agnostisme par Wikipedia"&gt; Agnostique méthodique &lt;/a&gt; inspiré de Huxley, il rejette le relativisme au nom d'un progrès critique permanent : les croyances doivent être révisables pour avancer vers la vérité, sans dogmatisme religieux ni &lt;a href="https://fr.wikipedia.org/wiki/Linguistique"  title=" "linguistique par Wikipedia"&gt; linguisticisme analytique &lt;/a&gt; étroit.  &lt;/p&gt; &lt;p&gt; Critique acerbe de la philosophie analytique post-Wittgenstein, qu'il accuse de stérilité théorique au profit d'un "thérapeutisme" linguistique, il défend une philosophie existentielle confrontant la mort et le sens de la vie. Dans Confessions of a Philosopher (1997), il retrace son cheminement intellectuel, mêlant autobiographie, politique et métaphysique, pour une pensée libératrice et humaniste . &lt;/p&gt; &lt;p&gt; Auteur prolifique (Wagner, Popper, poésie, romans), il rend la philosophie accessible sans la trivialiser, influençant des générations par ses entretiens télévisés disponibles sur YouTube. Son legs : une quête insatiable de sens face à la finitude, alliant rigueur et passion pour Wagner ou la démocratie.&lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F80" s="7" t="s">
         <v>677</v>
@@ -6470,6 +6473,11 @@
       </c>
       <c r="L80" s="2" t="s">
         <v>73</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe, homme politique et vulgarisateur britannique, spécialiste de Schopenhauer.</t>
+        </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3083,8 +3083,10 @@
       <c r="D6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>40</v>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Owen"  title=" Wikipedia"&gt;Robert OWEN&lt;/a&gt; était un industriel gallois devenu philosophe social, figure majeure du &lt;a href="https://laviedesidees.fr/Robert-Owen-pere-du-socialisme-britannique" style="color:#88A1E9" title="Robert Owen, père du socialisme britannique ? par idées de la vie"&gt;"socialisme utopique"&lt;/a&gt; et l’un des pères du mouvement coopératif et de l’urbanisme social. Il défend une thèse matérialiste du caractère humain : pour lui, le caractère n’est pas inné mais entièrement façonné par les "circonstances" physiques, morales et sociales auxquelles l’individu est exposé dès l’enfance. Il en conclut que l’on ne doit ni louer ni blâmer moralement les individus, mais transformer les institutions et l’environnement pour produire des caractères meilleurs, ce qui fait de l’éducation et de l’organisation sociale les leviers principaux de la réforme morale. &lt;/p&gt; &lt;p&gt; À &lt;a href="https://www.youtube.com/watch?v=QHWn6aPxKtQ" title="New Lanark: Robert Owen's Utopianism and the Latter Day Saints par Centre Place"&gt;New Lanark&lt;/a&gt;, il crée des écoles modèles, dont l’"Institute for the Formation of Character", qui proposent une éducation gratuite, non répressive, axée sur le jeu, la musique et la formation morale plutôt que sur la simple préparation au travail. À partir de 1817, il promeut des communautés coopératives auto-suffisantes, comme New Harmony aux États-Unis, conçues comme des petites villes idéales où la propriété est collective et où l’organisation rationnelle du travail permet de supprimer la misère et la concurrence&lt;/p&gt; &lt;p&gt;  Il critique vigoureusement les religions instituées, auxquelles il reproche d’entretenir le sectarisme et la division, et propose une "religion rationnelle" fondée sur la bienveillance, la coopération et l’éducation. Il devient un  &lt;a href="https://www.youtube.com/watch?v=VmDDCsdQNAY"  title="The Reformer Who Dreamed Of A Utopia | Robert Owen par History's forgotten people"&gt;inspirateur important &lt;/a&gt; du mouvement ouvrier britannique, soutient les premières lois sur le travail des enfants, participe aux débuts du syndicalisme et contribue à développer le mouvement coopératif, dont il est souvent présenté comme un fondateur. &lt;/p&gt; &lt;p&gt; Son texte majeur est &lt;a href="https://www.youtube.com/watch?v=rY9ic8AC2VU"  title=""A New View of Society and Other Writings" By Robert Owen par Novelzilla"&gt;"A New View of Society"&lt;/a&gt;, où il expose sa théorie de la formation du caractère et ses projets de réforme sociale globale, complété plus tard par "The Book of the New Moral World". Marx et Engels le rangeront parmi les "socialistes utopiques" : ils critiquent son manque d’analyse du capitalisme, mais reconnaissent en lui un précurseur dont les expériences concrètes ont nourri le socialisme et l’idée moderne de réforme par les institutions. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F6" s="7" t="s">
         <v>41</v>
@@ -3308,8 +3310,11 @@
       <c r="D11" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>89</v>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Stuart_Mill"  style="color:#6A142A"  title=" Wikipedia"&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href="https://www.youtube.com/watch?v=kDfp2afvj28" style="color:#88A1E9" title="John Stuart Mill - Synthèse par El Khader"&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». Son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href="https://www.youtube.com/watch?v=yCDOVcvNYpY" title=" L'utilitarisme par Culture Philo"&gt;"  l’Utilitarisme"&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href="https://www.youtube.com/watch?v=DVG_FL8jKe0" title="John Stuart Mill - De La Liberté par Let's make liberalism great again"&gt;" De la liberté"&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href="https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s" title="JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques"&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;&lt;audio controls title="John Stuart Mill par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F11" s="7" t="s">
         <v>90</v>
@@ -3445,8 +3450,14 @@
       <c r="D14" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>116</v>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%B8ren_Kierkegaard" title=" Wikipedia"&gt;Soren KIERKEGAARD&lt;/a&gt; était un philosophe et théologien danois, célèbre pour ses idées sur &lt;a href="https://www.youtube.com/watch?v=davjaNvPfLA&amp;ab_channel=Philo-Man" title="Kierkegaard: existe t'il des degrès de liberté par Philo-Man"&gt; l'existentialisme chrétien&lt;/a&gt;. Il a souvent écrit sous des pseudonymes, ce qui a permis à ses œuvres de présenter différentes perspectives et points de vue sur des questions philosophiques et religieuses.&lt;/p&gt; &lt;p&gt; Il met l'accent sur l'importance de la responsabilité individuelle, de la liberté et du choix dans la vie humaine. Selon lui, chaque individu est confronté à &lt;a href="https://www.youtube.com/watch?v=-VPfHoQAGfc"  title="Comment l’Angoisse Conduit à la Grandeur | Søren Kierkegaard par Philosophie et spiritisme"&gt; une angoisse existentielle&lt;/a&gt; inhérente à l'existence humaine, et il est nécessaire de prendre des décisions authentiques pour trouver un sens à la vie. &lt;/p&gt;
+&lt;p&gt; Il a mit en avant le paradoxe de la foi en cherchant à concilier la foi chrétienne avec la raison et la philosophie, soutenant que la foi authentique nécessite un saut au-delà de la rationalité humaine et a critiqué les formes institutionnelles de la religion, affirmant que la véritable religiosité découle d'une relation personnelle et passionnée avec Dieu.&lt;/p&gt;
+&lt;p&gt;Il a aussi développé le concept du  &lt;a href="https://www.youtube.com/watch?v=slWXX3JWaGg&amp;ab_channel=PhiloToutou"  title="l'angoisse est le vertige de la liberté par Philo Toutou"&gt; "paradoxe de l'individu"&lt;/a&gt; décrivant la tension entre l'universalité et la singularité de chaque personne et soulignant que chaque individu est un être unique, avec ses propres expériences, sentiments et pensées, et en même temps un être partageant des caractéristiques universelles avec les autres. &lt;/p&gt;
+&lt;p&gt; Il a développé le concept de la  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2013_num_111_4_8321" title="la constitution de l'hétique par persée"&gt; "suspension éthique"&lt;/a&gt; soulignant l'importance de l'engagement éthique dans la vie de chaque individu et a soutenu que la moralité véritable découle d'une compréhension profonde de soi et d'une relation authentique avec Dieu, plutôt que de simples règles ou normes sociales. Pour lui, la vie éthique implique de faire des choix courageux et responsables, même dans l'incertitude et l'angoisse.&lt;/p&gt;
+  &lt;audio controls title="Introduction à la philosophe de Kierkegaard par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-22.11.2022-ITEMA_23204156-2022C3372E0494-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F14" s="7" t="s">
         <v>117</v>
@@ -3538,8 +3549,10 @@
       <c r="D16" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>137</v>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Bain_(philosophe)"   title=" Wikipedia"&gt;Alexander BAIN&lt;/a&gt; était un philosophe utilitariste écossais issus d'une famille modeste de tisserand où son père lui transmet le goût du travail méticuleux, tandis que sa mère, pieuse et austère, l’initie aux rigueurs de la &lt;a href="https://www.olivierabel.fr/2022/09/24/la-morale-de-calvin/"  title="La morale de Calvin par olivierabel"&gt;morale calviniste&lt;/a&gt; mais il ne se contente pas des certitudes religieuses. Il dévore les livres, s’interroge sur le fonctionnement de l’esprit humain, et rêve de comprendre les lois invisibles qui régissent la pensée.&lt;/p&gt; &lt;p&gt; Il rencontre John Stuart Mill, qui devient son ami et mentor. Ensemble, ils discutent de l’associationnisme, cette théorie selon laquelle toutes les idées complexes se forment par la combinaison d’impressions simples. Bain y voit une clé pour déchiffrer l’énigme de la conscience. &lt;/p&gt; &lt;p&gt; Dans les années 1850, il publie ses œuvres majeures, "Les Sens et l’Intelligence" et "Les Émotions et la Volonté". Il y développe une vision  &lt;a href="https://www.youtube.com/shorts/TkMO99tn4Uc" title="Alexander BAIN par Timeless philosopher"&gt;scientifique de l’esprit&lt;/a&gt;, influencée par les découvertes en physiologie. Pour lui, chaque pensée, chaque émotion, a une base matérielle dans le cerveau. Il  fonde la première revue de psychologie scientifique &lt;a href="https://www.jstor.org/stable/41071221?seq=1" title="Revue des périodiques étrangers par JSTOR"&gt;"Mind"&lt;/a&gt; en 1876. Il y défend une approche expérimentale de l’esprit, préfigurant les travaux de William James et de Freud. Pourtant, dans l’intimité, le philosophe reste hanté par une question : si tout n’est que mécanisme, où est la place de la liberté humaine ? Peut-être dans cette capacité de l’esprit à s’auto-modifier, à créer de nouvelles associations d’idées… &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F16" s="7" t="s">
         <v>138</v>
@@ -3582,8 +3595,12 @@
       <c r="D17" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>145</v>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herbert_Spencer"  title=" Wikipedia"&gt;Herbert SPENCER&lt;/a&gt; était un philosophe, sociologue et anthropologue britanique et un parfait exemple d'autodidacte. Ingénieur de formation, il devient journaliste et se consacre entièrement à l'écriture. Son œuvre est immense, culminant avec son Système de &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1904_num_11_41_1823" title=" La philosophie d'Herbert Spencer  par Persée"&gt; philosophie synthétique&lt;/a&gt;, une série de volumes visant à unifier toutes les connaissances humaines (biologie, psychologie, sociologie, éthique) sous un seul principe directeur : l'évolution. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre (et la plus controversée) est son application de la théorie de l'évolution à la société humaine, une idée souvent résumée par l'expression qu'il a popularisée : la "survie du plus apte". Il a développé une théorie de l'évolution avant même la publication de "L'Origine des espèces de Charles Darwin". Cependant, alors que Darwin se concentrait sur le mécanisme biologique de la sélection naturelle, Spencer voyait &lt;a href="https://www.youtube.com/watch?v=pBbr4mBO3kA" style="color:#88A1E9" title=" 
+Social Darwinism | Herbert Spencer par Sociologylearners"&gt;l'évolution&lt;/a&gt;  comme une loi universelle s'appliquant à tous les phénomènes : l'univers, les organismes biologiques, l'esprit humain, les cultures et les sociétés progressent tous du simple au complexe, de l'homogène à l'hétérogène. &lt;/p&gt; &lt;p&gt; Il  a appliqué le principe de la "survie du plus apte" aux sociétés humaines. Il estimait que la compétition entre les individus et entre les sociétés était un moteur naturel et bénéfique du progrès. Elle permettait d'éliminer les "inaptes" et de favoriser les "plus aptes" (les plus talentueux, les plus travailleurs, les plus adaptés), conduisant ainsi à l'amélioration de l'espèce humaine.&lt;/p&gt; &lt;p&gt;  Il était un farouche partisan du libéralisme intégral et de l'État minimal (laissez-faire). Il s'opposait catégoriquement à toute intervention de l'État dans la vie sociale, comme l'aide aux pauvres, les lois sociales, l'éducation publique ou la santé publique. Pour lui, ces interventions artificielles perturbaient le processus naturel de sélection en maintenant en vie les "inaptes", ce qui affaiblissait la société à long terme. Il n'a pas simplement "appliqué" &lt;a href="https://www.youtube.com/watch?v=MfsLeQOZfEA"  title=" Le DARWINISME SOCIAL en 6 minutes !  par Culture Philo"&gt;Darwin aux sociétés&lt;/a&gt;. Il avait sa propre théorie évolutionniste, et c'est Darwin qui a ensuite emprunté l'expression "survie du plus apte" à Spencer. &lt;/p&gt; &lt;p&gt; Il était un penseur complexe qui a tenté de bâtir un système philosophique total. Bien que sa réputation soit aujourd'hui entachée par les usages politiques terribles qui ont été faits de ses idées, son influence sur la pensée moderne est indéniable. Il reste une figure essentielle pour comprendre l'optimisme scientiste et la foi dans le progrès qui caractérisent le XIXe siècle, ainsi que les dérives possibles lorsqu'on tente d'appliquer des lois naturelles au domaine social et moral. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F17" s="7" t="s">
         <v>146</v>
@@ -3852,8 +3869,10 @@
       <c r="D23" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>198</v>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Alexander" title=" Wikipedia"&gt;Samuel ALEXANDER&lt;/a&gt; était un philosophe britannique d’origine australienne, figure majeure de l’émergentisme britannique et du réalisme métaphysique. Sa pensée repose sur une ontologie moniste où l’espace-temps constitue la substance fondamentale de toute réalité : matière, vie, esprit et même divinité émergent à partir de cette matrice spatio-temporelle. Alexander rejette l’idéalisme (hégélien ou britannique) ainsi que le dualisme cartésien, et propose un naturalisme réaliste dans lequel les catégories (substance, causalité, universalité) ne sont pas des structures de l’entendement (comme chez Kant) mais des déterminations concrètes de l’être lui-même. &lt;/p&gt; &lt;p&gt; Le cœur de sa philosophie est la notion d’« émergence » : chaque niveau supérieur (matière → vie → esprit → valeurs → divinité) dépend des niveaux inférieurs sans être réductible à eux, car il possède des qualités nouvelles irréductibles. Cette « évolution émergente » est animée par un nisus (élan créateur interne) qui pousse la réalité vers des formes de complexité et de valeur toujours plus riches, sans recourir à un Dieu transcendant créateur. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=RJddJGpuwJA"  title="Samuel Alexander par See Hear Say Learn"&gt;"Son œuvre maîtresse&lt;/a&gt;, Space, Time, and Deity (1920), issue de ses conférences Gifford, expose ce système hiérarchique et panenthéiste : la divinité n’est pas un être séparé mais la qualité émergente ultime de l’esprit cosmique, intégrant les valeurs de vérité, beauté, bonté et liberté. Bien qu’il partage avec Bergson l’idée d’un élan créateur, Alexander s’oppose à la « durée pure » bergsonienne et insiste sur la continuité et la rationalité descriptive de la métaphysique comme science des structures les plus universelles du réel. &lt;/p&gt; &lt;p&gt; Il a exercé une influence notable sur des penseurs comme Whitehead et a suscité des critiques de Russell, tout en restant une référence centrale pour les débats sur l’émergence, le réalisme et la relation entre science et métaphysique. Sa philosophie offre une voie originale entre naturalisme scientifique et spiritualité immanente, où la valeur et le sens émergent naturellement de l’organisation croissante de l’espace-temps en formes de vie et de conscience. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F23" s="7" t="s">
         <v>199</v>
@@ -3901,8 +3920,11 @@
       <c r="D24" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>206</v>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis"  title=" Wikipedia"&gt;Jacob OSSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; Il se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="9"/>
@@ -4034,8 +4056,11 @@
       <c r="D27" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>233</v>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Santayana"   title=" Wikipedia"&gt;George SANTAYANA&lt;/a&gt; était un philosophe hispano-américain, né à Madrid et formé à Harvard, qui occupe une place singulière dans la philosophie du XXᵉ siècle par son alliance d’un naturalisme matérialiste rigoureux et d’une sensibilité littéraire, esthétique et religieuse. &lt;/p&gt; &lt;p&gt; Il défend un naturalisme radical : pour lui, tout ce qui existe relève de la matière et de ses configurations ; la conscience, la raison, la culture sont des phénomènes émergents de l’activité biologique et sociale. Il refuse cependant de réduire la vie de l’esprit à un simple épiphénomène sans intérêt : il prend au sérieux l’art, la religion, la morale comme réalités à expliquer, sans pour autant leur accorder un statut ontologique indépendant de la matière. - &lt;a href="https://www.youtube.com/watch?v=86qYBc2BA6k" title="the philosophy of george santayana par let’s talk philosophy"&gt;" Cette position &lt;/a&gt;  lui permet de critiquer à la fois l’idéalisme allemand et un matérialisme scientiste étroit, en proposant un matérialisme humaniste. &lt;/p&gt; &lt;p&gt; Sur le plan épistémologique, il est un sceptique profond : il soutient qu’aucune proposition n’est « évidente » en soi et que la croyance en l’existence du monde extérieur (y compris celle de soi) ne repose pas sur une démonstration absolue, mais sur des besoins vitaux et des habitudes d’action. Dans Scepticism and Animal Faith (1923), il développe l’idée d’une « foi animale » : des convictions inévitables, nécessaires à l’action, que le scepticisme ne peut entièrement dissoudre, et qu’il faut assumer lucidement plutôt que de prétendre les fonder rationnellement. Il résume cette attitude en disant que le scepticisme est la « chasteté de l’intellect », à préserver jusqu’à ce qu’il puisse être échangé contre une fidélité mature. &lt;/p&gt; &lt;p&gt; Pour articuler son naturalisme et la richesse de la vie spirituelle, il élabore, dans The Realms of Being (1927–1940), une ontologie en quatre « règnes » : l’essence (formes et possibilités intelligibles), la matière (le monde physique, seul véritablement existant), la vérité (ensemble des propositions vraies) et l’esprit (la conscience comme activité émergente). Cette architecture lui permet de garder une place  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_11_5754_t1_0593_0000_2" title="the essential wisdom of santayana par persée"&gt;à la vie intérieure, &lt;/a&gt; à l’art et à la religion sans renoncer au matérialisme, en traitant les essences comme objets de pensée plutôt que comme entités séparées. Il accorde une importance centrale à l’esthétique et à une lecture naturaliste de la religion et de la morale. Dans The Sense of Beauty et La Vie de la raison, il analyse la beauté comme « plaisir objectivé » et montre comment religion, art et éthique s’enracinent dans la nature humaine et ses besoins, tout en remplissant des fonctions symboliques et existentielles précieuses. Son influence s’étend à la philosophie américaine, à l’esthétique, et à certaines formes de réalisme critique, même si son style littéraire et son indépendance d’esprit le rendent parfois difficile à classer dans une école précise. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F27" s="7" t="s">
         <v>234</v>
@@ -4168,8 +4193,11 @@
       <c r="D30" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>260</v>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Edward_Moore"  title=" Wikipedia"&gt;George Edward MOORE&lt;/a&gt; était un philosophe anglais considéré comme l'un des fondateurs de la &lt;a href="https://www.youtube.com/watch?v=SPm8S3lmML8"  title=" G.E. Moore : « Preuve d'un monde extérieur » par Simon Cushing "&gt;philosophie analytique &lt;/a&gt; aux côtés de Bertrand Russell et Ludwig Wittgenstein. Il a enseigné toute sa carrière à l'université de Cambridge, où il a influencé des générations d'étudiants par sa clarté analytique et sa défense du sens commun. Ses travaux portent principalement sur l'éthique, l'épistémologie et la métaphysique, critiquant l'idéalisme dominant de son époque. &lt;/p&gt; &lt;p&gt; Il rejette les systèmes grandioses pour analyser minutieusement les concepts philosophiques, favorisant la clarté et le sens commun contre les excès métaphysiques. Il défend l'existence du monde externe via des &lt;a href="https://www.youtube.com/watch?v=p4fFl-J0Vks" title=" Le non-naturalisme de G.E. Moore (argumentation par questions ouvertes et intuitionnisme : métaét...r par Philosophy Vibe"&gt;arguments simples&lt;/a&gt;, comme pointer du doigt des objets dans "A Proof of the External World" (1939), et affirme des vérités évidentes comme "Voici une main humaine" dans "A Defence of Common Sense" (1925). En épistémologie, il combat le scepticisme en soulignant que les certitudes ordinaires résistent aux doutes philosophiques. &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Principia Ethica (1903), introduit l'argument de la "question ouverte" contre le naturalisme moral: définir le bien par plaisir ou désir laisse ouverte la question "Est-ce bon?". Le bien est une propriété non naturelle, appréhendée par intuition morale, intrinsèquement désirable en soi, comme la beauté des états de conscience. Cela inspire la méta-éthique et critique  &lt;a href="https://www.persee.fr/doc/enphi_0986-1653_1999_num_50_1_16015"  title="G. E. Moore et la critique de l'utilitarisme évolutionniste de Spencer par Persée"&gt;l'utilitarisme réducteur&lt;/a&gt;, bien qu'il nuance son intuitionnisme pour éviter les formes classiques. Viennent ensuite des Œuvres comme - Philosophical Studies (1922): recueil d'essais sur perception et connaissance ainsi que - Some Main Problems of Philosophy (1953, posthume): conférences sur le réalisme. &lt;/p&gt; 
+​</t>
+        </is>
       </c>
       <c r="F30" s="7" t="s">
         <v>261</v>
@@ -4395,8 +4423,11 @@
       <c r="D35" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="E35" s="11" t="s">
-        <v>304</v>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Otto_Weininger"  title=" Wikipedia"&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href="https://www.youtube.com/watch?v=wetIerJEucU" title=" Otto Weininger Le génie Maudit par Aliouca"&gt;maison de Beethoven à Vienne&lt;/a&gt;. Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href="https://www.youtube.com/watch?v=aFZpRoBlMQI" title=" Otto Weininger qui haîssait les femmes par Voyage Endormis"&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href="https://www.youtube.com/watch?v=vMfEJQVv3VM" title=" Otto Weininger Le mytère du féminin par Philosopheasy en Français"&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits "féminins" vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère "féminine" décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title="Otto Weininger et la question du genie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F35" s="7" t="s">
         <v>305</v>
@@ -4866,8 +4897,10 @@
       <c r="D45" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="E45" s="10" t="s">
-        <v>390</v>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski"   title=" Wikipedia"&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href="https://www.youtube.com/watch?v=Vvt7ns_jZvY"  title="The logic of reality  par TroughtLab"&gt;la logique et des mathématiques&lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique "vraie" modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F45" s="7" t="s">
         <v>391</v>
@@ -4910,8 +4943,11 @@
       <c r="D46" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="E46" s="17" t="s">
-        <v>398</v>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Gramsci"  title=" Wikipedia"&gt;Antonio GRAMSCI&lt;/a&gt;  était un philosophe marxiste italien et a aussi été un homme politique, un journaliste et l’un des &lt;a href="https://www.youtube.com/watch?v=Q8s8r43ANbQ"  title="L’hégémonie culturelle selon Antonio GRAMSCI  par France Culture"&gt;fondateurs du Parti communiste italien&lt;/a&gt;. Son apport le plus connu est la notion d’hégémonie culturelle. Pour lui, une classe dominante ne gouverne pas seulement par la force, mais aussi en imposant ses valeurs, ses idées et son sens commun dans la société civile. &lt;/p&gt; &lt;p&gt; Il a réfléchi à la manière dont une force politique peut contester ce pouvoir. Il distingue la « guerre de mouvement », plus directe, et la « guerre de position », plus lente, qui passe par les syndicats, les journaux, l’éducation et la culture. &lt;/p&gt; &lt;p&gt; Il est devenu  &lt;a href="https://www.youtube.com/watch?v=K3vf4DSL_GE"  title="Comprendre  Antonio GRAMSCI  par Politikon"&gt;une référence &lt;/a&gt; bien au-delà du marxisme strict, parce que ses idées servent à analyser les médias, l’école, la culture et les rapports de pouvoir dans les sociétés modernes. Ses Cahiers de prison ont joué un rôle central dans cette postérité intellectuelle. &lt;/p&gt; &lt;audio controls title="Qui est Antonio GRAMSCI par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.02.2017-ITEMA_21240143-2017C12410E0055-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F46" s="7" t="s">
         <v>399</v>
@@ -4997,8 +5033,10 @@
       <c r="D48" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>415</v>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_Murphy"  title=" Wikipedia"&gt;Joseph MURPHY&lt;/a&gt;  était un auteur et prédicateur irlandais, figure majeure du courant de la Nouvelle Pensée et de la littérature de développement personnel spirituel. Il a écrit une trentaine de livres sur la pensée, l’autosuggestion, la prière et la prospérité,  diffusés à des millions de lecteurs. &lt;/p&gt; &lt;p&gt; Pour lui, la réalité extérieure est largement façonnée par nos pensées, nos images mentales et nos croyances profondes. Il distingue un esprit conscient et un subconscient présenté comme un réservoir quasi illimité de puissance créatrice, qui enregistre nos croyances et les manifeste dans la santé, les relations, l’argent. La prière, la visualisation et l’autosuggestion sont des moyens privilégiés pour "programmer" ce subconscient avec des idées positives (foi, réussite, santé), ce qui, selon lui, finit par se traduire dans les faits. &lt;/p&gt; &lt;p&gt; Il cherche à harmoniser la métaphysique de la  &lt;a href="https://www.youtube.com/watch?v=SuwToXC2jFE"  title="Cesse de Chercher et Tout te Trouvera | Joseph MURPHY par Livre Interdit"&gt;Nouvelle Pensée, &lt;/a&gt; les Écritures bibliques, le symbolisme religieux et la psychologie moderne, en lisant aussi bien les textes orientaux que les auteurs de la Science chrétienne, de la Science de l’esprit ou de la Divine Science. &lt;/p&gt; &lt;p&gt; Dans son ouvrage qui fût un best-seller "Le pouvoir de votre subconscient", il expose une vision métaphysique du mental et de la prière affirmative. Il affirme que l’on peut utiliser ce mécanisme pour la guérison physique, la résolution de problèmes, la création d’opportunités et il présente de nombreux cas d’"applications". Il développe une méthode d’autosuggestion simple : répéter des phrases positives, imaginer la situation souhaitée comme déjà réalisée, se détendre profondément et remettre le résultat au subconscient, qui "sait" comment opérer. &lt;/p&gt; &lt;p&gt; Même si son discours ressemble souvent à du développement personnel psychologique, la trame de fond est  &lt;a href="https://www.youtube.com/watch?v=Flmk5Jtxfdg" title="LA MAGIE DE LA FOI | Joseph Murphy  par Audiolivres"&gt;profondément religieuse &lt;/a&gt; et mystique. Il interprète les textes bibliques de manière symbolique, comme des descriptions de lois mentales et spirituelles. Il s’inspire des philosophies orientales, voyant dans la convergence des traditions la confirmation d’une même loi spirituelle. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F48" s="7" t="s">
         <v>416</v>
@@ -5041,8 +5079,11 @@
       <c r="D49" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="E49" s="11" t="s">
-        <v>424</v>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Hayek"  title=" Wikipedia"&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme&lt;/a&gt;, il en fait un fondement de sa critique du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(politique)"  title=" Constructivisme  par Wikipedia"&gt;"constructivisme rationnel" :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'"ordre spontané" des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique. &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une "prétention au savoir" illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href="https://www.youtube.com/watch?v=TiGv4YcFieQ"  title="La route de la servitude  par Capsio"&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F49" s="7" t="s">
         <v>425</v>
@@ -5224,8 +5265,12 @@
       <c r="D53" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="E53" s="11" t="s">
-        <v>454</v>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Karl_Popper"  title=" Wikipedia"&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href="https://www.youtube.com/watch?v=AENUk4f6Ftg" title="K Popper la logique et la découverte scientifique par Philosophie Analytique"&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href="https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9" title="Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté"&gt; critère de falsifiabilité&lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href="https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde" title="sciences et  pseudosciences par François Jourde"&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href="https://www.youtube.com/watch?v=WheeYYBtSMA" title="la société ouverte et ses ennemis par GORVS S"&gt;  "La Société Ouverte et ses ennemis ",&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de "société ouverte" où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href="https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur" title="Le paradoxe de la tolérance par le Précepteur"&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; 
+  &lt;audio controls title="Introduction à la philosophe de Karl Popper par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F53" s="7" t="s">
         <v>455</v>
@@ -5273,8 +5318,10 @@
       <c r="D54" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>462</v>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders"  title=" Wikipedia"&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href="https://www.youtube.com/watch?v=r4eq7EoRtTQ"  title=" Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope"&gt;"l'obsolescence de l'homme"&lt;/a&gt;. Selon lui, l'homme moderne est   &lt;a href="https://books.openedition.org/pur/52513?lang=fr" title="La notion de « supraliminaire » chez Günther Anders par OpenEdition"&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression "prométhée honteux"  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href="https://www.youtube.com/watch?v=8xIiiYQJymQ"  title="L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée"&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href="https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde" title="l'être jetable Günther Anders par La vie des idées"&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title="Avoir raison avec... Günther Anders par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F54" s="7" t="s">
         <v>463</v>
@@ -5324,8 +5371,11 @@
       <c r="D55" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>469</v>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="9"/>
@@ -5505,8 +5555,11 @@
       <c r="D59" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="E59" s="11" t="s">
-        <v>502</v>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Titus_Burckhardt"  title=" Wikipedia"&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)" title=" Le Pérennialisme par Wikipedia"&gt;pérennialisme&lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href="https://www.youtube.com/watch?v=Thok9so1Zik" title=" Introdustion aux doctrines ésothériques de l’Islam par Red Draco"&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href="https://www.youtube.com/watch?v=Mx6E82Mt-v4" title=" Etre conservateur par Agar Hagar"&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F59" s="7" t="s">
         <v>503</v>
@@ -5642,8 +5695,11 @@
       <c r="D62" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="E62" s="11" t="s">
-        <v>526</v>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren" title=" Wikipedia"&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une "perplexité" ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il développe une "éthique de la perplexité" : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href="https://www.youtube.com/watch?v=L3sJ7AvOT08"  title=" José Luis Aranguren  par Lecturas Fragmentadas"&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique "progressiste" puis laïc engagé, il valorise la dissidence intellectuelle et une "justice sociale" cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F62" s="7" t="s">
         <v>527</v>
@@ -5774,8 +5830,11 @@
       <c r="D65" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="E65" s="11" t="s">
-        <v>551</v>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emil_Cioran" title=" Wikipedia"&gt;Emil CIORAN&lt;/a&gt;    était un  philosophe roumain d'expression française, incarne un agnosticisme viscéral teinté de scepticisme radical, loin des certitudes religieuses ou métaphysiques. Élevé dans une famille orthodoxe en Transylvanie, il rompt tôt avec la foi pour explorer le doute existentiel dans des œuvres comme Au cœur des ténèbres ou Précis de décomposition. Sa position religieuse est qualifiée de "quête agnostique" : ni athéisme militant ni théisme, mais une suspension perpétuelle du jugement face à un Dieu absent ou silencieux. &lt;/p&gt; &lt;p&gt;  Contrairement aux origines classiques de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il en fait une expérience intime de la "déchirure d'exister", où le doute devient négation corrosive de toute vérité absolue. Influencé par le scepticisme antique et Nietzsche, il radicalise le doute en "exaspération de la conscience", menant à une lucidité thanatique – conscience aiguë de la vanité humaine et du néant. Écrire devient pour lui un acte de démolition des systèmes, refusant toute synthèse dogmatique.&lt;/p&gt; &lt;p&gt;    Il  flirte avec des accents gnostiques ou dualistes dans Le Mauvais Démiurge, accusant un créateur défaillant d'un monde absurde, tout en niant toute transcendance accessible. Son agnosticisme poétique, "solaire" et fiévreux, naît d'une &lt;a href="https://www.youtube.com/watch?v=1mT-aprSfv0"  title="CIORAN: le génie qui a détruit l’illusion du bonheurt par Voyages endormis"&gt;désillusion lucide &lt;/a&gt; plutôt que d'une raison froide : il vit l'incertitude comme un &lt;a href="https://www.youtube.com/watch?v=8mDwa3swkW0"  title="Vivre c’est mourir doucement par Le Dolmen"&gt;"épuisement du discours", &lt;/a&gt;  privilégiant l'authenticité du désespoir à la quête de réponses. &lt;/p&gt; &lt;p&gt;    Son legs philosophique résonne avec l'agnosticisme moderne par ce refus des absolus, influençant penseurs comme Muguerza dans une "perplexité" partagée. À Paris depuis 1947, il incarne le sceptique cosmopolite, torturé par l'insoluble, qui préfère le vertige du non-savoir à l'illusion de la connaissance. &lt;/p&gt;         &lt;audio controls title="Emil Cioran, un philosophe-hurleur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24200-05.08.2023-ITEMA_23453909-2023C51135E0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F65" s="7" t="s">
         <v>552</v>
@@ -6088,8 +6147,11 @@
       <c r="D72" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="E72" s="11" t="s">
-        <v>610</v>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Warnock"  title=" Wikipedia"&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href="https://fr.wikipedia.org/wiki/Existentialisme"  title=" l’existentialisme Wikipedia"&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href="https://en.wikipedia.org/wiki/Ethics_Since_1900"  title=" Ethics Since 1900 Wikipedia"&gt;Ethics Since 1900&lt;/a&gt;, elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de "statementing", qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  
+</t>
+        </is>
       </c>
       <c r="F72" s="7" t="s">
         <v>611</v>
@@ -6274,8 +6336,11 @@
       <c r="D76" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>643</v>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ivan_Illich"  title=" Wikipedia"&gt;Ivan ILLICH&lt;/a&gt;  était un philosophe, théologien et critique social austro-américain d'origine multiculturelle, connu pour sa radicalité dans la dénonciation des institutions modernes qu'il juge aliénantes et contre-productives, prônant une société conviviale fondée sur &lt;a href="https://ecologica.education/2023/11/08/ivan-illich-penseur-de-lecologie-politique/" title="Ivan Illich, penseur de l’écologie politique par Ecologica"&gt;l'autonomie humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; En 1961, au Mexique, il fonde à Cuernavaca le CIDOC (Centre interculturel de documentation), un laboratoire expérimental attirant des milliers d'intellectuels pour des séminaires interdisciplinaires sur éducation, développement et religion ; fermé en 1976 pour éviter son institutionnalisation, ce lieu forge sa méthode provocatrice post-Mai 68. &lt;/p&gt; &lt;p&gt; Il héorise la contre-productivité : tout processus industriel (éducation, médecine, transport) passe d'amplificateur d'autonomie à générateur de dépendance et d'inégalités, inversant sa finalité. Pour lui, les racines chrétiennes sont perverties : Incarnation ouvre à l'amour interpersonnel, mais modernité institutionnalise en monopoles salvifiques, ni accomplissement ni négation du christianisme, mais sa dégénérescence.&lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  &lt;a href="https://www.youtube.com/watch?v=axeVcD8emQY"  title="IVAN ILLICH - Une société sans école par 1000 idées de culture generale"&gt;"Une société sans école" &lt;/a&gt; paru en 1971 : l'école, monopole étatique, désapprend plus qu'elle n'enseigne ; propose "réseaux d'apprentissage" pair-à-pair, libres et gratuits, pour restaurer l'éducation vernaculaire. - "La Convivialité" paru en 1973  : définit l'outil convivial (ex. : bicyclette) comme accessible, autonome et égalitaire ; introduit le "monopole radical" où la technique surpuissante exclut les alternatives et infantilise. - "Némésis médicale paru en 1975, Énergie et équité"  en 1973 et "Le Chômage créateur" en 1977 : démontre que santé, vitesse, emploi deviennent contre-productifs au-delà d'un seuil.&lt;/p&gt;    &lt;audio controls title="Ivan Illich : "L'école enseigne à l'enfant qu'il doit être inévitablement classé par un bureaucrate" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-02.05.2017-ITEMA_21310924-2012C3372E0981-NET_B3E76531-3403-4CED-9218-298FB5C06B8B_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F76" s="7" t="s">
         <v>644</v>
@@ -6451,7 +6516,7 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bryan_Magee"  title=" Wikipedia"&gt;Bryan MAGEE&lt;/a&gt; était un philosophe britannique , auteur, homme politique et célèbre vulgarisateur de la philosophie. Né à Londres dans une famille modeste, il étudie à Oxford puis à Yale grâce à une bourse Rhodes. Député travailliste (1974-1983) pour Leyton avant de rejoindre le SDP, il est surtout connu pour ses émissions BBC : Men of Ideas (1978) et The Great Philosophers (1987), où il interroge des géants comme Popper, Wittgenstein ou Habermas avec clarté et profondeur. &lt;/p&gt; &lt;p&gt; Il  excelle dans la philosophie de Schopenhauer, dont il publie une étude majeure (The Philosophy of Schopenhauer, 1983, révisée 1997), soulignant son influence sur Wagner, Wittgenstein et le bouddhisme.  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" "agnostisme par Wikipedia"&gt; Agnostique méthodique &lt;/a&gt; inspiré de Huxley, il rejette le relativisme au nom d'un progrès critique permanent : les croyances doivent être révisables pour avancer vers la vérité, sans dogmatisme religieux ni &lt;a href="https://fr.wikipedia.org/wiki/Linguistique"  title=" "linguistique par Wikipedia"&gt; linguisticisme analytique &lt;/a&gt; étroit.  &lt;/p&gt; &lt;p&gt; Critique acerbe de la philosophie analytique post-Wittgenstein, qu'il accuse de stérilité théorique au profit d'un "thérapeutisme" linguistique, il défend une philosophie existentielle confrontant la mort et le sens de la vie. Dans Confessions of a Philosopher (1997), il retrace son cheminement intellectuel, mêlant autobiographie, politique et métaphysique, pour une pensée libératrice et humaniste . &lt;/p&gt; &lt;p&gt; Auteur prolifique (Wagner, Popper, poésie, romans), il rend la philosophie accessible sans la trivialiser, influençant des générations par ses entretiens télévisés disponibles sur YouTube. Son legs : une quête insatiable de sens face à la finitude, alliant rigueur et passion pour Wagner ou la démocratie.&lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bryan_Magee"  title=" Wikipedia"&gt;Bryan MAGEE&lt;/a&gt; était un philosophe britannique, auteur, homme politique et célèbre vulgarisateur de la philosophie. Né à Londres dans une famille modeste, il étudie à Oxford puis à Yale grâce à une bourse Rhodes. Député travailliste (1974-1983) pour Leyton avant de rejoindre le SDP, il est surtout connu pour ses émissions BBC : Men of Ideas (1978) et The Great Philosophers (1987), où il interroge des géants comme Popper, Wittgenstein ou Habermas avec clarté et profondeur. &lt;/p&gt; &lt;p&gt; Il  excelle dans la philosophie de Schopenhauer, dont il publie une étude majeure (The Philosophy of Schopenhauer, 1983, révisée 1997), soulignant son influence sur Wagner, Wittgenstein et le bouddhisme.  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" "agnostisme par Wikipedia"&gt; Agnostique méthodique &lt;/a&gt; inspiré de Huxley, il rejette le relativisme au nom d'un progrès critique permanent : les croyances doivent être révisables pour avancer vers la vérité, sans dogmatisme religieux ni &lt;a href="https://fr.wikipedia.org/wiki/Linguistique"  title=" "linguistique par Wikipedia"&gt; linguisticisme analytique &lt;/a&gt; étroit.  &lt;/p&gt; &lt;p&gt; Critique acerbe de la philosophie analytique post-Wittgenstein, qu'il accuse de stérilité théorique au profit d'un "thérapeutisme" linguistique, il défend une philosophie existentielle confrontant la mort et le sens de la vie. Dans Confessions of a Philosopher (1997), il retrace son cheminement intellectuel, mêlant autobiographie, politique et métaphysique, pour une pensée libératrice et humaniste. &lt;/p&gt; &lt;p&gt; Auteur prolifique (Wagner, Popper, poésie, romans), il rend la philosophie accessible sans la trivialiser, influençant des générations par ses entretiens télévisés disponibles sur YouTube. Son legs : une quête insatiable de sens face à la finitude, alliant rigueur et passion pour Wagner ou la démocratie.&lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -6591,8 +6656,11 @@
       <c r="D83" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="E83" s="11" t="s">
-        <v>696</v>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raoul_Vaneigem"  title=" Wikipedia"&gt;Raoul VANEIGEM&lt;/a&gt; était un écrivain et philosophe belge, figure centrale de l’Internationale situationniste aux côtés de Guy Debord, surtout connu pour son &lt;a href="https://www.youtube.com/watch?v=sG-sy80_hJ4"  title="traité du savoir vivre par sortir du capitalisme"&gt;Traité de savoir-vivre à l’usage des jeunes générations &lt;/a&gt;  (1967), texte-phare qui a inspiré Mai 68. &lt;/p&gt; &lt;p&gt; Il dénonce ce qu’il appelle la « société du spectacle », c’est-à-dire un ordre social où la vie authentique est remplacée par des images, des rôles et des consommations passives. Pour lui, le capitalisme moderne produit un « nihilisme passif » : les individus acceptent l’absurde et la survie au lieu de vivre pleinement. Sa philosophie vise donc à réveiller le désir et la créativité contre la résignation et le conformisme. &lt;/p&gt; &lt;p&gt; Contrairement aux révolutions purement politiques, il prône une &lt;a href="https://le-carnet-et-les-instants.net/raoul-vaneigem-entretien/"  title="vaneigem toujours en quête du bonheur"&gt;révolution de la vie quotidienne, &lt;/a&gt; centrée sur la jouissance, la créativité et la gratuité. Son mot d’ordre célèbre, « Vivre sans temps mort, jouir sans entraves », résume un hédonisme radical qui refuse le sacrifice au nom du travail, du profit ou de l’autorité. La vraie révolution commence par la façon dont chacun organise son existence, ses plaisirs et ses relations. &lt;/p&gt; &lt;p&gt; Tout être humain porte une tendance fondamentale à s’autoréaliser comme créateur conscient de sa vie. Un « sujet radical » est celui qui prend conscience de cette pulsion et la relie à un projet collectif d’émancipation. Sa pensée articule ainsi l’individu et le collectif : la liberté personnelle n’est complète que si elle s’inscrit dans une lutte contre les structures qui aliènent (travail contraint, marchandisation, pouvoir hiérarchique). &lt;/p&gt; &lt;p&gt; Il s’inspire autant de Lautréamont, Fourier ou Hölderlin que du marxisme et de l’anarchisme pour penser une société autogérée et non marchande. Il défend l’autogestion politique et économique comme forme concrète d’une communauté où décident ceux qui vivent et créent, et non les détenteurs du capital ou de l’État. Son hédonisme n’est pas un simple plaisir égoïste, mais une éthique de la joie comme moteur de révolte et de construction d’un autre monde. &lt;/p&gt; &lt;/p&gt; Spécialiste du Moyen Âge et des mouvements hérétiques, il voit dans ces résistances au christianisme officiel les signes d’une civilisation future fondée sur la créativité et la gratuité plutôt que sur l’aliénation et le profit. Dans ses nombreux ouvrages, il explore l’histoire des révoltes, des plaisirs interdits et des communautés libres pour nourrir une pensée de l’insurrection permanente. Sa philosophie reste ainsi une invitation à  &lt;a href="https://www.youtube.com/watch?v=TQWvjqrHdiQ&amp;list=RDTQWvjqrHdiQ"  title="la vie s’écoule de vaneigem par sirbon83"&gt;refuser la survie &lt;/a&gt; imposée et à inventer, jour après jour, une vie digne d’être vécue, &lt;/p&gt;  
+</t>
+        </is>
       </c>
       <c r="F83" s="7" t="s">
         <v>697</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -6662,11 +6662,15 @@
 </t>
         </is>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>697</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>698</v>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yYJewNBDWFA</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Présentation de Raoul Vaneigem" par Michel Onfray</t>
+        </is>
       </c>
       <c r="H83" s="10" t="s">
         <v>699</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3332,8 +3332,10 @@
       <c r="K11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>93</v>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utilitarisme ; Conséquentialisme ; Phénoménisme</t>
+        </is>
       </c>
       <c r="M11" s="2" t="s">
         <v>94</v>
@@ -3475,8 +3477,10 @@
       <c r="K14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>122</v>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme ; Irrationalisme ; Absurde</t>
+        </is>
       </c>
       <c r="M14" s="2" t="s">
         <v>123</v>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme ; Darwinisme social</t>
+          <t xml:space="preserve">Positivisme ; Darwinisme social ; Minarchisme ; Volontarisme</t>
         </is>
       </c>
       <c r="M17" s="2" t="s">
@@ -3984,8 +3988,10 @@
       <c r="K25" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>220</v>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthroposophie ; Théosophisme</t>
+        </is>
       </c>
       <c r="M25" s="2" t="s">
         <v>221</v>
@@ -4165,8 +4171,10 @@
       <c r="K29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>255</v>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Positivisme Logique ; Athéisme</t>
+        </is>
       </c>
       <c r="M29" s="2" t="s">
         <v>256</v>
@@ -4215,8 +4223,10 @@
       <c r="K30" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>265</v>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Intuitionnisme ; Cognitivisme ; Particularisme</t>
+        </is>
       </c>
       <c r="M30" s="2" t="s">
         <v>266</v>
@@ -4918,8 +4928,10 @@
       <c r="K45" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>73</v>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Méréologie</t>
+        </is>
       </c>
       <c r="M45" s="2" t="s">
         <v>394</v>
@@ -5101,8 +5113,10 @@
       <c r="K49" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L49" s="2" t="s">
-        <v>54</v>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Individualisme méthodologique</t>
+        </is>
       </c>
       <c r="M49" s="2" t="s">
         <v>428</v>
@@ -5288,8 +5302,10 @@
       <c r="K53" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L53" s="2" t="s">
-        <v>457</v>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsificationnisme ; Dualisme ; Individualisme méthodologique ; Réalisme scientifique</t>
+        </is>
       </c>
       <c r="M53" s="2" t="s">
         <v>458</v>
@@ -5761,8 +5777,10 @@
       <c r="K63" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>538</v>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme Logique ; Analytique ; Phénoménisme</t>
+        </is>
       </c>
       <c r="M63" s="14" t="s">
         <v>539</v>
@@ -5852,8 +5870,10 @@
       <c r="K65" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>555</v>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pessimisme ; Existentialisme ; Absurde</t>
+        </is>
       </c>
       <c r="M65" s="2" t="s">
         <v>556</v>
@@ -7627,7 +7647,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie ; Réalisme</t>
+          <t xml:space="preserve">Phénoménologie ; Réalisme ; Ontologie</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -7743,7 +7763,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herméneutique</t>
+          <t xml:space="preserve">Herméneutique ; Chamanisme</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -8415,6 +8415,179 @@
         </is>
       </c>
       <c r="P113"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1">
+        <v>1903</v>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1983</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1903 – 1983</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joan ROBINSON</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joan_Robinson" title=" Wikipedia"&gt;Joan ROBINSON&lt;/a&gt; est une économiste britannique, l’une des grandes figures de l’école de Cambridge et du &lt;a href="https://fr.wikipedia.org/wiki/Keyn%C3%A9sianisme" title=" Wikipedia"&gt;keynésianisme&lt;/a&gt;. Née en 1903 dans une famille de la bonne société anglaise, elle étudie l’économie à Cambridge, où elle fera toute sa carrière. En 1933, son &lt;em&gt;Économie de la concurrence imparfaite&lt;/em&gt; montre que la plupart des marchés ne ressemblent pas au modèle de la concurrence parfaite : des entreprises en situation de monopole ou d’oligopole fixent leurs prix, et l’acheteur unique d’un travail, qu’elle appelle « monopsone », peut imposer de bas salaires.&lt;/p&gt; &lt;p&gt;Au début des années 1930, elle appartient au « Cirque », le petit groupe de jeunes économistes qui discute avec &lt;a href="https://fr.wikipedia.org/wiki/John_Maynard_Keynes" title=" Wikipedia"&gt;Keynes&lt;/a&gt; les idées de sa future &lt;em&gt;Théorie générale&lt;/em&gt; (1936). Elle devient ensuite l’une de ses interprètes les plus radicales : pour elle, l’économie se déroule dans un temps historique et incertain, où les crises et le chômage ne sont pas des accidents, mais des traits du capitalisme. Avec Piero Sraffa et Nicholas Kaldor, elle fonde ce qu’on appellera le post-keynésianisme, et dans &lt;em&gt;L’Accumulation du capital&lt;/em&gt; (1956) elle étudie la croissance et la répartition des revenus entre salaires et profits.&lt;/p&gt; &lt;p&gt;Dans les années 1950 et 1960, elle mène la « controverse des deux Cambridge » contre Paul Samuelson et Robert Solow, du Cambridge américain : elle conteste qu’on puisse mesurer le « capital » comme une quantité simple, ce qui ébranle la théorie dominante de la répartition. Samuelson finit par lui donner raison sur le plan logique. Grande voyageuse, elle admire un temps la Chine de Mao et la Corée du Nord, ce qui lui est reproché. Souvent citée pour le prix Nobel, elle ne l’a jamais reçu. Elle meurt à Cambridge en 1983.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/robinson-mini.webp</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keynésianisme</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">économiste britannique de Cambridge, proche de Keynes et figure du post-keynésianisme.</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P114"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1">
+        <v>1887</v>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1975</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887 – 1975</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julian HUXLEY</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julian_Huxley" title=" Wikipedia"&gt;Julian HUXLEY&lt;/a&gt; est un biologiste, écrivain et humaniste britannique, petit-fils de Thomas Huxley, le défenseur de Darwin, et frère du romancier Aldous Huxley. Spécialiste du comportement animal, il étudie les parades nuptiales des oiseaux et contribue à fonder l’éthologie. Son livre &lt;em&gt;Evolution : The Modern Synthesis&lt;/em&gt; (1942) donne son nom à la « synthèse moderne », qui réunit la théorie de Darwin et la génétique.&lt;/p&gt; &lt;p&gt;Grand vulgarisateur, il est en 1946 le premier directeur général de l’UNESCO, à laquelle il veut donner pour philosophie un « humanisme scientifique » mondial ; il participe aussi, en 1961, à la fondation du WWF. Dans un essai de 1957, il forge le mot &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;« transhumanisme »&lt;/a&gt; : l’espèce humaine, devenue consciente de l’évolution, peut se dépasser elle-même, « en restant homme, mais en se transcendant », en réalisant de nouvelles possibilités de sa nature grâce à la science. Pour lui, l’évolution est désormais entre nos mains et doit être conduite de façon consciente et responsable.&lt;/p&gt; &lt;p&gt;Cette confiance dans la maîtrise de l’évolution a sa face sombre. Huxley a longtemps défendu l’eugénisme, l’amélioration de l’espèce par le contrôle de la reproduction, et présida la Société britannique d’eugénisme de 1959 à 1962, même s’il dénonça les théories raciales des nazis dès les années 1930. Il meurt à Londres en 1975. Le mouvement transhumaniste de la fin du XXe siècle reprendra son mot, en l’appliquant aux technologies de l’amélioration humaine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/julianhuxley-mini.webp</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transhumanisme</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">biologiste britannique, premier directeur de l’UNESCO, inventeur du mot « transhumanisme ».</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P115"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1">
+        <v>1801</v>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1852</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1801 – 1852</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vincenzo GIOBERTI</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincenzo_Gioberti" title=" Wikipedia"&gt;Vincenzo GIOBERTI&lt;/a&gt; est un philosophe, prêtre et homme politique italien. Né à Turin en 1801, ordonné prêtre en 1825, il devient chapelain de la cour du roi de Sardaigne. Soupçonné de sympathies républicaines, il est arrêté en 1833 et contraint à l’exil : il vit à Paris, puis à Bruxelles, où il enseigne et écrit la plus grande partie de son œuvre.&lt;/p&gt; &lt;p&gt;Il est le principal représentant de l’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;. Contre la philosophie moderne, qui part depuis Descartes du sujet et de ses idées, il veut partir de l’être lui-même : l’esprit humain a une intuition directe de Dieu, l’Être absolu, et c’est dans cette lumière qu’il connaît toutes choses. Sa « formule idéale » résume tout le réel : « L’Être crée l’existant. » Il en tire une critique vigoureuse de Descartes et de son contemporain Antonio Rosmini, qu’il accuse de psychologisme. Plusieurs thèses ontologistes seront condamnées par le Saint-Office en 1861, après sa mort.&lt;/p&gt; &lt;p&gt;En 1843, son livre &lt;em&gt;De la primauté morale et civile des Italiens&lt;/em&gt; connaît un immense succès. Il y défend le « néo-guelfisme » : l’Italie, divisée, doit s’unir en une confédération d’États présidée par le pape. Ce programme fait de lui l’un des inspirateurs du &lt;a href="https://fr.wikipedia.org/wiki/Risorgimento" title=" Wikipedia"&gt;Risorgimento&lt;/a&gt;. Revenu triomphalement à Turin en 1848, il est président de la Chambre, puis chef du gouvernement du royaume de Sardaigne en 1848-1849. Désavoué, il repart pour Paris, où il meurt en 1852.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gioberti-mini.webp</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ontologisme</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et homme politique italien, théoricien de l’ontologisme et du Risorgimento.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P116"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -2872,7 +2872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
@@ -8119,6 +8119,11 @@
           <t xml:space="preserve">philosophe des sciences hongrois, penseur des « programmes de recherche » et de la logique de la découverte mathématique.</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -8588,6 +8593,696 @@
         </is>
       </c>
       <c r="P116"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1">
+        <v>1797</v>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1855</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1797 – 1855</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antonio ROSMINI</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Rosmini" title=" Wikipedia"&gt;Antonio ROSMINI&lt;/a&gt; est un prêtre et philosophe italien, l’un des grands penseurs catholiques du XIXe siècle. Né en 1797 à Rovereto, dans le Trentin, alors autrichien, dans une famille noble, il étudie à Padoue et devient prêtre en 1821. En 1828, il fonde l’Institut de la Charité, dont les membres, les rosminiens, se consacrent à l’enseignement et aux œuvres de charité. Ami du romancier Alessandro Manzoni, il veut réconcilier la foi catholique avec la philosophie moderne.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Nouvel essai sur l’origine des idées&lt;/em&gt; (1830), il cherche ce qui rend possible la connaissance. Contre les empiristes, pour qui tout vient des sens, et contre Kant, qui multiplie les formes a priori, il soutient qu’une seule idée est innée : l’idée de l’être, indéterminée, que l’esprit intuitionne avant toute expérience et qui lui permet de juger que les choses existent. Sa philosophie du droit fait de la personne le fondement de tout : la personne humaine est « le droit subsistant », qu’aucun État ne peut absorber ni sacrifier. Il est ainsi regardé comme un précurseur du &lt;a href="https://fr.wikipedia.org/wiki/Personnalisme" title=" Wikipedia"&gt;personnalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;En 1848, ses &lt;em&gt;Cinq plaies de la sainte Église&lt;/em&gt; dénoncent la coupure entre le clergé et le peuple, et sa &lt;em&gt;Constitution selon la justice sociale&lt;/em&gt; imagine une Italie fédérale et libérale ; les deux livres sont mis à l’Index en 1849. Rosmini se soumet et se retire à Stresa, au bord du lac Majeur, où il meurt en 1855. En 1887, Rome condamne quarante thèses tirées de ses œuvres ; il est réhabilité en 2001 et béatifié en 2007.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rosmini-mini.webp</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personnalisme ; Spiritualisme</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtre et philosophe italien, penseur de l’idée de l’être et de la personne, pionnier de la justice sociale.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1">
+        <v>1800</v>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1875</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800 – 1875</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casimir UBAGHS</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Casimir_Ubaghs" title=" Wikipedia (en)"&gt;Casimir UBAGHS&lt;/a&gt; est un philosophe et théologien catholique néerlandais, chef de file de ce qu’on a appelé l’école « ontologico-traditionaliste » de Louvain. Né en 1800 à Berg en Terblijt, près de Valkenburg, dans le Limbourg néerlandais, fils d’un aubergiste, il enseigne d’abord la philosophie au séminaire de Rolduc. En 1834, il est appelé à l’université catholique de Louvain, en Belgique, où il devient doyen de la faculté de philosophie et lettres et enseigne la logique, la métaphysique et l’anthropologie pendant trente ans.&lt;/p&gt; &lt;p&gt;Sa doctrine unit deux courants de son temps. Le traditionalisme, venu de Bonald, affirme que la raison humaine ne peut découvrir seule les vérités morales et religieuses : elles ont été révélées à l’origine et nous sont transmises par la parole et l’enseignement. Mais Ubaghs ajoute que, une fois éveillée par cette instruction, la raison peut les comprendre et les démontrer. L’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;, celui de Malebranche et de Gioberti, soutient que l’esprit connaît les vérités éternelles en ayant une vision directe, quoique obscure, de Dieu lui-même. À partir de 1846, la &lt;em&gt;Revue catholique&lt;/em&gt; de Louvain diffuse ces idées, qui gagnent aussi des disciples en France.&lt;/p&gt; &lt;p&gt;Très vite, des adversaires dénoncent ces thèses comme contraires à la doctrine de l’Église, qui distingue nettement ce que la raison peut connaître par elle-même et ce que seule la foi apporte. La controverse fait rage de 1858 à 1861. En 1864, Rome censure une série de propositions tirées de ses ouvrages, et Ubaghs, qui se soumet, doit quitter l’enseignement. Il vit alors retiré à Louvain, où il meurt en 1875. Son école disparaît avec lui, mais elle prépare le retour au thomisme imposé à la fin du siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ubaghs-mini.webp</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néerlandaise</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ontologisme</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et théologien néerlandais, chef de l’école ontologiste de Louvain.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P118"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1">
+        <v>1809</v>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1809 – 1882</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charles DARWIN</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Darwin" title=" Wikipedia"&gt;Charles DARWIN&lt;/a&gt; est un naturaliste britannique dont la théorie de l’évolution a bouleversé la science et la philosophie. Né en 1809 à Shrewsbury, petit-fils du médecin Erasmus Darwin, il abandonne la médecine puis des études de théologie pour l’histoire naturelle. De 1831 à 1836, il fait le tour du monde à bord du &lt;em&gt;Beagle&lt;/em&gt; : les fossiles d’Amérique du Sud et les espèces voisines d’une île à l’autre des Galápagos le convainquent que les espèces ne sont pas fixes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Origine des espèces&lt;/em&gt; (1859), il explique leur transformation par la « sélection naturelle » : dans chaque génération naissent des individus légèrement différents, et ceux dont les variations favorisent la survie et la reproduction transmettent davantage leurs traits. Sur des temps immenses, ce tri sans but suffit à produire la diversité et l’adaptation des êtres vivants. Il n’y a plus besoin d’un dessein divin pour expliquer l’ordre de la nature, ce qui ruine l’argument de William Paley et ouvre la voie au &lt;a href="https://fr.wikipedia.org/wiki/Naturalisme_%28philosophie%29" title=" Wikipedia"&gt;naturalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Filiation de l’homme&lt;/em&gt; (1871), il inscrit l’être humain dans cette histoire : nos facultés morales viennent des instincts sociaux de nos ancêtres animaux, renforcés par la sympathie, le langage et l’habitude. Darwin lui-même se dit agnostique et reste prudent sur la religion. Sa théorie sera détournée, avec le darwinisme social de Spencer, pour justifier la concurrence et les inégalités, ce qu’il n’avait pas voulu, même s’il partageait certains préjugés de son temps. Il meurt en 1882 et repose à l’abbaye de Westminster.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/darwin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturalisme</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">naturaliste britannique, auteur de la théorie de l’évolution par la sélection naturelle.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1">
+        <v>1817</v>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1878</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817 – 1878</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">George Henry LEWES</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/George_Henry_Lewes" title=" Wikipedia (en)"&gt;George Henry LEWES&lt;/a&gt; est un philosophe, critique et homme de lettres britannique. Né à Londres en 1817, petit-fils d’un comédien, il touche à tout : journalisme, théâtre, roman, critique littéraire, physiologie. Sa &lt;em&gt;Biographical History of Philosophy&lt;/em&gt; (1845-1846), histoire de la philosophie racontée à travers ses grandes figures, connaît un grand succès populaire. Il se fait aussi connaître par une biographie de Goethe (1855) qui reste longtemps une référence.&lt;/p&gt; &lt;p&gt;Il est l’un des principaux diffuseurs en Angleterre du &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title=" Wikipedia"&gt;positivisme&lt;/a&gt; d’Auguste Comte, auquel il consacre un livre en 1853 : seule la science peut nous faire connaître le monde, et la philosophie doit renoncer aux spéculations sur les causes premières. À partir des années 1850, il étudie la physiologie et la psychologie, et cherche dans ses &lt;em&gt;Problems of Life and Mind&lt;/em&gt; (1874-1879) à unir l’étude du cerveau et celle de l’esprit. Pour lui, le mental et le physique sont les deux faces d’un même processus, vu de l’intérieur et vu de l’extérieur.&lt;/p&gt; &lt;p&gt;C’est dans cet ouvrage qu’il forge le mot « émergent ». Certains effets ne sont que la somme de leurs causes, comme une force qui s’ajoute à une autre : il les dit « résultants ». D’autres, comme les propriétés de l’eau par rapport à celles de l’hydrogène et de l’oxygène, sont nouveaux et ne se déduisent pas de leurs composants : ils sont « émergents ». Cette distinction fonde l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mergentisme" title=" Wikipedia"&gt;émergentisme&lt;/a&gt;. De 1854 à sa mort, il vit avec la romancière George Eliot, qu’il encourage à écrire, sans pouvoir l’épouser. Il meurt à Londres en 1878.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lewes-mini.webp</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Émergentisme ; Positivisme</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et critique britannique, diffuseur de Comte, qui forgea le mot « émergent ».</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P120"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1">
+        <v>1820</v>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1893</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1820 – 1893</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">John TYNDALL</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Tyndall_%28physicien%29" title=" Wikipedia"&gt;John TYNDALL&lt;/a&gt; est un physicien irlandais, l’un des grands savants et vulgarisateurs de l’époque victorienne. Né en 1820 à Leighlinbridge, dans le comté de Carlow, fils d’un policier, il travaille d’abord comme géomètre, puis part étudier en Allemagne, à Marburg. En 1853, il entre à la Royal Institution de Londres, où il succède ensuite à Michael Faraday. Il étudie les glaciers, qu’il parcourt en alpiniste, le magnétisme et la diffusion de la lumière, qui explique pourquoi le ciel est bleu.&lt;/p&gt; &lt;p&gt;Vers 1859, il mesure l’absorption de la chaleur par les gaz et montre que la vapeur d’eau et le gaz carbonique retiennent le rayonnement de la Terre : c’est l’une des premières démonstrations expérimentales de l’effet de serre et de son rôle dans le climat. Ami de Thomas Huxley et de Darwin, il appartient au cercle des défenseurs du « naturalisme scientifique », pour qui la science doit expliquer la nature par ses seules lois, sans intervention divine, et s’émanciper de la tutelle des Églises.&lt;/p&gt; &lt;p&gt;En 1874, son « discours de Belfast » devant l’Association britannique pour l’avancement des sciences fait scandale. Retraçant l’histoire de l’atomisme depuis Démocrite et Épicure, il revendique pour la science le droit d’expliquer jusqu’à l’origine de la vie, et voit dans la matière « la promesse et la puissance de toute forme de vie ». Accusé de matérialisme, il se défend en invoquant le mystère qui demeure au fond des choses, dans un esprit proche de l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme" title=" Wikipedia"&gt;agnosticisme&lt;/a&gt;. Il meurt en 1893, empoisonné par erreur par sa femme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tyndall-mini.webp</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irlandaise</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturalisme ; Agnosticisme</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">physicien irlandais, découvreur de l’effet de serre du CO2, figure du naturalisme scientifique.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P121"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1">
+        <v>1838</v>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1916</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1838 – 1916</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ernst MACH</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ernst_Mach" title=" Wikipedia"&gt;Ernst MACH&lt;/a&gt; est un physicien et philosophe autrichien. Né en 1838 en Moravie, il enseigne la physique à Graz puis à Prague, où il étudie notamment les ondes de choc : le « nombre de Mach », rapport entre la vitesse d’un objet et celle du son, porte son nom. En 1895, l’université de Vienne crée pour lui une chaire de philosophie des sciences inductives. Ses travaux portent aussi sur la psychologie de la perception.&lt;/p&gt; &lt;p&gt;Pour Mach, la science ne découvre pas des choses cachées derrière les apparences. Le monde est fait d’« éléments » neutres, les couleurs, les sons, les pressions, les durées, qui sont des sensations quand on les rapporte à notre corps et des réalités physiques quand on les rapporte les unes aux autres. Le moi et la chose ne sont que des groupements relativement stables de ces éléments. Une loi scientifique est une description économique des phénomènes : elle résume le plus simplement possible une foule d’observations. Il faut donc chasser de la science toutes les notions métaphysiques, comme les atomes invisibles, qu’il refuse longtemps, ou l’espace et le temps absolus de Newton.&lt;/p&gt; &lt;p&gt;Sa critique de la mécanique newtonienne, dans &lt;em&gt;La Mécanique&lt;/em&gt; (1883), inspire Einstein, qui en tire ce qu’il appelle le « principe de Mach ». Son &lt;a href="https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nisme" title=" Wikipedia"&gt;phénoménisme&lt;/a&gt; influence William James, Bogdanov, que Lénine attaque pour cela, et surtout le Cercle de Vienne, dont l’association publique s’appelle en 1928 « Association Ernst Mach ». Son refus obstiné des atomes, au moment où la physique en prouve l’existence, lui vaut aussi de vives critiques, notamment de Max Planck. Il meurt en 1916 près de Munich.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mach-mini.webp</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autrichienne</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménisme ; Positivisme</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">physicien et philosophe autrichien, pour qui la science décrit des sensations, inspirateur du Cercle de Vienne.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1">
+        <v>1845</v>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1879</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1845 – 1879</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">William Kingdon CLIFFORD</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/William_Kingdon_Clifford" title=" Wikipedia"&gt;William Kingdon CLIFFORD&lt;/a&gt; est un mathématicien et philosophe britannique. Né en 1845 à Exeter, brillant étudiant de Cambridge, il devient professeur de mathématiques à l’University College de Londres. Il invente les algèbres qui portent son nom, utilisées aujourd’hui en physique, et pressent, bien avant Einstein, que la matière et son mouvement pourraient n’être que des courbures de l’espace. Grand vulgarisateur, il est l’un des esprits les plus audacieux de l’Angleterre victorienne.&lt;/p&gt; &lt;p&gt;Dans « L’éthique de la croyance » (1877), il soutient qu’« il est mal, toujours, partout et pour quiconque, de croire quoi que ce soit sur la foi de preuves insuffisantes ». Son exemple est celui d’un armateur qui, se persuadant que son vieux navire est sûr sans l’avoir vérifié, le laisse partir avec ses passagers : même si le bateau arrive à bon port, il était coupable de le croire. Croire est un acte qui engage la société tout entière. William James lui répondra dans &lt;em&gt;La Volonté de croire&lt;/em&gt;. Clifford en tire une critique sévère de la religion, et se veut ouvertement incroyant.&lt;/p&gt; &lt;p&gt;En métaphysique, il défend la théorie de l’« étoffe mentale » (mind-stuff) : chaque atome de matière possède un élément infime de conscience, et notre esprit est fait de la combinaison de ces éléments, comme notre cerveau l’est des atomes. C’est une forme de &lt;a href="https://fr.wikipedia.org/wiki/Panpsychisme" title=" Wikipedia"&gt;panpsychisme&lt;/a&gt;, qui veut réconcilier l’évolution et l’existence de la conscience. Atteint de tuberculose, il meurt à Madère en 1879, à trente-trois ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/clifford-mini.webp</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; ethique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panpsychisme ; Athéisme</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mathématicien et philosophe britannique, auteur de « L’éthique de la croyance ».</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P123"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1">
+        <v>1879</v>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1967</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1879 – 1967</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eugène DUPRÉEL</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eug%C3%A8ne_Dupr%C3%A9el" title=" Wikipedia"&gt;Eugène DUPRÉEL&lt;/a&gt; est un philosophe et sociologue belge, chef de file de ce qu’on a appelé l’« école de Bruxelles ». Né à Malines en 1879, il étudie le droit puis l’histoire à l’université libre de Bruxelles, avant de se tourner vers la philosophie sous l’influence du Français René Berthelot. Il enseigne à l’université libre de Bruxelles de 1907 à 1950 l’histoire de la philosophie grecque, la logique, la morale et la sociologie, et forme plusieurs générations de chercheurs.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Légende socratique et les sources de Platon&lt;/em&gt; (1922), il soutient que le Socrate que nous connaissons est en grande partie une création littéraire, et que bien des idées attribuées à Platon viennent en réalité des sophistes. Il réhabilite ces maîtres de rhétorique, méprisés depuis Socrate : en montrant qu’on peut argumenter pour et contre chaque thèse, ils avaient compris que personne n’est propriétaire de la vérité. Il reviendra sur eux dans &lt;em&gt;Les Sophistes&lt;/em&gt; (1948), consacré à Protagoras, Gorgias, Prodicos et Hippias.&lt;/p&gt; &lt;p&gt;Cette idée commande toute sa philosophie, un &lt;a href="https://fr.wikipedia.org/wiki/Pluralisme_%28philosophie%29" title=" Wikipedia"&gt;pluralisme&lt;/a&gt; : il n’existe pas un bien unique, mais des valeurs irréductiblement multiples, qui entrent en conflit et entre lesquelles toute action doit choisir. Sa sociologie étudie les rapports sociaux, la coopération, la concurrence et l’autorité, et montre comment les valeurs naissent de la vie en commun. Ses idées sur l’argumentation et le raisonnable inspirent son élève &lt;a href="https://fr.wikipedia.org/wiki/Cha%C3%AFm_Perelman" title=" Wikipedia"&gt;Chaïm Perelman&lt;/a&gt;, fondateur de la « nouvelle rhétorique ». Il meurt à Ixelles en 1967.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dupreel-mini.webp</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belge</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pluralisme ; Relativisme</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et sociologue belge, réhabilitateur des sophistes et penseur du pluralisme des valeurs.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P124"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1">
+        <v>1887</v>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1971</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887 – 1971</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charlie Dunbar BROAD</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charlie_Dunbar_Broad" title=" Wikipedia"&gt;Charlie Dunbar BROAD&lt;/a&gt; est un philosophe britannique, l’une des figures de Cambridge au temps de Russell, Moore et Wittgenstein. Né en 1887 à Londres, il étudie les sciences puis la philosophie au Trinity College de Cambridge. Après avoir enseigné à St Andrews et à Bristol, il revient à Cambridge, où il occupe de 1933 à 1953 la chaire de philosophie morale. Esprit clair et méthodique, il aime examiner toutes les positions possibles sur une question avant de choisir, et ses livres sont réputés pour leur précision et leur humour.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Esprit et sa place dans la nature&lt;/em&gt; (1925), il passe ainsi en revue dix-sept théories du rapport entre l’esprit et le corps et défend l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mergentisme" title=" Wikipedia"&gt;émergentisme&lt;/a&gt; : certaines propriétés d’un tout, comme celles des composés chimiques, de la vie ou de la conscience, ne peuvent pas être déduites des propriétés de ses parties, même si on les connaît parfaitement. Le monde se compose de niveaux d’organisation, chacun avec ses propres lois. Dans &lt;em&gt;Scientific Thought&lt;/em&gt; (1923), il propose aussi une théorie du temps où le passé et le présent existent, mais pas le futur : l’univers est un « bloc » qui s’accroît sans cesse.&lt;/p&gt; &lt;p&gt;En morale, ses &lt;em&gt;Cinq types de théories éthiques&lt;/em&gt; (1930) sont un classique de l’enseignement, consacré à Spinoza, Butler, Hume, Kant et Sidgwick. Broad s’intéresse aussi, avec un sérieux qui étonne ses collègues, à la recherche psychique, la télépathie et la survie après la mort, et préside à deux reprises la Society for Psychical Research. Il meurt à Cambridge en 1971.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/cdbroad-mini.webp</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie ; ethique</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Émergentisme ; Analytique</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe britannique de Cambridge, défenseur de l’émergentisme et de la théorie du « bloc croissant ».</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P125"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1">
+        <v>1896</v>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1896 – 1980</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean PIAGET</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Piaget" title=" Wikipedia"&gt;Jean PIAGET&lt;/a&gt; est un psychologue, biologiste et épistémologue suisse, l’un des plus grands théoriciens du développement de l’enfant. Né à Neuchâtel en 1896, passionné très jeune par les mollusques, il soutient une thèse de sciences naturelles avant de se tourner vers la psychologie. À Paris, dans le laboratoire d’Alfred Binet, il fait passer des tests d’intelligence à des enfants, et s’intéresse moins à leurs bonnes réponses qu’à la logique de leurs erreurs, qui révèlent une manière de penser propre à chaque âge. Il fera ensuite toute sa carrière à Genève, à l’institut Jean-Jacques-Rousseau et à l’université.&lt;/p&gt; &lt;p&gt;En observant les enfants, dont les siens, il montre que l’intelligence se construit par étapes : un stade sensori-moteur, où l’enfant agit sur les objets, puis la pensée symbolique, les opérations concrètes, vers sept ans, et enfin la pensée abstraite et formelle, à l’adolescence. L’enfant n’est pas un adulte en miniature ni une cire où l’expérience s’imprime : il assimile le monde à ses schémas d’action, puis les accommode quand le réel lui résiste. La connaissance n’est donc ni innée ni simplement reçue, elle est construite. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_%28psychologie%29" title=" Wikipedia"&gt;constructivisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Piaget en tire une philosophie de la connaissance, l’« épistémologie génétique », qui étudie comment se forment les grandes notions, le nombre, l’espace, le temps, la causalité, chez l’enfant comme dans l’histoire des sciences. Il fonde à Genève en 1955 un centre international qui réunit psychologues, logiciens et biologistes. Il critique aussi la philosophie qui prétend connaître sans enquête dans &lt;em&gt;Sagesse et illusions de la philosophie&lt;/em&gt; (1965). Il meurt à Genève en 1980.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/piaget-mini.webp</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suisse</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constructivisme ; Structuralisme</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">psychologue et épistémologue suisse, fondateur de l’épistémologie génétique.</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1">
+        <v>1920</v>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920 – 2019</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean STAROBINSKI</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Starobinski" title=" Wikipedia"&gt;Jean STAROBINSKI&lt;/a&gt; est un critique littéraire, historien des idées et médecin suisse. Né à Genève en 1920 de parents juifs polonais venus y étudier la médecine, il étudie les lettres classiques puis la médecine, et exerce un temps comme psychiatre. Il enseigne à l’université Johns-Hopkins de Baltimore, à Bâle, puis à Genève la littérature française, l’histoire des idées et l’histoire de la médecine. Il est l’une des grandes figures de l’« école de Genève » de la critique.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Jean-Jacques Rousseau. La transparence et l’obstacle&lt;/em&gt; (1957), il montre que toute l’œuvre de &lt;a href="https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau" title=" Wikipedia"&gt;Rousseau&lt;/a&gt; est animée par un rêve de transparence entre les cœurs, que la société, les masques et les apparences ne cessent de contrarier. Il renouvelle de même la lecture de Montesquieu, de Diderot et de tout le XVIIIe siècle, en particulier dans &lt;em&gt;L’Invention de la liberté&lt;/em&gt; (1964) et &lt;em&gt;Le Remède dans le mal&lt;/em&gt; (1989), qui montre comment les Lumières cherchent à guérir par la civilisation les maux causés par la civilisation.&lt;/p&gt; &lt;p&gt;Pour lui, la critique est une relation vivante avec l’œuvre, un regard qui va de la proximité à la distance, de l’adhésion à l’analyse, sans jamais oublier le plaisir de lire. Médecin, il écrit aussi une histoire de la mélancolie, et publie le premier, en 1964, les recherches de Saussure sur les anagrammes cachés dans la poésie latine. Membre de nombreuses académies, il a fait de l’interprétation des textes une véritable &lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique" title=" Wikipedia"&gt;herméneutique&lt;/a&gt;. Il meurt à Morges, dans le canton de Vaud, en 2019.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/starobinski-mini.webp</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suisse</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; ethique</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique, historien des idées et psychiatre suisse, grand lecteur de Rousseau et des Lumières.</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P127"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1">
+        <v>1940</v>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1940 – 2019</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo DASCAL</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Marcelo_Dascal" title=" Wikipedia (en)"&gt;Marcelo DASCAL&lt;/a&gt; est un philosophe et linguiste brésilien et israélien. Né à São Paulo en 1940 dans une famille juive, il étudie à la fois la philosophie et le génie électrique, puis la linguistique à Aix-en-Provence, avant de soutenir sa thèse à l’université hébraïque de Jérusalem sous la direction de Yehoshua Bar-Hillel. À partir de 1967, il enseigne à l’université de Tel-Aviv, dont il dirige la faculté des lettres de 1995 à 2000, tout en donnant des cours dans le monde entier, en particulier au Brésil.&lt;/p&gt; &lt;p&gt;Spécialiste de la pragmatique, l’étude de ce que nous faisons avec le langage, il montre que comprendre un énoncé exige toujours d’interpréter les intentions de celui qui parle. Grand connaisseur de &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz" title=" Wikipedia"&gt;Leibniz&lt;/a&gt;, il établit dans &lt;em&gt;La Sémiologie de Leibniz&lt;/em&gt; (1978) le rôle essentiel que celui-ci accordait aux langues et aux signes dans la pensée elle-même. Il souligne aussi que Leibniz, à côté de son rêve d’un calcul universel qui trancherait tous les différends, a pratiqué un art de la discussion tenant compte des raisons de chacun.&lt;/p&gt; &lt;p&gt;Il en tire une théorie des controverses : il distingue la discussion, qui se règle par une preuve, la dispute, où chacun veut gagner, et la controverse, où des positions opposées progressent sans qu’aucune démonstration ne tranche. Pour lui, le savoir naît de ces débats, chaque doctrine contenant des « grains de vérité ». Il fonde en 1996 l’Association internationale pour l’étude des controverses. Il meurt en Israël, à Kiryat Ono, en 2019.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dascal-mini.webp</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israélienne</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pluralisme ; Analytique</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe brésilien et israélien du langage, spécialiste de Leibniz et théoricien des controverses.</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P128"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -4909,7 +4909,7 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski"   title=" Wikipedia"&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href="https://www.youtube.com/watch?v=Vvt7ns_jZvY"  title="The logic of reality  par TroughtLab"&gt;la logique et des mathématiques&lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique "vraie" modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski"   title=" Wikipedia"&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href="https://www.youtube.com/watch?v=Vvt7ns_jZvY"  title="The logic of reality  par TroughtLab"&gt;la logique et des mathématiques&lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique "vraie" modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. Ses trois systèmes portent les noms de « protothétique », logique des propositions, d’« ontologie », logique des noms, et de « méréologie », théorie des parties et du tout. Cette dernière offre une alternative à la théorie des ensembles : une classe n’y est pas un objet abstrait, mais un tout concret formé de ses parties, ce qui évite le paradoxe de Russell. Professeur à l’université de Varsovie, il eut pour unique doctorant Alfred Tarski. Il meurt en 1939, quelques mois avant l’invasion de la Pologne. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F45" s="7" t="s">
@@ -4957,8 +4957,7 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Gramsci"  title=" Wikipedia"&gt;Antonio GRAMSCI&lt;/a&gt;  était un philosophe marxiste italien et a aussi été un homme politique, un journaliste et l’un des &lt;a href="https://www.youtube.com/watch?v=Q8s8r43ANbQ"  title="L’hégémonie culturelle selon Antonio GRAMSCI  par France Culture"&gt;fondateurs du Parti communiste italien&lt;/a&gt;. Son apport le plus connu est la notion d’hégémonie culturelle. Pour lui, une classe dominante ne gouverne pas seulement par la force, mais aussi en imposant ses valeurs, ses idées et son sens commun dans la société civile. &lt;/p&gt; &lt;p&gt; Il a réfléchi à la manière dont une force politique peut contester ce pouvoir. Il distingue la « guerre de mouvement », plus directe, et la « guerre de position », plus lente, qui passe par les syndicats, les journaux, l’éducation et la culture. &lt;/p&gt; &lt;p&gt; Il est devenu  &lt;a href="https://www.youtube.com/watch?v=K3vf4DSL_GE"  title="Comprendre  Antonio GRAMSCI  par Politikon"&gt;une référence &lt;/a&gt; bien au-delà du marxisme strict, parce que ses idées servent à analyser les médias, l’école, la culture et les rapports de pouvoir dans les sociétés modernes. Ses Cahiers de prison ont joué un rôle central dans cette postérité intellectuelle. &lt;/p&gt; &lt;audio controls title="Qui est Antonio GRAMSCI par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.02.2017-ITEMA_21240143-2017C12410E0055-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Gramsci"  title=" Wikipedia"&gt;Antonio GRAMSCI&lt;/a&gt; (1891-1937) est un philosophe marxiste et homme politique italien, l’un des fondateurs du Parti communiste italien. Né en Sardaigne dans une famille modeste, il étudie à Turin, où il anime le journal &lt;em&gt;L’Ordine Nuovo&lt;/em&gt; et le mouvement des conseils d’usine. Député, puis secrétaire général du parti, il est arrêté en 1926 par le régime fasciste ; le procureur aurait déclaré : « Il faut empêcher ce cerveau de fonctionner pendant vingt ans. »&lt;/p&gt; &lt;p&gt;En prison, malgré la maladie, il remplit une trentaine de cahiers, les &lt;em&gt;Cahiers de prison&lt;/em&gt;, publiés après sa mort. Il y cherche à comprendre pourquoi la révolution a réussi en Russie et échoué en Occident. Sa réponse est la notion d’&lt;a href="https://www.youtube.com/watch?v=Q8s8r43ANbQ"  title="L’hégémonie culturelle selon Antonio GRAMSCI  par France Culture"&gt;hégémonie culturelle&lt;/a&gt; : une classe dominante ne règne pas seulement par la force de l’État, mais par le consentement qu’elle obtient en diffusant ses valeurs et son « sens commun » à travers la société civile, l’école, l’Église, la presse ou les associations. Dans les sociétés occidentales, où cette société civile est solide, une attaque frontale, la « guerre de mouvement », échoue ; il faut d’abord mener une longue « guerre de position » pour conquérir les esprits. Ce combat revient aux « intellectuels organiques », liés à une classe sociale, qui élaborent et diffusent une nouvelle conception du monde. Gramsci appelle le marxisme une « philosophie de la praxis » et résume son attitude par la formule : « pessimisme de l’intelligence, optimisme de la volonté ».&lt;/p&gt; &lt;p&gt;Libéré trop tard, il meurt en 1937. Il est devenu &lt;a href="https://www.youtube.com/watch?v=K3vf4DSL_GE"  title="Comprendre  Antonio GRAMSCI  par Politikon"&gt;une référence&lt;/a&gt; mondiale, des études culturelles et postcoloniales à la théorie politique, à gauche comme à droite.&lt;/p&gt;  &lt;audio controls title="Qui est Antonio GRAMSCI par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.02.2017-ITEMA_21240143-2017C12410E0055-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F46" s="7" t="s">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3507,8 +3507,10 @@
       <c r="D15" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>126</v>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Secr%C3%A9tan" title=" Wikipedia"&gt;Charles SECRÉTAN&lt;/a&gt; était un philosophe suisse protestant, généralement rangé dans une forme de spiritualisme chrétien, avec une &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1925_num_5_2_2528" title="charles secretan et la philosophie de schelling par persée"&gt; forte influence de Schelling. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il faut d’abord le comprendre à partir de son idée centrale : la liberté. Dans Philosophie de la liberté, il soutient que la liberté n’est pas seulement une faculté humaine, mais un principe profond de la réalité, lié à Dieu lui-même.  Pour lui, la raison humaine ne suffit pas à tout expliquer seule. Il cherche donc à concilier la pensée philosophique et la foi chrétienne, en défendant ce qu’il appelle une “raison chrétienne” contre le rationalisme pur d’un côté et le fidéisme dogmatique de l’autre. &lt;/p&gt; &lt;p&gt; Sa philosophie a aussi une dimension morale très forte. Il insiste sur la responsabilité personnelle, la solidarité, la dignité de l’homme et la dimension éthique de la vie sociale, ce qui l’amène à réfléchir à la question des inégalités et des droits. &lt;/p&gt; &lt;p&gt; Sa pensée évolue vers des préoccupations plus sociales. Même s’il reste métaphysicien au départ, il s’oriente de plus en plus vers la morale, la religion vécue et les questions de société, avec l’idée qu’une communauté humaine juste doit être fondée sur la liberté et la solidarité. &lt;/p&gt; Né à Lausanne en 1815, il suit à Munich les cours de Schelling, puis enseigne la philosophie à Lausanne ; destitué en 1845 par le gouvernement radical, il enseigne à Neuchâtel avant de retrouver sa chaire. Sa &lt;em&gt;Philosophie de la liberté&lt;/em&gt; (1849) fait de Dieu une liberté absolue, qui crée par amour des êtres libres. Il plaide aussi pour l’égalité des femmes, à qui il consacre &lt;em&gt;Le Droit de la femme&lt;/em&gt; (1886). </t>
+        </is>
       </c>
       <c r="F15" s="7" t="s">
         <v>127</v>
@@ -6489,8 +6491,10 @@
       <c r="D79" s="8" t="s">
         <v>666</v>
       </c>
-      <c r="E79" s="12" t="s">
-        <v>667</v>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Geoffrey_Warnock"  title=" Wikipedia"&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J. L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href="https://fr.wikipedia.org/wiki/Intuitionnisme_social"   title="L’intuitionnisme par Kikipedia"&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; Dans &lt;em&gt;L’Objet de la morale&lt;/em&gt; (1971), il soutient que la morale a une fonction : améliorer la condition humaine, toujours menacée par la rareté des ressources, l’ignorance et surtout la « sympathie limitée » des hommes, qui se soucient d’abord d’eux-mêmes et de leurs proches. Les vertus morales servent à corriger cette tendance. </t>
+        </is>
       </c>
       <c r="F79" s="7" t="s">
         <v>668</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3032,8 +3032,10 @@
       <c r="D5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>29</v>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Wollstonecraft"   title=" Wikipedia"&gt;Mary WOLLSTONECRAFT&lt;/a&gt; était une philosophe féministe anglaise qui vécu à une époque de bouleversements politiques et intellectuels, notamment la  &lt;a href="https://www.persee.fr/doc/xvii_0291-3798_1999_num_49_1_2108"  title=" Mary Wollstonecraft, la Révolution française et A Vindication of the Rights of Woman  par Persée"&gt;Révolution française&lt;/a&gt;, ce qui a influencé ses idées sur les droits humains et l'égalé.  Elle est surtout connue pour ses ouvrages : &lt;/p&gt; &lt;p&gt;"A Vindication of the Rights of Woman" (1792) : Son œuvre la plus célèbre, dans laquelle elle argue que les femmes ne sont pas  &lt;a href="https://www.youtube.com/watch?v=hlxyCUh77GU"  title=" Mary Wollstonecraft : Le Vrai Pouvoir des Femmes, selon une Pionnière du Féminisme par les Grands esprits Feministes"&gt;inférieures par nature&lt;/a&gt;, mais que leur éducation et leur position sociale les maintiennent dans un état de dépendance. Elle plaide pour une éducation rationnelle et égalitaire, permettant aux femmes de développer leur raison et leur autonomie. &lt;/p&gt; &lt;p&gt;A Vindication of the Rights of Men" (1790) : Une réponse à Edmund Burke, qui défendait la monarchie et critiquait la Révolution française. Elle y défend les principes républicains et l'égalité des droits. &lt;/p&gt; &lt;p&gt;"Maria, or The Wrongs of Woman" (1798, posthume) : Un roman inachevé qui explore les injustices subies par les femmes, notamment dans le mariage et la société patriarcale. &lt;/p&gt; &lt;p&gt;"Letters Written During a Short Residence in Sweden, Norway, and Denmark" (1796) Un récit de voyage mêlant observations personnelles et réflexions philosophiques. &lt;/p&gt; &lt;p&gt; Elle défend les droits universels, y compris pour les femmes. Elle considère que la liberté et l'égalité sont des principes fondamentaux pour tous les êtres humains. Elle plaide pour une éducation qui développe la raison et la vertu, aussi bien pour les hommes que pour les femmes. Selon elle, une éducation égalitaire permettrait aux femmes de participer pleinement à la société. /p&gt; &lt;p&gt;  Elle est aujourd'hui considérée comme une pionnière du féminisme et une figure essentielle dans la lutte pour les droits des femmes. Ses idées ont inspiré des générations de féministes, de John Stuart Mill à Simone de Beauvoir. &lt;/p&gt;  &lt;audio controls title=" La figure de Mary Wollstonecraft, la défense des droits des femmes au siècle des Lumières par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-20.10.2024-ITEMA_23898838-2024C33085S0294-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F5" s="7" t="s">
         <v>30</v>
@@ -3129,8 +3131,14 @@
       <c r="D7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>49</v>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Ricardo" title=" Wikipedia"&gt;David RICARDO&lt;/a&gt; était un  philosophe et économiste anglais qui se consacra à l’étude théorique de   &lt;a href="https://www.lepoint.fr/eureka/david-ricardo-l-autodidacte-de-la-pensee-economique-liberale-16-08-2025-2596437_4706.php" title=" David Ricardo, l’autodidacte de la pensée économique libérale  par Le Point"&gt;l’économie politique&lt;/a&gt;, domaine dans lequel il allait marquer durablement la pensée moderne. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "On the Principles of Political Economy and Taxation" (1817), constitue un jalon fondamental dans la construction de la science économique. Il y développe plusieurs idées dont la théorie de   &lt;a href="https://www.youtube.com/watch?v=fhQ32X5faSo" title=" David Ricardo,  La théorie de la valeur-travail  par Des economistes et des hommes"&gt; la valeur-travail&lt;/a&gt; : selon lui, la valeur d’une marchandise dépend principalement de la quantité de travail nécessaire à sa production. Il nuance  en tenant compte de l’effet du capital, de la durée de production et des différences de composition en travail direct et indirect. &lt;/p&gt; &lt;p&gt; 
+Il est également à l’origine de la célèbre théorie &lt;a href="https://www.youtube.com/watch?v=ip9d1UJ4RYg"  title=" David Ricardo, Qu'est-ce que l'avantage comparatif ? par Dessine moi l'eco"&gt; des avantages comparatifs&lt;/a&gt;, qui fonde l’économie du commerce international moderne et démontre que deux pays ont intérêt à échanger entre eux même si l’un est plus productif dans toutes les activités : chacun doit se spécialiser dans la production où son avantage relatif est le plus grand, ce qui accroît la richesse globale. Cet argument devint la justification théorique la plus solide en faveur du libre-échange. &lt;/p&gt; &lt;p&gt;
+Dans ses analyses, il insiste sur le rôle central des profits dans le dynamisme économique : la croissance dépend de la capacité des capitalistes à réinvestir leurs profits, mais ceux-ci tendent à s’éroder à long terme sous l’effet de la hausse des rentes et de la pression sur les salaires de subsistance. Cela le conduit à une vision quelque peu pessimiste du développement à long terme, anticipant un état stationnaire où l’expansion économique se ralentirait considérablement. &lt;/p&gt; &lt;p&gt; 
+Il exerça aussi une influence durable sur la pensée économique postérieure. Karl Marx reprendra et transformera sa théorie de la valeur-travail pour élaborer sa propre analyse du capitalisme. Son raisonnement abstrait, fondé sur des modèles théoriques simplifiés, marque une étape décisive dans l’évolution de l’économie vers une science plus formaliste et déductive. &lt;/p&gt; &lt;audio controls title="David RICARDO La Mondialisation par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-09.10.2017-ITEMA_21457955-2017C29629S0282-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  
+</t>
+        </is>
       </c>
       <c r="F7" s="7" t="s">
         <v>50</v>
@@ -3173,8 +3181,10 @@
       <c r="D8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>59</v>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Shepherd"  title=" Wikipedia"&gt;Mary SHEPHERD&lt;/a&gt; était une philosophe écossaise connue surtout pour sa défense d’une métaphysique réaliste et sa critique approfondie de la conception de &lt;a href="https://www.youtube.com/watch?v=HNfw1g_omaM" style="color:#88A1E9" title="Mary Shepherd's Philosophy: Causation, Perception, and Mind  par Philosopher Friends"&gt;la causalité &lt;/a&gt; chez Hume et les philosophes écossais de son époque. &lt;/p&gt; &lt;p&gt; Elle soutient des principes comme "un être ne peut pas commencer à exister de lui-même" et "des causes semblables produisent nécessairement des effets semblables", cherchant à montrer qu’il y a une nécessité dans le lien causal, et non une simple habitude psychologique comme chez Hume.&lt;/p&gt; &lt;p&gt;  Elle défend l’idée que nos croyances existentielles peuvent être rationnellement justifiées par des arguments causaux, et ne reposent ni sur un simple scepticisme ni seulement sur l’instinct. Dans ses essais sur la perception, elle critique l’idéalisme de Berkeley et certaines positions de Reid, mais reste réaliste : pour elle, la perception et la causalité permettent de conclure à l’existence d’un univers externe. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "An Essay upon the Relation of Cause and Effect" paru en 1824 : livre où elle critique la théorie humienne de la causalité et discute aussi Thomas Brown et William Lawrence et "Essays on the Perception of an External Universe, and other Subjects Connected with the Doctrine of Causation" paru en 1827 : recueil de textes sur la perception du monde extérieur, la causalité, l’existence de Dieu, l’esprit et le corps, discutant notamment Berkeley et Thomas Reid. &lt;/p&gt; &lt;p&gt; Depuis la fin du XXᵉ siècle, des historiennes et historiens de la philosophie, ainsi que des éditions critiques de ses œuvres, contribuent à la réhabiliter comme une figure importante de la philosophie moderne, en particulier dans les études féministes de la philosophie. On note son influence sur la philosophie écossaise, et des contemporains la citent comme une interlocutrice de poids dans les débats sur la causalité et la connaissance. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F8" s="7" t="s">
         <v>60</v>
@@ -3266,8 +3276,11 @@
       <c r="D10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>78</v>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giacomo_Leopardi"  title=" Wikipedia"&gt;Giacomo LEOPARDI&lt;/a&gt;  était un poète &amp; philosophe italien souvent présenté comme l’un des plus profonds représentants du pessimisme moderne. À partir de 1819, il vit ce qu’il appelle une "conversion philosophique" : il quitte l’illusion d’un monde harmonieux pour la recherche du "vrai", au prix d’une vision très sombre de la condition humaine. &lt;/p&gt; &lt;p&gt; Il i résume   &lt;a href="https://www.youtube.com/watch?v=2IQ7BUruaMk"  style="color:#88A1E9"  title="Giacomo Léopardi : Pensées par Ina Culture"&gt;"sa pensée &lt;/a&gt; par l’idée d’"infelicità", un malheur constitutif de la condition humaine, et non pas seulement accidentel. Il se méfie de l’idée de progrès moral ou spirituel de l’humanité, qu’il voit comme un récit optimiste sans fondement réel.  La nature n’est pas non plus bonne ni providentielle, elle produit la vie mais aussi la souffrance, sans finalité morale ; l’existence est "un mal pour tous les éléments qui composent l’univers". &lt;/p&gt; &lt;p&gt; Pour lui, la raison dévoile la vérité, mais cette vérité est désespérante et détruit les illusions qui rendaient la vie supportable.  Il valorise les illusions (espoirs, rêves, mythes) comme un rempart contre le nihilisme et l’égoïsme ; la "pure raison", en les dissipant, isole les individus et dissout les liens sociaux. Son pessimisme n’est pas une complaisance à la tristesse ; c’est une lucidité douloureuse sur la finitude et la souffrance, qu’il assume jusqu’au bout. : Il ne cherche pas à "propager" une doctrine du désespoir, mais à chanter,  &lt;a href="https://www.youtube.com/watch?v=MbXrKkikvpg"  title="Dialogue du Tasse et de son démon familier, Giacomo Leopardi par Poème"&gt;en poète,&lt;/a&gt;  le mal de vivre et à en tirer une vision lucide de l’humain. &lt;/p&gt; &lt;p&gt;  Il écrit qu’une philosophie séparée de toute religion (comprise comme morale générale) devient une "doctrine de la scélératesse raisonnée", c’est‑à‑dire une pensée qui peut justifier l’absence de vertu.  Pour atteindre sa vraie perfection, la philosophie doit, selon lui, rencontrer la poésie, c’est‑à‑dire l’imagination, la sensibilité, la capacité de faire sentir ce qu’elle pense. &lt;/p&gt;   &lt;audio controls title="Le Zibaldone de Giacomo Leopardi par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11991-13.04.2014-ITEMA_20614026-2014C18021E0014-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F10" s="7" t="s">
         <v>79</v>
@@ -3312,7 +3325,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Stuart_Mill"  style="color:#6A142A"  title=" Wikipedia"&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href="https://www.youtube.com/watch?v=kDfp2afvj28" style="color:#88A1E9" title="John Stuart Mill - Synthèse par El Khader"&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». Son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href="https://www.youtube.com/watch?v=yCDOVcvNYpY" title=" L'utilitarisme par Culture Philo"&gt;"  l’Utilitarisme"&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href="https://www.youtube.com/watch?v=DVG_FL8jKe0" title="John Stuart Mill - De La Liberté par Let's make liberalism great again"&gt;" De la liberté"&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href="https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s" title="JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques"&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;&lt;audio controls title="John Stuart Mill par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Stuart_Mill"  style="color:#6A142A"  title=" Wikipedia"&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href="https://www.youtube.com/watch?v=kDfp2afvj28" style="color:#88A1E9" title="John Stuart Mill - Synthèse par El Khader"&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». Son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href="https://www.youtube.com/watch?v=yCDOVcvNYpY" title=" L'utilitarisme par Culture Philo"&gt;"  l’Utilitarisme"&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href="https://www.youtube.com/watch?v=DVG_FL8jKe0" title="John Stuart Mill - De La Liberté par Let's make liberalism great again"&gt;" De la liberté"&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href="https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s" title="JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques"&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;        &lt;audio controls title="John Stuart Mill par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
@@ -3359,8 +3372,10 @@
       <c r="D12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>97</v>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Harriet_Taylor_Mill"  title=" Wikipedia"&gt;Harriet TAYLOR MILL&lt;/a&gt; était  une philosophe et féministe britannique, connue pour ses contributions significatives à la &lt;a href="https://www.youtube.com/watch?v=WfRt-9tEBBU"  title=" Qu'est-ce que le Libéralisme ? par Cliolix"&gt;pensée libérale&lt;/a&gt; et féministe du XIXe siècle. Bien qu'elle ait souvent été éclipsée par son mari, le philosophe John Stuart Mill, ses idées et son influence sur le travail de son époux en particulier dans les domaines de la liberté individuelle, des droits des femmes et de l'économie politique sont aujourd'hui reconnues comme essentielles. Bien qu'elle ait peu publié sous son propre nom, son influence est évidente dans plusieurs des travaux de Mill, notamment : &lt;/p&gt; &lt;p&gt;"On Liberty" (1859) :  Considéré comme l'une des œuvres fondamentales de la philosophie libérale. L'essai défend la liberté individuelle et soutient que la société ne peut justifier d'intervenir dans la vie des individus que pour prévenir un préjudice à autrui. Ses idées sur l'importance de l'autonomie individuelle et de la liberté de pensée ont profondément marqué ce texte.&lt;/p&gt; &lt;p&gt;"The Subjection of Women" (1869) : Plaidoyer puissant pour l'égalité des sexes. Elle a joué un rôle clé dans la formulation des arguments de ce texte. Elle a soutenu que la subordination des femmes était une injustice sociale qui devait être abolie pour permettre à la société de progresser. Ses idées sur l'égalité des sexes étaient radicales pour l'époque et ont contribué à jeter les bases du mouvement féministe moderne. &lt;/p&gt; &lt;p&gt; Elle a écrit des essais et des articles sous son propre nom, notamment &lt;a href="https://www.youtube.com/watch?v=1bgBr24BhOk"  title=" Harriet Taylor, The Enfranchisement of Women, | Votes for Women par History Hub"&gt;"Enfranchisement of Women" &lt;/a&gt;(1851), dans lequel elle plaide pour le droit de vote des femmes. Elle a également contribué à des discussions sur l'économie politique, en particulier sur les questions de travail et de réforme sociale. &lt;/p&gt; &lt;p&gt; Reconnue comme une penseuse importante en son propre droit, ses idées sur la liberté, l'égalité et les droits des femmes ont eu un impact durable sur la philosophie politique et le féminisme. &lt;/p&gt;   &lt;audio controls title="Avoir raison avec... Harriet Taylor Mill  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-14.08.2023-ITEMA_23459320-2023C35448E0012-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F12" s="7" t="s">
         <v>98</v>
@@ -3654,8 +3669,11 @@
       <c r="D18" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>154</v>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Henry_Huxley"   title=" Wikipedia"&gt;Thomas Henry HUXLEY&lt;/a&gt; était un biologiste, vulgarisateur scientifique et grand défenseur de Darwin dans l’Angleterre victorienne. Mais il a aussi élaboré une position philosophique influente : l’agnosticisme, terme qu’il forgea en 1869 pour définir une attitude rigoureuse face aux limites de la connaissance. &lt;/p&gt; &lt;p&gt; Pour lui,  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme" " title="agnosticisme par wikipedia"&gt;l’agnosticisme &lt;/a&gt; n’est ni une religion, ni une doctrine affirmant que Dieu n’existe pas. C’est avant tout une méthode intellectuelle : on doit suivre la raison et les preuves aussi loin qu’elles conduisent, sans prétendre savoir avec certitude ce qui n’est ni démontré ni démontrable. Ainsi, concernant Dieu, l’âme immortelle ou l’origine ultime du monde, il suspend son jugement : il estime que l’on ne dispose pas de preuves suffisantes pour affirmer ou nier catégoriquement ces réalités. &lt;/p&gt; &lt;p&gt;  Sa philosophie est donc une forme d’empirisme critique, héritière de David Hume et, sur certains points, de Kant. La science peut établir des connaissances sur les phénomènes observables, contrôlables et soumis à l’expérience ; elle ne peut pas légitimement franchir ce cadre pour parler avec certitude d’une réalité métaphysique située « derrière » ou au-delà de l’expérience. Il refusait autant le dogmatisme théologique que le matérialisme athée qui prétendrait résoudre définitivement les questions ultimes. &lt;/p&gt; &lt;p&gt; Chez lui, &lt;a href="https://fr.wikipedia.org/wiki/%C3%89piph%C3%A9nom%C3%A9nisme" " title="épiphénoménisme par wikipedia"&gt; l’épiphénoménisme &lt;/a&gt; est une thèse centrale sur l’esprit et le corps, exposée surtout dans son discours de 1874, On the Hypothesis that Animals are Automata. Il y soutient que les états de conscience (sensations, sentiments, pensées telles qu’on les vit) sont réels, mais qu’ils sont des effets collatéraux des processus physico-chimiques du cerveau et du système nerveux, sans pouvoir à leur tour agir sur ces processus. &lt;/p&gt; &lt;p&gt; Pour le dire avec sa célèbre image : la conscience est au corps ce que le sifflet à vapeur est à une locomotive. Le sifflet accompagne le fonctionnement de la machine et en dépend, mais il n’influe pas sur son mouvement ; de même, selon Huxley, la conscience accompagne l’activité nerveuse sans la déterminer. Les comportements, y compris les actions que nous attribuons à la « volonté », sont entièrement expliqués par des chaînes de causes physiques dans l’organisme. Il ne nie donc pas l’existence de la conscience (contrairement à un matérialisme éliminativiste), mais il refuse de lui accorder un rôle causal dans l’explication scientifique du comportement. Sur le plan métaphysique, cela revient à un dualisme très affaibli : il y a bien quelque chose comme un « esprit » ou une vie consciente, mais celle-ci est un épiphénomène, un « spectateur inerte » des mécanismes corporels. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=jdMeImpsaR4" " title="évolution et agnosticism par open source "&gt; Cette position &lt;/a&gt;  s’inscrit dans son projet plus large de naturaliser la biologie et de soumettre l’être vivant à des lois mécaniques, tout en restant fidèle à son agnosticisme : il admet que le lien exact entre irritation nerveuse et état de conscience reste inexpliqué, voire mystérieux, mais il refuse d’en tirer des conclusions métaphysiques sur une âme immatérielle ou une liberté surnaturelle. Il reconnaît explicitement le caractère énigmatique du passage du physique au conscient, tout en maintenant que la science doit traiter le corps comme un automate. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F18" s="7" t="s">
         <v>155</v>
@@ -3831,8 +3849,11 @@
       <c r="D22" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>190</v>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexius_Meinong"   title=" Wikipedia"&gt;Alexius MEINONG&lt;/a&gt;  était un philosophe et psychologue autrichien, élève de Franz Brentano à Vienne, qui enseigna principalement à l'université de Graz où il fonda un institut de psychologie expérimentale. Issu d'une famille noble, il s'intéresse d'abord à la psychologie descriptive avant de développer une ontologie audacieuse influencée par l'intentionnalité brentanienne. Sa carrière est marquée par des contributions en philosophie de l'esprit, axiologie et surtout sa célèbre théorie des objets, qui élargit radicalement le domaine de ce qui peut être pensé. &lt;/p&gt; p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Meinongianisme"  title="Meinongianisme par Wikipedia"&gt;Sa théorie des objets, &lt;/a&gt; exposée dans Recherches sur la théorie des objets et la psychologie (1904), postule que tout ce qui est visé par la pensée existe comme objet, indépendamment de son existence réelle. Il distingue le Sein (être : existence pour les concrets, subsistance pour les idéaux comme les nombres) du Sosein (caractérisation nucléaire et extra-nucléaire), avec le principe d'indifférence : un&lt;a href="https://www.youtube.com/watch?v=4Yway8Xo3iA"  title="Alexius Meinong Théorie de l’objet par Jdgrandtour"&gt; objet est ontologiquement neutre &lt;/a&gt; quant à l'existence. Ainsi, la montagne d'or ou le rond carré sont des objets « außerseiend » (hors de l'être), pensables sans contradictoire. &lt;/p&gt; &lt;p&gt; Il  introduit aussi les assomptions, actes mentaux fictifs intermédiaires entre jugements et représentations, essentiels pour la pensée hypothétique ou fictionnelle. Critiqué par Russell pour le paradoxe (« l'entité actuelle n'existe pas »), il raffine sa théorie en distinguant propriétés incomplètes et propriétés extra-nucléaires (comme l'existence elle-même). Son système, jungle ontologique foisonnante, préfigure la méta-ontologie analytique. &lt;/p&gt; &lt;p&gt; Influençant Husserl, Russell ou la philosophie analytique contemporaine, il reste une figure clé de l'école de Graz, opposée au psychologisme. Son blason familial évoque son lignage noble, mais c'est sa audace ontologique qui perdure. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F22" s="7" t="s">
         <v>191</v>
@@ -3923,12 +3944,14 @@
       <c r="C24" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>205</v>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jacob OSIS</t>
+        </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis"  title=" Wikipedia"&gt;Jacob OSSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; Il se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis"  title=" Wikipedia"&gt;Jacob OSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; Il se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4066,7 +4089,7 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Santayana"   title=" Wikipedia"&gt;George SANTAYANA&lt;/a&gt; était un philosophe hispano-américain, né à Madrid et formé à Harvard, qui occupe une place singulière dans la philosophie du XXᵉ siècle par son alliance d’un naturalisme matérialiste rigoureux et d’une sensibilité littéraire, esthétique et religieuse. &lt;/p&gt; &lt;p&gt; Il défend un naturalisme radical : pour lui, tout ce qui existe relève de la matière et de ses configurations ; la conscience, la raison, la culture sont des phénomènes émergents de l’activité biologique et sociale. Il refuse cependant de réduire la vie de l’esprit à un simple épiphénomène sans intérêt : il prend au sérieux l’art, la religion, la morale comme réalités à expliquer, sans pour autant leur accorder un statut ontologique indépendant de la matière. - &lt;a href="https://www.youtube.com/watch?v=86qYBc2BA6k" title="the philosophy of george santayana par let’s talk philosophy"&gt;" Cette position &lt;/a&gt;  lui permet de critiquer à la fois l’idéalisme allemand et un matérialisme scientiste étroit, en proposant un matérialisme humaniste. &lt;/p&gt; &lt;p&gt; Sur le plan épistémologique, il est un sceptique profond : il soutient qu’aucune proposition n’est « évidente » en soi et que la croyance en l’existence du monde extérieur (y compris celle de soi) ne repose pas sur une démonstration absolue, mais sur des besoins vitaux et des habitudes d’action. Dans Scepticism and Animal Faith (1923), il développe l’idée d’une « foi animale » : des convictions inévitables, nécessaires à l’action, que le scepticisme ne peut entièrement dissoudre, et qu’il faut assumer lucidement plutôt que de prétendre les fonder rationnellement. Il résume cette attitude en disant que le scepticisme est la « chasteté de l’intellect », à préserver jusqu’à ce qu’il puisse être échangé contre une fidélité mature. &lt;/p&gt; &lt;p&gt; Pour articuler son naturalisme et la richesse de la vie spirituelle, il élabore, dans The Realms of Being (1927–1940), une ontologie en quatre « règnes » : l’essence (formes et possibilités intelligibles), la matière (le monde physique, seul véritablement existant), la vérité (ensemble des propositions vraies) et l’esprit (la conscience comme activité émergente). Cette architecture lui permet de garder une place  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_11_5754_t1_0593_0000_2" title="the essential wisdom of santayana par persée"&gt;à la vie intérieure, &lt;/a&gt; à l’art et à la religion sans renoncer au matérialisme, en traitant les essences comme objets de pensée plutôt que comme entités séparées. Il accorde une importance centrale à l’esthétique et à une lecture naturaliste de la religion et de la morale. Dans The Sense of Beauty et La Vie de la raison, il analyse la beauté comme « plaisir objectivé » et montre comment religion, art et éthique s’enracinent dans la nature humaine et ses besoins, tout en remplissant des fonctions symboliques et existentielles précieuses. Son influence s’étend à la philosophie américaine, à l’esthétique, et à certaines formes de réalisme critique, même si son style littéraire et son indépendance d’esprit le rendent parfois difficile à classer dans une école précise. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Santayana"   title=" Wikipedia"&gt;George SANTAYANA&lt;/a&gt; était un philosophe hispano-américain, né à Madrid et formé à Harvard, qui occupe une place singulière dans la philosophie du XXᵉ siècle par son alliance d’un naturalisme matérialiste rigoureux et d’une sensibilité littéraire, esthétique et religieuse. &lt;/p&gt; &lt;p&gt; Il défend un naturalisme radical : pour lui, tout ce qui existe relève de la matière et de ses configurations ; la conscience, la raison, la culture sont des phénomènes émergents de l’activité biologique et sociale. Il refuse cependant de réduire la vie de l’esprit à un simple épiphénomène sans intérêt : il prend au sérieux l’art, la religion, la morale comme réalités à expliquer, sans pour autant leur accorder un statut ontologique indépendant de la matière. &lt;a href="https://www.youtube.com/watch?v=86qYBc2BA6k" title="the philosophy of george santayana par let’s talk philosophy"&gt;" Cette position &lt;/a&gt;  lui permet de critiquer à la fois l’idéalisme allemand et un matérialisme scientiste étroit, en proposant un matérialisme humaniste. &lt;/p&gt; &lt;p&gt; Sur le plan épistémologique, il est un sceptique profond : il soutient qu’aucune proposition n’est « évidente » en soi et que la croyance en l’existence du monde extérieur (y compris celle de soi) ne repose pas sur une démonstration absolue, mais sur des besoins vitaux et des habitudes d’action. Dans Scepticism and Animal Faith (1923), il développe l’idée d’une « foi animale » : des convictions inévitables, nécessaires à l’action, que le scepticisme ne peut entièrement dissoudre, et qu’il faut assumer lucidement plutôt que de prétendre les fonder rationnellement. Il résume cette attitude en disant que le scepticisme est la « chasteté de l’intellect », à préserver jusqu’à ce qu’il puisse être échangé contre une fidélité mature. &lt;/p&gt; &lt;p&gt; Pour articuler son naturalisme et la richesse de la vie spirituelle, il élabore, dans The Realms of Being (1927–1940), une ontologie en quatre « règnes » : l’essence (formes et possibilités intelligibles), la matière (le monde physique, seul véritablement existant), la vérité (ensemble des propositions vraies) et l’esprit (la conscience comme activité émergente). Cette architecture lui permet de garder une place  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_11_5754_t1_0593_0000_2" title="the essential wisdom of santayana par persée"&gt;à la vie intérieure, &lt;/a&gt; à l’art et à la religion sans renoncer au matérialisme, en traitant les essences comme objets de pensée plutôt que comme entités séparées. Il accorde une importance centrale à l’esthétique et à une lecture naturaliste de la religion et de la morale. Dans The Sense of Beauty et La Vie de la raison, il analyse la beauté comme « plaisir objectivé » et montre comment religion, art et éthique s’enracinent dans la nature humaine et ses besoins, tout en remplissant des fonctions symboliques et existentielles précieuses. Son influence s’étend à la philosophie américaine, à l’esthétique, et à certaines formes de réalisme critique, même si son style littéraire et son indépendance d’esprit le rendent parfois difficile à classer dans une école précise. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4205,7 +4228,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Edward_Moore"  title=" Wikipedia"&gt;George Edward MOORE&lt;/a&gt; était un philosophe anglais considéré comme l'un des fondateurs de la &lt;a href="https://www.youtube.com/watch?v=SPm8S3lmML8"  title=" G.E. Moore : « Preuve d'un monde extérieur » par Simon Cushing "&gt;philosophie analytique &lt;/a&gt; aux côtés de Bertrand Russell et Ludwig Wittgenstein. Il a enseigné toute sa carrière à l'université de Cambridge, où il a influencé des générations d'étudiants par sa clarté analytique et sa défense du sens commun. Ses travaux portent principalement sur l'éthique, l'épistémologie et la métaphysique, critiquant l'idéalisme dominant de son époque. &lt;/p&gt; &lt;p&gt; Il rejette les systèmes grandioses pour analyser minutieusement les concepts philosophiques, favorisant la clarté et le sens commun contre les excès métaphysiques. Il défend l'existence du monde externe via des &lt;a href="https://www.youtube.com/watch?v=p4fFl-J0Vks" title=" Le non-naturalisme de G.E. Moore (argumentation par questions ouvertes et intuitionnisme : métaét...r par Philosophy Vibe"&gt;arguments simples&lt;/a&gt;, comme pointer du doigt des objets dans "A Proof of the External World" (1939), et affirme des vérités évidentes comme "Voici une main humaine" dans "A Defence of Common Sense" (1925). En épistémologie, il combat le scepticisme en soulignant que les certitudes ordinaires résistent aux doutes philosophiques. &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Principia Ethica (1903), introduit l'argument de la "question ouverte" contre le naturalisme moral: définir le bien par plaisir ou désir laisse ouverte la question "Est-ce bon?". Le bien est une propriété non naturelle, appréhendée par intuition morale, intrinsèquement désirable en soi, comme la beauté des états de conscience. Cela inspire la méta-éthique et critique  &lt;a href="https://www.persee.fr/doc/enphi_0986-1653_1999_num_50_1_16015"  title="G. E. Moore et la critique de l'utilitarisme évolutionniste de Spencer par Persée"&gt;l'utilitarisme réducteur&lt;/a&gt;, bien qu'il nuance son intuitionnisme pour éviter les formes classiques. Viennent ensuite des Œuvres comme - Philosophical Studies (1922): recueil d'essais sur perception et connaissance ainsi que - Some Main Problems of Philosophy (1953, posthume): conférences sur le réalisme. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Edward_Moore"  title=" Wikipedia"&gt;George Edward MOORE&lt;/a&gt; était un philosophe anglais considéré comme l'un des fondateurs de la &lt;a href="https://www.youtube.com/watch?v=SPm8S3lmML8"  title=" G.E. Moore : « Preuve d'un monde extérieur » par Simon Cushing "&gt;philosophie analytique &lt;/a&gt; aux côtés de Bertrand Russell et Ludwig Wittgenstein. Il a enseigné toute sa carrière à l'université de Cambridge, où il a influencé des générations d'étudiants par sa clarté analytique et sa défense du sens commun. Ses travaux portent principalement sur l'éthique, l'épistémologie et la métaphysique, critiquant l'idéalisme dominant de son époque. &lt;/p&gt; &lt;p&gt; Il rejette les systèmes grandioses pour analyser minutieusement les concepts philosophiques, favorisant la clarté et le sens commun contre les excès métaphysiques. Il défend l'existence du monde externe via des &lt;a href="https://www.youtube.com/watch?v=p4fFl-J0Vks" title=" Le non-naturalisme de G.E. Moore (argumentation par questions ouvertes et intuitionnisme : métaét...r par Philosophy Vibe"&gt;arguments simples&lt;/a&gt;, comme pointer du doigt des objets dans "A Proof of the External World" (1939), et affirme des vérités évidentes comme "Voici une main humaine" dans "A Defence of Common Sense" (1925). En épistémologie, il combat le scepticisme en soulignant que les certitudes ordinaires résistent aux doutes philosophiques. &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Principia Ethica (1903), introduit l'argument de la "question ouverte" contre le naturalisme moral: définir le bien par plaisir ou désir laisse ouverte la question "Est-ce bon?". Le bien est une propriété non naturelle, appréhendée par intuition morale, intrinsèquement désirable en soi, comme la beauté des états de conscience. Cela inspire la méta-éthique et critique  &lt;a href="https://www.persee.fr/doc/enphi_0986-1653_1999_num_50_1_16015"  title="G. E. Moore et la critique de l'utilitarisme évolutionniste de Spencer par Persée"&gt;l'utilitarisme réducteur&lt;/a&gt;, bien qu'il nuance son intuitionnisme pour éviter les formes classiques. Viennent ensuite des Œuvres comme ; Philosophical Studies (1922): recueil d'essais sur perception et connaissance ainsi que ; Some Main Problems of Philosophy (1953, posthume): conférences sur le réalisme. &lt;/p&gt; 
 ​</t>
         </is>
       </c>
@@ -4252,8 +4275,10 @@
       <c r="D31" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>270</v>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile"  title=" Wikipedia"&gt;Giovanni GENTILE&lt;/a&gt; était un philosophe italien connu pour  son rôle de  &lt;a href="https://www.persee.fr/doc/xxs_0294-1759_1989_num_21_1_2089"  title="Giovanni Gentile, philosophe du fascisme par Persée"&gt;"philosophe officiel"&lt;/a&gt; du fascisme italien. Sa philosophie, qu'il appelle "l'idéalisme actuel" ou "actualisme", est une réinterprétation radicale de l'idéalisme hégélien. Ses idées clés sont :&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Id%C3%A9alisme_actuel"  title="Giovanni Gentile, L’Esprit, acte pur par Wikipedia"&gt;L'Acte Pur&lt;/a&gt; : Au cœur de sa philosophie se trouve le concept de "l'acte pur" de la pensée où la seule réalité est celle du "penser dans son actualité" ou "l'acte de penser". L'esprit ne se contente pas de connaître une réalité préexistante, il la crée dans l'acte même de penser. Il n'y a pas de réalité en soi, indépendante du sujet pensant. Tout ce qui est, est l'actualisation de la pensée. &lt;/p&gt; &lt;p&gt;Unité de Sujet et Objet : il rejette la dualité traditionnelle entre sujet connaissant et objet connu. Dans l'acte pur de la pensée, le sujet et l'objet sont indissociables et se constituent mutuellement. La connaissance n'est pas une simple &lt;a href="https://www.youtube.com/watch?v=OvkBWeT-51A"  title="Giovanni Gentile, pedagogia pur par non Puoi Non Saperlo"&gt;réception passive&lt;/a&gt; d'informations, mais un acte créateur. &lt;/p&gt; &lt;p&gt;Rejet de l'Individualisme et Primauté de l'État : L'individu n'a pas de sens pris en dehors de l'État. L'État n'est pas une somme d'individus, mais une entité éthique et spirituelle supérieure qui donne forme et signification à l'existence individuelle. Les droits individuels sont subordonnés à l'État, car c'est l'État qui les rend possibles et qui en définit le cadre. &lt;/p&gt; &lt;p&gt;L'État Éthique Totalitaire : L'État doit être un "État éthique" qui incarne la volonté collective et la réalisation de l'esprit. Cette conception justifie le totalitarisme, car l'État est le seul détenteur de l'autorité, et l'individu doit lui être parfaitement soumis pour le bien collectif. Il n'y a pas de liberté individuelle en dehors de l'État. &lt;/p&gt;  </t>
+        </is>
       </c>
       <c r="F31" s="7" t="s">
         <v>271</v>
@@ -4340,8 +4365,10 @@
       <c r="D33" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>288</v>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Buber"  title=" Wikipedia"&gt;Martin BUBER&lt;/a&gt; était un philosophe juif autrichien surtout célèbre pour sa pensée du dialogue et de la rencontre "Ich und Du" (I and Thou). Sa biographie et son œuvre ont eu une influence durable sur la philosophie politique, la théologie et l’éducation.  Son parcours intellectuel est marqué par une “philosophie du dialogue” qui cherche à rendre l’existence vécue comme  &lt;a href="https://www.youtube.com/watch?v=x2C7AQRu-iw" title=" La Solitude Moderne : La Réponse de Martin Buber (Philosophie Pratique) par Philosopheasy en français"&gt;relation authentique &lt;/a&gt; plutôt que comme simple connaissance ou instrumentalisation de l’autre. &lt;/p&gt; &lt;p&gt;  Avec Franz Rosenzweig, il fonde et dirige des institutions d’éducation juive et développe une pédagogie fondée sur le dialogue entre les individus et entre le peuple juif et le monde extérieur. Cette collaboration est centrale dans son développement. Son oeuvre majeure : &lt;a href="https://www.youtube.com/watch?v=obuZPJirPkE" title=" Martin Buber : Moi et Tu par PhilosophyToons"&gt;" l’essai Ich und Du" &lt;/a&gt; paru en 1923 propose que les relations humaines ne peuvent pas être réduites à des rapports utilitaires ou à des abstractions. Cette pensée s’applique à l’éthique, à la religion, et à l’éducation. Il oppose l’“I–It” (je-tu) à l’“I–Thou” (je-toi), arguant que l’existence humaine se réalise vraiment dans des relations vécues comme présence et écoute réciproque.&lt;/p&gt; &lt;p&gt;  Il a été actif dans l’éducation des adultes juifs en Allemagne et a plaidé pour une pédagogie fondée sur l’engagement personnel et la relation authentique plutôt que sur l’instruction pure. Ses idées inspirent des discussions sur le droit à la différence, le pluralisme religieux et les approches éthiques des conflits, tout en restant critiques des formes de discours essentialistes. &lt;/p&gt;  &lt;audio controls title="Martin Buber, sentinelle de l'humanité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-03.01.2016-ITEMA_20879863-2015C14958E0049-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F33" s="7" t="s">
         <v>289</v>
@@ -4857,8 +4884,12 @@
       <c r="D44" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>381</v>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein"  title=" Wikipedia"&gt;Ludwig WITTGENSTEIN&lt;/a&gt; était un philosophe autrichien énigmatique et influent souvent divisée en deux périodes distinctes, le "premier" et le "second" Wittgenstein. Le premier, &lt;a href="https://www.youtube.com/watch?v=4w5xzgna1l0&amp;list=PLyfQgbpaPz7hZqscDHbJVRNtcDRHZ5mGr"  title="Tractatus logico-philosophicus, Ludwig Wittgenstein par Thibault BELZACQ"&gt; "le Tractatus Logico-Philosophicus"&lt;/a&gt;  (1921) est un texte dense, écrit de manière aphoristique, et qui se présente comme la solution à tous les problèmes philosophiques. Sa thèse centrale est que le langage a pour but de décrire le monde, qui est constitué de faits.&lt;/p&gt;
+&lt;p&gt; La théorie de la représentation :   &lt;a href="https://www.youtube.com/watch?v=To2Eva4vK3s" title="Le Philosophe qui a Changé le Langage à Jamais | Ludwig Wittgenstein  par Le Coseiller"&gt; le langage&lt;/a&gt; est une "image" du monde. Une phrase a un sens si et seulement si elle dépeint un état de choses possible dans la réalité. Le langage et le monde partagent une structure logique commune. &lt;/p&gt;
+&lt;p&gt; La distinction entre "dire" et "montrer" : le langage ne peut dire que ce qui a un sens. Les choses qui ne peuvent pas être décrites (comme la logique elle-même, l'éthique, la métaphysique, la religion) ne peuvent pas être "dites", mais elles se "montrent" à travers le langage. Le célèbre dernier aphorisme du Tractatus est : "Ce dont on ne peut parler, il faut le taire." &lt;/p&gt; &lt;p&gt; La fin de la philosophie ? : il pensait avoir résolu les problèmes de la philosophie en montrant qu'ils provenaient d'une mauvaise utilisation du langage. Les questions métaphysiques (sur l'être, l'âme, etc.) sont, selon lui, dénuées de sens, car elles tentent de "dire" ce qui ne peut qu'être "montré". Après la publication de cet ouvrage, il a abandonné la philosophie pendant près de dix ans, pensant avoir achevé son travail. &lt;/p&gt; &lt;p&gt; Le "second" :   &lt;a href="https://wittgenstein.fr/category/lectures-des-recherches-philosophiques/"  title="Ludwig Wittgenstein  par Julien Gautier"&gt; les "Recherches philosophiques"&lt;/a&gt;  à la fin des années 1920. Il a commencé à remettre en question les fondations de son propre Tractatus. Publiées à titre posthume en 1953, elles marquent une rupture radicale avec sa première pensée.&lt;/p&gt; &lt;p&gt; Le concept de  &lt;a href="https://www.youtube.com/watch?v=To2Eva4vK3s"  title="Ludwig Wittgenstein la philosophie qui a changé le langage par Le Conseiller"&gt; "jeux de langage" : &lt;/a&gt; Il abandonne la théorie de la représentation pour une nouvelle conception du langage qui n'est pas un miroir du monde, mais un outil. Le sens d'un mot n'est pas son référent dans la réalité, mais son usage dans un contexte donné. Il introduit la notion de "jeux de langage" pour désigner les différentes activités humaines où le langage est utilisé (commander, questionner, raconter une blague, etc.). Chaque "jeu" a ses propres règles et sa propre grammaire.&lt;/p&gt; &lt;p&gt;La philosophie comme thérapie : il ne considère plus que les problèmes philosophiques peuvent être résolus, mais qu'ils peuvent être dissous. L'objectif de la philosophie est de démêler les confusions que le langage crée, en montrant comment les mots sont utilisés dans différents "jeux". La philosophie n'est plus une quête de la vérité ultime, mais une "thérapie" qui aide à "voir clair" dans notre usage du langage. &lt;/p&gt; &lt;p&gt; "Formes de vie" : La signification du langage est profondément enracinée dans notre pratique collective et nos actions, dans ce qu'il appelle nos "formes de vie". Les règles d'un "jeu de langage" ne peuvent être comprises qu'à l'intérieur de ces pratiques sociales partagées. Il s'oppose à l'idée d'un "langage privé", montrant que le sens nécessite un accord public et une communauté d'utilisateurs. &lt;/p&gt;  &lt;audio controls title="Ludwig Wittgenstein ou la philosophie de l’indicible par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-12.07.2020-ITEMA_22380918-2020C22785E0017-1779455909.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F44" s="7" t="s">
         <v>382</v>
@@ -5094,7 +5125,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Hayek"  title=" Wikipedia"&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme&lt;/a&gt;, il en fait un fondement de sa critique du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(politique)"  title=" Constructivisme  par Wikipedia"&gt;"constructivisme rationnel" :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'"ordre spontané" des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique. &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une "prétention au savoir" illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href="https://www.youtube.com/watch?v=TiGv4YcFieQ"  title="La route de la servitude  par Capsio"&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine.https://fr.wikipedia.org/wiki/Friedrich_Hayek &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Hayek"  title=" Wikipedia"&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme&lt;/a&gt;, il en fait un fondement de sa critique du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(politique)"  title=" Constructivisme  par Wikipedia"&gt;"constructivisme rationnel" :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'"ordre spontané" des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique. &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une "prétention au savoir" illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href="https://www.youtube.com/watch?v=TiGv4YcFieQ"  title="La route de la servitude  par Capsio"&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5337,7 +5368,7 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders"  title=" Wikipedia"&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href="https://www.youtube.com/watch?v=r4eq7EoRtTQ"  title=" Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope"&gt;"l'obsolescence de l'homme"&lt;/a&gt;. Selon lui, l'homme moderne est   &lt;a href="https://books.openedition.org/pur/52513?lang=fr" title="La notion de « supraliminaire » chez Günther Anders par OpenEdition"&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression "prométhée honteux"  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href="https://www.youtube.com/watch?v=8xIiiYQJymQ"  title="L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée"&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href="https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde" title="l'être jetable Günther Anders par La vie des idées"&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&lt;audio controls title="Avoir raison avec... Günther Anders par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders"  title=" Wikipedia"&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href="https://www.youtube.com/watch?v=r4eq7EoRtTQ"  title=" Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope"&gt;"l'obsolescence de l'homme"&lt;/a&gt;. Selon lui, l'homme moderne est   &lt;a href="https://books.openedition.org/pur/52513?lang=fr" title="La notion de « supraliminaire » chez Günther Anders par OpenEdition"&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression "prométhée honteux"  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href="https://www.youtube.com/watch?v=8xIiiYQJymQ"  title="L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée"&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href="https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde" title="l'être jetable Günther Anders par La vie des idées"&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;audio controls title="Avoir raison avec... Günther Anders par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F54" s="7" t="s">
@@ -5390,7 +5421,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate.https://de.wikipedia.org/wiki/Fernand_Van_Steenberghen &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison.https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate. &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5619,8 +5650,11 @@
       <c r="D60" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>510</v>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isaiah_Berlin" title=" Wikipedia"&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href="https://www.youtube.com/watch?v=zSCS0toL5wc" title="Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français"&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M"  title="Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français"&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M" title=" Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français"&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant "décence humaine" face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : "Karl Marx: His Life and Environment" paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. "The Hedgehog and the Fox" paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. "Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F60" s="7" t="s">
         <v>511</v>
@@ -5668,8 +5702,10 @@
       <c r="D61" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="E61" s="12" t="s">
-        <v>518</v>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eugenio_Garin" title=" Wikipedia"&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F61" s="7" t="s">
         <v>519</v>
@@ -5714,7 +5750,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren" title=" Wikipedia"&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une "perplexité" ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il développe une "éthique de la perplexité" : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href="https://www.youtube.com/watch?v=L3sJ7AvOT08"  title=" José Luis Aranguren  par Lecturas Fragmentadas"&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme.https://www.athees.net/pourquoi-latheisme-et-pas-lagnosticisme/ &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique "progressiste" puis laïc engagé, il valorise la dissidence intellectuelle et une "justice sociale" cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren" title=" Wikipedia"&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une "perplexité" ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il développe une "éthique de la perplexité" : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href="https://www.youtube.com/watch?v=L3sJ7AvOT08"  title=" José Luis Aranguren  par Lecturas Fragmentadas"&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme. &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique "progressiste" puis laïc engagé, il valorise la dissidence intellectuelle et une "justice sociale" cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -5805,8 +5841,11 @@
       <c r="D64" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="E64" s="17" t="s">
-        <v>543</v>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Langshaw_Austin" title=" Wikipedia"&gt;John LANGSHAW AUSTIN&lt;/a&gt;  était un philosophe britanique de la philosophie analytique, né à Lancaster. Issu d'une famille modeste, il étudie les lettres classiques et la philosophie à Oxford, où il excelle et devient fellow en 1933. Pendant la Seconde Guerre mondiale, il sert dans les services de renseignement britanniques, jouant un rôle clé dans la préparation du Débarquement de Normandie grâce à son analyse précise de renseignements topographiques, avant de reprendre sa carrière académique à Oxford comme professeur de philosophie morale. &lt;/p&gt; &lt;p&gt; Il est le représentant emblématique de la « philosophie du langage ordinaire », une approche qu'il qualifie lui-même de &lt;a href="https://www.persee.fr/doc/igram_0222-9838_2010_num_124_1_4073"  title="Place et raison de l’analyse phénoménologique en linguistique par Persée"&gt;« phénoménologie linguistique ».&lt;/a&gt;  Il critique les théories abstraites des philosophes en analysant les usages quotidiens des mots, montrant leur subtilité et leur capacité à marquer des distinctions fines que les systèmes formels ignorent. Son travail sur la perception défend un réalisme direct contre les doctrines des  &lt;a href="https://www.youtube.com/watch?v=JhzzLyLCRis"  title="Les performatifs ces mots qui nous changent par Survivre aux sciences humaines"&gt;« sense-data », &lt;/a&gt; en s'appuyant sur le sens commun linguistique. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la théorie des actes de langage, développée dans ses conférences de Harvard publiées posthumement sous le titre How to Do Things with Words (en français Quand dire, c'est faire). Il distingue les énoncés performatifs, qui accomplissent une action (comme « Je vous déclare mari et femme »), des énoncés constatifs descriptifs, avant de montrer que tout discours est performatif : locutoire (dire quelque chose), illocutoire (intention) et perlocutoire (effet). Cette idée fonde la pragmatique moderne et influence Searle ou la philosophie du droit. &lt;/p&gt; &lt;p&gt; L'héritage d'Austin perdure dans le  &lt;a href="https://www.erudit.org/fr/revues/philoso/2006-v33-n1-philoso1132/012957ar/"  title="Le contexte sémantique par Survivre aux Eridit"&gt;contextualisme sémantique, &lt;/a&gt; où la vérité d'une affirmation dépend du contexte d'énonciation, et dans l'ordinaireisme via Stanley Cavell. Mort prématurément d'un cancer à 48 ans, son œuvre concise mais profonde révolutionne la compréhension du langage comme action sociale, reliant philosophie, linguistique et sciences cognitives. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F64" s="7" t="s">
         <v>544</v>
@@ -5898,8 +5937,11 @@
       <c r="D66" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="E66" s="17" t="s">
-        <v>560</v>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Grice" title=" Wikipedia"&gt;Paul GRICE&lt;/a&gt;  était un philosophe britanique de l'école analytique, est né à Birmingham et a étudié à Oxford, où il a été influencé par des figures comme Gilbert Ryle et J.L. Austin, dont il fut un collaborateur proche au sein du "samedi matin" oxonien. Il a enseigné à Oxford avant de rejoindre les États-Unis, notamment Berkeley, où il a terminé sa carrière. Spécialiste de philosophie du langage et de l'esprit, il a révolutionné la pragmatique en distinguant le sens littéral du sens impliqué dans les échanges. &lt;/p&gt; &lt;p&gt; Il  est surtout célèbre pour son &lt;a href="https://www.youtube.com/watch?v=xt4zFGdTUow"  title=" Paul Grice, cooperative principe  par Evan Ashworthe"&gt;"principe de coopération" &lt;/a&gt; et ses quatre &lt;a href="https://www.youtube.com/watch?v=WGKzjVQZAgw"  title=" Paul Grice, les maximes  par Steve Aswald"&gt; maximes conversationnelles, &lt;/a&gt; exposées dans sa conférence &lt;a href="https://www.persee.fr/doc/comm_0588-8018_1979_num_30_1_1446"  title=" Logique et conversation  par Persée"&gt;"Logic and Conversation" &lt;/a&gt; (1967). Ces maximes – quantité (fournir ni trop ni trop peu d'informations), qualité (dire la vérité et avoir des preuves), relation (être pertinent) et manière (être clair, éviter l'ambiguïté, être bref et ordonné) – sous-tendent toute communication efficace. Elles expliquent comment les interlocuteurs infèrent des significations au-delà des mots explicites. &lt;/p&gt; &lt;p&gt; Son concept clé d'"implicature conversationnelle" montre que les violations apparentes des maximes (par exemple, être vague pour suggérer quelque chose) génèrent des sens implicites attendus par les participants rationnels. Complétant la théorie des actes de langage d'Austin (locutoire, illocutoire, perlocutoire), il met l'accent sur l'intention du locuteur et la reconnaissance mutuelle des intentions, fondant ainsi une approche inférentielle de la communication. &lt;/p&gt; &lt;p&gt; L'héritage de Grice imprègne la linguistique, la psychologie cognitive et l'IA, influençant des penseurs comme Sperber et Wilson ou la philosophie contemporaine du témoignage et de  &lt;a href="https://www.youtube.com/watch?v=FVSfFGcVP7U"  title=" Paul Grice, aspect of reason  par Philosophie Analytique"&gt;la rationalité. &lt;/a&gt; Ses idées sur la signification non naturelle et la distinction sens/force restent des outils analytiques majeurs pour décoder ironie, sarcasme ou sous-entendus. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F66" s="7" t="s">
         <v>561</v>
@@ -6080,8 +6122,11 @@
       <c r="D70" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="E70" s="11" t="s">
-        <v>595</v>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stephen_Toulmin"  title=" Wikipedia"&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href="https://www.youtube.com/watch?v=J1WDW2F-KBs"  title=" le modèle de Toulmin  par Mooc Cyu"&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme "probablement"), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects "field-dependent" (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique. &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un "champ stable" partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href="https://www.youtube.com/watch?v=hv7BUYzRiiU"  title=" le cartesian theatre de Toulmin  par Edwin gardner"&gt;"pluralistic conceptual relativism" &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F70" s="7" t="s">
         <v>596</v>
@@ -6124,8 +6169,10 @@
       <c r="D71" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>603</v>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antony_Flew"  title=" Wikipedia"&gt;Antony FLEW&lt;/a&gt; était un philosophe analytique britanique connu pour ses travaux en philosophie de la religion et son &lt;a href="https://www.youtube.com/watch?v=kPxo32o7M_U"  title=" De l'athéisme au théisme : l'histoire fascinante du célèbre philosophe Antony Flew  par Vers Jésus"&gt;évolution spectaculaire &lt;/a&gt; d'un athéisme militant vers un déisme basé sur l'évidence scientifique. &lt;/p&gt; &lt;p&gt; Figure majeure de l'athéisme académique pendant plus de 50 ans, il présenta son célèbre argument &lt;a href="https://www.youtube.com/watch?v=VoLNeEWqJfU"  title=" Theology and Falsification - Antony Flew | Reading  par Jamie Micheli"&gt;"Theology and Falsification" &lt;/a&gt; en 1950 au Socratic Club, affirmant que les énoncés théologiques sont invérifiables et donc vides de sens. En 2004, âgé de 81 ans, il annonça son adhésion au déisme, inspiré par le "fine-tuning" de l'univers, la complexité de l'ADN et l'origine de la vie, sans jamais embrasser une religion révélée. Il mourut en 2010, réaffirmant un Dieu aristotélicien, "horloger divin" distant.&lt;/p&gt; &lt;p&gt; Il défendait la "présomption d'athéisme" : partir du rejet de Dieu jusqu'à preuve empirique contraire, critiquant la vie après la mort, la défense du libre arbitre face au mal et la cohérence du concept divin. Son virage déiste, détaillé dans "There Is a God" paru en 2007, mettait l'accent sur l'intelligence derrière la complexité cosmique et biologique, rejetant le matérialisme pur comme insuffisant pour expliquer conscience et moralité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : "The Presumption of Atheism" paru en 1976 : Fondement rationnel de l'athéisme comme position par défaut. "God and Philosophy" paru en 1966 : Critique des preuves traditionnelles de Dieu et "Thinking About Thinking" paru en 1975 : Introduction du sophisme écossais.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F71" s="7" t="s">
         <v>604</v>
@@ -6262,8 +6309,11 @@
       <c r="D74" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E74" s="11" t="s">
-        <v>625</v>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anthony_Quinton"  title=" Wikipedia"&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3"  title=" Anthony Quinton Hume 2000  par Persée"&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions. &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href="https://fr.wikipedia.org/wiki/Nominalisme"  title=" nominalisme par Wikipedia"&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href="https://fr.wikipedia.org/wiki/Conservatisme"  title=" conservatisme par Wikipedia"&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F74" s="7" t="s">
         <v>626</v>
@@ -6359,7 +6409,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ivan_Illich"  title=" Wikipedia"&gt;Ivan ILLICH&lt;/a&gt;  était un philosophe, théologien et critique social austro-américain d'origine multiculturelle, connu pour sa radicalité dans la dénonciation des institutions modernes qu'il juge aliénantes et contre-productives, prônant une société conviviale fondée sur &lt;a href="https://ecologica.education/2023/11/08/ivan-illich-penseur-de-lecologie-politique/" title="Ivan Illich, penseur de l’écologie politique par Ecologica"&gt;l'autonomie humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; En 1961, au Mexique, il fonde à Cuernavaca le CIDOC (Centre interculturel de documentation), un laboratoire expérimental attirant des milliers d'intellectuels pour des séminaires interdisciplinaires sur éducation, développement et religion ; fermé en 1976 pour éviter son institutionnalisation, ce lieu forge sa méthode provocatrice post-Mai 68. &lt;/p&gt; &lt;p&gt; Il héorise la contre-productivité : tout processus industriel (éducation, médecine, transport) passe d'amplificateur d'autonomie à générateur de dépendance et d'inégalités, inversant sa finalité. Pour lui, les racines chrétiennes sont perverties : Incarnation ouvre à l'amour interpersonnel, mais modernité institutionnalise en monopoles salvifiques, ni accomplissement ni négation du christianisme, mais sa dégénérescence.&lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  &lt;a href="https://www.youtube.com/watch?v=axeVcD8emQY"  title="IVAN ILLICH - Une société sans école par 1000 idées de culture generale"&gt;"Une société sans école" &lt;/a&gt; paru en 1971 : l'école, monopole étatique, désapprend plus qu'elle n'enseigne ; propose "réseaux d'apprentissage" pair-à-pair, libres et gratuits, pour restaurer l'éducation vernaculaire. - "La Convivialité" paru en 1973  : définit l'outil convivial (ex. : bicyclette) comme accessible, autonome et égalitaire ; introduit le "monopole radical" où la technique surpuissante exclut les alternatives et infantilise. - "Némésis médicale paru en 1975, Énergie et équité"  en 1973 et "Le Chômage créateur" en 1977 : démontre que santé, vitesse, emploi deviennent contre-productifs au-delà d'un seuil.&lt;/p&gt;    &lt;audio controls title="Ivan Illich : "L'école enseigne à l'enfant qu'il doit être inévitablement classé par un bureaucrate" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-02.05.2017-ITEMA_21310924-2012C3372E0981-NET_B3E76531-3403-4CED-9218-298FB5C06B8B_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ivan_Illich"  title=" Wikipedia"&gt;Ivan ILLICH&lt;/a&gt;  était un philosophe, théologien et critique social austro-américain d'origine multiculturelle, connu pour sa radicalité dans la dénonciation des institutions modernes qu'il juge aliénantes et contre-productives, prônant une société conviviale fondée sur &lt;a href="https://ecologica.education/2023/11/08/ivan-illich-penseur-de-lecologie-politique/" title="Ivan Illich, penseur de l’écologie politique par Ecologica"&gt;l'autonomie humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; En 1961, au Mexique, il fonde à Cuernavaca le CIDOC (Centre interculturel de documentation), un laboratoire expérimental attirant des milliers d'intellectuels pour des séminaires interdisciplinaires sur éducation, développement et religion ; fermé en 1976 pour éviter son institutionnalisation, ce lieu forge sa méthode provocatrice post-Mai 68. &lt;/p&gt; &lt;p&gt; Il héorise la contre-productivité : tout processus industriel (éducation, médecine, transport) passe d'amplificateur d'autonomie à générateur de dépendance et d'inégalités, inversant sa finalité. Pour lui, les racines chrétiennes sont perverties : Incarnation ouvre à l'amour interpersonnel, mais modernité institutionnalise en monopoles salvifiques, ni accomplissement ni négation du christianisme, mais sa dégénérescence.&lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : &lt;a href="https://www.youtube.com/watch?v=axeVcD8emQY"  title="IVAN ILLICH - Une société sans école par 1000 idées de culture generale"&gt;"Une société sans école" &lt;/a&gt; paru en 1971 : l'école, monopole étatique, désapprend plus qu'elle n'enseigne ; propose "réseaux d'apprentissage" pair-à-pair, libres et gratuits, pour restaurer l'éducation vernaculaire. "La Convivialité" paru en 1973  : définit l'outil convivial (ex. : bicyclette) comme accessible, autonome et égalitaire ; introduit le "monopole radical" où la technique surpuissante exclut les alternatives et infantilise. "Némésis médicale paru en 1975, Énergie et équité"  en 1973 et "Le Chômage créateur" en 1977 : démontre que santé, vitesse, emploi deviennent contre-productifs au-delà d'un seuil.&lt;/p&gt;    &lt;audio controls title="Ivan Illich : "L'école enseigne à l'enfant qu'il doit être inévitablement classé par un bureaucrate" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-02.05.2017-ITEMA_21310924-2012C3372E0981-NET_B3E76531-3403-4CED-9218-298FB5C06B8B_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -6727,11 +6777,16 @@
       <c r="C84" s="7" t="s">
         <v>702</v>
       </c>
-      <c r="D84" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>704</v>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Javier MUGUERZA</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Javier_Muguerza"   title=" Wikipedia"&gt;Javier MUGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la "perplexité" comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses "trois Critiques" (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F84" s="7" t="s">
         <v>705</v>
@@ -6774,8 +6829,15 @@
       <c r="D85" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="E85" s="10" t="s">
-        <v>711</v>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Derek_Parfit"   title=" Wikipedia"&gt;Derek PARFIT&lt;/a&gt; était un philosophe britannique spécialiste de la  morale analytique, connu pour ses travaux sur l’identité personnelle, la rationalité pratique et l’éthique. Célèbre pour sa thèse selon laquelle  &lt;a href="https://www.youtube.com/watch?v=ae5jSi2BL0Y"  title="Identités fragmentées (Derek Parfit) par Noé Jacomet "&gt; l’identité personnelle &lt;/a&gt; n’est pas "ce qui importe" réellement dans la survie.  Deux grands ouvrages structurent son influence :&lt;/p&gt; &lt;p&gt;"Reasons and Persons" paru en 1984 est souvent considéré comme l’un des livres les plus importants de philosophie morale du XXᵉ siècle. L’ouvrage traite notamment de la rationalité, de l’identité personnelle à travers le temps et de nos obligations envers les générations futures, en s’appuyant sur une multitude d’expériences de pensée. &lt;/p&gt; &lt;p&gt;"On What Matters" paru en 2011 propose une théorie unifiée de la morale, parfois appelée la "Triple Theory".  Il y défend un réalisme moral robuste et cherche à montrer que le conséquentialisme, le kantisme et le contractualisme convergent vers des jugements moraux communs quand ils sont correctement révisés. &lt;/p&gt; &lt;p&gt; Il remet en question le rôle central de l’intérêt personnel et &lt;a href="https://laviedesidees.fr/David-Edmonds-Parfit"  title=" "une vie de philosophe par laviedesidées"&gt; propose une conception &lt;/a&gt; plus impersonnelle des raisons morales. Il critique les théories morales auto‑destructrices   qui, suivies rigoureusement, ne servent plus les objectifs qu’elles se donnent. Il défend un réalisme normatif : pour lui, il existe des vérités morales objectives, indépendantes de nos désirs ou de nos conventions sociales. &lt;/p&gt; &lt;p&gt; Il a profondément marqué la réflexion sur nos devoirs envers les générations futures et la taille optimale de la population. Il formule des paradoxes célèbres en éthique populationnelle, montrant combien il est difficile de concilier l’idée de maximiser le bien‑être total avec l’intuition que certains scénarios sont moralement problématiques. Il soutient que les personnes aisées ont de fortes obligations envers les plus pauvres et envers ceux qui ne sont pas encore nés, perspective qui a influencé de nombreux débats sur l’altruisme efficace, le climat et la justice intergénérationnelle. &lt;/p&gt; 
+​
+​
+​
+​
+</t>
+        </is>
       </c>
       <c r="F85" s="7" t="s">
         <v>712</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -4698,8 +4698,11 @@
       <c r="D40" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E40" s="11" t="s">
-        <v>346</v>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset"  title=" Wikipedia"&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href="https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/"  title="José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ"&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, &lt;em&gt;La Révolte des masses&lt;/em&gt;, analyse la montée de  &lt;a href="https://www.youtube.com/watch?v=bse3ho0Hk7U"  title="José Ortéga y Gasset : le règne de l’homme masse par Ego Non"&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. Paru en 1929, ce livre décrit l’homme moyen satisfait de lui-même, qui profite des conquêtes de la civilisation sans en reconnaître les exigences. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la dictature de Primo de Rivera, puis en faveur de la République, dont il est élu député en 1931.  &lt;a href="https://www.youtube.com/watch?v=jdB0729NoPg"  title="José Ortéga y Gasset : méditation sur la technique par Edition Allia"&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. En 1923, il fonde la &lt;em&gt;Revista de Occidente&lt;/em&gt;, qui fait connaître la pensée allemande en Espagne. Exilé pendant la guerre civile, il ne rentre qu’en 1945. &lt;/p&gt;   &lt;audio controls title=" José ORTEGA y GASSET, penser la diversité culturelle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F40" s="7" t="s">
         <v>347</v>
@@ -5704,7 +5707,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eugenio_Garin" title=" Wikipedia"&gt;Eugenio GARIN&lt;/a&gt;  fut un grand historien italien de la philosophie, surtout connu pour ses travaux sur la Renaissance et l’humanisme italien. Né à Rieti, il enseigna à Florence puis à l’École normale supérieure de Pise, et il a profondément renouvelé l’étude des idées en les replaçant toujours dans leur contexte historique. &lt;/p&gt; &lt;p&gt; Dans sa méthode, il refusait l’idée d’une vérité philosophique intemporelle et abstraite. Il défendait au contraire une lecture historique des œuvres, attentive aux rapports entre pensée, culture, politique et institutions, ce qui le rapprochait d’une attitude critique envers les certitudes absolues. &lt;/p&gt; &lt;p&gt; Son lien avec  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme &lt;/a&gt; n’est pas celui d’un fondateur ou d’un théoricien direct, mais plutôt celui d’un penseur qui a mis en avant la complexité, le doute et la diversité des positions humaines. Ses travaux sur l’humanisme montrent que la pensée de la Renaissance est traversée par des tensions entre savoir, foi, scepticisme et prudence intellectuelle. &lt;/p&gt; &lt;p&gt; Garin prolonge, d’une certaine manière, l’esprit de l’agnosticisme sans en faire un sujet central. Chez lui, l’essentiel est de comprendre comment les hommes pensent dans une époque donnée, plutôt que de chercher une réponse définitive aux grandes questions métaphysiques. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eugenio_Garin" title=" Wikipedia"&gt;Eugenio GARIN&lt;/a&gt; (1909-2004) est un historien italien de la philosophie, l’un des grands spécialistes de la Renaissance et de l’humanisme italien. Né à Rieti, il étudie à Florence, enseigne d’abord au lycée, puis à l’université de Florence à partir de 1949, et enfin à l’École normale supérieure de Pise. Ses livres, comme &lt;em&gt;L’Humanisme italien&lt;/em&gt; (1947), &lt;em&gt;Moyen Âge et Renaissance&lt;/em&gt; (1954) ou &lt;em&gt;La Culture philosophique de la Renaissance italienne&lt;/em&gt; (1961), ont renouvelé l’étude de cette période.&lt;/p&gt; &lt;p&gt;Pour Garin, l’humanisme n’est pas un simple goût des lettres antiques, comme le pensait Paul Oskar Kristeller, mais une véritable philosophie : en retrouvant les textes anciens par la philologie, les humanistes découvrent l’histoire, et l’homme comme un être qui se façonne lui-même dans la cité. Il refuse l’idée d’une vérité philosophique intemporelle, et lit les œuvres dans leur contexte, attentif aux rapports entre la pensée, la culture, la politique et les institutions. Il montre aussi la place de la magie, de l’astrologie et de l’hermétisme dans la pensée de la Renaissance.&lt;/p&gt; &lt;p&gt;Sans être un théoricien de l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;agnosticisme&lt;/a&gt;, il en partage la prudence : ses travaux décrivent une Renaissance traversée de tensions entre savoir, foi et scepticisme, et il préfère comprendre comment les hommes pensent à une époque donnée plutôt que trancher les grandes questions métaphysiques. Il a aussi écrit l’histoire de la philosophie italienne du XXe siècle, de Croce et Gentile à Gramsci.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F61" s="7" t="s">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -5424,8 +5424,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt;  était un philosophe et prêtre belge thomiste, spécialiste de la philosophie médiévale, qui s'opposa fermement à l'agnosticisme tout en le confrontant dans ses écrits. Professeur à l'Institut supérieur de philosophie de Louvain, il consacra sa carrière à défendre la synthèse thomiste d'Aristote et du christianisme, notamment dans &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages &lt;/a&gt; comme La philosophie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il publia explicitement Saint Thomas contre l'agnosticisme (1974), où il argue que Thomas d'Aquin réfute l'inconnaissabilité de Dieu par la raison naturelle. Pour lui, la métaphysique thomiste démontre l'existence de Dieu via les voies de la causalité et de la finalité, rejetant ainsi le doute agnostique comme une erreur épistémologique moderne. &lt;/p&gt; &lt;p&gt; Catholique convaincu, il critiquait l'agnosticisme kantien ou contemporain pour son renoncement prématuré à la connaissance métaphysique, affirmant que la raison humaine accède à l'être divin sans mysticisme. Ses travaux sur Siger de Brabant et l'aristotélisme latin soulignent les limites du scepticisme médiéval, qu'il voit corrigé par l'Aquinate. &lt;/p&gt; &lt;p&gt; Contrairement aux agnostiques comme Muguerza ou Cioran, il incarne une posture anti-agnostique rigoureuse, ancrée dans la tradition scolastique, où la foi éclaire mais ne supplante pas la raison. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt; (1904-1993) est un prêtre et philosophe belge, grand historien de la philosophie médiévale et représentant du néothomisme de Louvain. Né à Heverlee, il enseigne pendant toute sa carrière à l’Institut supérieur de philosophie de l’université catholique de Louvain, fondé par le cardinal Mercier pour renouveler la pensée de Thomas d’Aquin.&lt;/p&gt; &lt;p&gt;Historien, il consacre ses recherches au XIIIe siècle, l’âge d’or de la scolastique : &lt;em&gt;Siger de Brabant d’après ses œuvres inédites&lt;/em&gt; (1931-1942), &lt;em&gt;Aristote en Occident&lt;/em&gt; (1946) et &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages&lt;/a&gt; comme &lt;em&gt;La Philosophie au XIIIe siècle&lt;/em&gt; (1966). Il y montre comment l’entrée massive des œuvres d’Aristote bouleverse les universités, et conteste l’expression d’« averroïsme latin » : Siger et ses collègues de la faculté des arts pratiquaient plutôt un « aristotélisme hétérodoxe ». Contre Étienne Gilson, il refuse aussi de voir en Bonaventure le chef d’un « augustinisme » opposé à Thomas : sa philosophie est, selon lui, un aristotélisme teinté de néoplatonisme.&lt;/p&gt; &lt;p&gt;Philosophe, il défend une métaphysique réaliste et la possibilité de démontrer l’existence de Dieu par la raison, contre l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;agnosticisme&lt;/a&gt; hérité de Kant. Dans &lt;em&gt;Dieu caché&lt;/em&gt; (1961), puis dans &lt;em&gt;Le Problème de l’existence de Dieu dans les écrits de saint Thomas d’Aquin&lt;/em&gt; (1980), il examine les preuves classiques avec rigueur, jugeant même certaines des « cinq voies » de Thomas insuffisantes, et propose sa propre démonstration à partir de la finitude des êtres.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F55" s="7"/>
@@ -5467,8 +5466,10 @@
       <c r="D56" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>478</v>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Frithjof_Schuon"  title=" Wikipedia"&gt;Frithjof SCHUON&lt;/a&gt;  était un philosophe et maître spirituel suisse, figure centrale de l'école traditionaliste ou &lt;a href="https://www.youtube.com/watch?v=VGiKDhwdrcA&amp;list=PL190FE1CAB151FD5E"  title="Frithjof Schuon: Messenger of the Perennialist Philosophy Trailer par WorldWisdominc"&gt; pérennialiste &lt;/a&gt; aux côtés de René Guénon, Ananda Coomaraswamy et Titus Burckhardt. Initié au soufisme, il voyage en Afrique du Nord, fonde la tariqa Maryamiyya (branche soufie), et s'installe aux États-Unis en 1980 où il vit jusqu'à sa mort. Né à Bâle, il reçoit en 1932, à Mostaganem, en Algérie, l’initiation du maître soufi Ahmad al-Alawi, et vit longtemps à Lausanne. Son livre majeur, &lt;em&gt;De l’unité transcendante des religions&lt;/em&gt; (1948), a été salué par T. S. Eliot. &lt;/p&gt; &lt;p&gt; Il défend la "philosophia perennis", affirmant l'existence d'un Principe absolu (Dieu) d'où émane l'univers, et une Vérité unique sous-jacente à toutes les religions malgré leurs formes exotériques différentes. Les révélations divines (christianisme,&lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1963_num_164_2_7952"  title="Frithjof Schuon. Comprendre l'Islam par Persée"&gt; islam, &lt;/a&gt;  hindouisme, etc.) ne sont que des langages adaptés exprimant la même essence ésotérique primordiale. L'homme accède à une connaissance supra-rationnelle (gnose, intellect divin) par delà la raison discursive, via la métaphysique intégrale inspirée de Platon, Shankara ou Ibn Arabī. &lt;/p&gt; &lt;p&gt; Il dénonce la modernité comme un "âge sombre" marqué par le rationalisme, le matérialisme, l'individualisme, le progressisme et le relativisme. Il distingue ésotérisme (noyau universel, initiation intérieure) et exotérisme (formes religieuses orthodoxes), recommandant une pratique fidèle à une tradition choisie. Il  n'est pas un philosophe spéculatif au sens classique, mais un métaphysicien voyant dans la Tradition le remède au nihilisme contemporain. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F56" s="7" t="s">
         <v>479</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3087,7 +3087,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Owen"  title=" Wikipedia"&gt;Robert OWEN&lt;/a&gt; était un industriel gallois devenu philosophe social, figure majeure du &lt;a href="https://laviedesidees.fr/Robert-Owen-pere-du-socialisme-britannique" style="color:#88A1E9" title="Robert Owen, père du socialisme britannique ? par idées de la vie"&gt;"socialisme utopique"&lt;/a&gt; et l’un des pères du mouvement coopératif et de l’urbanisme social. Il défend une thèse matérialiste du caractère humain : pour lui, le caractère n’est pas inné mais entièrement façonné par les "circonstances" physiques, morales et sociales auxquelles l’individu est exposé dès l’enfance. Il en conclut que l’on ne doit ni louer ni blâmer moralement les individus, mais transformer les institutions et l’environnement pour produire des caractères meilleurs, ce qui fait de l’éducation et de l’organisation sociale les leviers principaux de la réforme morale. &lt;/p&gt; &lt;p&gt; À &lt;a href="https://www.youtube.com/watch?v=QHWn6aPxKtQ" title="New Lanark: Robert Owen's Utopianism and the Latter Day Saints par Centre Place"&gt;New Lanark&lt;/a&gt;, il crée des écoles modèles, dont l’"Institute for the Formation of Character", qui proposent une éducation gratuite, non répressive, axée sur le jeu, la musique et la formation morale plutôt que sur la simple préparation au travail. À partir de 1817, il promeut des communautés coopératives auto-suffisantes, comme New Harmony aux États-Unis, conçues comme des petites villes idéales où la propriété est collective et où l’organisation rationnelle du travail permet de supprimer la misère et la concurrence&lt;/p&gt; &lt;p&gt;  Il critique vigoureusement les religions instituées, auxquelles il reproche d’entretenir le sectarisme et la division, et propose une "religion rationnelle" fondée sur la bienveillance, la coopération et l’éducation. Il devient un  &lt;a href="https://www.youtube.com/watch?v=VmDDCsdQNAY"  title="The Reformer Who Dreamed Of A Utopia | Robert Owen par History's forgotten people"&gt;inspirateur important &lt;/a&gt; du mouvement ouvrier britannique, soutient les premières lois sur le travail des enfants, participe aux débuts du syndicalisme et contribue à développer le mouvement coopératif, dont il est souvent présenté comme un fondateur. &lt;/p&gt; &lt;p&gt; Son texte majeur est &lt;a href="https://www.youtube.com/watch?v=rY9ic8AC2VU"  title=""A New View of Society and Other Writings" By Robert Owen par Novelzilla"&gt;"A New View of Society"&lt;/a&gt;, où il expose sa théorie de la formation du caractère et ses projets de réforme sociale globale, complété plus tard par "The Book of the New Moral World". Marx et Engels le rangeront parmi les "socialistes utopiques" : ils critiquent son manque d’analyse du capitalisme, mais reconnaissent en lui un précurseur dont les expériences concrètes ont nourri le socialisme et l’idée moderne de réforme par les institutions. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Owen"  title=" Wikipedia"&gt;Robert OWEN&lt;/a&gt; était un industriel gallois devenu philosophe social, figure majeure du &lt;a href="https://laviedesidees.fr/Robert-Owen-pere-du-socialisme-britannique" style="color:#88A1E9" title="Robert Owen, père du socialisme britannique ? par idées de la vie"&gt;"socialisme utopique"&lt;/a&gt; et l’un des pères du mouvement coopératif et de l’urbanisme social. Il défend une thèse matérialiste du caractère humain : pour lui, le caractère n’est pas inné mais entièrement façonné par les "circonstances" physiques, morales et sociales auxquelles l’individu est exposé dès l’enfance. Il en conclut que l’on ne doit ni louer ni blâmer moralement les individus, mais transformer les institutions et l’environnement pour produire des caractères meilleurs, ce qui fait de l’éducation et de l’organisation sociale les leviers principaux de la réforme morale. &lt;/p&gt; &lt;p&gt; À &lt;a href="https://www.youtube.com/watch?v=QHWn6aPxKtQ" title="New Lanark: Robert Owen's Utopianism and the Latter Day Saints par Centre Place"&gt;New Lanark&lt;/a&gt;, il crée des écoles modèles, dont l’"Institute for the Formation of Character", qui proposent une éducation gratuite, non répressive, axée sur le jeu, la musique et la formation morale plutôt que sur la simple préparation au travail. À partir de 1817, il promeut des communautés coopératives auto-suffisantes, comme New Harmony aux États-Unis, conçues comme des petites villes idéales où la propriété est collective et où l’organisation rationnelle du travail permet de supprimer la misère et la concurrence&lt;/p&gt; &lt;p&gt;  Il critique vigoureusement les religions instituées, auxquelles il reproche d’entretenir le sectarisme et la division, et propose une "religion rationnelle" fondée sur la bienveillance, la coopération et l’éducation. Il devient un  &lt;a href="https://www.youtube.com/watch?v=VmDDCsdQNAY"  title="The Reformer Who Dreamed Of A Utopia | Robert Owen par History's forgotten people"&gt;inspirateur important &lt;/a&gt; du mouvement ouvrier britannique, soutient les premières lois sur le travail des enfants, participe aux débuts du syndicalisme et contribue à développer le mouvement coopératif, dont il est souvent présenté comme un fondateur. &lt;/p&gt; &lt;p&gt; Son texte majeur est "A New View of Society", où il expose sa théorie de la formation du caractère et ses projets de réforme sociale globale, complété plus tard par "The Book of the New Moral World". Marx et Engels le rangeront parmi les "socialistes utopiques" : ils critiquent son manque d’analyse du capitalisme, mais reconnaissent en lui un précurseur dont les expériences concrètes ont nourri le socialisme et l’idée moderne de réforme par les institutions. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F6" s="7" t="s">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Stuart_Mill"  style="color:#6A142A"  title=" Wikipedia"&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href="https://www.youtube.com/watch?v=kDfp2afvj28" style="color:#88A1E9" title="John Stuart Mill - Synthèse par El Khader"&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». Son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href="https://www.youtube.com/watch?v=yCDOVcvNYpY" title=" L'utilitarisme par Culture Philo"&gt;"  l’Utilitarisme"&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href="https://www.youtube.com/watch?v=DVG_FL8jKe0" title="John Stuart Mill - De La Liberté par Let's make liberalism great again"&gt;" De la liberté"&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre &lt;a href="https://www.youtube.com/watch?v=bMJbqBzED4E&amp;t=12s" title="JOHN STUART MILL: le Conformisme et la Tyrannie de la Majorité par Voix Philosophiques"&gt;la tyrannie de l’opinion&lt;/a&gt; et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;        &lt;audio controls title="John Stuart Mill par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Stuart_Mill"  style="color:#6A142A"  title=" Wikipedia"&gt;John STUART MILL&lt;/a&gt; était un philosophe et économiste anglais théoricien de  &lt;a href="https://www.youtube.com/watch?v=kDfp2afvj28" style="color:#88A1E9" title="John Stuart Mill - Synthèse par El Khader"&gt;l’utilitarisme réformé&lt;/a&gt;, défenseur des droits des femmes et pionnier du libéralisme moderne, Connu pour sa célèbre maxime : « Mieux vaut un Socrate insatisfait qu’un imbécile satisfait ». Son œuvre reste une boussole pour les démocraties contemporaines. &lt;/p&gt; &lt;p&gt; Héritier de Bentham, il dépasse sa vision mécaniste du bonheur. Dans  &lt;a href="https://www.youtube.com/watch?v=yCDOVcvNYpY" title=" L'utilitarisme par Culture Philo"&gt;"  l’Utilitarisme"&lt;/a&gt; (1863), il défend une morale où le plaisir intellectuel et moral prime sur les satisfactions matérielles. Contrairement aux critiques, son approche n’écrase pas l’individu sous la majorité : le bonheur collectif ne peut prospérer sans respecter les droits fondamentaux. &lt;/p&gt; &lt;p&gt;Dans son manifeste &lt;a href="https://www.youtube.com/watch?v=DVG_FL8jKe0" title="John Stuart Mill - De La Liberté par Let's make liberalism great again"&gt;" De la liberté"&lt;/a&gt; paru en 1859, il érige la liberté d’expression et de pensée en pilier de la société. Son « principe de non-nuisance » limite le pouvoir de l’État : « La seule raison légitime pour laquelle l’humanité peut interférer avec la liberté d’action d’un individu est la protection de soi-même ». Une pensée qui résonne aujourd’hui dans les débats sur la censure ou la vaccination obligatoire.&lt;/p&gt; &lt;p&gt;  Influencé par sa compagne Harriet Taylor, il dénonce le mariage comme « seule forme d’esclavage légal ». Il réclame le droit de vote des femmes, l’égalité éducative et professionnelle. Son combat, radical pour l’époque, en fait un précurseur des luttes pour l’émancipation. &lt;/p&gt; &lt;p&gt; À l’ère des réseaux sociaux et des populismes, ses mises en garde contre la tyrannie de l’opinion et son plaidoyer pour une démocratie délibérative offrent des outils précieux. Comme il l’écrivait : « Toutes les bonnes idées passent par trois phases : le ridicule, la discussion, l’adoption. » Mill, lui, a franchi ces étapes pour devenir un phare incontournable. &lt;/p&gt;        &lt;audio controls title="John Stuart Mill par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/09/s36/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_529c9cca-bbd6-4726-8de9-19c9b272eee2_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
@@ -4890,8 +4890,8 @@
       <c r="E44" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein"  title=" Wikipedia"&gt;Ludwig WITTGENSTEIN&lt;/a&gt; était un philosophe autrichien énigmatique et influent souvent divisée en deux périodes distinctes, le "premier" et le "second" Wittgenstein. Le premier, &lt;a href="https://www.youtube.com/watch?v=4w5xzgna1l0&amp;list=PLyfQgbpaPz7hZqscDHbJVRNtcDRHZ5mGr"  title="Tractatus logico-philosophicus, Ludwig Wittgenstein par Thibault BELZACQ"&gt; "le Tractatus Logico-Philosophicus"&lt;/a&gt;  (1921) est un texte dense, écrit de manière aphoristique, et qui se présente comme la solution à tous les problèmes philosophiques. Sa thèse centrale est que le langage a pour but de décrire le monde, qui est constitué de faits.&lt;/p&gt;
-&lt;p&gt; La théorie de la représentation :   &lt;a href="https://www.youtube.com/watch?v=To2Eva4vK3s" title="Le Philosophe qui a Changé le Langage à Jamais | Ludwig Wittgenstein  par Le Coseiller"&gt; le langage&lt;/a&gt; est une "image" du monde. Une phrase a un sens si et seulement si elle dépeint un état de choses possible dans la réalité. Le langage et le monde partagent une structure logique commune. &lt;/p&gt;
-&lt;p&gt; La distinction entre "dire" et "montrer" : le langage ne peut dire que ce qui a un sens. Les choses qui ne peuvent pas être décrites (comme la logique elle-même, l'éthique, la métaphysique, la religion) ne peuvent pas être "dites", mais elles se "montrent" à travers le langage. Le célèbre dernier aphorisme du Tractatus est : "Ce dont on ne peut parler, il faut le taire." &lt;/p&gt; &lt;p&gt; La fin de la philosophie ? : il pensait avoir résolu les problèmes de la philosophie en montrant qu'ils provenaient d'une mauvaise utilisation du langage. Les questions métaphysiques (sur l'être, l'âme, etc.) sont, selon lui, dénuées de sens, car elles tentent de "dire" ce qui ne peut qu'être "montré". Après la publication de cet ouvrage, il a abandonné la philosophie pendant près de dix ans, pensant avoir achevé son travail. &lt;/p&gt; &lt;p&gt; Le "second" :   &lt;a href="https://wittgenstein.fr/category/lectures-des-recherches-philosophiques/"  title="Ludwig Wittgenstein  par Julien Gautier"&gt; les "Recherches philosophiques"&lt;/a&gt;  à la fin des années 1920. Il a commencé à remettre en question les fondations de son propre Tractatus. Publiées à titre posthume en 1953, elles marquent une rupture radicale avec sa première pensée.&lt;/p&gt; &lt;p&gt; Le concept de  &lt;a href="https://www.youtube.com/watch?v=To2Eva4vK3s"  title="Ludwig Wittgenstein la philosophie qui a changé le langage par Le Conseiller"&gt; "jeux de langage" : &lt;/a&gt; Il abandonne la théorie de la représentation pour une nouvelle conception du langage qui n'est pas un miroir du monde, mais un outil. Le sens d'un mot n'est pas son référent dans la réalité, mais son usage dans un contexte donné. Il introduit la notion de "jeux de langage" pour désigner les différentes activités humaines où le langage est utilisé (commander, questionner, raconter une blague, etc.). Chaque "jeu" a ses propres règles et sa propre grammaire.&lt;/p&gt; &lt;p&gt;La philosophie comme thérapie : il ne considère plus que les problèmes philosophiques peuvent être résolus, mais qu'ils peuvent être dissous. L'objectif de la philosophie est de démêler les confusions que le langage crée, en montrant comment les mots sont utilisés dans différents "jeux". La philosophie n'est plus une quête de la vérité ultime, mais une "thérapie" qui aide à "voir clair" dans notre usage du langage. &lt;/p&gt; &lt;p&gt; "Formes de vie" : La signification du langage est profondément enracinée dans notre pratique collective et nos actions, dans ce qu'il appelle nos "formes de vie". Les règles d'un "jeu de langage" ne peuvent être comprises qu'à l'intérieur de ces pratiques sociales partagées. Il s'oppose à l'idée d'un "langage privé", montrant que le sens nécessite un accord public et une communauté d'utilisateurs. &lt;/p&gt;  &lt;audio controls title="Ludwig Wittgenstein ou la philosophie de l’indicible par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-12.07.2020-ITEMA_22380918-2020C22785E0017-1779455909.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
+&lt;p&gt; La théorie de la représentation :    le langage est une "image" du monde. Une phrase a un sens si et seulement si elle dépeint un état de choses possible dans la réalité. Le langage et le monde partagent une structure logique commune. &lt;/p&gt;
+&lt;p&gt; La distinction entre "dire" et "montrer" : le langage ne peut dire que ce qui a un sens. Les choses qui ne peuvent pas être décrites (comme la logique elle-même, l'éthique, la métaphysique, la religion) ne peuvent pas être "dites", mais elles se "montrent" à travers le langage. Le célèbre dernier aphorisme du Tractatus est : "Ce dont on ne peut parler, il faut le taire." &lt;/p&gt; &lt;p&gt; La fin de la philosophie ? : il pensait avoir résolu les problèmes de la philosophie en montrant qu'ils provenaient d'une mauvaise utilisation du langage. Les questions métaphysiques (sur l'être, l'âme, etc.) sont, selon lui, dénuées de sens, car elles tentent de "dire" ce qui ne peut qu'être "montré". Après la publication de cet ouvrage, il a abandonné la philosophie pendant près de dix ans, pensant avoir achevé son travail. &lt;/p&gt; &lt;p&gt; Le "second" :   &lt;a href="https://wittgenstein.fr/category/lectures-des-recherches-philosophiques/"  title="Ludwig Wittgenstein  par Julien Gautier"&gt; les "Recherches philosophiques"&lt;/a&gt;  à la fin des années 1920. Il a commencé à remettre en question les fondations de son propre Tractatus. Publiées à titre posthume en 1953, elles marquent une rupture radicale avec sa première pensée.&lt;/p&gt; &lt;p&gt; Le concept de   "jeux de langage" :  Il abandonne la théorie de la représentation pour une nouvelle conception du langage qui n'est pas un miroir du monde, mais un outil. Le sens d'un mot n'est pas son référent dans la réalité, mais son usage dans un contexte donné. Il introduit la notion de "jeux de langage" pour désigner les différentes activités humaines où le langage est utilisé (commander, questionner, raconter une blague, etc.). Chaque "jeu" a ses propres règles et sa propre grammaire.&lt;/p&gt; &lt;p&gt;La philosophie comme thérapie : il ne considère plus que les problèmes philosophiques peuvent être résolus, mais qu'ils peuvent être dissous. L'objectif de la philosophie est de démêler les confusions que le langage crée, en montrant comment les mots sont utilisés dans différents "jeux". La philosophie n'est plus une quête de la vérité ultime, mais une "thérapie" qui aide à "voir clair" dans notre usage du langage. &lt;/p&gt; &lt;p&gt; "Formes de vie" : La signification du langage est profondément enracinée dans notre pratique collective et nos actions, dans ce qu'il appelle nos "formes de vie". Les règles d'un "jeu de langage" ne peuvent être comprises qu'à l'intérieur de ces pratiques sociales partagées. Il s'oppose à l'idée d'un "langage privé", montrant que le sens nécessite un accord public et une communauté d'utilisateurs. &lt;/p&gt;  &lt;audio controls title="Ludwig Wittgenstein ou la philosophie de l’indicible par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-12.07.2020-ITEMA_22380918-2020C22785E0017-1779455909.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F44" s="7" t="s">

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -4931,14 +4931,18 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
-        <v>1889</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>388</v>
+      <c r="A45" s="7">
+        <v>1886</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1939</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886 – 1939</t>
+        </is>
       </c>
       <c r="D45" s="8" t="s">
         <v>389</v>

--- a/data/frise-philosophes-modernes.xlsx
+++ b/data/frise-philosophes-modernes.xlsx
@@ -3454,20 +3454,88 @@
         </is>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1">
+        <v>1809</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1809 – 1882</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charles DARWIN</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Darwin" title=" Wikipedia"&gt;Charles DARWIN&lt;/a&gt; est un naturaliste britannique dont la&lt;a href="https://www.youtube.com/watch?v=2R83wJLAlW8" title="La théorie de l'évolution de Charles Darwin, expliquée simplement par Podium Culture"&gt; théorie de l’évolution&lt;/a&gt; a bouleversé la science et la philosophie. Né en 1809 à Shrewsbury, petit-fils du médecin Erasmus Darwin, il abandonne la médecine puis des études de théologie pour l’histoire naturelle. De 1831 à 1836, il fait le tour du monde à bord du &lt;em&gt;Beagle&lt;/em&gt; : les fossiles d’Amérique du Sud et les espèces voisines d’une île à l’autre des Galápagos le convainquent que les espèces ne sont pas fixes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Origine des espèces&lt;/em&gt; (1859), il explique leur transformation par la « sélection naturelle » : dans chaque génération naissent des individus légèrement différents, et ceux dont les variations favorisent la survie et la reproduction transmettent davantage leurs traits. Sur des temps immenses, ce tri sans but suffit à produire la diversité et l’adaptation des êtres vivants. Il n’y a plus besoin d’un dessein divin pour expliquer l’ordre de la nature, ce qui ruine l’argument de William Paley et ouvre la voie au &lt;a href="https://fr.wikipedia.org/wiki/Naturalisme_%28philosophie%29" title=" Wikipedia"&gt;naturalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Filiation de l’homme&lt;/em&gt; (1871), il inscrit l’être &lt;a href="https://www.youtube.com/watch?v=6-7qvnnlhhM" title="Qu'est-ce que la théorie de Darwin ? - C'est Pas Sorcier par C'est pas sorcier"&gt;humain dans cette histoire&lt;/a&gt; : nos facultés morales viennent des instincts sociaux de nos ancêtres animaux, renforcés par la sympathie, le langage et l’habitude. Il lui-même se dit agnostique et reste prudent sur la religion. Sa théorie sera détournée, avec le darwinisme social de Spencer, pour justifier la concurrence et les inégalités, ce qu’il n’avait pas voulu, même s’il partageait certains préjugés de son temps. Il meurt en 1882 et repose à l’abbaye de Westminster.&lt;/p&gt;  &lt;audio controls title="Darwin, l'arbre du vivant, et la première graine de vie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25684-20.08.2025-ITEMA_24220588-2025F54261S0232-NET_MFI_90B5F88E-4214-4744-82DC-9F5738C09306-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bxNBAkRp2FU</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Charles Darwin: sa vie et sa théorie de l'évolution" par Science bestiale</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/darwin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturalisme</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">naturaliste britannique, auteur de la théorie de l’évolution par la sélection naturelle.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="288.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>1813</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%B8ren_Kierkegaard" title=" Wikipedia"&gt;Soren KIERKEGAARD&lt;/a&gt; était un philosophe et théologien danois, célèbre pour ses idées sur &lt;a href="https://www.youtube.com/watch?v=davjaNvPfLA&amp;ab_channel=Philo-Man" title="Kierkegaard: existe t'il des degrès de liberté par Philo-Man"&gt; l'existentialisme chrétien&lt;/a&gt;. Il a souvent écrit sous des pseudonymes, ce qui a permis à ses œuvres de présenter différentes perspectives et points de vue sur des questions philosophiques et religieuses.&lt;/p&gt; &lt;p&gt; Il met l'accent sur l'importance de la responsabilité individuelle, de la liberté et du choix dans la vie humaine. Selon lui, chaque individu est confronté à &lt;a href="https://www.youtube.com/watch?v=-VPfHoQAGfc"  title="Comment l’Angoisse Conduit à la Grandeur | Søren Kierkegaard par Philosophie et spiritisme"&gt; une angoisse existentielle&lt;/a&gt; inhérente à l'existence humaine, et il est nécessaire de prendre des décisions authentiques pour trouver un sens à la vie. &lt;/p&gt;
 &lt;p&gt; Il a mit en avant le paradoxe de la foi en cherchant à concilier la foi chrétienne avec la raison et la philosophie, soutenant que la foi authentique nécessite un saut au-delà de la rationalité humaine et a critiqué les formes institutionnelles de la religion, affirmant que la véritable religiosité découle d'une relation personnelle et passionnée avec Dieu.&lt;/p&gt;
@@ -3476,126 +3544,80 @@
   &lt;audio controls title="Introduction à la philosophe de Kierkegaard par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-22.11.2022-ITEMA_23204156-2022C3372E0494-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Existentialisme ; Irrationalisme ; Absurde</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>1815</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Secr%C3%A9tan" title=" Wikipedia"&gt;Charles SECRÉTAN&lt;/a&gt; était un philosophe suisse protestant, généralement rangé dans une forme de spiritualisme chrétien, avec une &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1925_num_5_2_2528" title="charles secretan et la philosophie de schelling par persée"&gt; forte influence de Schelling. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il faut d’abord le comprendre à partir de son idée centrale : la liberté. Dans Philosophie de la liberté, il soutient que la liberté n’est pas seulement une faculté humaine, mais un principe profond de la réalité, lié à Dieu lui-même.  Pour lui, la raison humaine ne suffit pas à tout expliquer seule. Il cherche donc à concilier la pensée philosophique et la foi chrétienne, en défendant ce qu’il appelle une “raison chrétienne” contre le rationalisme pur d’un côté et le fidéisme dogmatique de l’autre. &lt;/p&gt; &lt;p&gt; Sa philosophie a aussi une dimension morale très forte. Il insiste sur la responsabilité personnelle, la solidarité, la dignité de l’homme et la dimension éthique de la vie sociale, ce qui l’amène à réfléchir à la question des inégalités et des droits. &lt;/p&gt; &lt;p&gt; Sa pensée évolue vers des préoccupations plus sociales. Même s’il reste métaphysicien au départ, il s’oriente de plus en plus vers la morale, la religion vécue et les questions de société, avec l’idée qu’une communauté humaine juste doit être fondée sur la liberté et la solidarité. &lt;/p&gt; Né à Lausanne en 1815, il suit à Munich les cours de Schelling, puis enseigne la philosophie à Lausanne ; destitué en 1845 par le gouvernement radical, il enseigne à Neuchâtel avant de retrouver sa chaire. Sa &lt;em&gt;Philosophie de la liberté&lt;/em&gt; (1849) fait de Dieu une liberté absolue, qui crée par amour des êtres libres. Il plaide aussi pour l’égalité des femmes, à qui il consacre &lt;em&gt;Le Droit de la femme&lt;/em&gt; (1886). </t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">charles secretan par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>133</v>
+        <v>121</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme ; Irrationalisme ; Absurde</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
-        <v>1818</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>134</v>
+        <v>1815</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1895</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Bain_(philosophe)"   title=" Wikipedia"&gt;Alexander BAIN&lt;/a&gt; était un philosophe utilitariste écossais issus d'une famille modeste de tisserand où son père lui transmet le goût du travail méticuleux, tandis que sa mère, pieuse et austère, l’initie aux rigueurs de la &lt;a href="https://www.olivierabel.fr/2022/09/24/la-morale-de-calvin/"  title="La morale de Calvin par olivierabel"&gt;morale calviniste&lt;/a&gt; mais il ne se contente pas des certitudes religieuses. Il dévore les livres, s’interroge sur le fonctionnement de l’esprit humain, et rêve de comprendre les lois invisibles qui régissent la pensée.&lt;/p&gt; &lt;p&gt; Il rencontre John Stuart Mill, qui devient son ami et mentor. Ensemble, ils discutent de l’associationnisme, cette théorie selon laquelle toutes les idées complexes se forment par la combinaison d’impressions simples. Bain y voit une clé pour déchiffrer l’énigme de la conscience. &lt;/p&gt; &lt;p&gt; Dans les années 1850, il publie ses œuvres majeures, "Les Sens et l’Intelligence" et "Les Émotions et la Volonté". Il y développe une vision  &lt;a href="https://www.youtube.com/shorts/TkMO99tn4Uc" title="Alexander BAIN par Timeless philosopher"&gt;scientifique de l’esprit&lt;/a&gt;, influencée par les découvertes en physiologie. Pour lui, chaque pensée, chaque émotion, a une base matérielle dans le cerveau. Il  fonde la première revue de psychologie scientifique &lt;a href="https://www.jstor.org/stable/41071221?seq=1" title="Revue des périodiques étrangers par JSTOR"&gt;"Mind"&lt;/a&gt; en 1876. Il y défend une approche expérimentale de l’esprit, préfigurant les travaux de William James et de Freud. Pourtant, dans l’intimité, le philosophe reste hanté par une question : si tout n’est que mécanisme, où est la place de la liberté humaine ? Peut-être dans cette capacité de l’esprit à s’auto-modifier, à créer de nouvelles associations d’idées… &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Secr%C3%A9tan" title=" Wikipedia"&gt;Charles SECRÉTAN&lt;/a&gt; était un philosophe suisse protestant, généralement rangé dans une forme de spiritualisme chrétien, avec une &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1925_num_5_2_2528" title="charles secretan et la philosophie de schelling par persée"&gt; forte influence de Schelling. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il faut d’abord le comprendre à partir de son idée centrale : la liberté. Dans Philosophie de la liberté, il soutient que la liberté n’est pas seulement une faculté humaine, mais un principe profond de la réalité, lié à Dieu lui-même.  Pour lui, la raison humaine ne suffit pas à tout expliquer seule. Il cherche donc à concilier la pensée philosophique et la foi chrétienne, en défendant ce qu’il appelle une “raison chrétienne” contre le rationalisme pur d’un côté et le fidéisme dogmatique de l’autre. &lt;/p&gt; &lt;p&gt; Sa philosophie a aussi une dimension morale très forte. Il insiste sur la responsabilité personnelle, la solidarité, la dignité de l’homme et la dimension éthique de la vie sociale, ce qui l’amène à réfléchir à la question des inégalités et des droits. &lt;/p&gt; &lt;p&gt; Sa pensée évolue vers des préoccupations plus sociales. Même s’il reste métaphysicien au départ, il s’oriente de plus en plus vers la morale, la religion vécue et les questions de société, avec l’idée qu’une communauté humaine juste doit être fondée sur la liberté et la solidarité. &lt;/p&gt; Né à Lausanne en 1815, il suit à Munich les cours de Schelling, puis enseigne la philosophie à Lausanne ; destitué en 1845 par le gouvernement radical, il enseigne à Neuchâtel avant de retrouver sa chaire. Sa &lt;em&gt;Philosophie de la liberté&lt;/em&gt; (1849) fait de Dieu une liberté absolue, qui crée par amour des êtres libres. Il plaide aussi pour l’égalité des femmes, à qui il consacre &lt;em&gt;Le Droit de la femme&lt;/em&gt; (1886). </t>
         </is>
       </c>
       <c r="F16" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>140</v>
+        <v>127</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">charles secretan par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3603,143 +3625,145 @@
         </is>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="120.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Bain_(philosophe)"   title=" Wikipedia"&gt;Alexander BAIN&lt;/a&gt; était un philosophe utilitariste écossais issus d'une famille modeste de tisserand où son père lui transmet le goût du travail méticuleux, tandis que sa mère, pieuse et austère, l’initie aux rigueurs de la &lt;a href="https://www.olivierabel.fr/2022/09/24/la-morale-de-calvin/"  title="La morale de Calvin par olivierabel"&gt;morale calviniste&lt;/a&gt; mais il ne se contente pas des certitudes religieuses. Il dévore les livres, s’interroge sur le fonctionnement de l’esprit humain, et rêve de comprendre les lois invisibles qui régissent la pensée.&lt;/p&gt; &lt;p&gt; Il rencontre John Stuart Mill, qui devient son ami et mentor. Ensemble, ils discutent de l’associationnisme, cette théorie selon laquelle toutes les idées complexes se forment par la combinaison d’impressions simples. Bain y voit une clé pour déchiffrer l’énigme de la conscience. &lt;/p&gt; &lt;p&gt; Dans les années 1850, il publie ses œuvres majeures, "Les Sens et l’Intelligence" et "Les Émotions et la Volonté". Il y développe une vision  &lt;a href="https://www.youtube.com/shorts/TkMO99tn4Uc" title="Alexander BAIN par Timeless philosopher"&gt;scientifique de l’esprit&lt;/a&gt;, influencée par les découvertes en physiologie. Pour lui, chaque pensée, chaque émotion, a une base matérielle dans le cerveau. Il  fonde la première revue de psychologie scientifique &lt;a href="https://www.jstor.org/stable/41071221?seq=1" title="Revue des périodiques étrangers par JSTOR"&gt;"Mind"&lt;/a&gt; en 1876. Il y défend une approche expérimentale de l’esprit, préfigurant les travaux de William James et de Freud. Pourtant, dans l’intimité, le philosophe reste hanté par une question : si tout n’est que mécanisme, où est la place de la liberté humaine ? Peut-être dans cette capacité de l’esprit à s’auto-modifier, à créer de nouvelles associations d’idées… &lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herbert_Spencer"  title=" Wikipedia"&gt;Herbert SPENCER&lt;/a&gt; était un philosophe, sociologue et anthropologue britanique et un parfait exemple d'autodidacte. Ingénieur de formation, il devient journaliste et se consacre entièrement à l'écriture. Son œuvre est immense, culminant avec son Système de &lt;a href="https://www.persee.fr/doc/phlou_0776-5541_1904_num_11_41_1823" title=" La philosophie d'Herbert Spencer  par Persée"&gt; philosophie synthétique&lt;/a&gt;, une série de volumes visant à unifier toutes les connaissances humaines (biologie, psychologie, sociologie, éthique) sous un seul principe directeur : l'évolution. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre (et la plus controversée) est son application de la théorie de l'évolution à la société humaine, une idée souvent résumée par l'expression qu'il a popularisée : la "survie du plus apte". Il a développé une théorie de l'évolution avant même la publication de "L'Origine des espèces de Charles Darwin". Cependant, alors que Darwin se concentrait sur le mécanisme biologique de la sélection naturelle, Spencer voyait &lt;a href="https://www.youtube.com/watch?v=pBbr4mBO3kA" style="color:#88A1E9" title=" 
 Social Darwinism | Herbert Spencer par Sociologylearners"&gt;l'évolution&lt;/a&gt;  comme une loi universelle s'appliquant à tous les phénomènes : l'univers, les organismes biologiques, l'esprit humain, les cultures et les sociétés progressent tous du simple au complexe, de l'homogène à l'hétérogène. &lt;/p&gt; &lt;p&gt; Il  a appliqué le principe de la "survie du plus apte" aux sociétés humaines. Il estimait que la compétition entre les individus et entre les sociétés était un moteur naturel et bénéfique du progrès. Elle permettait d'éliminer les "inaptes" et de favoriser les "plus aptes" (les plus talentueux, les plus travailleurs, les plus adaptés), conduisant ainsi à l'amélioration de l'espèce humaine.&lt;/p&gt; &lt;p&gt;  Il était un farouche partisan du libéralisme intégral et de l'État minimal (laissez-faire). Il s'opposait catégoriquement à toute intervention de l'État dans la vie sociale, comme l'aide aux pauvres, les lois sociales, l'éducation publique ou la santé publique. Pour lui, ces interventions artificielles perturbaient le processus naturel de sélection en maintenant en vie les "inaptes", ce qui affaiblissait la société à long terme. Il n'a pas simplement "appliqué" &lt;a href="https://www.youtube.com/watch?v=MfsLeQOZfEA"  title=" Le DARWINISME SOCIAL en 6 minutes !  par Culture Philo"&gt;Darwin aux sociétés&lt;/a&gt;. Il avait sa propre théorie évolutionniste, et c'est Darwin qui a ensuite emprunté l'expression "survie du plus apte" à Spencer. &lt;/p&gt; &lt;p&gt; Il était un penseur complexe qui a tenté de bâtir un système philosophique total. Bien que sa réputation soit aujourd'hui entachée par les usages politiques terribles qui ont été faits de ses idées, son influence sur la pensée moderne est indéniable. Il reste une figure essentielle pour comprendre l'optimisme scientiste et la foi dans le progrès qui caractérisent le XIXe siècle, ainsi que les dérives possibles lorsqu'on tente d'appliquer des lois naturelles au domaine social et moral. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Positivisme ; Darwinisme social ; Minarchisme ; Volontarisme</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="381" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>1825</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>1895</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Henry_Huxley"   title=" Wikipedia"&gt;Thomas Henry HUXLEY&lt;/a&gt; était un biologiste, vulgarisateur scientifique et grand défenseur de Darwin dans l’Angleterre victorienne. Mais il a aussi élaboré une position philosophique influente : l’agnosticisme, terme qu’il forgea en 1869 pour définir une attitude rigoureuse face aux limites de la connaissance. &lt;/p&gt; &lt;p&gt; Pour lui,  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme" " title="agnosticisme par wikipedia"&gt;l’agnosticisme &lt;/a&gt; n’est ni une religion, ni une doctrine affirmant que Dieu n’existe pas. C’est avant tout une méthode intellectuelle : on doit suivre la raison et les preuves aussi loin qu’elles conduisent, sans prétendre savoir avec certitude ce qui n’est ni démontré ni démontrable. Ainsi, concernant Dieu, l’âme immortelle ou l’origine ultime du monde, il suspend son jugement : il estime que l’on ne dispose pas de preuves suffisantes pour affirmer ou nier catégoriquement ces réalités. &lt;/p&gt; &lt;p&gt;  Sa philosophie est donc une forme d’empirisme critique, héritière de David Hume et, sur certains points, de Kant. La science peut établir des connaissances sur les phénomènes observables, contrôlables et soumis à l’expérience ; elle ne peut pas légitimement franchir ce cadre pour parler avec certitude d’une réalité métaphysique située « derrière » ou au-delà de l’expérience. Il refusait autant le dogmatisme théologique que le matérialisme athée qui prétendrait résoudre définitivement les questions ultimes. &lt;/p&gt; &lt;p&gt; Chez lui, &lt;a href="https://fr.wikipedia.org/wiki/%C3%89piph%C3%A9nom%C3%A9nisme" " title="épiphénoménisme par wikipedia"&gt; l’épiphénoménisme &lt;/a&gt; est une thèse centrale sur l’esprit et le corps, exposée surtout dans son discours de 1874, On the Hypothesis that Animals are Automata. Il y soutient que les états de conscience (sensations, sentiments, pensées telles qu’on les vit) sont réels, mais qu’ils sont des effets collatéraux des processus physico-chimiques du cerveau et du système nerveux, sans pouvoir à leur tour agir sur ces processus. &lt;/p&gt; &lt;p&gt; Pour le dire avec sa célèbre image : la conscience est au corps ce que le sifflet à vapeur est à une locomotive. Le sifflet accompagne le fonctionnement de la machine et en dépend, mais il n’influe pas sur son mouvement ; de même, selon Huxley, la conscience accompagne l’activité nerveuse sans la déterminer. Les comportements, y compris les actions que nous attribuons à la « volonté », sont entièrement expliqués par des chaînes de causes physiques dans l’organisme. Il ne nie donc pas l’existence de la conscience (contrairement à un matérialisme éliminativiste), mais il refuse de lui accorder un rôle causal dans l’explication scientifique du comportement. Sur le plan métaphysique, cela revient à un dualisme très affaibli : il y a bien quelque chose comme un « esprit » ou une vie consciente, mais celle-ci est un épiphénomène, un « spectateur inerte » des mécanismes corporels. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=jdMeImpsaR4" " title="évolution et agnosticism par open source "&gt; Cette position &lt;/a&gt;  s’inscrit dans son projet plus large de naturaliser la biologie et de soumettre l’être vivant à des lois mécaniques, tout en restant fidèle à son agnosticisme : il admet que le lien exact entre irritation nerveuse et état de conscience reste inexpliqué, voire mystérieux, mais il refuse d’en tirer des conclusions métaphysiques sur une âme immatérielle ou une liberté surnaturelle. Il reconnaît explicitement le caractère énigmatique du passage du physique au conscient, tout en maintenant que la science doit traiter le corps comme un automate. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="M18" s="14" t="s">
-        <v>159</v>
+        <v>149</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Darwinisme social ; Minarchisme ; Volontarisme</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="381" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
-        <v>1838</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>160</v>
+        <v>1825</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>1895</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>163</v>
+        <v>153</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Henry_Huxley"   title=" Wikipedia"&gt;Thomas Henry HUXLEY&lt;/a&gt; était un biologiste, vulgarisateur scientifique et grand défenseur de Darwin dans l’Angleterre victorienne. Mais il a aussi élaboré une position philosophique influente : l’agnosticisme, terme qu’il forgea en 1869 pour définir une attitude rigoureuse face aux limites de la connaissance. &lt;/p&gt; &lt;p&gt; Pour lui,  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme" " title="agnosticisme par wikipedia"&gt;l’agnosticisme &lt;/a&gt; n’est ni une religion, ni une doctrine affirmant que Dieu n’existe pas. C’est avant tout une méthode intellectuelle : on doit suivre la raison et les preuves aussi loin qu’elles conduisent, sans prétendre savoir avec certitude ce qui n’est ni démontré ni démontrable. Ainsi, concernant Dieu, l’âme immortelle ou l’origine ultime du monde, il suspend son jugement : il estime que l’on ne dispose pas de preuves suffisantes pour affirmer ou nier catégoriquement ces réalités. &lt;/p&gt; &lt;p&gt;  Sa philosophie est donc une forme d’empirisme critique, héritière de David Hume et, sur certains points, de Kant. La science peut établir des connaissances sur les phénomènes observables, contrôlables et soumis à l’expérience ; elle ne peut pas légitimement franchir ce cadre pour parler avec certitude d’une réalité métaphysique située « derrière » ou au-delà de l’expérience. Il refusait autant le dogmatisme théologique que le matérialisme athée qui prétendrait résoudre définitivement les questions ultimes. &lt;/p&gt; &lt;p&gt; Chez lui, &lt;a href="https://fr.wikipedia.org/wiki/%C3%89piph%C3%A9nom%C3%A9nisme" " title="épiphénoménisme par wikipedia"&gt; l’épiphénoménisme &lt;/a&gt; est une thèse centrale sur l’esprit et le corps, exposée surtout dans son discours de 1874, On the Hypothesis that Animals are Automata. Il y soutient que les états de conscience (sensations, sentiments, pensées telles qu’on les vit) sont réels, mais qu’ils sont des effets collatéraux des processus physico-chimiques du cerveau et du système nerveux, sans pouvoir à leur tour agir sur ces processus. &lt;/p&gt; &lt;p&gt; Pour le dire avec sa célèbre image : la conscience est au corps ce que le sifflet à vapeur est à une locomotive. Le sifflet accompagne le fonctionnement de la machine et en dépend, mais il n’influe pas sur son mouvement ; de même, selon Huxley, la conscience accompagne l’activité nerveuse sans la déterminer. Les comportements, y compris les actions que nous attribuons à la « volonté », sont entièrement expliqués par des chaînes de causes physiques dans l’organisme. Il ne nie donc pas l’existence de la conscience (contrairement à un matérialisme éliminativiste), mais il refuse de lui accorder un rôle causal dans l’explication scientifique du comportement. Sur le plan métaphysique, cela revient à un dualisme très affaibli : il y a bien quelque chose comme un « esprit » ou une vie consciente, mais celle-ci est un épiphénomène, un « spectateur inerte » des mécanismes corporels. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=jdMeImpsaR4" " title="évolution et agnosticism par open source "&gt; Cette position &lt;/a&gt;  s’inscrit dans son projet plus large de naturaliser la biologie et de soumettre l’être vivant à des lois mécaniques, tout en restant fidèle à son agnosticisme : il admet que le lien exact entre irritation nerveuse et état de conscience reste inexpliqué, voire mystérieux, mais il refuse d’en tirer des conclusions métaphysiques sur une âme immatérielle ou une liberté surnaturelle. Il reconnaît explicitement le caractère énigmatique du passage du physique au conscient, tout en maintenant que la science doit traiter le corps comme un automate. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F19" s="7" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>166</v>
+        <v>156</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>159</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3747,186 +3771,179 @@
         </is>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>1838</v>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>1906</v>
+      <c r="B20" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>172</v>
+        <v>162</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>175</v>
+        <v>165</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>166</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M20" s="15" t="s">
+      <c r="M21" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>1850</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B22" s="1" t="n">
         <v>1937</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E22" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">thomas masaryk par Slavier</t>
         </is>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="M21" s="15" t="s">
+      <c r="M22" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
         <v>1853</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexius_Meinong"   title=" Wikipedia"&gt;Alexius MEINONG&lt;/a&gt;  était un philosophe et psychologue autrichien, élève de Franz Brentano à Vienne, qui enseigna principalement à l'université de Graz où il fonda un institut de psychologie expérimentale. Issu d'une famille noble, il s'intéresse d'abord à la psychologie descriptive avant de développer une ontologie audacieuse influencée par l'intentionnalité brentanienne. Sa carrière est marquée par des contributions en philosophie de l'esprit, axiologie et surtout sa célèbre théorie des objets, qui élargit radicalement le domaine de ce qui peut être pensé. &lt;/p&gt; p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Meinongianisme"  title="Meinongianisme par Wikipedia"&gt;Sa théorie des objets, &lt;/a&gt; exposée dans Recherches sur la théorie des objets et la psychologie (1904), postule que tout ce qui est visé par la pensée existe comme objet, indépendamment de son existence réelle. Il distingue le Sein (être : existence pour les concrets, subsistance pour les idéaux comme les nombres) du Sosein (caractérisation nucléaire et extra-nucléaire), avec le principe d'indifférence : un&lt;a href="https://www.youtube.com/watch?v=4Yway8Xo3iA"  title="Alexius Meinong Théorie de l’objet par Jdgrandtour"&gt; objet est ontologiquement neutre &lt;/a&gt; quant à l'existence. Ainsi, la montagne d'or ou le rond carré sont des objets « außerseiend » (hors de l'être), pensables sans contradictoire. &lt;/p&gt; &lt;p&gt; Il  introduit aussi les assomptions, actes mentaux fictifs intermédiaires entre jugements et représentations, essentiels pour la pensée hypothétique ou fictionnelle. Critiqué par Russell pour le paradoxe (« l'entité actuelle n'existe pas »), il raffine sa théorie en distinguant propriétés incomplètes et propriétés extra-nucléaires (comme l'existence elle-même). Son système, jungle ontologique foisonnante, préfigure la méta-ontologie analytique. &lt;/p&gt; &lt;p&gt; Influençant Husserl, Russell ou la philosophie analytique contemporaine, il reste une figure clé de l'école de Graz, opposée au psychologisme. Son blason familial évoque son lignage noble, mais c'est sa audace ontologique qui perdure. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G23" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="279" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>1859</v>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>1938</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Alexander" title=" Wikipedia"&gt;Samuel ALEXANDER&lt;/a&gt; était un philosophe britannique d’origine australienne, figure majeure de l’émergentisme britannique et du réalisme métaphysique. Sa pensée repose sur une ontologie moniste où l’espace-temps constitue la substance fondamentale de toute réalité : matière, vie, esprit et même divinité émergent à partir de cette matrice spatio-temporelle. Alexander rejette l’idéalisme (hégélien ou britannique) ainsi que le dualisme cartésien, et propose un naturalisme réaliste dans lequel les catégories (substance, causalité, universalité) ne sont pas des structures de l’entendement (comme chez Kant) mais des déterminations concrètes de l’être lui-même. &lt;/p&gt; &lt;p&gt; Le cœur de sa philosophie est la notion d’« émergence » : chaque niveau supérieur (matière → vie → esprit → valeurs → divinité) dépend des niveaux inférieurs sans être réductible à eux, car il possède des qualités nouvelles irréductibles. Cette « évolution émergente » est animée par un nisus (élan créateur interne) qui pousse la réalité vers des formes de complexité et de valeur toujours plus riches, sans recourir à un Dieu transcendant créateur. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=RJddJGpuwJA"  title="Samuel Alexander par See Hear Say Learn"&gt;"Son œuvre maîtresse&lt;/a&gt;, Space, Time, and Deity (1920), issue de ses conférences Gifford, expose ce système hiérarchique et panenthéiste : la divinité n’est pas un être séparé mais la qualité émergente ultime de l’esprit cosmique, intégrant les valeurs de vérité, beauté, bonté et liberté. Bien qu’il partage avec Bergson l’idée d’un élan créateur, Alexander s’oppose à la « durée pure » bergsonienne et insiste sur la continuité et la rationalité descriptive de la métaphysique comme science des structures les plus universelles du réel. &lt;/p&gt; &lt;p&gt; Il a exercé une influence notable sur des penseurs comme Whitehead et a suscité des critiques de Russell, tout en restant une référence centrale pour les débats sur l’émergence, le réalisme et la relation entre science et métaphysique. Sa philosophie offre une voie originale entre naturalisme scientifique et spiritualité immanente, où la valeur et le sens émergent naturellement de l’organisation croissante de l’espace-temps en formes de vie et de conscience. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>194</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3936,90 +3953,95 @@
     </row>
     <row r="24" customFormat="false" ht="279" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_Alexander" title=" Wikipedia"&gt;Samuel ALEXANDER&lt;/a&gt; était un philosophe britannique d’origine australienne, figure majeure de l’émergentisme britannique et du réalisme métaphysique. Sa pensée repose sur une ontologie moniste où l’espace-temps constitue la substance fondamentale de toute réalité : matière, vie, esprit et même divinité émergent à partir de cette matrice spatio-temporelle. Alexander rejette l’idéalisme (hégélien ou britannique) ainsi que le dualisme cartésien, et propose un naturalisme réaliste dans lequel les catégories (substance, causalité, universalité) ne sont pas des structures de l’entendement (comme chez Kant) mais des déterminations concrètes de l’être lui-même. &lt;/p&gt; &lt;p&gt; Le cœur de sa philosophie est la notion d’« émergence » : chaque niveau supérieur (matière → vie → esprit → valeurs → divinité) dépend des niveaux inférieurs sans être réductible à eux, car il possède des qualités nouvelles irréductibles. Cette « évolution émergente » est animée par un nisus (élan créateur interne) qui pousse la réalité vers des formes de complexité et de valeur toujours plus riches, sans recourir à un Dieu transcendant créateur. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=RJddJGpuwJA"  title="Samuel Alexander par See Hear Say Learn"&gt;"Son œuvre maîtresse&lt;/a&gt;, Space, Time, and Deity (1920), issue de ses conférences Gifford, expose ce système hiérarchique et panenthéiste : la divinité n’est pas un être séparé mais la qualité émergente ultime de l’esprit cosmique, intégrant les valeurs de vérité, beauté, bonté et liberté. Bien qu’il partage avec Bergson l’idée d’un élan créateur, Alexander s’oppose à la « durée pure » bergsonienne et insiste sur la continuité et la rationalité descriptive de la métaphysique comme science des structures les plus universelles du réel. &lt;/p&gt; &lt;p&gt; Il a exercé une influence notable sur des penseurs comme Whitehead et a suscité des critiques de Russell, tout en restant une référence centrale pour les débats sur l’émergence, le réalisme et la relation entre science et métaphysique. Sa philosophie offre une voie originale entre naturalisme scientifique et spiritualité immanente, où la valeur et le sens émergent naturellement de l’organisation croissante de l’espace-temps en formes de vie et de conscience. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="279" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
         <v>1860</v>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B25" s="7" t="n">
         <v>1919</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Jacob OSIS</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://lv.wikipedia.org/wiki/J%C4%93kabs_Osis"  title=" Wikipedia"&gt;Jacob OSIS&lt;/a&gt; connu sous le nom de Jakob Ohse ou Iakov Oze, était considéré comme le premier philosophe letton académiquement formé et l’une des figures centrales de l’« école de Tartu » (ou « école de Jurjev ») en philosophie. Né en Courlande (Empire russe) dans une famille paysanne lettonne, il étudie la théologie puis la philosophie à l’université de Tartu (alors appelée Université de Dorpat / Jurjev), où il devient l’élève et le successeur intellectuel de Gustav Teichmüller. &lt;/p&gt; &lt;p&gt; Il se définit lui-même comme le fondateur d’un « personnalisme critique », doctrine qu’il élabore à partir des éléments qu’il puise chez Leibniz, Hermann Lotze et surtout Teichmüller. Son projet est de réviser l’idéalisme allemand (notamment hégélien) et de résister aux tendances matérialistes et positivistes de son époque, en recentrant la philosophie sur la notion de personne et de centres psychiques actifs. Pour Osis, la réalité ultime ne réside pas dans des substances matérielles ou dans un Esprit absolu, mais dans un système de centres conscients, analogues aux monades leibniziennes, dont chaque personne est un exemple. &lt;/p&gt; &lt;p&gt; Dans sa métaphysique, il soutient que la véritable réalité est une pluralité de « centres psychiques » ou de monades, chacun étant un sujet vivant, actif et doué de volonté, qui se représente le monde depuis son propre point de vue. La personne n’est pas un objet parmi d’autres, mais un commencement actif et autonome, à la fois être, pensée et action, ce qui le rapproche des développements ultérieurs du personnalisme français (par exemple chez Emmanuel Mounier), eux aussi influencés par Leibniz. Cette conception vise à préserver la dignité et l’irréductibilité de la personne face aux réductions naturalistes ou aux systèmes abstraits qui dissolvent l’individu dans un tout indifférencié. &lt;/p&gt; &lt;p&gt; Il  joue un rôle fondateur dans l’histoire intellectuelle lettone : il est non seulement le premier philosophe letton formé académiquement, mais aussi l’un des promoteurs de la création de l’Université de Lettonie et de l’enracinement d’une culture philosophique nationale. Son influence s’exerce surtout à travers ses élèves lettons et russes, même si une grande partie de son œuvre systématique reste manuscrite ou peu diffusée en dehors de l’espace germano-russe. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I25" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="368.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>1861</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anthroposophie ; Théosophisme</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>221</v>
+      <c r="L25" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4027,280 +4049,280 @@
         </is>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="368.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
         <v>1861</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>225</v>
+        <v>215</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>216</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anthroposophie ; Théosophisme</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="n">
+        <v>1861</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P26">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P27">
         <v>2</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="321.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+    <row r="28" customFormat="false" ht="321.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
         <v>1863</v>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B28" s="7" t="n">
         <v>1952</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D28" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Santayana"   title=" Wikipedia"&gt;George SANTAYANA&lt;/a&gt; était un philosophe hispano-américain, né à Madrid et formé à Harvard, qui occupe une place singulière dans la philosophie du XXᵉ siècle par son alliance d’un naturalisme matérialiste rigoureux et d’une sensibilité littéraire, esthétique et religieuse. &lt;/p&gt; &lt;p&gt; Il défend un naturalisme radical : pour lui, tout ce qui existe relève de la matière et de ses configurations ; la conscience, la raison, la culture sont des phénomènes émergents de l’activité biologique et sociale. Il refuse cependant de réduire la vie de l’esprit à un simple épiphénomène sans intérêt : il prend au sérieux l’art, la religion, la morale comme réalités à expliquer, sans pour autant leur accorder un statut ontologique indépendant de la matière. &lt;a href="https://www.youtube.com/watch?v=86qYBc2BA6k" title="the philosophy of george santayana par let’s talk philosophy"&gt;" Cette position &lt;/a&gt;  lui permet de critiquer à la fois l’idéalisme allemand et un matérialisme scientiste étroit, en proposant un matérialisme humaniste. &lt;/p&gt; &lt;p&gt; Sur le plan épistémologique, il est un sceptique profond : il soutient qu’aucune proposition n’est « évidente » en soi et que la croyance en l’existence du monde extérieur (y compris celle de soi) ne repose pas sur une démonstration absolue, mais sur des besoins vitaux et des habitudes d’action. Dans Scepticism and Animal Faith (1923), il développe l’idée d’une « foi animale » : des convictions inévitables, nécessaires à l’action, que le scepticisme ne peut entièrement dissoudre, et qu’il faut assumer lucidement plutôt que de prétendre les fonder rationnellement. Il résume cette attitude en disant que le scepticisme est la « chasteté de l’intellect », à préserver jusqu’à ce qu’il puisse être échangé contre une fidélité mature. &lt;/p&gt; &lt;p&gt; Pour articuler son naturalisme et la richesse de la vie spirituelle, il élabore, dans The Realms of Being (1927–1940), une ontologie en quatre « règnes » : l’essence (formes et possibilités intelligibles), la matière (le monde physique, seul véritablement existant), la vérité (ensemble des propositions vraies) et l’esprit (la conscience comme activité émergente). Cette architecture lui permet de garder une place  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_11_5754_t1_0593_0000_2" title="the essential wisdom of santayana par persée"&gt;à la vie intérieure, &lt;/a&gt; à l’art et à la religion sans renoncer au matérialisme, en traitant les essences comme objets de pensée plutôt que comme entités séparées. Il accorde une importance centrale à l’esthétique et à une lecture naturaliste de la religion et de la morale. Dans The Sense of Beauty et La Vie de la raison, il analyse la beauté comme « plaisir objectivé » et montre comment religion, art et éthique s’enracinent dans la nature humaine et ses besoins, tout en remplissant des fonctions symboliques et existentielles précieuses. Son influence s’étend à la philosophie américaine, à l’esthétique, et à certaines formes de réalisme critique, même si son style littéraire et son indépendance d’esprit le rendent parfois difficile à classer dans une école précise. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H28" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="2" t="s">
+      <c r="I28" s="9"/>
+      <c r="J28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="M27" s="14" t="s">
+      <c r="M28" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
         <v>1866</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B29" s="1" t="n">
         <v>1938</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E29" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Positivisme Logique ; Athéisme</t>
-        </is>
+      <c r="L29" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="30" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Edward_Moore"  title=" Wikipedia"&gt;George Edward MOORE&lt;/a&gt; était un philosophe anglais considéré comme l'un des fondateurs de la &lt;a href="https://www.youtube.com/watch?v=SPm8S3lmML8"  title=" G.E. Moore : « Preuve d'un monde extérieur » par Simon Cushing "&gt;philosophie analytique &lt;/a&gt; aux côtés de Bertrand Russell et Ludwig Wittgenstein. Il a enseigné toute sa carrière à l'université de Cambridge, où il a influencé des générations d'étudiants par sa clarté analytique et sa défense du sens commun. Ses travaux portent principalement sur l'éthique, l'épistémologie et la métaphysique, critiquant l'idéalisme dominant de son époque. &lt;/p&gt; &lt;p&gt; Il rejette les systèmes grandioses pour analyser minutieusement les concepts philosophiques, favorisant la clarté et le sens commun contre les excès métaphysiques. Il défend l'existence du monde externe via des &lt;a href="https://www.youtube.com/watch?v=p4fFl-J0Vks" title=" Le non-naturalisme de G.E. Moore (argumentation par questions ouvertes et intuitionnisme : métaét...r par Philosophy Vibe"&gt;arguments simples&lt;/a&gt;, comme pointer du doigt des objets dans "A Proof of the External World" (1939), et affirme des vérités évidentes comme "Voici une main humaine" dans "A Defence of Common Sense" (1925). En épistémologie, il combat le scepticisme en soulignant que les certitudes ordinaires résistent aux doutes philosophiques. &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Principia Ethica (1903), introduit l'argument de la "question ouverte" contre le naturalisme moral: définir le bien par plaisir ou désir laisse ouverte la question "Est-ce bon?". Le bien est une propriété non naturelle, appréhendée par intuition morale, intrinsèquement désirable en soi, comme la beauté des états de conscience. Cela inspire la méta-éthique et critique  &lt;a href="https://www.persee.fr/doc/enphi_0986-1653_1999_num_50_1_16015"  title="G. E. Moore et la critique de l'utilitarisme évolutionniste de Spencer par Persée"&gt;l'utilitarisme réducteur&lt;/a&gt;, bien qu'il nuance son intuitionnisme pour éviter les formes classiques. Viennent ensuite des Œuvres comme ; Philosophical Studies (1922): recueil d'essais sur perception et connaissance ainsi que ; Some Main Problems of Philosophy (1953, posthume): conférences sur le réalisme. &lt;/p&gt; 
-​</t>
-        </is>
+        <v>250</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>264</v>
+        <v>72</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Intuitionnisme ; Cognitivisme ; Particularisme</t>
+          <t xml:space="preserve">Analytique ; Positivisme Logique ; Athéisme</t>
         </is>
       </c>
       <c r="M30" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile"  title=" Wikipedia"&gt;Giovanni GENTILE&lt;/a&gt; était un philosophe italien connu pour  son rôle de  &lt;a href="https://www.persee.fr/doc/xxs_0294-1759_1989_num_21_1_2089"  title="Giovanni Gentile, philosophe du fascisme par Persée"&gt;"philosophe officiel"&lt;/a&gt; du fascisme italien. Sa philosophie, qu'il appelle "l'idéalisme actuel" ou "actualisme", est une réinterprétation radicale de l'idéalisme hégélien. Ses idées clés sont :&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Id%C3%A9alisme_actuel"  title="Giovanni Gentile, L’Esprit, acte pur par Wikipedia"&gt;L'Acte Pur&lt;/a&gt; : Au cœur de sa philosophie se trouve le concept de "l'acte pur" de la pensée où la seule réalité est celle du "penser dans son actualité" ou "l'acte de penser". L'esprit ne se contente pas de connaître une réalité préexistante, il la crée dans l'acte même de penser. Il n'y a pas de réalité en soi, indépendante du sujet pensant. Tout ce qui est, est l'actualisation de la pensée. &lt;/p&gt; &lt;p&gt;Unité de Sujet et Objet : il rejette la dualité traditionnelle entre sujet connaissant et objet connu. Dans l'acte pur de la pensée, le sujet et l'objet sont indissociables et se constituent mutuellement. La connaissance n'est pas une simple &lt;a href="https://www.youtube.com/watch?v=OvkBWeT-51A"  title="Giovanni Gentile, pedagogia pur par non Puoi Non Saperlo"&gt;réception passive&lt;/a&gt; d'informations, mais un acte créateur. &lt;/p&gt; &lt;p&gt;Rejet de l'Individualisme et Primauté de l'État : L'individu n'a pas de sens pris en dehors de l'État. L'État n'est pas une somme d'individus, mais une entité éthique et spirituelle supérieure qui donne forme et signification à l'existence individuelle. Les droits individuels sont subordonnés à l'État, car c'est l'État qui les rend possibles et qui en définit le cadre. &lt;/p&gt; &lt;p&gt;L'État Éthique Totalitaire : L'État doit être un "État éthique" qui incarne la volonté collective et la réalisation de l'esprit. Cette conception justifie le totalitarisme, car l'État est le seul détenteur de l'autorité, et l'individu doit lui être parfaitement soumis pour le bien collectif. Il n'y a pas de liberté individuelle en dehors de l'État. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Edward_Moore"  title=" Wikipedia"&gt;George Edward MOORE&lt;/a&gt; était un philosophe anglais considéré comme l'un des fondateurs de la &lt;a href="https://www.youtube.com/watch?v=SPm8S3lmML8"  title=" G.E. Moore : « Preuve d'un monde extérieur » par Simon Cushing "&gt;philosophie analytique &lt;/a&gt; aux côtés de Bertrand Russell et Ludwig Wittgenstein. Il a enseigné toute sa carrière à l'université de Cambridge, où il a influencé des générations d'étudiants par sa clarté analytique et sa défense du sens commun. Ses travaux portent principalement sur l'éthique, l'épistémologie et la métaphysique, critiquant l'idéalisme dominant de son époque. &lt;/p&gt; &lt;p&gt; Il rejette les systèmes grandioses pour analyser minutieusement les concepts philosophiques, favorisant la clarté et le sens commun contre les excès métaphysiques. Il défend l'existence du monde externe via des &lt;a href="https://www.youtube.com/watch?v=p4fFl-J0Vks" title=" Le non-naturalisme de G.E. Moore (argumentation par questions ouvertes et intuitionnisme : métaét...r par Philosophy Vibe"&gt;arguments simples&lt;/a&gt;, comme pointer du doigt des objets dans "A Proof of the External World" (1939), et affirme des vérités évidentes comme "Voici une main humaine" dans "A Defence of Common Sense" (1925). En épistémologie, il combat le scepticisme en soulignant que les certitudes ordinaires résistent aux doutes philosophiques. &lt;/p&gt; &lt;p&gt; Son ouvrage majeur, Principia Ethica (1903), introduit l'argument de la "question ouverte" contre le naturalisme moral: définir le bien par plaisir ou désir laisse ouverte la question "Est-ce bon?". Le bien est une propriété non naturelle, appréhendée par intuition morale, intrinsèquement désirable en soi, comme la beauté des états de conscience. Cela inspire la méta-éthique et critique  &lt;a href="https://www.persee.fr/doc/enphi_0986-1653_1999_num_50_1_16015"  title="G. E. Moore et la critique de l'utilitarisme évolutionniste de Spencer par Persée"&gt;l'utilitarisme réducteur&lt;/a&gt;, bien qu'il nuance son intuitionnisme pour éviter les formes classiques. Viennent ensuite des Œuvres comme ; Philosophical Studies (1922): recueil d'essais sur perception et connaissance ainsi que ; Some Main Problems of Philosophy (1953, posthume): conférences sur le réalisme. &lt;/p&gt; 
+​</t>
         </is>
       </c>
       <c r="F31" s="7" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Intuitionnisme ; Cognitivisme ; Particularisme</t>
+        </is>
       </c>
       <c r="M31" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4308,43 +4330,45 @@
         </is>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
         <v>1875</v>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>1961</v>
+      <c r="B32" s="7" t="s">
+        <v>267</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>279</v>
+        <v>269</v>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile"  title=" Wikipedia"&gt;Giovanni GENTILE&lt;/a&gt; était un philosophe italien connu pour  son rôle de  &lt;a href="https://www.persee.fr/doc/xxs_0294-1759_1989_num_21_1_2089"  title="Giovanni Gentile, philosophe du fascisme par Persée"&gt;"philosophe officiel"&lt;/a&gt; du fascisme italien. Sa philosophie, qu'il appelle "l'idéalisme actuel" ou "actualisme", est une réinterprétation radicale de l'idéalisme hégélien. Ses idées clés sont :&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Id%C3%A9alisme_actuel"  title="Giovanni Gentile, L’Esprit, acte pur par Wikipedia"&gt;L'Acte Pur&lt;/a&gt; : Au cœur de sa philosophie se trouve le concept de "l'acte pur" de la pensée où la seule réalité est celle du "penser dans son actualité" ou "l'acte de penser". L'esprit ne se contente pas de connaître une réalité préexistante, il la crée dans l'acte même de penser. Il n'y a pas de réalité en soi, indépendante du sujet pensant. Tout ce qui est, est l'actualisation de la pensée. &lt;/p&gt; &lt;p&gt;Unité de Sujet et Objet : il rejette la dualité traditionnelle entre sujet connaissant et objet connu. Dans l'acte pur de la pensée, le sujet et l'objet sont indissociables et se constituent mutuellement. La connaissance n'est pas une simple &lt;a href="https://www.youtube.com/watch?v=OvkBWeT-51A"  title="Giovanni Gentile, pedagogia pur par non Puoi Non Saperlo"&gt;réception passive&lt;/a&gt; d'informations, mais un acte créateur. &lt;/p&gt; &lt;p&gt;Rejet de l'Individualisme et Primauté de l'État : L'individu n'a pas de sens pris en dehors de l'État. L'État n'est pas une somme d'individus, mais une entité éthique et spirituelle supérieure qui donne forme et signification à l'existence individuelle. Les droits individuels sont subordonnés à l'État, car c'est l'État qui les rend possibles et qui en définit le cadre. &lt;/p&gt; &lt;p&gt;L'État Éthique Totalitaire : L'État doit être un "État éthique" qui incarne la volonté collective et la réalisation de l'esprit. Cette conception justifie le totalitarisme, car l'État est le seul détenteur de l'autorité, et l'individu doit lui être parfaitement soumis pour le bien collectif. Il n'y a pas de liberté individuelle en dehors de l'État. &lt;/p&gt;  </t>
+        </is>
       </c>
       <c r="F32" s="7" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>282</v>
+        <v>272</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="2" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4352,52 +4376,43 @@
         </is>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>285</v>
+        <v>1875</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>1961</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Buber"  title=" Wikipedia"&gt;Martin BUBER&lt;/a&gt; était un philosophe juif autrichien surtout célèbre pour sa pensée du dialogue et de la rencontre "Ich und Du" (I and Thou). Sa biographie et son œuvre ont eu une influence durable sur la philosophie politique, la théologie et l’éducation.  Son parcours intellectuel est marqué par une “philosophie du dialogue” qui cherche à rendre l’existence vécue comme  &lt;a href="https://www.youtube.com/watch?v=x2C7AQRu-iw" title=" La Solitude Moderne : La Réponse de Martin Buber (Philosophie Pratique) par Philosopheasy en français"&gt;relation authentique &lt;/a&gt; plutôt que comme simple connaissance ou instrumentalisation de l’autre. &lt;/p&gt; &lt;p&gt;  Avec Franz Rosenzweig, il fonde et dirige des institutions d’éducation juive et développe une pédagogie fondée sur le dialogue entre les individus et entre le peuple juif et le monde extérieur. Cette collaboration est centrale dans son développement. Son oeuvre majeure : &lt;a href="https://www.youtube.com/watch?v=obuZPJirPkE" title=" Martin Buber : Moi et Tu par PhilosophyToons"&gt;" l’essai Ich und Du" &lt;/a&gt; paru en 1923 propose que les relations humaines ne peuvent pas être réduites à des rapports utilitaires ou à des abstractions. Cette pensée s’applique à l’éthique, à la religion, et à l’éducation. Il oppose l’“I–It” (je-tu) à l’“I–Thou” (je-toi), arguant que l’existence humaine se réalise vraiment dans des relations vécues comme présence et écoute réciproque.&lt;/p&gt; &lt;p&gt;  Il a été actif dans l’éducation des adultes juifs en Allemagne et a plaidé pour une pédagogie fondée sur l’engagement personnel et la relation authentique plutôt que sur l’instruction pure. Ses idées inspirent des discussions sur le droit à la différence, le pluralisme religieux et les approches éthiques des conflits, tout en restant critiques des formes de discours essentialistes. &lt;/p&gt;  &lt;audio controls title="Martin Buber, sentinelle de l'humanité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-03.01.2016-ITEMA_20879863-2015C14958E0049-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
+        <v>278</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>279</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>291</v>
+        <v>281</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>282</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Existentialisme ; Hassidisme</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>284</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4405,43 +4420,52 @@
         </is>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="212.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
-        <v>1879</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>1934</v>
+        <v>1878</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>295</v>
+        <v>287</v>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Buber"  title=" Wikipedia"&gt;Martin BUBER&lt;/a&gt; était un philosophe juif autrichien surtout célèbre pour sa pensée du dialogue et de la rencontre "Ich und Du" (I and Thou). Sa biographie et son œuvre ont eu une influence durable sur la philosophie politique, la théologie et l’éducation.  Son parcours intellectuel est marqué par une “philosophie du dialogue” qui cherche à rendre l’existence vécue comme  &lt;a href="https://www.youtube.com/watch?v=x2C7AQRu-iw" title=" La Solitude Moderne : La Réponse de Martin Buber (Philosophie Pratique) par Philosopheasy en français"&gt;relation authentique &lt;/a&gt; plutôt que comme simple connaissance ou instrumentalisation de l’autre. &lt;/p&gt; &lt;p&gt;  Avec Franz Rosenzweig, il fonde et dirige des institutions d’éducation juive et développe une pédagogie fondée sur le dialogue entre les individus et entre le peuple juif et le monde extérieur. Cette collaboration est centrale dans son développement. Son oeuvre majeure : &lt;a href="https://www.youtube.com/watch?v=obuZPJirPkE" title=" Martin Buber : Moi et Tu par PhilosophyToons"&gt;" l’essai Ich und Du" &lt;/a&gt; paru en 1923 propose que les relations humaines ne peuvent pas être réduites à des rapports utilitaires ou à des abstractions. Cette pensée s’applique à l’éthique, à la religion, et à l’éducation. Il oppose l’“I–It” (je-tu) à l’“I–Thou” (je-toi), arguant que l’existence humaine se réalise vraiment dans des relations vécues comme présence et écoute réciproque.&lt;/p&gt; &lt;p&gt;  Il a été actif dans l’éducation des adultes juifs en Allemagne et a plaidé pour une pédagogie fondée sur l’engagement personnel et la relation authentique plutôt que sur l’instruction pure. Ses idées inspirent des discussions sur le droit à la différence, le pluralisme religieux et les approches éthiques des conflits, tout en restant critiques des formes de discours essentialistes. &lt;/p&gt;  &lt;audio controls title="Martin Buber, sentinelle de l'humanité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-03.01.2016-ITEMA_20879863-2015C14958E0049-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F34" s="7" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>298</v>
+        <v>290</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M34" s="13" t="s">
-        <v>301</v>
+        <v>121</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme ; Hassidisme</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4449,51 +4473,43 @@
         </is>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
-        <v>1880</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>134</v>
+        <v>1879</v>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1934</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Otto_Weininger"  title=" Wikipedia"&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href="https://www.youtube.com/watch?v=wetIerJEucU" title=" Otto Weininger Le génie Maudit par Aliouca"&gt;maison de Beethoven à Vienne&lt;/a&gt;. Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href="https://www.youtube.com/watch?v=aFZpRoBlMQI" title=" Otto Weininger qui haîssait les femmes par Voyage Endormis"&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href="https://www.youtube.com/watch?v=vMfEJQVv3VM" title=" Otto Weininger Le mytère du féminin par Philosopheasy en Français"&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits "féminins" vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère "féminine" décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title="Otto Weininger et la question du genie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
-        </is>
+        <v>294</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>295</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>307</v>
+        <v>297</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>298</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>121</v>
+        <v>299</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>301</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4501,43 +4517,51 @@
         </is>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="313.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
-        <v>1881</v>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>1966</v>
+        <v>1880</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>311</v>
+        <v>303</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Otto_Weininger"  title=" Wikipedia"&gt;Otto WEININGER&lt;/a&gt;  était un philosophe autrichien, juif converti au protestantisme, qui publie à 23 ans Sexe et caractère (1903), un ouvrage controversé qui explose en popularité après son suicide dans la   &lt;a href="https://www.youtube.com/watch?v=wetIerJEucU" title=" Otto Weininger Le génie Maudit par Aliouca"&gt;maison de Beethoven à Vienne&lt;/a&gt;. Étudiant brillant à Vienne, influencé par Kant, Schopenhauer et la psychologie naissante, il rejette ses origines juives et développe une  &lt;a href="https://www.youtube.com/watch?v=aFZpRoBlMQI" title=" Otto Weininger qui haîssait les femmes par Voyage Endormis"&gt;vision misogyne &lt;/a&gt; et antisémite extrême, voyant en lui-même une incarnation tragique de ses propres critiques. Son court génie mystique et autodestructeur marque la modernité viennoise, admiré par Wittgenstein et Freud malgré le scandale. &lt;/p&gt; &lt;p&gt; Dans Sexe et caractère, il postule une bisexualité ontologique chez tout humain : le principe masculin incarne l'esprit, la logique, la moralité, la création et l'individualité ;    &lt;a href="https://www.youtube.com/watch?v=vMfEJQVv3VM" title=" Otto Weininger Le mytère du féminin par Philosopheasy en Français"&gt;le féminin &lt;/a&gt; représente la matière, l'instinct sexuel, l'amoralité, la passivité et le collectif. La femme idéale n'existe pas, car la féminité est une déficience ; l'homme supérieur transcende ses traits "féminins" vers un idéal asexué de génie pur. Il assimile Juifs, femmes et homosexuels à cette sphère "féminine" décadente, opposée à l'aryen mâle ascétique. &lt;/p&gt; &lt;p&gt; Il  prolonge cette métaphysique dualiste (esprit/chair) en éthique individualiste : le sens de la vie est la vertu par la raison et l'empathie objective, dans un univers solipsiste où l'individu éthique est seul face à l'absolu moral. Il critique la modernité comme triomphe du féminin/juif/sensuel, prônant une ascèse quasi-chrétienne pour une humanité nouvelle. Son style aphoristique, prophétique, préfigure existentialisme et psychanalyse. &lt;/p&gt; &lt;p&gt; Son influence persiste malgré l'appropriation nazie partielle ; il y voit un antidote à la vanité, tandis que sa tombe à Vienne symbolise ce destin fulgurant. Il incarne le paradoxe d'un penseur autophobe qui illumine les abysses de l'identité. &lt;/p&gt;   &lt;audio controls title="Otto Weininger et la question du genie par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-18.02.2017-ITEMA_21234114-2017C22785E0004-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F36" s="7" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>314</v>
+        <v>306</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>307</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
-        <v>315</v>
+        <v>22</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>299</v>
+        <v>121</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>317</v>
+        <v>84</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4545,43 +4569,43 @@
         </is>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="313.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>1931</v>
+        <v>1966</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>320</v>
+        <v>310</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
-        <v>22</v>
+        <v>315</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>326</v>
+        <v>316</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>317</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4589,48 +4613,43 @@
         </is>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="361.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
         <v>1882</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>1945</v>
+        <v>1931</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>329</v>
+        <v>319</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>141</v>
+        <v>324</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="M38" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>325</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4643,132 +4662,137 @@
         <v>1882</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="9"/>
+        <v>329</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>331</v>
+      </c>
       <c r="H39" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>339</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K39" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="361.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="M39" s="15" t="s">
+      <c r="M40" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="n">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="225.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
         <v>1883</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B41" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D41" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Ortega_y_Gasset"  title=" Wikipedia"&gt;José ORTEGA Y GASSET&lt;/a&gt;  était un philosophe espagnol connu pour avoir défendu une pensée centrée sur la vie concrète, la perspective et la situation historique de chaque individu. Il a aussi été essayiste, sociologue et une figure importante de la vie intellectuelle espagnole. &lt;/p&gt; &lt;p&gt; Sa philosophie est souvent résumée par l’idée que &lt;a href="https://www.cjd.net/ressources/idees/jose-ortega-y-gasset-chaque-vie-est-un-point-de-vue-sur-lunivers/"  title="José Ortéga y Gasset : chaque vie est un point de vue sur l’univers par CDJ"&gt; « je suis moi et ma circonstance » &lt;/a&gt; : l’être humain ne peut pas être compris séparément du monde, du temps et du contexte dans lesquels il vit. De là vient son perspectivisme, selon lequel toute vérité humaine est liée à un point de vue situé, sans que cela tombe dans un relativisme total. &lt;/p&gt; &lt;p&gt; Il  a aussi développé la notion de raison vitale, puis de raison historique, pour critiquer une philosophie trop abstraite et rappeler que la pensée doit partir de la vie réelle et de son évolution dans le temps. Son œuvre la plus célèbre, &lt;em&gt;La Révolte des masses&lt;/em&gt;, analyse la montée de  &lt;a href="https://www.youtube.com/watch?v=bse3ho0Hk7U"  title="José Ortéga y Gasset : le règne de l’homme masse par Ego Non"&gt;l’« homme-masse » &lt;/a&gt; et les tensions de la modernité. Paru en 1929, ce livre décrit l’homme moyen satisfait de lui-même, qui profite des conquêtes de la civilisation sans en reconnaître les exigences. &lt;/p&gt; &lt;p&gt; Politiquement, il a défendu la modernisation de l’Espagne et s’est engagé contre la dictature de Primo de Rivera, puis en faveur de la République, dont il est élu député en 1931.  &lt;a href="https://www.youtube.com/watch?v=jdB0729NoPg"  title="José Ortéga y Gasset : méditation sur la technique par Edition Allia"&gt;Son influence &lt;/a&gt;  dépasse l’Espagne, car il a marqué la philosophie continentale par sa réflexion sur la culture européenne, l’histoire et la place de l’individu dans la société moderne. En 1923, il fonde la &lt;em&gt;Revista de Occidente&lt;/em&gt;, qui fait connaître la pensée allemande en Espagne. Exilé pendant la guerre civile, il ne rentre qu’en 1945. &lt;/p&gt;   &lt;audio controls title=" José ORTEGA y GASSET, penser la diversité culturelle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10076-12.01.2024-ITEMA_23612353-2024C36128S0012-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G41" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>349</v>
-      </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="223.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
-        <v>1883</v>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>1946</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>351</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4776,48 +4800,43 @@
         </is>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="223.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>1966</v>
+        <v>1946</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>362</v>
+        <v>353</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>354</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>299</v>
+        <v>53</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="M42" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>358</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4825,679 +4844,680 @@
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
-        <v>1885</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>367</v>
+        <v>1884</v>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>1966</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>370</v>
+        <v>361</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>373</v>
+        <v>364</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>365</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I44" s="9"/>
+      <c r="J44" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
         <v>1889</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B45" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D45" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein"  title=" Wikipedia"&gt;Ludwig WITTGENSTEIN&lt;/a&gt; était un philosophe autrichien énigmatique et influent souvent divisée en deux périodes distinctes, le "premier" et le "second" Wittgenstein. Le premier, &lt;a href="https://www.youtube.com/watch?v=4w5xzgna1l0&amp;list=PLyfQgbpaPz7hZqscDHbJVRNtcDRHZ5mGr"  title="Tractatus logico-philosophicus, Ludwig Wittgenstein par Thibault BELZACQ"&gt; "le Tractatus Logico-Philosophicus"&lt;/a&gt;  (1921) est un texte dense, écrit de manière aphoristique, et qui se présente comme la solution à tous les problèmes philosophiques. Sa thèse centrale est que le langage a pour but de décrire le monde, qui est constitué de faits.&lt;/p&gt;
 &lt;p&gt; La théorie de la représentation :    le langage est une "image" du monde. Une phrase a un sens si et seulement si elle dépeint un état de choses possible dans la réalité. Le langage et le monde partagent une structure logique commune. &lt;/p&gt;
 &lt;p&gt; La distinction entre "dire" et "montrer" : le langage ne peut dire que ce qui a un sens. Les choses qui ne peuvent pas être décrites (comme la logique elle-même, l'éthique, la métaphysique, la religion) ne peuvent pas être "dites", mais elles se "montrent" à travers le langage. Le célèbre dernier aphorisme du Tractatus est : "Ce dont on ne peut parler, il faut le taire." &lt;/p&gt; &lt;p&gt; La fin de la philosophie ? : il pensait avoir résolu les problèmes de la philosophie en montrant qu'ils provenaient d'une mauvaise utilisation du langage. Les questions métaphysiques (sur l'être, l'âme, etc.) sont, selon lui, dénuées de sens, car elles tentent de "dire" ce qui ne peut qu'être "montré". Après la publication de cet ouvrage, il a abandonné la philosophie pendant près de dix ans, pensant avoir achevé son travail. &lt;/p&gt; &lt;p&gt; Le "second" :   &lt;a href="https://wittgenstein.fr/category/lectures-des-recherches-philosophiques/"  title="Ludwig Wittgenstein  par Julien Gautier"&gt; les "Recherches philosophiques"&lt;/a&gt;  à la fin des années 1920. Il a commencé à remettre en question les fondations de son propre Tractatus. Publiées à titre posthume en 1953, elles marquent une rupture radicale avec sa première pensée.&lt;/p&gt; &lt;p&gt; Le concept de   "jeux de langage" :  Il abandonne la théorie de la représentation pour une nouvelle conception du langage qui n'est pas un miroir du monde, mais un outil. Le sens d'un mot n'est pas son référent dans la réalité, mais son usage dans un contexte donné. Il introduit la notion de "jeux de langage" pour désigner les différentes activités humaines où le langage est utilisé (commander, questionner, raconter une blague, etc.). Chaque "jeu" a ses propres règles et sa propre grammaire.&lt;/p&gt; &lt;p&gt;La philosophie comme thérapie : il ne considère plus que les problèmes philosophiques peuvent être résolus, mais qu'ils peuvent être dissous. L'objectif de la philosophie est de démêler les confusions que le langage crée, en montrant comment les mots sont utilisés dans différents "jeux". La philosophie n'est plus une quête de la vérité ultime, mais une "thérapie" qui aide à "voir clair" dans notre usage du langage. &lt;/p&gt; &lt;p&gt; "Formes de vie" : La signification du langage est profondément enracinée dans notre pratique collective et nos actions, dans ce qu'il appelle nos "formes de vie". Les règles d'un "jeu de langage" ne peuvent être comprises qu'à l'intérieur de ces pratiques sociales partagées. Il s'oppose à l'idée d'un "langage privé", montrant que le sens nécessite un accord public et une communauté d'utilisateurs. &lt;/p&gt;  &lt;audio controls title="Ludwig Wittgenstein ou la philosophie de l’indicible par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13957-12.07.2020-ITEMA_22380918-2020C22785E0017-1779455909.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F45" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7">
-        <v>1886</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1939</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1886 – 1939</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski"   title=" Wikipedia"&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href="https://www.youtube.com/watch?v=Vvt7ns_jZvY"  title="The logic of reality  par TroughtLab"&gt;la logique et des mathématiques&lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique "vraie" modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. Ses trois systèmes portent les noms de « protothétique », logique des propositions, d’« ontologie », logique des noms, et de « méréologie », théorie des parties et du tout. Cette dernière offre une alternative à la théorie des ensembles : une classe n’y est pas un objet abstrait, mais un tout concret formé de ses parties, ce qui évite le paradoxe de Russell. Professeur à l’université de Varsovie, il eut pour unique doctorant Alfred Tarski. Il meurt en 1939, quelques mois avant l’invasion de la Pologne. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>393</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Méréologie</t>
-        </is>
+        <v>385</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
-        <v>1891</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>396</v>
+      <c r="P45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7">
+        <v>1886</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1939</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886 – 1939</t>
+        </is>
       </c>
       <c r="D46" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Gramsci"  title=" Wikipedia"&gt;Antonio GRAMSCI&lt;/a&gt; (1891-1937) est un philosophe marxiste et homme politique italien, l’un des fondateurs du Parti communiste italien. Né en Sardaigne dans une famille modeste, il étudie à Turin, où il anime le journal &lt;em&gt;L’Ordine Nuovo&lt;/em&gt; et le mouvement des conseils d’usine. Député, puis secrétaire général du parti, il est arrêté en 1926 par le régime fasciste ; le procureur aurait déclaré : « Il faut empêcher ce cerveau de fonctionner pendant vingt ans. »&lt;/p&gt; &lt;p&gt;En prison, malgré la maladie, il remplit une trentaine de cahiers, les &lt;em&gt;Cahiers de prison&lt;/em&gt;, publiés après sa mort. Il y cherche à comprendre pourquoi la révolution a réussi en Russie et échoué en Occident. Sa réponse est la notion d’&lt;a href="https://www.youtube.com/watch?v=Q8s8r43ANbQ"  title="L’hégémonie culturelle selon Antonio GRAMSCI  par France Culture"&gt;hégémonie culturelle&lt;/a&gt; : une classe dominante ne règne pas seulement par la force de l’État, mais par le consentement qu’elle obtient en diffusant ses valeurs et son « sens commun » à travers la société civile, l’école, l’Église, la presse ou les associations. Dans les sociétés occidentales, où cette société civile est solide, une attaque frontale, la « guerre de mouvement », échoue ; il faut d’abord mener une longue « guerre de position » pour conquérir les esprits. Ce combat revient aux « intellectuels organiques », liés à une classe sociale, qui élaborent et diffusent une nouvelle conception du monde. Gramsci appelle le marxisme une « philosophie de la praxis » et résume son attitude par la formule : « pessimisme de l’intelligence, optimisme de la volonté ».&lt;/p&gt; &lt;p&gt;Libéré trop tard, il meurt en 1937. Il est devenu &lt;a href="https://www.youtube.com/watch?v=K3vf4DSL_GE"  title="Comprendre  Antonio GRAMSCI  par Politikon"&gt;une référence&lt;/a&gt; mondiale, des études culturelles et postcoloniales à la théorie politique, à gauche comme à droite.&lt;/p&gt;  &lt;audio controls title="Qui est Antonio GRAMSCI par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.02.2017-ITEMA_21240143-2017C12410E0055-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        <v>389</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stanis%C5%82aw_Le%C5%9Bniewski"   title=" Wikipedia"&gt;Stanislaw LESNIEWSKI&lt;/a&gt;  était un logicien &amp; philosophe polonais, figure clé de l'École de Varsovie aux côtés de Łukasiewicz et Tarski. Spécialiste des fondements de &lt;a href="https://www.youtube.com/watch?v=Vvt7ns_jZvY"  title="The logic of reality  par TroughtLab"&gt;la logique et des mathématiques&lt;/a&gt;, il développa trois systèmes logiques originaux pour résoudre les paradoxes comme celui de Russell, en rejetant le formalisme pur au profit d'une logique interprétée et ancrée dans la réalité. &lt;/p&gt; &lt;p&gt; Il  rejette le conventionalisme et les logiques multi-valuées, insistant sur une logique "vraie" modélisant la réalité, avec une distinction stricte entre langage-objet et métalange. Perfectionniste, il privilégie des définitions exactes, un extensionalisme radical et un nominalisme anti-abstrait, critiquant Russell, Zermelo ou Łukasiewicz.  Ses conférences à Varsovie dès 1919 couvrent groupes, définitions inductives et comparaisons avec Whitehead, mais ses notes furent détruites lors de l'Insurrection de Varsovie  en 1944. &lt;/p&gt; &lt;p&gt; Bien que marginaux par leur complexité, ses apports (catégories sémantiques, méréologie) influencent la sémantique moderne, la philosophie analytique et la logique formelle. Ses trois systèmes portent les noms de « protothétique », logique des propositions, d’« ontologie », logique des noms, et de « méréologie », théorie des parties et du tout. Cette dernière offre une alternative à la théorie des ensembles : une classe n’y est pas un objet abstrait, mais un tout concret formé de ses parties, ce qui évite le paradoxe de Russell. Professeur à l’université de Varsovie, il eut pour unique doctorant Alfred Tarski. Il meurt en 1939, quelques mois avant l’invasion de la Pologne. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F46" s="7" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytique ; Méréologie</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Gramsci"  title=" Wikipedia"&gt;Antonio GRAMSCI&lt;/a&gt; (1891-1937) est un philosophe marxiste et homme politique italien, l’un des fondateurs du Parti communiste italien. Né en Sardaigne dans une famille modeste, il étudie à Turin, où il anime le journal &lt;em&gt;L’Ordine Nuovo&lt;/em&gt; et le mouvement des conseils d’usine. Député, puis secrétaire général du parti, il est arrêté en 1926 par le régime fasciste ; le procureur aurait déclaré : « Il faut empêcher ce cerveau de fonctionner pendant vingt ans. »&lt;/p&gt; &lt;p&gt;En prison, malgré la maladie, il remplit une trentaine de cahiers, les &lt;em&gt;Cahiers de prison&lt;/em&gt;, publiés après sa mort. Il y cherche à comprendre pourquoi la révolution a réussi en Russie et échoué en Occident. Sa réponse est la notion d’&lt;a href="https://www.youtube.com/watch?v=Q8s8r43ANbQ"  title="L’hégémonie culturelle selon Antonio GRAMSCI  par France Culture"&gt;hégémonie culturelle&lt;/a&gt; : une classe dominante ne règne pas seulement par la force de l’État, mais par le consentement qu’elle obtient en diffusant ses valeurs et son « sens commun » à travers la société civile, l’école, l’Église, la presse ou les associations. Dans les sociétés occidentales, où cette société civile est solide, une attaque frontale, la « guerre de mouvement », échoue ; il faut d’abord mener une longue « guerre de position » pour conquérir les esprits. Ce combat revient aux « intellectuels organiques », liés à une classe sociale, qui élaborent et diffusent une nouvelle conception du monde. Gramsci appelle le marxisme une « philosophie de la praxis » et résume son attitude par la formule : « pessimisme de l’intelligence, optimisme de la volonté ».&lt;/p&gt; &lt;p&gt;Libéré trop tard, il meurt en 1937. Il est devenu &lt;a href="https://www.youtube.com/watch?v=K3vf4DSL_GE"  title="Comprendre  Antonio GRAMSCI  par Politikon"&gt;une référence&lt;/a&gt; mondiale, des études culturelles et postcoloniales à la théorie politique, à gauche comme à droite.&lt;/p&gt;  &lt;audio controls title="Qui est Antonio GRAMSCI par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.02.2017-ITEMA_21240143-2017C12410E0055-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="244.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
         <v>1895</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B48" s="1" t="n">
         <v>1961</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E48" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
         <v>1898</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C49" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D49" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_Murphy"  title=" Wikipedia"&gt;Joseph MURPHY&lt;/a&gt;  était un auteur et prédicateur irlandais, figure majeure du courant de la Nouvelle Pensée et de la littérature de développement personnel spirituel. Il a écrit une trentaine de livres sur la pensée, l’autosuggestion, la prière et la prospérité,  diffusés à des millions de lecteurs. &lt;/p&gt; &lt;p&gt; Pour lui, la réalité extérieure est largement façonnée par nos pensées, nos images mentales et nos croyances profondes. Il distingue un esprit conscient et un subconscient présenté comme un réservoir quasi illimité de puissance créatrice, qui enregistre nos croyances et les manifeste dans la santé, les relations, l’argent. La prière, la visualisation et l’autosuggestion sont des moyens privilégiés pour "programmer" ce subconscient avec des idées positives (foi, réussite, santé), ce qui, selon lui, finit par se traduire dans les faits. &lt;/p&gt; &lt;p&gt; Il cherche à harmoniser la métaphysique de la  &lt;a href="https://www.youtube.com/watch?v=SuwToXC2jFE"  title="Cesse de Chercher et Tout te Trouvera | Joseph MURPHY par Livre Interdit"&gt;Nouvelle Pensée, &lt;/a&gt; les Écritures bibliques, le symbolisme religieux et la psychologie moderne, en lisant aussi bien les textes orientaux que les auteurs de la Science chrétienne, de la Science de l’esprit ou de la Divine Science. &lt;/p&gt; &lt;p&gt; Dans son ouvrage qui fût un best-seller "Le pouvoir de votre subconscient", il expose une vision métaphysique du mental et de la prière affirmative. Il affirme que l’on peut utiliser ce mécanisme pour la guérison physique, la résolution de problèmes, la création d’opportunités et il présente de nombreux cas d’"applications". Il développe une méthode d’autosuggestion simple : répéter des phrases positives, imaginer la situation souhaitée comme déjà réalisée, se détendre profondément et remettre le résultat au subconscient, qui "sait" comment opérer. &lt;/p&gt; &lt;p&gt; Même si son discours ressemble souvent à du développement personnel psychologique, la trame de fond est  &lt;a href="https://www.youtube.com/watch?v=Flmk5Jtxfdg" title="LA MAGIE DE LA FOI | Joseph Murphy  par Audiolivres"&gt;profondément religieuse &lt;/a&gt; et mystique. Il interprète les textes bibliques de manière symbolique, comme des descriptions de lois mentales et spirituelles. Il s’inspire des philosophies orientales, voyant dans la convergence des traditions la confirmation d’une même loi spirituelle. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F49" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="2" t="s">
+      <c r="I49" s="9"/>
+      <c r="J49" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="192.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
         <v>1899</v>
       </c>
-      <c r="B49" s="7" t="n">
+      <c r="B50" s="7" t="n">
         <v>1992</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C50" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D50" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Hayek"  title=" Wikipedia"&gt;Friedrich HAYEK&lt;/a&gt; était un économiste et philosophe autrichien, Nobel d'économie en 1974, adopta explicitement l'agnosticisme dès l'âge de 15 ans, rompant avec son éducation catholique pour une position sceptique sur les questions métaphysiques. Élevé dans un milieu chrétien viennois, il rejeta tôt les dogmes religieux, privilégiant une raison limitée face aux certitudes absolues sur Dieu ou l'au-delà, dans l'esprit d'un libéralisme épistémique. &lt;/p&gt; &lt;p&gt; Sans lien avec l'origine historique de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;L'agnosticisme&lt;/a&gt;, il en fait un fondement de sa critique du &lt;a href="https://fr.wikipedia.org/wiki/Constructivisme_(politique)"  title=" Constructivisme  par Wikipedia"&gt;"constructivisme rationnel" :&lt;/a&gt;  la connaissance humaine est dispersée, partielle et imparfaite, rendant impossible toute planification globale ou prétention à une vérité totale, qu'elle soit scientifique ou théologique. Dans La Constitution de la liberté ou Droit, législation et liberté, il valorise l'"ordre spontané" des marchés et des traditions comme résultante d'actions humaines non concertées, opposé à tout hubris métaphysique. &lt;/p&gt; &lt;p&gt; Son agnosticisme se teinte d'un scepticisme épistémologique anti-totalitaire : l'État ou les idéologies ne peuvent prétendre appréhender la complexité sociale mieux que les individus libres. Il critique ainsi le scientisme socialiste comme une "prétention au savoir" illusoire, écho à l'agnosticisme par son humilité face à l'inconnaissable, tout en défendant une morale laïque des règles générales &lt;a href="https://www.youtube.com/watch?v=TiGv4YcFieQ"  title="La route de la servitude  par Capsio"&gt; (la route de la servitude).&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Père spirituel du néolibéralisme (Société du Mont-Pèlerin, 1947), il prolonge l'agnosticisme dans une philosophie politique : liberté comme non-coercition, égalité devant la loi plutôt que des fins substantielles, refusant toute utopie divine ou humaine. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F50" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G50" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>427</v>
-      </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Individualisme méthodologique</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>435</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Individualisme méthodologique</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="210.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="I51" s="9"/>
+      <c r="J51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L51" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="M51" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="242.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
         <v>1901</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B52" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E52" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F52" s="20" t="s">
         <v>441</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G52" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H52" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J52" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M52" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
         <v>1902</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B53" s="1" t="n">
         <v>1967</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E53" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="2" t="s">
+      <c r="F53" s="20"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I53" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="J53" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="K53" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="L52" s="2" t="s">
+      <c r="L53" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="345.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
         <v>1902</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B54" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C54" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D54" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Karl_Popper"  title=" Wikipedia"&gt;Karl POPPER&lt;/a&gt; était un philosophe autrichien-britannique qui  a révolutionné la philosophie des sciences avec son critère de falsifiabilité, exposé dans  &lt;a href="https://www.youtube.com/watch?v=AENUk4f6Ftg" title="K Popper la logique et la découverte scientifique par Philosophie Analytique"&gt;La Logique de la découverte scientifique &lt;/a&gt;  (1934). Ce principe définit une théorie comme scientifique si elle peut être testée et potentiellement réfutée par l'expérience, contrairement aux pseudosciences comme la psychanalyse ou le marxisme, qui résistent à toute infirmation. &lt;/p&gt;&lt;p&gt;Son &lt;a href="https://www.youtube.com/watch?v=sFbctDTNXTQ&amp;ab_channel=EcoledelaLibert%C3%A9" title="Qu'est ce qu'un énoncé falsifiable par Ecole de la Liberté"&gt; critère de falsifiabilité&lt;/a&gt;, qu'il a proposé comme critère de démarcation entre  &lt;a href="https://www.youtube.com/watch?v=gNZMnyaTuII&amp;ab_channel=Fran%C3%A7oisJourde" title="sciences et  pseudosciences par François Jourde"&gt; les sciences et les pseudosciences. &lt;/a&gt; Selon lui, une théorie scientifique doit être testable et potentiellement réfutable par des observations ou des expériences. Par exemple, la théorie de la relativité d'Einstein est scientifique parce qu'elle fait des prédictions précises qui peuvent être testées et éventuellement réfutées. Il critiquait l'idée selon laquelle la science progresse par accumulation de preuves confirmatives par induction et soutenait que la science avance plutôt par conjectures et réfutations, où les scientifiques proposent des hypothèses audacieuses qui sont ensuite soumises à des tests rigoureux. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages &lt;a href="https://www.youtube.com/watch?v=WheeYYBtSMA" title="la société ouverte et ses ennemis par GORVS S"&gt;  "La Société Ouverte et ses ennemis ",&lt;/a&gt;  il défend la démocratie libérale et critique les systèmes totalitaires. Il introduit le concept de "société ouverte" où les individus sont libres de critiquer les institutions et où les changements sociaux se font par des réformes progressives plutôt que par des révolutions violentes. Il s'opposait aux théories historicistes comme celles de Hegel et Marx, qui prétendaient que l'histoire se déroulait selon des lois inévitables et prédéterminées et a mis en avant &lt;a href="https://www.youtube.com/watch?v=PS25rur5438&amp;ab_channel=LePr%C3%A9cepteur" title="Le paradoxe de la tolérance par le Précepteur"&gt; le paradoxe de la tolérance. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il approfondit ensuite ses idées avec la théorie des trois mondes : le monde 1 physique, le monde 2 mental et le monde 3 objectif des idées et théories, interactifs et autonomes. Dans De nuages et d'horloges (1972), il explore le déterminisme contre l'indéterminisme quantique. Ses débats avec Adorno, Habermas ou Kuhn enrichissent la philosophie critique, tandis que son élève Soros applique ses principes à l'économie. Il reste un champion de la rationalité sans dogme. Malgré des critiques (comme son rejet excessif de l'historicisme ou son optimisme démocratique), l'héritage de Popper perdure en épistémologie, philosophie politique et méthodologie scientifique. Ses œuvres, traduites mondialement, inspirent des penseurs libéraux et scientifiques. En France, il influence les débats sur la science et la société, confirmant son rôle pivotal dans la pensée moderne. &lt;/p&gt; 
   &lt;audio controls title="Introduction à la philosophe de Karl Popper par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-22.03.2023-ITEMA_23325005-2013C3372E0766-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F54" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="10" t="s">
+      <c r="G54" s="9"/>
+      <c r="H54" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I54" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falsificationnisme ; Dualisme ; Individualisme méthodologique ; Réalisme scientifique</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
-        <v>1902</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders"  title=" Wikipedia"&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href="https://www.youtube.com/watch?v=r4eq7EoRtTQ"  title=" Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope"&gt;"l'obsolescence de l'homme"&lt;/a&gt;. Selon lui, l'homme moderne est   &lt;a href="https://books.openedition.org/pur/52513?lang=fr" title="La notion de « supraliminaire » chez Günther Anders par OpenEdition"&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression "prométhée honteux"  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href="https://www.youtube.com/watch?v=8xIiiYQJymQ"  title="L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée"&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href="https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde" title="l'être jetable Günther Anders par La vie des idées"&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;audio controls title="Avoir raison avec... Günther Anders par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"GÜNTHER ANDERS : L'obsolescence de l'homme" par Parole de Philosophe</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsificationnisme ; Dualisme ; Individualisme méthodologique ; Réalisme scientifique</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="245.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%BCnther_Anders"  title=" Wikipedia"&gt;Günther ANDERS&lt;/a&gt; était un  philosophe et journaliste  autrichien connu pour ses réflexions sur l'ère atomique, l'obsolescence de l'homme et l'aliénation causée par la société de consommation, la critique de la technique moderne et de la domination qu'elle exerce sur l'humanité. &lt;/p&gt; &lt;p&gt; Son concept le plus célèbre est   &lt;a href="https://www.youtube.com/watch?v=r4eq7EoRtTQ"  title=" Günther Anders et L'Obsolescence de l'homme | 1. Une critique de l'ère de la technique par Le Philoscope"&gt;"l'obsolescence de l'homme"&lt;/a&gt;. Selon lui, l'homme moderne est   &lt;a href="https://books.openedition.org/pur/52513?lang=fr" title="La notion de « supraliminaire » chez Günther Anders par OpenEdition"&gt; dépassé par les technologies&lt;/a&gt; qu'il a créées. Il est incapable de comprendre les conséquences de ses propres inventions, en particulier les technologies de destruction massive comme la bombe atomique.  Il utilise l'expression "prométhée honteux"  pour décrire l'homme qui, face à la perfection de la machine, ressent de la honte et de l'envie. La machine est parfaite, efficace, sans défaut, tandis que l'homme est imparfait et limité.&lt;/p&gt; &lt;p&gt; Il  critique vivement la   &lt;a href="https://www.youtube.com/watch?v=8xIiiYQJymQ"  title="L'OBSOLESCENCE DE L'HOMME / Günther Anders par Alain Bajomée"&gt;  société de consommation&lt;/a&gt; qui, selon lui, aliène l'individu. Les médias, en particulier la télévision, contribuent à cet état de fait en nous transformant en téléspectateurs passifs. Ils nous coupent de la réalité vécue et nous enferment dans un monde de représentations où l'émotion est préfabriquée et où l'action est remplacée par la simple consommation d'images. Pour lui  le monde moderne n'est plus un lieu de relations directes, mais une fantasmagorie, c'est-à-dire une illusion. Les événements lointains, comme les guerres, nous parviennent sous la forme de spectacles télévisés, ce qui anesthésie notre capacité d'empathie et de réaction. &lt;/p&gt; &lt;p&gt;  Ses analyses de la technologie, des médias et de l'aliénation de l'homme sont plus pertinentes que jamais à l'ère du numérique, d'internet et de l'intelligence artificielle. Il nous invite à une réflexion critique sur notre relation aux technologies et sur les dangers qu'elles représentent si nous ne parvenons pas à en maîtriser le développement. &lt;a href="https://laviedesidees.fr/Gunther-Anders-L-humain-etranger-au-monde" title="l'être jetable Günther Anders par La vie des idées"&gt; Son message&lt;/a&gt;  est un appel à la conscience et à la responsabilité, nous exhortant à ne pas abandonner notre humanité au profit de la machine. &lt;/p&gt; &lt;audio controls title="Avoir raison avec... Günther Anders par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-07.08.2023-ITEMA_23454836-2023C35448E0001-21.mp3" type="audio/mpeg" align="center"&gt;&lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"GÜNTHER ANDERS : L'obsolescence de l'homme" par Parole de Philosophe</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L54" s="2" t="s">
+      <c r="L55" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
         <v>1904</v>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B56" s="7" t="n">
         <v>1993</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fernand_van_Steenberghen"  title=" Wikipedia"&gt;Fernand van STEENBERGHEN&lt;/a&gt; (1904-1993) est un prêtre et philosophe belge, grand historien de la philosophie médiévale et représentant du néothomisme de Louvain. Né à Heverlee, il enseigne pendant toute sa carrière à l’Institut supérieur de philosophie de l’université catholique de Louvain, fondé par le cardinal Mercier pour renouveler la pensée de Thomas d’Aquin.&lt;/p&gt; &lt;p&gt;Historien, il consacre ses recherches au XIIIe siècle, l’âge d’or de la scolastique : &lt;em&gt;Siger de Brabant d’après ses œuvres inédites&lt;/em&gt; (1931-1942), &lt;em&gt;Aristote en Occident&lt;/em&gt; (1946) et &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_8011"  title=" In memory of Fernand van steenberghen  par Persée"&gt;des ouvrages&lt;/a&gt; comme &lt;em&gt;La Philosophie au XIIIe siècle&lt;/em&gt; (1966). Il y montre comment l’entrée massive des œuvres d’Aristote bouleverse les universités, et conteste l’expression d’« averroïsme latin » : Siger et ses collègues de la faculté des arts pratiquaient plutôt un « aristotélisme hétérodoxe ». Contre Étienne Gilson, il refuse aussi de voir en Bonaventure le chef d’un « augustinisme » opposé à Thomas : sa philosophie est, selon lui, un aristotélisme teinté de néoplatonisme.&lt;/p&gt; &lt;p&gt;Philosophe, il défend une métaphysique réaliste et la possibilité de démontrer l’existence de Dieu par la raison, contre l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;agnosticisme&lt;/a&gt; hérité de Kant. Dans &lt;em&gt;Dieu caché&lt;/em&gt; (1961), puis dans &lt;em&gt;Le Problème de l’existence de Dieu dans les écrits de saint Thomas d’Aquin&lt;/em&gt; (1980), il examine les preuves classiques avec rigueur, jugeant même certaines des « cinq voies » de Thomas insuffisantes, et propose sa propre démonstration à partir de la finitude des êtres.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="10" t="s">
+      <c r="F56" s="7"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="10" t="s">
         <v>470</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Frithjof_Schuon"  title=" Wikipedia"&gt;Frithjof SCHUON&lt;/a&gt;  était un philosophe et maître spirituel suisse, figure centrale de l'école traditionaliste ou &lt;a href="https://www.youtube.com/watch?v=VGiKDhwdrcA&amp;list=PL190FE1CAB151FD5E"  title="Frithjof Schuon: Messenger of the Perennialist Philosophy Trailer par WorldWisdominc"&gt; pérennialiste &lt;/a&gt; aux côtés de René Guénon, Ananda Coomaraswamy et Titus Burckhardt. Initié au soufisme, il voyage en Afrique du Nord, fonde la tariqa Maryamiyya (branche soufie), et s'installe aux États-Unis en 1980 où il vit jusqu'à sa mort. Né à Bâle, il reçoit en 1932, à Mostaganem, en Algérie, l’initiation du maître soufi Ahmad al-Alawi, et vit longtemps à Lausanne. Son livre majeur, &lt;em&gt;De l’unité transcendante des religions&lt;/em&gt; (1948), a été salué par T. S. Eliot. &lt;/p&gt; &lt;p&gt; Il défend la "philosophia perennis", affirmant l'existence d'un Principe absolu (Dieu) d'où émane l'univers, et une Vérité unique sous-jacente à toutes les religions malgré leurs formes exotériques différentes. Les révélations divines (christianisme,&lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1963_num_164_2_7952"  title="Frithjof Schuon. Comprendre l'Islam par Persée"&gt; islam, &lt;/a&gt;  hindouisme, etc.) ne sont que des langages adaptés exprimant la même essence ésotérique primordiale. L'homme accède à une connaissance supra-rationnelle (gnose, intellect divin) par delà la raison discursive, via la métaphysique intégrale inspirée de Platon, Shankara ou Ibn Arabī. &lt;/p&gt; &lt;p&gt; Il dénonce la modernité comme un "âge sombre" marqué par le rationalisme, le matérialisme, l'individualisme, le progressisme et le relativisme. Il distingue ésotérisme (noyau universel, initiation intérieure) et exotérisme (formes religieuses orthodoxes), recommandant une pratique fidèle à une tradition choisie. Il  n'est pas un philosophe spéculatif au sens classique, mais un métaphysicien voyant dans la Tradition le remède au nihilisme contemporain. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>481</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>471</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>130</v>
+        <v>472</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>210</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5505,47 +5525,67 @@
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
-        <v>1907</v>
-      </c>
-      <c r="B57" s="7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="M57" s="22" t="s">
-        <v>491</v>
+    <row r="57" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1">
+        <v>1904</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1991</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1904 - 1991</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">María ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/María_Zambrano" title=" Wikipedia"&gt;María ZAMBRANO&lt;/a&gt;&amp;nbsp;était une philosophe et essayiste espagnole, disciple de José Ortega y Gasset. Engagée du côté de la République pendant la guerre civile, elle dut s'exiler en 1939 et vécut près de quarante-cinq ans loin de son pays, au Mexique, à Cuba, à Porto Rico, en Italie, en France et en Suisse, avant de revenir en Espagne en 1984.&lt;/p&gt; &lt;p&gt;Sa pensée s'éloigne de celle de son maître. Elle &lt;a href="https://www.youtube.com/watch?v=twWnh_P4OWc" title="Maria ZAMBRANO – Une Vie, une Œuvre : 1904-1991 (France Culture, 1992) par ÉCLAIR BRUT"&gt;reproche à la philosophie&lt;/a&gt; occidentale d'avoir séparé la raison de la vie, de l'émotion et du sacré. Elle propose une « raison poétique », une manière de penser qui ne cherche pas à dominer la réalité par des concepts, mais à l'accueillir, à l'écouter et à la laisser apparaître, comme le fait la poésie.&lt;/p&gt; &lt;p&gt;L'exil occupe une place centrale dans sa pensée : loin d'être seulement une perte, il devient pour elle une condition philosophique, une manière de vivre dépouillée qui ouvre à une vérité plus profonde. Elle voyait dans la figure d'Antigone, à laquelle elle consacra une pièce, &lt;em&gt;La Tombe d'Antigone&lt;/em&gt;, le symbole de toutes les victimes de l'histoire et de la conscience qui refuse l'injustice.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.senscritique.com/contact/Maria_Zambrano/189988/collection" title="ses livres par sans critique"&gt;Dans des livres comme&lt;/a&gt; &lt;em&gt;Philosophie et poésie&lt;/em&gt; (1939), &lt;em&gt;L'Homme et le divin&lt;/em&gt; (1955) ou &lt;em&gt;Les Clairières du bois&lt;/em&gt; (1977), elle explore le rêve, la mémoire, l'exil et le sacré, dans un style qui mêle philosophie et littérature. Longtemps méconnue, elle reçut en 1988 le prix Cervantès, la plus haute distinction littéraire du monde hispanique, et elle est aujourd'hui considérée comme l'une des grandes voix de la pensée espagnole du XXe siècle.&lt;/p&gt;  &lt;audio controls title="Avoir raison avec ... Maria Zambrano par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/17362-28.07.2025-ITEMA_24205833-2025C35448E0001-ITE_00148591_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRaPzFTjzX4</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"María Zambrano : philosophe de la raison poétique" par France Culture</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mariazambrano-mini.webp</t>
+        </is>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espagnole</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existentialisme</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe espagnole, disciple d'Ortega y Gasset, penseuse de la « raison poétique ».</t>
+        </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5554,43 +5594,47 @@
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
         <v>1907</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>494</v>
+        <v>477</v>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Frithjof_Schuon"  title=" Wikipedia"&gt;Frithjof SCHUON&lt;/a&gt;  était un philosophe et maître spirituel suisse, figure centrale de l'école traditionaliste ou &lt;a href="https://www.youtube.com/watch?v=VGiKDhwdrcA&amp;list=PL190FE1CAB151FD5E"  title="Frithjof Schuon: Messenger of the Perennialist Philosophy Trailer par WorldWisdominc"&gt; pérennialiste &lt;/a&gt; aux côtés de René Guénon, Ananda Coomaraswamy et Titus Burckhardt. Initié au soufisme, il voyage en Afrique du Nord, fonde la tariqa Maryamiyya (branche soufie), et s'installe aux États-Unis en 1980 où il vit jusqu'à sa mort. Né à Bâle, il reçoit en 1932, à Mostaganem, en Algérie, l’initiation du maître soufi Ahmad al-Alawi, et vit longtemps à Lausanne. Son livre majeur, &lt;em&gt;De l’unité transcendante des religions&lt;/em&gt; (1948), a été salué par T. S. Eliot. &lt;/p&gt; &lt;p&gt; Il défend la "philosophia perennis", affirmant l'existence d'un Principe absolu (Dieu) d'où émane l'univers, et une Vérité unique sous-jacente à toutes les religions malgré leurs formes exotériques différentes. Les révélations divines (christianisme,&lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1963_num_164_2_7952"  title="Frithjof Schuon. Comprendre l'Islam par Persée"&gt; islam, &lt;/a&gt;  hindouisme, etc.) ne sont que des langages adaptés exprimant la même essence ésotérique primordiale. L'homme accède à une connaissance supra-rationnelle (gnose, intellect divin) par delà la raison discursive, via la métaphysique intégrale inspirée de Platon, Shankara ou Ibn Arabī. &lt;/p&gt; &lt;p&gt; Il dénonce la modernité comme un "âge sombre" marqué par le rationalisme, le matérialisme, l'individualisme, le progressisme et le relativisme. Il distingue ésotérisme (noyau universel, initiation intérieure) et exotérisme (formes religieuses orthodoxes), recommandant une pratique fidèle à une tradition choisie. Il  n'est pas un philosophe spéculatif au sens classique, mais un métaphysicien voyant dans la Tradition le remède au nihilisme contemporain. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F58" s="7" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="I58" s="9"/>
+        <v>481</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>471</v>
+      </c>
       <c r="J58" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>63</v>
+        <v>210</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5598,46 +5642,48 @@
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>499</v>
+        <v>1907</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>1992</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Titus_Burckhardt"  title=" Wikipedia"&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)" title=" Le Pérennialisme par Wikipedia"&gt;pérennialisme&lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href="https://www.youtube.com/watch?v=Thok9so1Zik" title=" Introdustion aux doctrines ésothériques de l’Islam par Red Draco"&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href="https://www.youtube.com/watch?v=Mx6E82Mt-v4" title=" Etre conservateur par Agar Hagar"&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; 
-</t>
-        </is>
+        <v>485</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>486</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>489</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
-        <v>130</v>
+        <v>374</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>506</v>
+        <v>490</v>
+      </c>
+      <c r="M59" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5645,51 +5691,43 @@
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="238.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isaiah_Berlin" title=" Wikipedia"&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href="https://www.youtube.com/watch?v=zSCS0toL5wc" title="Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français"&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M"  title="Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français"&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M" title=" Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français"&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant "décence humaine" face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : "Karl Marx: His Life and Environment" paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. "The Hedgehog and the Fox" paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. "Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; 
-</t>
-        </is>
+        <v>493</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>494</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>513</v>
+        <v>496</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>497</v>
       </c>
       <c r="I60" s="9"/>
       <c r="J60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;russe</t>
-        </is>
+        <v>498</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5697,45 +5735,46 @@
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="234" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B61" s="7" t="n">
-        <v>2004</v>
+        <v>1908</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>499</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eugenio_Garin" title=" Wikipedia"&gt;Eugenio GARIN&lt;/a&gt; (1909-2004) est un historien italien de la philosophie, l’un des grands spécialistes de la Renaissance et de l’humanisme italien. Né à Rieti, il étudie à Florence, enseigne d’abord au lycée, puis à l’université de Florence à partir de 1949, et enfin à l’École normale supérieure de Pise. Ses livres, comme &lt;em&gt;L’Humanisme italien&lt;/em&gt; (1947), &lt;em&gt;Moyen Âge et Renaissance&lt;/em&gt; (1954) ou &lt;em&gt;La Culture philosophique de la Renaissance italienne&lt;/em&gt; (1961), ont renouvelé l’étude de cette période.&lt;/p&gt; &lt;p&gt;Pour Garin, l’humanisme n’est pas un simple goût des lettres antiques, comme le pensait Paul Oskar Kristeller, mais une véritable philosophie : en retrouvant les textes anciens par la philologie, les humanistes découvrent l’histoire, et l’homme comme un être qui se façonne lui-même dans la cité. Il refuse l’idée d’une vérité philosophique intemporelle, et lit les œuvres dans leur contexte, attentif aux rapports entre la pensée, la culture, la politique et les institutions. Il montre aussi la place de la magie, de l’astrologie et de l’hermétisme dans la pensée de la Renaissance.&lt;/p&gt; &lt;p&gt;Sans être un théoricien de l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;agnosticisme&lt;/a&gt;, il en partage la prudence : ses travaux décrivent une Renaissance traversée de tensions entre savoir, foi et scepticisme, et il préfère comprendre comment les hommes pensent à une époque donnée plutôt que trancher les grandes questions métaphysiques. Il a aussi écrit l’histoire de la philosophie italienne du XXe siècle, de Croce et Gentile à Gramsci.&lt;/p&gt;</t>
+        <v>501</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Titus_Burckhardt"  title=" Wikipedia"&gt;Titus BURCKHARDT&lt;/a&gt;  était un philosophe et métaphysicien suisse-allemand, figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9rennialisme_(spiritualit%C3%A9)" title=" Le Pérennialisme par Wikipedia"&gt;pérennialisme&lt;/a&gt;, naît à Florence dans une famille cultivée – son père est l’historien d’art Carl Burckhardt. Dès l’adolescence, il s’intéresse aux sagesses orientales et à l’art sacré, étudiant l’arabe et voyageant en Afrique du Nord. Installé à Fès dès 1936, il se convertit à l’islam sous la guidance du maître soufi et y réside de longues années, s’immergeant dans la tradition shadhiliyya. &lt;/p&gt; &lt;p&gt; Il  incarne l’école traditionaliste aux côtés de Guénon et Schuon, défendant une « philosophie pérenne » : une sagesse primordiale unique se manifestant dans toutes les traditions révélées, contre la modernité profane et matérialiste. Ses écrits, comme &lt;a href="https://www.youtube.com/watch?v=Thok9so1Zik" title=" Introdustion aux doctrines ésothériques de l’Islam par Red Draco"&gt; Introduction aux doctrines ésotériques de l’islam &lt;/a&gt;  (1959) ou De l’unité transcendante des religions (1953), explorent le soufisme comme voie ésotérique de connaissance divine, reliant beauté, vérité et sacré. &lt;/p&gt; &lt;p&gt; Spécialiste des arts islamiques, il publie Sacred Art in East and West (1967) et Art of Islam: Language and Meaning (1976), voyant dans l’architecture, la calligraphie et les &lt;a href="https://www.youtube.com/watch?v=Mx6E82Mt-v4" title=" Etre conservateur par Agar Hagar"&gt;motifs géométriques &lt;/a&gt;  des symboles de la réalité divine. Directeur artistique chez Urs Graf Verlag, il édite des fac-similés de manuscrits celtiques illuminés et préside la mission UNESCO pour la sauvegarde de la médina de Fès (1975-1978), fusionnant érudition et engagement spirituel.  &lt;/p&gt; &lt;p&gt; Son héritage, clair et profond, influence les études sur le soufisme, l’art sacré et le traditionalisme. Mort à Lausanne, Burckhardt reste un passeur entre Orient et Occident, promouvant l’universalité du message spirituel au-delà des formes religieuses. &lt;/p&gt; 
+</t>
         </is>
       </c>
       <c r="F61" s="7" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>521</v>
+        <v>504</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>505</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>522</v>
+        <v>482</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5743,222 +5782,224 @@
         </is>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
         <v>1909</v>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isaiah_Berlin" title=" Wikipedia"&gt;Isaiah BERLIN&lt;/a&gt;  était un philosophe russo-britanique considéré comme l'un des grands défenseurs du  &lt;a href="https://www.youtube.com/watch?v=zSCS0toL5wc" title="Isaiah Berlin : Le pouvoir du pluralisme des valeurs, déverrouiller votre potentiel par Philosopheasy en français"&gt;libéralisme pluraliste &lt;/a&gt; au XXe siècle, marqué par son expérience des totalitarismes et sa maîtrise exceptionnelle de la conversation intellectuelle. Pendant la Seconde Guerre mondiale, initialement écarté pour ses origines lettones, il sert comme diplomate à New York puis à Moscou (1945-1946), où il rencontre des dissidents et renforce son anticommunisme, rapportant des analyses prophétiques sur le stalinisme. &lt;/p&gt; &lt;p&gt; Il  rejette tout monisme téléologique (hégélien, marxiste, utilitariste) au profit d'un pluralisme tragique : &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M"  title="Isaiah Berlin, les 2 concepts de liberté par Sprouts en Français"&gt;valeurs humaines &lt;/a&gt; objectives mais souvent mutuellement exclusives, rendant la vie un compromis sans utopie finale. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=s-SVrbkJE5M" title=" Les deux concepts de liberté selon Isaiah Berlin par Sprouts en Français"&gt;Liberté négative &lt;/a&gt; comme cœur du libéralisme : espace protégé contre autrui ou État, contre utopies rationalistes écrasant la diversité humaine ; influencé par Machiavel et son rejet des totalitarismes. Historien des idées, il voit la pensée comme constellation culturelle, critiquant déterminisme  et prônant "décence humaine" face à idéologies absolues. &lt;/p&gt; &lt;p&gt; Ses oeuvres maitresses sont : "Karl Marx: His Life and Environment" paru en 1939 : biographie intellectuelle objective, critiquant le marxisme comme monisme historiciste. "The Hedgehog and the Fox" paru en 1953 : essai sur Tolstoï, opposant hérissons (vision unifiante : Platon, Hegel) et renards (pluralistes : Aristote, Shakespeare), appliqué à l'histoire comme chaos de perspectives. "Two Concepts of Liberty paru en 1958 : distinction fondatrice entre liberté négative (absence d'interférence, hobbesienne) et positive (autonomie, rousseauiste), avertissant que la seconde peut dégénérer en tyrannie si imposée. &lt;/p&gt; &lt;p&gt; Père de l'histoire intellectuelle analytique, il inspire Rawls, Arendt, Popper, et en France débats sur multiculturalisme (Sternhell le lie aux anti-Lumières). Critiqué pour relativisme présumé, son optimisme libéral perdure contre populismes. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="I62" s="9"/>
+      <c r="J62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;russe</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="136.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eugenio_Garin" title=" Wikipedia"&gt;Eugenio GARIN&lt;/a&gt; (1909-2004) est un historien italien de la philosophie, l’un des grands spécialistes de la Renaissance et de l’humanisme italien. Né à Rieti, il étudie à Florence, enseigne d’abord au lycée, puis à l’université de Florence à partir de 1949, et enfin à l’École normale supérieure de Pise. Ses livres, comme &lt;em&gt;L’Humanisme italien&lt;/em&gt; (1947), &lt;em&gt;Moyen Âge et Renaissance&lt;/em&gt; (1954) ou &lt;em&gt;La Culture philosophique de la Renaissance italienne&lt;/em&gt; (1961), ont renouvelé l’étude de cette période.&lt;/p&gt; &lt;p&gt;Pour Garin, l’humanisme n’est pas un simple goût des lettres antiques, comme le pensait Paul Oskar Kristeller, mais une véritable philosophie : en retrouvant les textes anciens par la philologie, les humanistes découvrent l’histoire, et l’homme comme un être qui se façonne lui-même dans la cité. Il refuse l’idée d’une vérité philosophique intemporelle, et lit les œuvres dans leur contexte, attentif aux rapports entre la pensée, la culture, la politique et les institutions. Il montre aussi la place de la magie, de l’astrologie et de l’hermétisme dans la pensée de la Renaissance.&lt;/p&gt; &lt;p&gt;Sans être un théoricien de l’&lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;agnosticisme&lt;/a&gt;, il en partage la prudence : ses travaux décrivent une Renaissance traversée de tensions entre savoir, foi et scepticisme, et il préfère comprendre comment les hommes pensent à une époque donnée plutôt que trancher les grandes questions métaphysiques. Il a aussi écrit l’histoire de la philosophie italienne du XXe siècle, de Croce et Gentile à Gramsci.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B64" s="7" t="n">
         <v>1996</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C64" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D64" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E64" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Jos%C3%A9_Luis_L%C3%B3pez_Aranguren" title=" Wikipedia"&gt;José Luis Lopez ARANGUREN&lt;/a&gt;   philosophe et essayiste espagnol influent, intègre l'agnosticisme dans une réflexion éthique et religieuse évolutive, passant d'un catholicisme initial à une "perplexité" ouverte sur le doute. Né à Ávila, formé par Ortega y Gasset et Zubiri, il occupe la chaire d'éthique à l'Université Complutense de Madrid dès 1955. Catholique critique, il explore dans Catholicisme et protestantisme comme formes d'existence  les tensions entre foi et morale, influençant des disciples comme Muguerza. &lt;/p&gt; &lt;p&gt; Sans lien avec les origines historiques de  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il développe une "éthique de la perplexité" : refus des certitudes dogmatiques au profit d'une raison ouverte, dialoguant avec le protestantisme (Karl Barth) et la critique sociale. Exclu de l'université en 1965 pour contestation antifranquiste, il enseigne à Berkeley, nouant amitié avec Marcuse, et approfondit une pensée humaniste contre la technocratie. &lt;a href="https://www.youtube.com/watch?v=L3sJ7AvOT08"  title=" José Luis Aranguren  par Lecturas Fragmentadas"&gt;Ses œuvres &lt;/a&gt; comme Ética (1958) et Propuestas morales (1985) lient morale, religion et politique sans absolutisme. &lt;/p&gt; &lt;p&gt; Sa position religieuse oscille : catholique "progressiste" puis laïc engagé, il valorise la dissidence intellectuelle et une "justice sociale" cosmopolite, écho à l'agnosticisme par son rejet des systèmes fermés. Penseur de la transition démocratique espagnole, il reçoit le Prix national d'essai (1989) et le Prince des Asturies (1995), léguant une philosophie de la solidarité humaniste. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F64" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G64" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="H62" s="10" t="s">
+      <c r="H64" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="2" t="s">
+      <c r="I64" s="9"/>
+      <c r="J64" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K64" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L64" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M64" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="351" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="351" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="n">
         <v>1910</v>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B65" s="7" t="n">
         <v>1989</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C65" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D65" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E65" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F65" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G65" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H65" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="2" t="s">
+      <c r="I65" s="9"/>
+      <c r="J65" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Positivisme Logique ; Analytique ; Phénoménisme</t>
         </is>
       </c>
-      <c r="M63" s="14" t="s">
+      <c r="M65" s="14" t="s">
         <v>539</v>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="306" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="306" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="n">
         <v>1911</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D66" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Langshaw_Austin" title=" Wikipedia"&gt;John LANGSHAW AUSTIN&lt;/a&gt;  était un philosophe britanique de la philosophie analytique, né à Lancaster. Issu d'une famille modeste, il étudie les lettres classiques et la philosophie à Oxford, où il excelle et devient fellow en 1933. Pendant la Seconde Guerre mondiale, il sert dans les services de renseignement britanniques, jouant un rôle clé dans la préparation du Débarquement de Normandie grâce à son analyse précise de renseignements topographiques, avant de reprendre sa carrière académique à Oxford comme professeur de philosophie morale. &lt;/p&gt; &lt;p&gt; Il est le représentant emblématique de la « philosophie du langage ordinaire », une approche qu'il qualifie lui-même de &lt;a href="https://www.persee.fr/doc/igram_0222-9838_2010_num_124_1_4073"  title="Place et raison de l’analyse phénoménologique en linguistique par Persée"&gt;« phénoménologie linguistique ».&lt;/a&gt;  Il critique les théories abstraites des philosophes en analysant les usages quotidiens des mots, montrant leur subtilité et leur capacité à marquer des distinctions fines que les systèmes formels ignorent. Son travail sur la perception défend un réalisme direct contre les doctrines des  &lt;a href="https://www.youtube.com/watch?v=JhzzLyLCRis"  title="Les performatifs ces mots qui nous changent par Survivre aux sciences humaines"&gt;« sense-data », &lt;/a&gt; en s'appuyant sur le sens commun linguistique. &lt;/p&gt; &lt;p&gt; Sa contribution la plus célèbre est la théorie des actes de langage, développée dans ses conférences de Harvard publiées posthumement sous le titre How to Do Things with Words (en français Quand dire, c'est faire). Il distingue les énoncés performatifs, qui accomplissent une action (comme « Je vous déclare mari et femme »), des énoncés constatifs descriptifs, avant de montrer que tout discours est performatif : locutoire (dire quelque chose), illocutoire (intention) et perlocutoire (effet). Cette idée fonde la pragmatique moderne et influence Searle ou la philosophie du droit. &lt;/p&gt; &lt;p&gt; L'héritage d'Austin perdure dans le  &lt;a href="https://www.erudit.org/fr/revues/philoso/2006-v33-n1-philoso1132/012957ar/"  title="Le contexte sémantique par Survivre aux Eridit"&gt;contextualisme sémantique, &lt;/a&gt; où la vérité d'une affirmation dépend du contexte d'énonciation, et dans l'ordinaireisme via Stanley Cavell. Mort prématurément d'un cancer à 48 ans, son œuvre concise mais profonde révolutionne la compréhension du langage comme action sociale, reliant philosophie, linguistique et sciences cognitives. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F66" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G66" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="H64" s="10" t="s">
+      <c r="H66" s="10" t="s">
         <v>546</v>
-      </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
-        <v>1911</v>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emil_Cioran" title=" Wikipedia"&gt;Emil CIORAN&lt;/a&gt;    était un  philosophe roumain d'expression française, incarne un agnosticisme viscéral teinté de scepticisme radical, loin des certitudes religieuses ou métaphysiques. Élevé dans une famille orthodoxe en Transylvanie, il rompt tôt avec la foi pour explorer le doute existentiel dans des œuvres comme Au cœur des ténèbres ou Précis de décomposition. Sa position religieuse est qualifiée de "quête agnostique" : ni athéisme militant ni théisme, mais une suspension perpétuelle du jugement face à un Dieu absent ou silencieux. &lt;/p&gt; &lt;p&gt;  Contrairement aux origines classiques de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il en fait une expérience intime de la "déchirure d'exister", où le doute devient négation corrosive de toute vérité absolue. Influencé par le scepticisme antique et Nietzsche, il radicalise le doute en "exaspération de la conscience", menant à une lucidité thanatique – conscience aiguë de la vanité humaine et du néant. Écrire devient pour lui un acte de démolition des systèmes, refusant toute synthèse dogmatique.&lt;/p&gt; &lt;p&gt;    Il  flirte avec des accents gnostiques ou dualistes dans Le Mauvais Démiurge, accusant un créateur défaillant d'un monde absurde, tout en niant toute transcendance accessible. Son agnosticisme poétique, "solaire" et fiévreux, naît d'une &lt;a href="https://www.youtube.com/watch?v=1mT-aprSfv0"  title="CIORAN: le génie qui a détruit l’illusion du bonheurt par Voyages endormis"&gt;désillusion lucide &lt;/a&gt; plutôt que d'une raison froide : il vit l'incertitude comme un &lt;a href="https://www.youtube.com/watch?v=8mDwa3swkW0"  title="Vivre c’est mourir doucement par Le Dolmen"&gt;"épuisement du discours", &lt;/a&gt;  privilégiant l'authenticité du désespoir à la quête de réponses. &lt;/p&gt; &lt;p&gt;    Son legs philosophique résonne avec l'agnosticisme moderne par ce refus des absolus, influençant penseurs comme Muguerza dans une "perplexité" partagée. À Paris depuis 1947, il incarne le sceptique cosmopolite, torturé par l'insoluble, qui préfère le vertige du non-savoir à l'illusion de la connaissance. &lt;/p&gt;         &lt;audio controls title="Emil Cioran, un philosophe-hurleur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24200-05.08.2023-ITEMA_23453909-2023C51135E0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pessimisme ; Existentialisme ; Absurde</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Grice" title=" Wikipedia"&gt;Paul GRICE&lt;/a&gt;  était un philosophe britanique de l'école analytique, est né à Birmingham et a étudié à Oxford, où il a été influencé par des figures comme Gilbert Ryle et J.L. Austin, dont il fut un collaborateur proche au sein du "samedi matin" oxonien. Il a enseigné à Oxford avant de rejoindre les États-Unis, notamment Berkeley, où il a terminé sa carrière. Spécialiste de philosophie du langage et de l'esprit, il a révolutionné la pragmatique en distinguant le sens littéral du sens impliqué dans les échanges. &lt;/p&gt; &lt;p&gt; Il  est surtout célèbre pour son &lt;a href="https://www.youtube.com/watch?v=xt4zFGdTUow"  title=" Paul Grice, cooperative principe  par Evan Ashworthe"&gt;"principe de coopération" &lt;/a&gt; et ses quatre &lt;a href="https://www.youtube.com/watch?v=WGKzjVQZAgw"  title=" Paul Grice, les maximes  par Steve Aswald"&gt; maximes conversationnelles, &lt;/a&gt; exposées dans sa conférence &lt;a href="https://www.persee.fr/doc/comm_0588-8018_1979_num_30_1_1446"  title=" Logique et conversation  par Persée"&gt;"Logic and Conversation" &lt;/a&gt; (1967). Ces maximes – quantité (fournir ni trop ni trop peu d'informations), qualité (dire la vérité et avoir des preuves), relation (être pertinent) et manière (être clair, éviter l'ambiguïté, être bref et ordonné) – sous-tendent toute communication efficace. Elles expliquent comment les interlocuteurs infèrent des significations au-delà des mots explicites. &lt;/p&gt; &lt;p&gt; Son concept clé d'"implicature conversationnelle" montre que les violations apparentes des maximes (par exemple, être vague pour suggérer quelque chose) génèrent des sens implicites attendus par les participants rationnels. Complétant la théorie des actes de langage d'Austin (locutoire, illocutoire, perlocutoire), il met l'accent sur l'intention du locuteur et la reconnaissance mutuelle des intentions, fondant ainsi une approche inférentielle de la communication. &lt;/p&gt; &lt;p&gt; L'héritage de Grice imprègne la linguistique, la psychologie cognitive et l'IA, influençant des penseurs comme Sperber et Wilson ou la philosophie contemporaine du témoignage et de  &lt;a href="https://www.youtube.com/watch?v=FVSfFGcVP7U"  title=" Paul Grice, aspect of reason  par Philosophie Analytique"&gt;la rationalité. &lt;/a&gt; Ses idées sur la signification non naturelle et la distinction sens/force restent des outils analytiques majeurs pour décoder ironie, sarcasme ou sous-entendus. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>563</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="2" t="s">
@@ -5971,7 +6012,7 @@
         <v>73</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5979,43 +6020,48 @@
         </is>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="255" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
-        <v>1914</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>565</v>
+        <v>1911</v>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>1995</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>568</v>
+        <v>550</v>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emil_Cioran" title=" Wikipedia"&gt;Emil CIORAN&lt;/a&gt;    était un  philosophe roumain d'expression française, incarne un agnosticisme viscéral teinté de scepticisme radical, loin des certitudes religieuses ou métaphysiques. Élevé dans une famille orthodoxe en Transylvanie, il rompt tôt avec la foi pour explorer le doute existentiel dans des œuvres comme Au cœur des ténèbres ou Précis de décomposition. Sa position religieuse est qualifiée de "quête agnostique" : ni athéisme militant ni théisme, mais une suspension perpétuelle du jugement face à un Dieu absent ou silencieux. &lt;/p&gt; &lt;p&gt;  Contrairement aux origines classiques de &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme&lt;/a&gt;, il en fait une expérience intime de la "déchirure d'exister", où le doute devient négation corrosive de toute vérité absolue. Influencé par le scepticisme antique et Nietzsche, il radicalise le doute en "exaspération de la conscience", menant à une lucidité thanatique – conscience aiguë de la vanité humaine et du néant. Écrire devient pour lui un acte de démolition des systèmes, refusant toute synthèse dogmatique.&lt;/p&gt; &lt;p&gt;    Il  flirte avec des accents gnostiques ou dualistes dans Le Mauvais Démiurge, accusant un créateur défaillant d'un monde absurde, tout en niant toute transcendance accessible. Son agnosticisme poétique, "solaire" et fiévreux, naît d'une &lt;a href="https://www.youtube.com/watch?v=1mT-aprSfv0"  title="CIORAN: le génie qui a détruit l’illusion du bonheurt par Voyages endormis"&gt;désillusion lucide &lt;/a&gt; plutôt que d'une raison froide : il vit l'incertitude comme un &lt;a href="https://www.youtube.com/watch?v=8mDwa3swkW0"  title="Vivre c’est mourir doucement par Le Dolmen"&gt;"épuisement du discours", &lt;/a&gt;  privilégiant l'authenticité du désespoir à la quête de réponses. &lt;/p&gt; &lt;p&gt;    Son legs philosophique résonne avec l'agnosticisme moderne par ce refus des absolus, influençant penseurs comme Muguerza dans une "perplexité" partagée. À Paris depuis 1947, il incarne le sceptique cosmopolite, torturé par l'insoluble, qui préfère le vertige du non-savoir à l'illusion de la connaissance. &lt;/p&gt;         &lt;audio controls title="Emil Cioran, un philosophe-hurleur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24200-05.08.2023-ITEMA_23453909-2023C51135E0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F67" s="7" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>571</v>
+        <v>553</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>554</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="2" t="s">
-        <v>572</v>
+        <v>409</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>73</v>
+        <v>121</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pessimisme ; Existentialisme ; Absurde</t>
+        </is>
       </c>
       <c r="M67" s="2" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6023,49 +6069,46 @@
         </is>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>1919</v>
-      </c>
-      <c r="B68" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le consequentialisme par Noé Jacomet</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>579</v>
-      </c>
+    <row r="68" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Grice" title=" Wikipedia"&gt;Paul GRICE&lt;/a&gt;  était un philosophe britanique de l'école analytique, est né à Birmingham et a étudié à Oxford, où il a été influencé par des figures comme Gilbert Ryle et J.L. Austin, dont il fut un collaborateur proche au sein du "samedi matin" oxonien. Il a enseigné à Oxford avant de rejoindre les États-Unis, notamment Berkeley, où il a terminé sa carrière. Spécialiste de philosophie du langage et de l'esprit, il a révolutionné la pragmatique en distinguant le sens littéral du sens impliqué dans les échanges. &lt;/p&gt; &lt;p&gt; Il  est surtout célèbre pour son &lt;a href="https://www.youtube.com/watch?v=xt4zFGdTUow"  title=" Paul Grice, cooperative principe  par Evan Ashworthe"&gt;"principe de coopération" &lt;/a&gt; et ses quatre &lt;a href="https://www.youtube.com/watch?v=WGKzjVQZAgw"  title=" Paul Grice, les maximes  par Steve Aswald"&gt; maximes conversationnelles, &lt;/a&gt; exposées dans sa conférence &lt;a href="https://www.persee.fr/doc/comm_0588-8018_1979_num_30_1_1446"  title=" Logique et conversation  par Persée"&gt;"Logic and Conversation" &lt;/a&gt; (1967). Ces maximes – quantité (fournir ni trop ni trop peu d'informations), qualité (dire la vérité et avoir des preuves), relation (être pertinent) et manière (être clair, éviter l'ambiguïté, être bref et ordonné) – sous-tendent toute communication efficace. Elles expliquent comment les interlocuteurs infèrent des significations au-delà des mots explicites. &lt;/p&gt; &lt;p&gt; Son concept clé d'"implicature conversationnelle" montre que les violations apparentes des maximes (par exemple, être vague pour suggérer quelque chose) génèrent des sens implicites attendus par les participants rationnels. Complétant la théorie des actes de langage d'Austin (locutoire, illocutoire, perlocutoire), il met l'accent sur l'intention du locuteur et la reconnaissance mutuelle des intentions, fondant ainsi une approche inférentielle de la communication. &lt;/p&gt; &lt;p&gt; L'héritage de Grice imprègne la linguistique, la psychologie cognitive et l'IA, influençant des penseurs comme Sperber et Wilson ou la philosophie contemporaine du témoignage et de  &lt;a href="https://www.youtube.com/watch?v=FVSfFGcVP7U"  title=" Paul Grice, aspect of reason  par Philosophie Analytique"&gt;la rationalité. &lt;/a&gt; Ses idées sur la signification non naturelle et la distinction sens/force restent des outils analytiques majeurs pour décoder ironie, sarcasme ou sous-entendus. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="I68" s="9"/>
       <c r="J68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>167</v>
+        <v>547</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>580</v>
+        <v>73</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+        <v>564</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6073,462 +6116,469 @@
         </is>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="179.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
-        <v>1922</v>
+        <v>1914</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>583</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>584</v>
+        <v>567</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>568</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="n">
+        <v>1919</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le consequentialisme par Noé Jacomet</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="I71" s="9"/>
+      <c r="J71" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="K71" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="L69" s="2" t="s">
+      <c r="L71" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="n">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="n">
         <v>1922</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B72" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C72" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D72" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Stephen_Toulmin"  title=" Wikipedia"&gt;Stephen TOULMIN&lt;/a&gt;  était un philosophe britanique  influencé par Wittgenstein, est un penseur majeur de la philosophie des sciences et de l'argumentation pratique. Né en Angleterre, il étudie à Cambridge, enseigne à Oxford, Leeds, puis aux États-Unis (notamment à Northwestern et USC). Critique du formalisme logique absolu, il prône une approche contextualisée des raisonnements, applicable au droit, à la médecine ou à la diplomatie, loin des abstractions syllogistiques. &lt;/p&gt; &lt;p&gt; Son œuvre fondatrice, The Uses of Argument (1958), introduit le  &lt;a href="https://www.youtube.com/watch?v=J1WDW2F-KBs"  title=" le modèle de Toulmin  par Mooc Cyu"&gt;modèle d'argumentation de Toulmin &lt;/a&gt;  : une structure à six composantes pour analyser les débats réels. La claim (thèse), les grounds (données), le warrant (justification liant données et thèse), le backing (soutien du warrant), les qualifiers (modalisateurs comme "probablement"), et les rebuttals (contre-arguments). Ce schéma met en lumière les aspects "field-dependent" (dépendants du domaine) versus invariants, rendant l'argumentation plus réaliste et dialogique. &lt;/p&gt; &lt;p&gt; Dans Human Understanding (1972), il propose un modèle évolutionniste du changement conceptuel en philosophie des sciences, opposé au paradigmatisme révolutionnaire de Kuhn. Les idées évoluent par innovation et sélection darwinienne, dans un "champ stable" partagé, évitant relativisme et absolutisme. Il défend une  &lt;a href="https://www.youtube.com/watch?v=hv7BUYzRiiU"  title=" le cartesian theatre de Toulmin  par Edwin gardner"&gt;"pluralistic conceptual relativism" &lt;/a&gt;  où les concepts s'évaluent par leur pouvoir explicatif contextuel. &lt;/p&gt; &lt;p&gt; Son héritage  imprègne la rhétorique moderne, l'analyse du discours et l'éducation argumentative, favorisant des échanges constructifs intégrant réfutations. Son appel à ramener la philosophie dans la vie pratique résonne encore en éthique appliquée et en résolution de conflits. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F72" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G72" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="H70" s="9" t="s">
+      <c r="H72" s="9" t="s">
         <v>598</v>
-      </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
-        <v>1923</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>601</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antony_Flew"  title=" Wikipedia"&gt;Antony FLEW&lt;/a&gt; était un philosophe analytique britanique connu pour ses travaux en philosophie de la religion et son &lt;a href="https://www.youtube.com/watch?v=kPxo32o7M_U"  title=" De l'athéisme au théisme : l'histoire fascinante du célèbre philosophe Antony Flew  par Vers Jésus"&gt;évolution spectaculaire &lt;/a&gt; d'un athéisme militant vers un déisme basé sur l'évidence scientifique. &lt;/p&gt; &lt;p&gt; Figure majeure de l'athéisme académique pendant plus de 50 ans, il présenta son célèbre argument &lt;a href="https://www.youtube.com/watch?v=VoLNeEWqJfU"  title=" Theology and Falsification - Antony Flew | Reading  par Jamie Micheli"&gt;"Theology and Falsification" &lt;/a&gt; en 1950 au Socratic Club, affirmant que les énoncés théologiques sont invérifiables et donc vides de sens. En 2004, âgé de 81 ans, il annonça son adhésion au déisme, inspiré par le "fine-tuning" de l'univers, la complexité de l'ADN et l'origine de la vie, sans jamais embrasser une religion révélée. Il mourut en 2010, réaffirmant un Dieu aristotélicien, "horloger divin" distant.&lt;/p&gt; &lt;p&gt; Il défendait la "présomption d'athéisme" : partir du rejet de Dieu jusqu'à preuve empirique contraire, critiquant la vie après la mort, la défense du libre arbitre face au mal et la cohérence du concept divin. Son virage déiste, détaillé dans "There Is a God" paru en 2007, mettait l'accent sur l'intelligence derrière la complexité cosmique et biologique, rejetant le matérialisme pur comme insuffisant pour expliquer conscience et moralité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : "The Presumption of Atheism" paru en 1976 : Fondement rationnel de l'athéisme comme position par défaut. "God and Philosophy" paru en 1966 : Critique des preuves traditionnelles de Dieu et "Thinking About Thinking" paru en 1975 : Introduction du sophisme écossais.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
-        <v>1924</v>
-      </c>
-      <c r="B72" s="7" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Warnock"  title=" Wikipedia"&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href="https://fr.wikipedia.org/wiki/Existentialisme"  title=" l’existentialisme Wikipedia"&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href="https://en.wikipedia.org/wiki/Ethics_Since_1900"  title=" Ethics Since 1900 Wikipedia"&gt;Ethics Since 1900&lt;/a&gt;, elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de "statementing", qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  
-</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>613</v>
       </c>
       <c r="I72" s="9"/>
       <c r="J72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>264</v>
+        <v>141</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>73</v>
       </c>
       <c r="M72" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="158.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="n">
+        <v>1923</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antony_Flew"  title=" Wikipedia"&gt;Antony FLEW&lt;/a&gt; était un philosophe analytique britanique connu pour ses travaux en philosophie de la religion et son &lt;a href="https://www.youtube.com/watch?v=kPxo32o7M_U"  title=" De l'athéisme au théisme : l'histoire fascinante du célèbre philosophe Antony Flew  par Vers Jésus"&gt;évolution spectaculaire &lt;/a&gt; d'un athéisme militant vers un déisme basé sur l'évidence scientifique. &lt;/p&gt; &lt;p&gt; Figure majeure de l'athéisme académique pendant plus de 50 ans, il présenta son célèbre argument &lt;a href="https://www.youtube.com/watch?v=VoLNeEWqJfU"  title=" Theology and Falsification - Antony Flew | Reading  par Jamie Micheli"&gt;"Theology and Falsification" &lt;/a&gt; en 1950 au Socratic Club, affirmant que les énoncés théologiques sont invérifiables et donc vides de sens. En 2004, âgé de 81 ans, il annonça son adhésion au déisme, inspiré par le "fine-tuning" de l'univers, la complexité de l'ADN et l'origine de la vie, sans jamais embrasser une religion révélée. Il mourut en 2010, réaffirmant un Dieu aristotélicien, "horloger divin" distant.&lt;/p&gt; &lt;p&gt; Il défendait la "présomption d'athéisme" : partir du rejet de Dieu jusqu'à preuve empirique contraire, critiquant la vie après la mort, la défense du libre arbitre face au mal et la cohérence du concept divin. Son virage déiste, détaillé dans "There Is a God" paru en 2007, mettait l'accent sur l'intelligence derrière la complexité cosmique et biologique, rejetant le matérialisme pur comme insuffisant pour expliquer conscience et moralité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : "The Presumption of Atheism" paru en 1976 : Fondement rationnel de l'athéisme comme position par défaut. "God and Philosophy" paru en 1966 : Critique des preuves traditionnelles de Dieu et "Thinking About Thinking" paru en 1975 : Introduction du sophisme écossais.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Warnock"  title=" Wikipedia"&gt;Mary WARNOCK&lt;/a&gt; était une  philosophe britannique spécialiste de l'éthique, de l'existentialisme et de la philosophie de l'esprit, est née Helen Mary Wilson à Winchester. Éduquée à Oxford où elle excelle en philosophie, elle devient fellow à St Hugh's College en 1949, épouse du philosophe Geoffrey Warnock, et dirige le Girton College de Cambridge (1985-1991). Élevée au rang de baronne en 1985, elle marque la sphère publique par ses rapports gouvernementaux sur l'éducation spécialisée et la fécondation in vitro. &lt;/p&gt; &lt;p&gt; Ses premiers travaux portent sur &lt;a href="https://fr.wikipedia.org/wiki/Existentialisme"  title=" l’existentialisme Wikipedia"&gt;l'existentialisme, &lt;/a&gt;  avec des analyses de Sartre et de l'éthique existentielle dans Existentialist Ethics (1967), où elle explore la liberté et la responsabilité face à l'absurde. Dans &lt;a href="https://en.wikipedia.org/wiki/Ethics_Since_1900"  title=" Ethics Since 1900 Wikipedia"&gt;Ethics Since 1900&lt;/a&gt;, elle critique l'émotivisme et le préscriptivisme au profit d'une approche rationnelle et contextuelle de la morale. &lt;/p&gt; &lt;p&gt;Elle  préside deux enquêtes décisives : le rapport de 1978 intègre les enfants handicapés dans l'enseignement ordinaire via un système de "statementing", qu'elle critiquera plus tard pour son coût et ses lacunes ; celui de 1984 sur l'embryologie humaine fonde la loi de 1990, régulant FIV et recherche sur embryons (limite de 14 jours), en équilibrant progrès scientifique et éthique. Défenseure d'une éthique nuancée (euthanasie assistée, intelligence animale), elle incarne une philosophie appliquée au bien commun, influençant débats sur bioéthique et éducation sans dogmatisme.&lt;/p&gt;  
+</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="I74" s="9"/>
+      <c r="J74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M74" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="n">
         <v>1924</v>
       </c>
-      <c r="B73" s="7" t="n">
+      <c r="B75" s="7" t="n">
         <v>2003</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C75" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D75" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E75" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="10" t="s">
+      <c r="F75" s="7"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="I73" s="10" t="s">
+      <c r="I75" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="J73" s="2" t="s">
+      <c r="J75" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="K75" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="L73" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="M73" s="14" t="s">
+      <c r="M75" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="339" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="n">
         <v>1925</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B76" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C76" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D76" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anthony_Quinton"  title=" Wikipedia"&gt;Anthony QUINTON&lt;/a&gt;  était un philosophe politique et moral anglais, métaphysicien et matérialiste, est une figure oxonienne conservatrice. Éduqué à Christ Church (Oxford) après un service dans la RAF, il fut Fellow à All Souls (1949-1955), tutor à New College, puis président de Trinity College (1978-1987). Pair à vie (Baron Quinton) depuis 1983, il présida la British Library (1985-1990) et anima Round Britain Quiz à la BBC. &lt;/p&gt; &lt;p&gt; Dans The Politics of Imperfection (1978), il théorise le conservatisme britannique comme marqué par le traditionalisme (valeur de ce qui résiste au temps), l'organicisme (société comme organisme historique) et le scepticisme politique (méfiance envers les utopies rationnelles). Inspiré par &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_2001_num_33_1_2448_t1_0691_0000_3"  title=" Anthony Quinton Hume 2000  par Persée"&gt;Hume et Hooker, &lt;/a&gt;  il oppose cette sagesse collective empirique aux idéaux abstraits de la gauche, prônant une évolution prudente des institutions. &lt;/p&gt; &lt;p&gt; En métaphysique, il défend un  &lt;a href="https://fr.wikipedia.org/wiki/Nominalisme"  title=" nominalisme par Wikipedia"&gt;nominalisme &lt;/a&gt; des classes naturelles : les propriétés sont des classes objectives de choses similaires, évitant le réalisme des universaux sans tomber dans le subjectivisme pur. Matérialiste de l'esprit, il analyse la conscience comme fonction du cerveau, tout en valorisant le sens commun contre les excès analytiques ou continentaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique (ouvrages sur Hume, The Nature of Things), admirateur de Thatcher, il incarne un  &lt;a href="https://fr.wikipedia.org/wiki/Conservatisme"  title=" conservatisme par Wikipedia"&gt;conservatisme &lt;/a&gt; intellectuel élégant, influençant la philosophie morale et politique par son réalisme sceptique. Son legs persiste dans les débats sur tradition et rationalité politique. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F76" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G76" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H76" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="I74" s="10" t="s">
+      <c r="I76" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="J76" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="K76" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L74" s="2" t="s">
+      <c r="L76" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M74" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="n">
         <v>1925</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B77" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C77" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D77" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E77" s="17" t="s">
         <v>634</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F77" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="G77" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="H75" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="2" t="s">
+      <c r="I77" s="9"/>
+      <c r="J77" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="M75" s="14" t="s">
+      <c r="M77" s="14" t="s">
         <v>639</v>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="267.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="n">
         <v>1926</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>641</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ivan_Illich"  title=" Wikipedia"&gt;Ivan ILLICH&lt;/a&gt;  était un philosophe, théologien et critique social austro-américain d'origine multiculturelle, connu pour sa radicalité dans la dénonciation des institutions modernes qu'il juge aliénantes et contre-productives, prônant une société conviviale fondée sur &lt;a href="https://ecologica.education/2023/11/08/ivan-illich-penseur-de-lecologie-politique/" title="Ivan Illich, penseur de l’écologie politique par Ecologica"&gt;l'autonomie humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; En 1961, au Mexique, il fonde à Cuernavaca le CIDOC (Centre interculturel de documentation), un laboratoire expérimental attirant des milliers d'intellectuels pour des séminaires interdisciplinaires sur éducation, développement et religion ; fermé en 1976 pour éviter son institutionnalisation, ce lieu forge sa méthode provocatrice post-Mai 68. &lt;/p&gt; &lt;p&gt; Il héorise la contre-productivité : tout processus industriel (éducation, médecine, transport) passe d'amplificateur d'autonomie à générateur de dépendance et d'inégalités, inversant sa finalité. Pour lui, les racines chrétiennes sont perverties : Incarnation ouvre à l'amour interpersonnel, mais modernité institutionnalise en monopoles salvifiques, ni accomplissement ni négation du christianisme, mais sa dégénérescence.&lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : &lt;a href="https://www.youtube.com/watch?v=axeVcD8emQY"  title="IVAN ILLICH - Une société sans école par 1000 idées de culture generale"&gt;"Une société sans école" &lt;/a&gt; paru en 1971 : l'école, monopole étatique, désapprend plus qu'elle n'enseigne ; propose "réseaux d'apprentissage" pair-à-pair, libres et gratuits, pour restaurer l'éducation vernaculaire. "La Convivialité" paru en 1973  : définit l'outil convivial (ex. : bicyclette) comme accessible, autonome et égalitaire ; introduit le "monopole radical" où la technique surpuissante exclut les alternatives et infantilise. "Némésis médicale paru en 1975, Énergie et équité"  en 1973 et "Le Chômage créateur" en 1977 : démontre que santé, vitesse, emploi deviennent contre-productifs au-delà d'un seuil.&lt;/p&gt;    &lt;audio controls title="Ivan Illich : "L'école enseigne à l'enfant qu'il doit être inévitablement classé par un bureaucrate" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-02.05.2017-ITEMA_21310924-2012C3372E0981-NET_B3E76531-3403-4CED-9218-298FB5C06B8B_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F78" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="G78" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="H76" s="9" t="s">
+      <c r="H78" s="9" t="s">
         <v>646</v>
-      </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="358.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>1926</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>656</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>657</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>659</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>662</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>73</v>
+        <v>647</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -6536,45 +6586,42 @@
         </is>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Geoffrey_Warnock"  title=" Wikipedia"&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J. L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href="https://fr.wikipedia.org/wiki/Intuitionnisme_social"   title="L’intuitionnisme par Kikipedia"&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; Dans &lt;em&gt;L’Objet de la morale&lt;/em&gt; (1971), il soutient que la morale a une fonction : améliorer la condition humaine, toujours menacée par la rareté des ressources, l’ignorance et surtout la « sympathie limitée » des hommes, qui se soucient d’abord d’eux-mêmes et de leurs proches. Les vertus morales servent à corriger cette tendance. </t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="I79" s="9"/>
+    <row r="79" customFormat="false" ht="358.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>653</v>
+      </c>
       <c r="J79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>671</v>
+        <v>53</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>73</v>
+        <v>654</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6582,48 +6629,43 @@
         </is>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="153" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bryan_Magee"  title=" Wikipedia"&gt;Bryan MAGEE&lt;/a&gt; était un philosophe britannique, auteur, homme politique et célèbre vulgarisateur de la philosophie. Né à Londres dans une famille modeste, il étudie à Oxford puis à Yale grâce à une bourse Rhodes. Député travailliste (1974-1983) pour Leyton avant de rejoindre le SDP, il est surtout connu pour ses émissions BBC : Men of Ideas (1978) et The Great Philosophers (1987), où il interroge des géants comme Popper, Wittgenstein ou Habermas avec clarté et profondeur. &lt;/p&gt; &lt;p&gt; Il  excelle dans la philosophie de Schopenhauer, dont il publie une étude majeure (The Philosophy of Schopenhauer, 1983, révisée 1997), soulignant son influence sur Wagner, Wittgenstein et le bouddhisme.  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" "agnostisme par Wikipedia"&gt; Agnostique méthodique &lt;/a&gt; inspiré de Huxley, il rejette le relativisme au nom d'un progrès critique permanent : les croyances doivent être révisables pour avancer vers la vérité, sans dogmatisme religieux ni &lt;a href="https://fr.wikipedia.org/wiki/Linguistique"  title=" "linguistique par Wikipedia"&gt; linguisticisme analytique &lt;/a&gt; étroit.  &lt;/p&gt; &lt;p&gt; Critique acerbe de la philosophie analytique post-Wittgenstein, qu'il accuse de stérilité théorique au profit d'un "thérapeutisme" linguistique, il défend une philosophie existentielle confrontant la mort et le sens de la vie. Dans Confessions of a Philosopher (1997), il retrace son cheminement intellectuel, mêlant autobiographie, politique et métaphysique, pour une pensée libératrice et humaniste. &lt;/p&gt; &lt;p&gt; Auteur prolifique (Wagner, Popper, poésie, romans), il rend la philosophie accessible sans la trivialiser, influençant des générations par ses entretiens télévisés disponibles sur YouTube. Son legs : une quête insatiable de sens face à la finitude, alliant rigueur et passion pour Wagner ou la démocratie.&lt;/p&gt; 
-</t>
-        </is>
+        <v>658</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>659</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe, homme politique et vulgarisateur britannique, spécialiste de Schopenhauer.</t>
-        </is>
+      <c r="M80" s="2" t="s">
+        <v>663</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -6631,48 +6673,45 @@
         </is>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
-        <v>1933</v>
-      </c>
-      <c r="B81" s="7" t="n">
-        <v>2018</v>
+        <v>1929</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>664</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>682</v>
+        <v>666</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Geoffrey_Warnock"  title=" Wikipedia"&gt;Geoffrey WARNOCK&lt;/a&gt;  était un philosophe anglais de l’ordinaire, formé à Oxford après un service militaire dans les Irish Guards. Fellow à Magdalen College dès 1949, puis Principal de Hertford College (1971-1988) et Vice-Chancelier d’Oxford (1981-1985), il est connu pour avoir édité et publié les œuvres posthumes de J. L. Austin, dont Philosophical Papers et Sense and Sensibilia. &lt;/p&gt; &lt;p&gt; Dans Contemporary Moral Philosophy (1967), il critique l’émotivisme et le préscriptivisme (Ayer, Stevenson, Hare) pour leur réduction du discours moral à des attitudes ou impératifs sans justification rationnelle. Il prône un retour à un &lt;a href="https://fr.wikipedia.org/wiki/Intuitionnisme_social"   title="L’intuitionnisme par Kikipedia"&gt;intuitionnisme réformé, &lt;/a&gt;  où les jugements moraux s’appuient sur des considérations objectives et partagées, comme le bien-être humain, sans dogmatisme. &lt;/p&gt; &lt;p&gt; Il  défend une éthique pratique et modérée, opposée aux excès relativistes ou formalistes, valorisant le rôle du philosophe dans l’analyse claire des concepts moraux ordinaires. Proche de son épouse Mary Warnock (philosophe éthicienne), il incarne l’Oxford analytique appliquée à la vie publique. &lt;/p&gt; &lt;p&gt; Son legs, discret mais solide, influence la philosophie morale britannique par son équilibre entre rigueur logique et humanisme concret, reliant Austin et Williams dans une tradition oxonienne sceptique. &lt;/p&gt; Dans &lt;em&gt;L’Objet de la morale&lt;/em&gt; (1971), il soutient que la morale a une fonction : améliorer la condition humaine, toujours menacée par la rareté des ressources, l’ignorance et surtout la « sympathie limitée » des hommes, qui se soucient d’abord d’eux-mêmes et de leurs proches. Les vertus morales servent à corriger cette tendance. </t>
+        </is>
       </c>
       <c r="F81" s="7" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>685</v>
+        <v>669</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>670</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="2" t="s">
-        <v>409</v>
+        <v>33</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>53</v>
+        <v>671</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="M81" s="14" t="s">
-        <v>687</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
+        <v>73</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>672</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -6680,43 +6719,48 @@
         </is>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B82" s="7" t="n">
-        <v>2026</v>
+        <v>1930</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>673</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>690</v>
+        <v>675</v>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bryan_Magee"  title=" Wikipedia"&gt;Bryan MAGEE&lt;/a&gt; était un philosophe britannique, auteur, homme politique et célèbre vulgarisateur de la philosophie. Né à Londres dans une famille modeste, il étudie à Oxford puis à Yale grâce à une bourse Rhodes. Député travailliste (1974-1983) pour Leyton avant de rejoindre le SDP, il est surtout connu pour ses émissions BBC : Men of Ideas (1978) et The Great Philosophers (1987), où il interroge des géants comme Popper, Wittgenstein ou Habermas avec clarté et profondeur. &lt;/p&gt; &lt;p&gt; Il  excelle dans la philosophie de Schopenhauer, dont il publie une étude majeure (The Philosophy of Schopenhauer, 1983, révisée 1997), soulignant son influence sur Wagner, Wittgenstein et le bouddhisme.  &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" "agnostisme par Wikipedia"&gt; Agnostique méthodique &lt;/a&gt; inspiré de Huxley, il rejette le relativisme au nom d'un progrès critique permanent : les croyances doivent être révisables pour avancer vers la vérité, sans dogmatisme religieux ni &lt;a href="https://fr.wikipedia.org/wiki/Linguistique"  title=" "linguistique par Wikipedia"&gt; linguisticisme analytique &lt;/a&gt; étroit.  &lt;/p&gt; &lt;p&gt; Critique acerbe de la philosophie analytique post-Wittgenstein, qu'il accuse de stérilité théorique au profit d'un "thérapeutisme" linguistique, il défend une philosophie existentielle confrontant la mort et le sens de la vie. Dans Confessions of a Philosopher (1997), il retrace son cheminement intellectuel, mêlant autobiographie, politique et métaphysique, pour une pensée libératrice et humaniste. &lt;/p&gt; &lt;p&gt; Auteur prolifique (Wagner, Popper, poésie, romans), il rend la philosophie accessible sans la trivialiser, influençant des générations par ses entretiens télévisés disponibles sur YouTube. Son legs : une quête insatiable de sens face à la finitude, alliant rigueur et passion pour Wagner ou la démocratie.&lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F82" s="7" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>693</v>
+        <v>678</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>679</v>
       </c>
       <c r="I82" s="9"/>
       <c r="J82" s="2" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>694</v>
+        <v>73</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe, homme politique et vulgarisateur britannique, spécialiste de Schopenhauer.</t>
+        </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -6724,50 +6768,48 @@
         </is>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="183" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raoul_Vaneigem"  title=" Wikipedia"&gt;Raoul VANEIGEM&lt;/a&gt; était un écrivain et philosophe belge, figure centrale de l’Internationale situationniste aux côtés de Guy Debord, surtout connu pour son &lt;a href="https://www.youtube.com/watch?v=sG-sy80_hJ4"  title="traité du savoir vivre par sortir du capitalisme"&gt;Traité de savoir-vivre à l’usage des jeunes générations &lt;/a&gt;  (1967), texte-phare qui a inspiré Mai 68. &lt;/p&gt; &lt;p&gt; Il dénonce ce qu’il appelle la « société du spectacle », c’est-à-dire un ordre social où la vie authentique est remplacée par des images, des rôles et des consommations passives. Pour lui, le capitalisme moderne produit un « nihilisme passif » : les individus acceptent l’absurde et la survie au lieu de vivre pleinement. Sa philosophie vise donc à réveiller le désir et la créativité contre la résignation et le conformisme. &lt;/p&gt; &lt;p&gt; Contrairement aux révolutions purement politiques, il prône une &lt;a href="https://le-carnet-et-les-instants.net/raoul-vaneigem-entretien/"  title="vaneigem toujours en quête du bonheur"&gt;révolution de la vie quotidienne, &lt;/a&gt; centrée sur la jouissance, la créativité et la gratuité. Son mot d’ordre célèbre, « Vivre sans temps mort, jouir sans entraves », résume un hédonisme radical qui refuse le sacrifice au nom du travail, du profit ou de l’autorité. La vraie révolution commence par la façon dont chacun organise son existence, ses plaisirs et ses relations. &lt;/p&gt; &lt;p&gt; Tout être humain porte une tendance fondamentale à s’autoréaliser comme créateur conscient de sa vie. Un « sujet radical » est celui qui prend conscience de cette pulsion et la relie à un projet collectif d’émancipation. Sa pensée articule ainsi l’individu et le collectif : la liberté personnelle n’est complète que si elle s’inscrit dans une lutte contre les structures qui aliènent (travail contraint, marchandisation, pouvoir hiérarchique). &lt;/p&gt; &lt;p&gt; Il s’inspire autant de Lautréamont, Fourier ou Hölderlin que du marxisme et de l’anarchisme pour penser une société autogérée et non marchande. Il défend l’autogestion politique et économique comme forme concrète d’une communauté où décident ceux qui vivent et créent, et non les détenteurs du capital ou de l’État. Son hédonisme n’est pas un simple plaisir égoïste, mais une éthique de la joie comme moteur de révolte et de construction d’un autre monde. &lt;/p&gt; &lt;/p&gt; Spécialiste du Moyen Âge et des mouvements hérétiques, il voit dans ces résistances au christianisme officiel les signes d’une civilisation future fondée sur la créativité et la gratuité plutôt que sur l’aliénation et le profit. Dans ses nombreux ouvrages, il explore l’histoire des révoltes, des plaisirs interdits et des communautés libres pour nourrir une pensée de l’insurrection permanente. Sa philosophie reste ainsi une invitation à  &lt;a href="https://www.youtube.com/watch?v=TQWvjqrHdiQ&amp;list=RDTQWvjqrHdiQ"  title="la vie s’écoule de vaneigem par sirbon83"&gt;refuser la survie &lt;/a&gt; imposée et à inventer, jour après jour, une vie digne d’être vécue, &lt;/p&gt;  
-</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yYJewNBDWFA</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Présentation de Raoul Vaneigem" par Michel Onfray</t>
-        </is>
+        <v>681</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>684</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="2" t="s">
-        <v>472</v>
+        <v>409</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="M83" s="14" t="s">
-        <v>701</v>
+        <v>687</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -6775,69 +6817,164 @@
         </is>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="217.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="333.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>702</v>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Javier MUGUERZA</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Javier_Muguerza"   title=" Wikipedia"&gt;Javier MUGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la "perplexité" comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses "trois Critiques" (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; 
-</t>
-        </is>
+        <v>688</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>690</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="I84" s="9"/>
       <c r="J84" s="2" t="s">
         <v>109</v>
       </c>
       <c r="K84" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="287.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raoul_Vaneigem"  title=" Wikipedia"&gt;Raoul VANEIGEM&lt;/a&gt; était un écrivain et philosophe belge, figure centrale de l’Internationale situationniste aux côtés de Guy Debord, surtout connu pour son &lt;a href="https://www.youtube.com/watch?v=sG-sy80_hJ4"  title="traité du savoir vivre par sortir du capitalisme"&gt;Traité de savoir-vivre à l’usage des jeunes générations &lt;/a&gt;  (1967), texte-phare qui a inspiré Mai 68. &lt;/p&gt; &lt;p&gt; Il dénonce ce qu’il appelle la « société du spectacle », c’est-à-dire un ordre social où la vie authentique est remplacée par des images, des rôles et des consommations passives. Pour lui, le capitalisme moderne produit un « nihilisme passif » : les individus acceptent l’absurde et la survie au lieu de vivre pleinement. Sa philosophie vise donc à réveiller le désir et la créativité contre la résignation et le conformisme. &lt;/p&gt; &lt;p&gt; Contrairement aux révolutions purement politiques, il prône une &lt;a href="https://le-carnet-et-les-instants.net/raoul-vaneigem-entretien/"  title="vaneigem toujours en quête du bonheur"&gt;révolution de la vie quotidienne, &lt;/a&gt; centrée sur la jouissance, la créativité et la gratuité. Son mot d’ordre célèbre, « Vivre sans temps mort, jouir sans entraves », résume un hédonisme radical qui refuse le sacrifice au nom du travail, du profit ou de l’autorité. La vraie révolution commence par la façon dont chacun organise son existence, ses plaisirs et ses relations. &lt;/p&gt; &lt;p&gt; Tout être humain porte une tendance fondamentale à s’autoréaliser comme créateur conscient de sa vie. Un « sujet radical » est celui qui prend conscience de cette pulsion et la relie à un projet collectif d’émancipation. Sa pensée articule ainsi l’individu et le collectif : la liberté personnelle n’est complète que si elle s’inscrit dans une lutte contre les structures qui aliènent (travail contraint, marchandisation, pouvoir hiérarchique). &lt;/p&gt; &lt;p&gt; Il s’inspire autant de Lautréamont, Fourier ou Hölderlin que du marxisme et de l’anarchisme pour penser une société autogérée et non marchande. Il défend l’autogestion politique et économique comme forme concrète d’une communauté où décident ceux qui vivent et créent, et non les détenteurs du capital ou de l’État. Son hédonisme n’est pas un simple plaisir égoïste, mais une éthique de la joie comme moteur de révolte et de construction d’un autre monde. &lt;/p&gt; &lt;/p&gt; Spécialiste du Moyen Âge et des mouvements hérétiques, il voit dans ces résistances au christianisme officiel les signes d’une civilisation future fondée sur la créativité et la gratuité plutôt que sur l’aliénation et le profit. Dans ses nombreux ouvrages, il explore l’histoire des révoltes, des plaisirs interdits et des communautés libres pour nourrir une pensée de l’insurrection permanente. Sa philosophie reste ainsi une invitation à  &lt;a href="https://www.youtube.com/watch?v=TQWvjqrHdiQ&amp;list=RDTQWvjqrHdiQ"  title="la vie s’écoule de vaneigem par sirbon83"&gt;refuser la survie &lt;/a&gt; imposée et à inventer, jour après jour, une vie digne d’être vécue, &lt;/p&gt;  
+</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yYJewNBDWFA</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Présentation de Raoul Vaneigem" par Michel Onfray</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="M85" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="217.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="7" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Javier MUGUERZA</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://es.wikipedia.org/wiki/Javier_Muguerza"   title=" Wikipedia"&gt;Javier MUGUERZA&lt;/a&gt;  était un philosophe espagnol majeur, disciple de José Luis López Aranguren et José Ferrater Mora, connu pour son &lt;a href="https://fr.wikipedia.org/wiki/Agnosticisme"  title=" Agnosticisme  par Wikipedia"&gt;l'agnosticisme &lt;/a&gt; déclaré et sa défense de la "perplexité" comme posture éthique et rationnelle face aux certitudes dogmatiques. Né à Coín (Malaga), il a doctoré en 1965 à l'Université Complutense de Madrid avec une thèse sur Frege, avant de devenir catedrático en philosophie morale dans plusieurs universités (La Laguna, Autónoma de Barcelona, UNED). Il a fondé l'Institut de Philosophie du CSIC et la revue Isegoría en 1990, promouvant un dialogue ibéro-américain en philosophie morale et politique. &lt;/p&gt; &lt;p&gt; Bien que non lié à l'origine historique de l'agnosticisme (Huxley, 1869), Muguerza en incarne une version moderne et personnelle, influencée par Kant et la philosophie critique. Dans des essais comme « La profession de foi de l'incroyant », il adopte une position agnostique : vivre « comme si Dieu n'existait pas » tout en reconnaissant que la solidarité humaine pourrait requérir une motivation quasi-religieuse pour transcender la simple justice. Sa pensée, marquée par La raison sans espoir (1977) et Depuis la perplexité (1990), valorise le dissensus et l'impératif de la dissidence contre tout autoritarisme, y compris religieux. &lt;/p&gt; &lt;p&gt; Il dialogue ouvertement avec la théologie chrétienne tout en maintenant une laïcité ferme, analysant des dilemmes comme la question socratique d'Euthyphron (Dieu fonde-t-il la morale ?) ou le problème du mal d'Épicure. Il critique les éthiques religieuses pour leur risque de subordonner la morale à la religion, plaidant pour une éthique publique cosmopolite et utopique, sans recours à une loi naturelle théologique. Ses "trois Critiques" (analytique, dialogique, onirique) renouvellent Kant en soulignant l'incertitude rationnelle. &lt;/p&gt; &lt;p&gt; Figure de la transition démocratique espagnole, il a dirigé plus de vingt thèses et reçu un doctorat honoris causa de La Laguna en 2007. Son legs : une philosophie du dissensus qui fait écho à l'agnosticisme en refusant les réponses absolues, favorisant une raison perpleja et engagée. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L84" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M84" s="2" t="s">
+      <c r="M86" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="n">
         <v>1942</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B87" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C87" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D87" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Derek_Parfit"   title=" Wikipedia"&gt;Derek PARFIT&lt;/a&gt; était un philosophe britannique spécialiste de la  morale analytique, connu pour ses travaux sur l’identité personnelle, la rationalité pratique et l’éthique. Célèbre pour sa thèse selon laquelle  &lt;a href="https://www.youtube.com/watch?v=ae5jSi2BL0Y"  title="Identités fragmentées (Derek Parfit) par Noé Jacomet "&gt; l’identité personnelle &lt;/a&gt; n’est pas "ce qui importe" réellement dans la survie.  Deux grands ouvrages structurent son influence :&lt;/p&gt; &lt;p&gt;"Reasons and Persons" paru en 1984 est souvent considéré comme l’un des livres les plus importants de philosophie morale du XXᵉ siècle. L’ouvrage traite notamment de la rationalité, de l’identité personnelle à travers le temps et de nos obligations envers les générations futures, en s’appuyant sur une multitude d’expériences de pensée. &lt;/p&gt; &lt;p&gt;"On What Matters" paru en 2011 propose une théorie unifiée de la morale, parfois appelée la "Triple Theory".  Il y défend un réalisme moral robuste et cherche à montrer que le conséquentialisme, le kantisme et le contractualisme convergent vers des jugements moraux communs quand ils sont correctement révisés. &lt;/p&gt; &lt;p&gt; Il remet en question le rôle central de l’intérêt personnel et &lt;a href="https://laviedesidees.fr/David-Edmonds-Parfit"  title=" "une vie de philosophe par laviedesidées"&gt; propose une conception &lt;/a&gt; plus impersonnelle des raisons morales. Il critique les théories morales auto‑destructrices   qui, suivies rigoureusement, ne servent plus les objectifs qu’elles se donnent. Il défend un réalisme normatif : pour lui, il existe des vérités morales objectives, indépendantes de nos désirs ou de nos conventions sociales. &lt;/p&gt; &lt;p&gt; Il a profondément marqué la réflexion sur nos devoirs envers les générations futures et la taille optimale de la population. Il formule des paradoxes célèbres en éthique populationnelle, montrant combien il est difficile de concilier l’idée de maximiser le bien‑être total avec l’intuition que certains scénarios sont moralement problématiques. Il soutient que les personnes aisées ont de fortes obligations envers les plus pauvres et envers ceux qui ne sont pas encore nés, perspective qui a influencé de nombreux débats sur l’altruisme efficace, le climat et la justice intergénérationnelle. &lt;/p&gt; 
 ​
@@ -6847,232 +6984,120 @@
 </t>
         </is>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F87" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="G87" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H87" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="2" t="s">
+      <c r="I87" s="10"/>
+      <c r="J87" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K85" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="L85" s="2" t="s">
+      <c r="L87" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="M87" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
         <v>1954</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B88" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E88" s="14" t="s">
         <v>720</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="J88" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L86" s="2" t="s">
+      <c r="L88" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="M88" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1">
-        <v>1904</v>
-      </c>
-      <c r="B87" s="1">
-        <v>1991</v>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1904 - 1991</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">María ZAMBRANO</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/María_Zambrano"  title=" Wikipedia"&gt;María ZAMBRANO&lt;/a&gt; (1904-1991) est une philosophe et essayiste espagnole, disciple de José Ortega y Gasset. Engagée du côté de la République pendant la guerre civile, elle dut s'exiler en 1939 et vécut près de quarante-cinq ans loin de son pays, au Mexique, à Cuba, à Porto Rico, en Italie, en France et en Suisse, avant de revenir en Espagne en 1984.&lt;/p&gt; &lt;p&gt;Sa pensée s'éloigne de celle de son maître. Elle reproche à la philosophie occidentale d'avoir séparé la raison de la vie, de l'émotion et du sacré. Elle propose une « raison poétique », une manière de penser qui ne cherche pas à dominer la réalité par des concepts, mais à l'accueillir, à l'écouter et à la laisser apparaître, comme le fait la poésie.&lt;/p&gt; &lt;p&gt;L'exil occupe une place centrale dans sa pensée : loin d'être seulement une perte, il devient pour elle une condition philosophique, une manière de vivre dépouillée qui ouvre à une vérité plus profonde. Elle voyait dans la figure d'Antigone, à laquelle elle consacra une pièce, &lt;em&gt;La Tombe d'Antigone&lt;/em&gt;, le symbole de toutes les victimes de l'histoire et de la conscience qui refuse l'injustice.&lt;/p&gt; &lt;p&gt;Dans des livres comme &lt;em&gt;Philosophie et poésie&lt;/em&gt; (1939), &lt;em&gt;L'Homme et le divin&lt;/em&gt; (1955) ou &lt;em&gt;Les Clairières du bois&lt;/em&gt; (1977), elle explore le rêve, la mémoire, l'exil et le sacré, dans un style qui mêle philosophie et littérature. Longtemps méconnue, elle reçut en 1988 le prix Cervantès, la plus haute distinction littéraire du monde hispanique, et elle est aujourd'hui considérée comme l'une des grandes voix de la pensée espagnole du XXe siècle.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Espagnole</t>
-        </is>
-      </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; esthetique</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Existentialisme</t>
-        </is>
-      </c>
-      <c r="M87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe espagnole, disciple d'Ortega y Gasset, penseuse de la « raison poétique ».</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1">
-        <v>1919</v>
-      </c>
-      <c r="B88" s="1">
-        <v>1999</v>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1919 - 1999</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Iris MURDOCH</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Murdoch"  title=" Wikipedia"&gt;Iris MURDOCH&lt;/a&gt; (1919-1999) est une philosophe et romancière britannique, née à Dublin. Elle enseigna la philosophie à Oxford, où elle fut, avec Elizabeth Anscombe, Philippa Foot et Mary Midgley, l'une des figures d'un groupe de femmes philosophes qui renouvelèrent la réflexion morale après la Seconde Guerre mondiale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Souveraineté du bien&lt;/em&gt; (1970), elle critique à la fois l'existentialisme et la philosophie analytique de son temps, qui réduisaient la morale à des choix de la volonté. Pour elle, la vie morale se joue d'abord dans la manière de voir : être bon, c'est porter sur les autres et sur le monde une « attention » juste et aimante, qui nous arrache à notre égoïsme. Elle reprend l'idée platonicienne du Bien comme réalité supérieure qui attire l'âme vers la vérité.&lt;/p&gt; &lt;p&gt;Murdoch donne l'exemple d'une belle-mère qui méprise sa belle-fille, mais qui, sans rien changer à son comportement extérieur, s'efforce de la regarder autrement, avec justice et bienveillance, jusqu'à la voir telle qu'elle est vraiment. Ce travail intérieur, invisible, est pour Murdoch l'essentiel de la vie morale. Elle voyait aussi dans l'art et la beauté, et notamment dans la contemplation de la nature, un moyen de se détacher de soi.&lt;/p&gt; &lt;p&gt;Elle est aussi l'autrice de vingt-six romans, dont &lt;em&gt;La Mer, la mer&lt;/em&gt;, qui reçut le Booker Prize en 1978, où elle met en scène les illusions et les passions de personnages en quête de sens. Atteinte de la maladie d'Alzheimer à la fin de sa vie, elle a inspiré le film &lt;em&gt;Iris&lt;/em&gt; (2001). Sa philosophie morale connaît aujourd'hui un grand regain d'intérêt.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Britannique</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Platonisme</t>
-        </is>
-      </c>
-      <c r="M88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe et romancière britannique, penseuse d'une morale de l'attention inspirée de Platon.</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="P88">
-        <v>2</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B89" s="1">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920 - 2010</t>
+          <t xml:space="preserve">1919 - 1999</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippa FOOT</t>
-        </is>
-      </c>
-      <c r="E89" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippa_Foot"  title=" Wikipedia"&gt;Philippa FOOT&lt;/a&gt; (1920-2010) est une philosophe britannique qui enseigna à Oxford puis aux États-Unis. Avec Elizabeth Anscombe et Iris Murdoch, elle contribua à faire revivre l'éthique de la vertu, inspirée d'Aristote, face aux morales du devoir et aux morales de l'utilité qui dominaient la philosophie anglo-saxonne.&lt;/p&gt; &lt;p&gt;Elle est connue du grand public pour avoir inventé en 1967 le célèbre « dilemme du tramway » : un tramway fou va tuer cinq personnes, mais on peut le détourner vers une voie où il n'en tuera qu'une. Faut-il le faire ? Cette expérience de pensée, discutée depuis par des milliers de philosophes, sert aujourd'hui aussi à réfléchir aux choix des voitures autonomes.&lt;/p&gt; &lt;p&gt;Philippa Foot fut aussi l'une des fondatrices d'Oxfam, grande organisation de lutte contre la pauvreté, ce qui montre son souci de relier la philosophie morale à l'action. Au début de sa carrière, elle critiqua vivement l'idée, alors dominante, que les jugements moraux ne sont que l'expression de nos sentiments ou de nos choix, en montrant que des mots comme « grossier » ou « courageux » décrivent des faits autant qu'ils expriment des valeurs.&lt;/p&gt; &lt;p&gt;Dans son livre &lt;em&gt;Le Bien naturel&lt;/em&gt; (2001), elle défend l'idée que le bien et le mal moraux ne sont pas de simples préférences : comme une plante ou un animal peut être en bonne ou en mauvaise santé selon sa nature, un être humain peut être bon ou défectueux selon ce qui est nécessaire à une vie humaine réussie. Les vertus comme le courage, la justice ou la tempérance sont ainsi ancrées dans notre nature d'êtres vivants et sociaux.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
+          <t xml:space="preserve">Iris MURDOCH</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iris_Murdoch"  title=" Wikipedia"&gt;Iris MURDOCH&lt;/a&gt; (1919-1999) est une philosophe et romancière britannique, née à Dublin. Elle enseigna la philosophie à Oxford, où elle fut, avec Elizabeth Anscombe, Philippa Foot et Mary Midgley, l'une des figures d'un groupe de femmes philosophes qui renouvelèrent la réflexion morale après la Seconde Guerre mondiale.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Souveraineté du bien&lt;/em&gt; (1970), elle critique à la fois l'existentialisme et la philosophie analytique de son temps, qui réduisaient la morale à des choix de la volonté. Pour elle, la vie morale se joue d'abord dans la manière de voir : être bon, c'est porter sur les autres et sur le monde une « attention » juste et aimante, qui nous arrache à notre égoïsme. Elle reprend l'idée platonicienne du Bien comme réalité supérieure qui attire l'âme vers la vérité.&lt;/p&gt; &lt;p&gt;Murdoch donne l'exemple d'une belle-mère qui méprise sa belle-fille, mais qui, sans rien changer à son comportement extérieur, s'efforce de la regarder autrement, avec justice et bienveillance, jusqu'à la voir telle qu'elle est vraiment. Ce travail intérieur, invisible, est pour Murdoch l'essentiel de la vie morale. Elle voyait aussi dans l'art et la beauté, et notamment dans la contemplation de la nature, un moyen de se détacher de soi.&lt;/p&gt; &lt;p&gt;Elle est aussi l'autrice de vingt-six romans, dont &lt;em&gt;La Mer, la mer&lt;/em&gt;, qui reçut le Booker Prize en 1978, où elle met en scène les illusions et les passions de personnages en quête de sens. Atteinte de la maladie d'Alzheimer à la fin de sa vie, elle a inspiré le film &lt;em&gt;Iris&lt;/em&gt; (2001). Sa philosophie morale connaît aujourd'hui un grand regain d'intérêt.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Britannique</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ethique</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Éthique de la vertu</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe britannique, refondatrice de l'éthique de la vertu et inventrice du « dilemme du tramway ».</t>
+      <c r="L89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platonisme</t>
+        </is>
+      </c>
+      <c r="M89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et romancière britannique, penseuse d'une morale de l'attention inspirée de Platon.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7091,51 +7116,49 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1">
-        <v>1912</v>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2009</t>
-        </is>
+        <v>1920</v>
+      </c>
+      <c r="B90" s="1">
+        <v>2010</v>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912 – 2009</t>
+          <t xml:space="preserve">1920 - 2010</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arne NÆSS</t>
+          <t xml:space="preserve">Philippa FOOT</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arne_N%C3%A6ss" title=" Wikipedia"&gt;Arne NÆSS&lt;/a&gt; est un philosophe norvégien, fondateur de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologie_profonde" title=" Wikipedia"&gt;écologie profonde&lt;/a&gt;. Né à Oslo, il participe dans les années 1930 aux discussions du Cercle de Vienne, puis devient à vingt-sept ans professeur à l’université d’Oslo, où il enseigne de 1939 à 1969. Longtemps seul professeur de philosophie de Norvège, il marque durablement l’enseignement du pays. Résistant pendant l’occupation allemande, il est aussi un alpiniste de haut niveau, qui dirige en 1950 la première ascension du Tirich Mir, dans l’Hindou Kouch.&lt;/p&gt; &lt;p&gt;D’abord spécialiste de logique et de philosophie du langage, il étudie ensuite Spinoza et Gandhi, et s’engage dans la défense de la nature après la lecture du &lt;em&gt;Printemps silencieux&lt;/em&gt; de Rachel Carson. En 1973, il distingue une écologie « superficielle », qui lutte contre la pollution pour préserver la santé et le confort des pays riches, et une écologie « profonde », qui reconnaît une valeur propre à tous les êtres vivants, indépendamment de leur utilité pour l’homme. Il en tire une plate-forme en huit points, qui appelle à réduire la pression humaine sur la nature.&lt;/p&gt; &lt;p&gt;Sa philosophie personnelle, qu’il appelle « écosophie T », du nom de son refuge de montagne, Tvergastein, repose sur la « réalisation de soi » : plus on s’identifie aux autres êtres, plus le soi s’élargit, et la protection de la nature devient l’expression même de ce soi élargi. Il est aussi le premier président norvégien du parti écologiste et pratique la désobéissance civile, en s’enchaînant en 1970 avec d’autres militants pour empêcher la construction d’un barrage. Il meurt à Oslo en 2009.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/naess-mini.webp</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippa_Foot"  title=" Wikipedia"&gt;Philippa FOOT&lt;/a&gt; (1920-2010) est une philosophe britannique qui enseigna à Oxford puis aux États-Unis. Avec Elizabeth Anscombe et Iris Murdoch, elle contribua à faire revivre l'éthique de la vertu, inspirée d'Aristote, face aux morales du devoir et aux morales de l'utilité qui dominaient la philosophie anglo-saxonne.&lt;/p&gt; &lt;p&gt;Elle est connue du grand public pour avoir inventé en 1967 le célèbre « dilemme du tramway » : un tramway fou va tuer cinq personnes, mais on peut le détourner vers une voie où il n'en tuera qu'une. Faut-il le faire ? Cette expérience de pensée, discutée depuis par des milliers de philosophes, sert aujourd'hui aussi à réfléchir aux choix des voitures autonomes.&lt;/p&gt; &lt;p&gt;Philippa Foot fut aussi l'une des fondatrices d'Oxfam, grande organisation de lutte contre la pauvreté, ce qui montre son souci de relier la philosophie morale à l'action. Au début de sa carrière, elle critiqua vivement l'idée, alors dominante, que les jugements moraux ne sont que l'expression de nos sentiments ou de nos choix, en montrant que des mots comme « grossier » ou « courageux » décrivent des faits autant qu'ils expriment des valeurs.&lt;/p&gt; &lt;p&gt;Dans son livre &lt;em&gt;Le Bien naturel&lt;/em&gt; (2001), elle défend l'idée que le bien et le mal moraux ne sont pas de simples préférences : comme une plante ou un animal peut être en bonne ou en mauvaise santé selon sa nature, un être humain peut être bon ou défectueux selon ce qui est nécessaire à une vie humaine réussie. Les vertus comme le courage, la justice ou la tempérance sont ainsi ancrées dans notre nature d'êtres vivants et sociaux.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norvégienne</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; metaphysique</t>
+          <t xml:space="preserve">ethique</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecologisme</t>
+          <t xml:space="preserve">Éthique de la vertu</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe norvégien, alpiniste et fondateur de l’écologie profonde.</t>
+          <t xml:space="preserve">philosophe britannique, refondatrice de l'éthique de la vertu et inventrice du « dilemme du tramway ».</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7144,56 +7167,56 @@
         </is>
       </c>
       <c r="P90">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916 – 2003</t>
+          <t xml:space="preserve">1912 – 2009</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georg Henrik VON WRIGHT</t>
+          <t xml:space="preserve">Arne NÆSS</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georg_Henrik_von_Wright" title=" Wikipedia"&gt;Georg Henrik VON WRIGHT&lt;/a&gt; est un philosophe et logicien finlandais de langue suédoise. Né à Helsinki, élève d’Eino Kaila, il part à Cambridge en 1939, où il devient l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein" title=" Wikipedia"&gt;Ludwig Wittgenstein&lt;/a&gt;, auquel il succède en 1948 à la chaire de philosophie, avant de rentrer en Finlande en 1951. Nommé en 1961 membre de l’Académie de Finlande, il est l’un des intellectuels les plus respectés des pays nordiques. À la mort de Wittgenstein, il est l’un des trois exécuteurs testamentaires chargés de publier ses manuscrits, dont les &lt;em&gt;Recherches philosophiques&lt;/em&gt; et &lt;em&gt;De la certitude&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Logicien, il étudie l’induction et les probabilités, puis la logique modale. En 1951, il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_d%C3%A9ontique" title=" Wikipedia"&gt;logique déontique&lt;/a&gt;, la logique des normes : elle étudie les rapports entre ce qui est obligatoire, permis et interdit, comme la logique modale étudie le nécessaire et le possible. Il développe aussi une logique de l’action et du changement. Dans &lt;em&gt;Explication et compréhension&lt;/em&gt; (1971), il défend l’idée que les actions humaines ne s’expliquent pas comme des phénomènes naturels, par des causes, mais se comprennent à partir des intentions et des raisons des personnes qui agissent.&lt;/p&gt; &lt;p&gt;Dans les dernières décennies de sa vie, il devient un critique inquiet de la civilisation technique. Dans &lt;em&gt;Le Mythe du progrès&lt;/em&gt; (1993), il se demande si le développement des sciences et des techniques, qui menace l’environnement et la diversité des cultures, constitue vraiment un progrès pour l’humanité. Il défend un humanisme fondé sur la raison et la mesure. Il meurt à Helsinki en 2003.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arne_N%C3%A6ss" title=" Wikipedia"&gt;Arne NÆSS&lt;/a&gt; est un philosophe norvégien, fondateur de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cologie_profonde" title=" Wikipedia"&gt;écologie profonde&lt;/a&gt;. Né à Oslo, il participe dans les années 1930 aux discussions du Cercle de Vienne, puis devient à vingt-sept ans professeur à l’université d’Oslo, où il enseigne de 1939 à 1969. Longtemps seul professeur de philosophie de Norvège, il marque durablement l’enseignement du pays. Résistant pendant l’occupation allemande, il est aussi un alpiniste de haut niveau, qui dirige en 1950 la première ascension du Tirich Mir, dans l’Hindou Kouch.&lt;/p&gt; &lt;p&gt;D’abord spécialiste de logique et de philosophie du langage, il étudie ensuite Spinoza et Gandhi, et s’engage dans la défense de la nature après la lecture du &lt;em&gt;Printemps silencieux&lt;/em&gt; de Rachel Carson. En 1973, il distingue une écologie « superficielle », qui lutte contre la pollution pour préserver la santé et le confort des pays riches, et une écologie « profonde », qui reconnaît une valeur propre à tous les êtres vivants, indépendamment de leur utilité pour l’homme. Il en tire une plate-forme en huit points, qui appelle à réduire la pression humaine sur la nature.&lt;/p&gt; &lt;p&gt;Sa philosophie personnelle, qu’il appelle « écosophie T », du nom de son refuge de montagne, Tvergastein, repose sur la « réalisation de soi » : plus on s’identifie aux autres êtres, plus le soi s’élargit, et la protection de la nature devient l’expression même de ce soi élargi. Il est aussi le premier président norvégien du parti écologiste et pratique la désobéissance civile, en s’enchaînant en 1970 avec d’autres militants pour empêcher la construction d’un barrage. Il meurt à Oslo en 2009.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vonwright-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/naess-mini.webp</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finlandaise</t>
+          <t xml:space="preserve">Norvégienne</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">logique ; ethique</t>
+          <t xml:space="preserve">ethique ; metaphysique</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Humanisme</t>
+          <t xml:space="preserve">Ecologisme</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et logicien finlandais, successeur de Wittgenstein à Cambridge, fondateur de la logique déontique.</t>
+          <t xml:space="preserve">philosophe norvégien, alpiniste et fondateur de l’écologie profonde.</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7202,36 +7225,36 @@
         </is>
       </c>
       <c r="P91">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1">
-        <v>1929</v>
+        <v>1916</v>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929 – 2015</t>
+          <t xml:space="preserve">1916 – 2003</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaakko HINTIKKA</t>
+          <t xml:space="preserve">Georg Henrik VON WRIGHT</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaakko_Hintikka" title=" Wikipedia"&gt;Jaakko HINTIKKA&lt;/a&gt; est un logicien et philosophe finlandais, l’un des penseurs les plus inventifs de la philosophie analytique. Né à Vantaa, près d’Helsinki, élève de Georg Henrik von Wright, il enseigne à Helsinki, puis aux États-Unis, à Stanford, en Floride et à Boston. Auteur de plus de cinquante livres et de plus de quatre cent cinquante articles, il a reçu en 2005 le prix Rolf Schock, l’une des plus hautes distinctions en logique et en philosophie.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Knowledge and Belief&lt;/em&gt; (1962), il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_%C3%A9pist%C3%A9mique" title=" Wikipedia"&gt;logique épistémique&lt;/a&gt;, qui étudie avec précision les notions de connaissance et de croyance : que signifie « je sais que », « je crois que », ou « il sait que je sais » ? Pour cela, il utilise l’idée de « mondes possibles », les différentes façons dont le monde pourrait être compatibles avec ce que l’on sait. Ces travaux sont aujourd’hui utilisés en informatique, en intelligence artificielle et en théorie des jeux.&lt;/p&gt; &lt;p&gt;Il propose aussi une « sémantique des jeux » : comprendre une phrase logique, c’est comprendre un jeu entre deux joueurs, l’un qui cherche à la vérifier, l’autre à la réfuter. Avec Gabriel Sandu, il en tire une nouvelle logique, dite « logique IF », plus expressive que la logique classique, dont il pensait qu’elle devrait servir de fondement aux mathématiques. Historien de la philosophie, il a aussi écrit sur Aristote, Descartes, Kant et Wittgenstein, notamment une lecture célèbre du « Je pense, donc je suis » comme acte plutôt que comme raisonnement. Il meurt en 2015.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georg_Henrik_von_Wright" title=" Wikipedia"&gt;Georg Henrik VON WRIGHT&lt;/a&gt; est un philosophe et logicien finlandais de langue suédoise. Né à Helsinki, élève d’Eino Kaila, il part à Cambridge en 1939, où il devient l’ami de &lt;a href="https://fr.wikipedia.org/wiki/Ludwig_Wittgenstein" title=" Wikipedia"&gt;Ludwig Wittgenstein&lt;/a&gt;, auquel il succède en 1948 à la chaire de philosophie, avant de rentrer en Finlande en 1951. Nommé en 1961 membre de l’Académie de Finlande, il est l’un des intellectuels les plus respectés des pays nordiques. À la mort de Wittgenstein, il est l’un des trois exécuteurs testamentaires chargés de publier ses manuscrits, dont les &lt;em&gt;Recherches philosophiques&lt;/em&gt; et &lt;em&gt;De la certitude&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Logicien, il étudie l’induction et les probabilités, puis la logique modale. En 1951, il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_d%C3%A9ontique" title=" Wikipedia"&gt;logique déontique&lt;/a&gt;, la logique des normes : elle étudie les rapports entre ce qui est obligatoire, permis et interdit, comme la logique modale étudie le nécessaire et le possible. Il développe aussi une logique de l’action et du changement. Dans &lt;em&gt;Explication et compréhension&lt;/em&gt; (1971), il défend l’idée que les actions humaines ne s’expliquent pas comme des phénomènes naturels, par des causes, mais se comprennent à partir des intentions et des raisons des personnes qui agissent.&lt;/p&gt; &lt;p&gt;Dans les dernières décennies de sa vie, il devient un critique inquiet de la civilisation technique. Dans &lt;em&gt;Le Mythe du progrès&lt;/em&gt; (1993), il se demande si le développement des sciences et des techniques, qui menace l’environnement et la diversité des cultures, constitue vraiment un progrès pour l’humanité. Il défend un humanisme fondé sur la raison et la mesure. Il meurt à Helsinki en 2003.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hintikka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vonwright-mini.webp</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -7241,17 +7264,17 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">logique ; epistemologie</t>
+          <t xml:space="preserve">logique ; ethique</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique</t>
+          <t xml:space="preserve">Analytique ; Humanisme</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">logicien et philosophe finlandais, fondateur de la logique épistémique et de la sémantique des jeux.</t>
+          <t xml:space="preserve">philosophe et logicien finlandais, successeur de Wittgenstein à Cambridge, fondateur de la logique déontique.</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7265,51 +7288,51 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1">
-        <v>1923</v>
+        <v>1929</v>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2015</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1923 – 2010</t>
+          <t xml:space="preserve">1929 – 2015</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mihailo MARKOVIĆ</t>
+          <t xml:space="preserve">Jaakko HINTIKKA</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mihailo_Markovi%C4%87" title=" Wikipedia (en)"&gt;Mihailo MARKOVIĆ&lt;/a&gt; est un philosophe serbe, l’une des figures majeures de l’école Praxis, puis un acteur controversé du nationalisme serbe. Né à Belgrade, il rejoint jeune le Parti communiste et combat dans la résistance des partisans pendant la Seconde Guerre mondiale. Il soutient deux thèses de doctorat, à Belgrade puis à Londres, où il étudie la logique auprès d’A. J. Ayer, et devient professeur à l’université de Belgrade.&lt;/p&gt; &lt;p&gt;Après la rupture entre Tito et Staline en 1948, il publie en 1952 la première grande critique de la philosophie stalinienne en Yougoslavie. Dans les années 1960, il devient l’un des principaux théoriciens de l’école Praxis, qui défend un marxisme humaniste inspiré des écrits du jeune Marx, centré sur la liberté créatrice de l’homme et la critique de l’aliénation, à l’Ouest comme à l’Est. Il collabore à la revue &lt;em&gt;Praxis&lt;/em&gt; et à l’école d’été de Korčula, où se rencontrent des penseurs marxistes du monde entier. Ses critiques de la bureaucratie lui valent d’être suspendu de l’université en 1975 avec sept collègues.&lt;/p&gt; &lt;p&gt;Son parcours prend ensuite un tour très différent : membre de l’Académie serbe des sciences et des arts, il est l’un des auteurs du Mémorandum de 1986, texte qui formule les revendications du nationalisme serbe, puis devient l’un des idéologues du parti de &lt;a href="https://fr.wikipedia.org/wiki/Slobodan_Milo%C5%A1evi%C4%87" title=" Wikipedia"&gt;Slobodan Milošević&lt;/a&gt;. Ce soutien, pendant les guerres de Yougoslavie, lui a été vivement reproché, notamment par ses anciens compagnons de l’école Praxis. Il meurt à Belgrade en 2010.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaakko_Hintikka" title=" Wikipedia"&gt;Jaakko HINTIKKA&lt;/a&gt; est un logicien et philosophe finlandais, l’un des penseurs les plus inventifs de la philosophie analytique. Né à Vantaa, près d’Helsinki, élève de Georg Henrik von Wright, il enseigne à Helsinki, puis aux États-Unis, à Stanford, en Floride et à Boston. Auteur de plus de cinquante livres et de plus de quatre cent cinquante articles, il a reçu en 2005 le prix Rolf Schock, l’une des plus hautes distinctions en logique et en philosophie.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Knowledge and Belief&lt;/em&gt; (1962), il fonde la &lt;a href="https://fr.wikipedia.org/wiki/Logique_%C3%A9pist%C3%A9mique" title=" Wikipedia"&gt;logique épistémique&lt;/a&gt;, qui étudie avec précision les notions de connaissance et de croyance : que signifie « je sais que », « je crois que », ou « il sait que je sais » ? Pour cela, il utilise l’idée de « mondes possibles », les différentes façons dont le monde pourrait être compatibles avec ce que l’on sait. Ces travaux sont aujourd’hui utilisés en informatique, en intelligence artificielle et en théorie des jeux.&lt;/p&gt; &lt;p&gt;Il propose aussi une « sémantique des jeux » : comprendre une phrase logique, c’est comprendre un jeu entre deux joueurs, l’un qui cherche à la vérifier, l’autre à la réfuter. Avec Gabriel Sandu, il en tire une nouvelle logique, dite « logique IF », plus expressive que la logique classique, dont il pensait qu’elle devrait servir de fondement aux mathématiques. Historien de la philosophie, il a aussi écrit sur Aristote, Descartes, Kant et Wittgenstein, notamment une lecture célèbre du « Je pense, donc je suis » comme acte plutôt que comme raisonnement. Il meurt en 2015.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/markovic-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hintikka-mini.webp</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serbe</t>
+          <t xml:space="preserve">Finlandaise</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">logique ; epistemologie</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme ; Humanisme</t>
+          <t xml:space="preserve">Analytique</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe serbe de l’école Praxis, critique du stalinisme, devenu ensuite idéologue du nationalisme serbe.</t>
+          <t xml:space="preserve">logicien et philosophe finlandais, fondateur de la logique épistémique et de la sémantique des jeux.</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7323,41 +7346,41 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1927 – 1993</t>
+          <t xml:space="preserve">1923 – 2010</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gajo PETROVIĆ</t>
+          <t xml:space="preserve">Mihailo MARKOVIĆ</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Gajo_Petrovi%C4%87" title=" Wikipedia (en)"&gt;Gajo PETROVIĆ&lt;/a&gt; est un philosophe croate, principal fondateur de l’école Praxis, le grand courant du marxisme humaniste yougoslave. Né à Karlovac, il étudie la philosophie à Zagreb, puis, en 1946-1948, en Union soviétique, où il découvre l’étouffement de la pensée sous Staline. Dès 1949, sa critique d’un dirigeant de la ligne officielle lui vaut d’être exclu du Parti communiste. Réintégré à l’université, il y enseigne la logique et la philosophie jusqu’à sa retraite.&lt;/p&gt; &lt;p&gt;Il fonde en 1964 avec d’autres philosophes de Zagreb la revue &lt;em&gt;Praxis&lt;/em&gt;, publiée jusqu’en 1974 et connue dans le monde entier, ainsi que l’école d’été de Korčula, qui réunit dans une île de l’Adriatique des penseurs de l’Est et de l’Ouest, d’&lt;a href="https://fr.wikipedia.org/wiki/Ernst_Bloch" title=" Wikipedia"&gt;Ernst Bloch&lt;/a&gt; à &lt;a href="https://fr.wikipedia.org/wiki/Herbert_Marcuse" title=" Wikipedia"&gt;Herbert Marcuse&lt;/a&gt; et Jürgen Habermas. Il préside aussi l’Association yougoslave de philosophie. Contre le marxisme dogmatique des partis, il revient aux écrits du jeune Marx : l’homme est un être de « praxis », c’est-à-dire d’activité libre et créatrice, qui se fait lui-même en transformant le monde.&lt;/p&gt; &lt;p&gt;Pour Petrović, la philosophie doit être une « critique impitoyable de tout ce qui existe », y compris du socialisme réel et de ses bureaucraties. En 1968, il soutient ouvertement les manifestations étudiantes, ce qui lui vaut une nouvelle exclusion du parti, et la revue est contrainte de cesser de paraître en 1974. Ses livres, comme &lt;em&gt;Marx au milieu du XXe siècle&lt;/em&gt; (1967), ont été traduits dans de nombreuses langues. Il meurt à Zagreb en 1993, à soixante-six ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mihailo_Markovi%C4%87" title=" Wikipedia (en)"&gt;Mihailo MARKOVIĆ&lt;/a&gt; est un philosophe serbe, l’une des figures majeures de l’école Praxis, puis un acteur controversé du nationalisme serbe. Né à Belgrade, il rejoint jeune le Parti communiste et combat dans la résistance des partisans pendant la Seconde Guerre mondiale. Il soutient deux thèses de doctorat, à Belgrade puis à Londres, où il étudie la logique auprès d’A. J. Ayer, et devient professeur à l’université de Belgrade.&lt;/p&gt; &lt;p&gt;Après la rupture entre Tito et Staline en 1948, il publie en 1952 la première grande critique de la philosophie stalinienne en Yougoslavie. Dans les années 1960, il devient l’un des principaux théoriciens de l’école Praxis, qui défend un marxisme humaniste inspiré des écrits du jeune Marx, centré sur la liberté créatrice de l’homme et la critique de l’aliénation, à l’Ouest comme à l’Est. Il collabore à la revue &lt;em&gt;Praxis&lt;/em&gt; et à l’école d’été de Korčula, où se rencontrent des penseurs marxistes du monde entier. Ses critiques de la bureaucratie lui valent d’être suspendu de l’université en 1975 avec sept collègues.&lt;/p&gt; &lt;p&gt;Son parcours prend ensuite un tour très différent : membre de l’Académie serbe des sciences et des arts, il est l’un des auteurs du Mémorandum de 1986, texte qui formule les revendications du nationalisme serbe, puis devient l’un des idéologues du parti de &lt;a href="https://fr.wikipedia.org/wiki/Slobodan_Milo%C5%A1evi%C4%87" title=" Wikipedia"&gt;Slobodan Milošević&lt;/a&gt;. Ce soutien, pendant les guerres de Yougoslavie, lui a été vivement reproché, notamment par ses anciens compagnons de l’école Praxis. Il meurt à Belgrade en 2010.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/petrovic-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/markovic-mini.webp</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Croate</t>
+          <t xml:space="preserve">Serbe</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -7367,7 +7390,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe croate, fondateur de la revue Praxis, penseur d’un marxisme humaniste et critique.</t>
+          <t xml:space="preserve">philosophe serbe de l’école Praxis, critique du stalinisme, devenu ensuite idéologue du nationalisme serbe.</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7381,56 +7404,51 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1">
-        <v>1936</v>
+        <v>1927</v>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026</t>
+          <t xml:space="preserve">1993</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936 – 2026</t>
+          <t xml:space="preserve">1927 – 1993</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ioanna KUÇURADI</t>
+          <t xml:space="preserve">Gajo PETROVIĆ</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C4%B0oanna_Ku%C3%A7uradi" title=" Wikipedia"&gt;Ioanna KUÇURADI&lt;/a&gt; est une philosophe turque d’origine grecque, l’une des grandes figures internationales de la philosophie des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_l%27homme" title=" Wikipedia"&gt;droits de l’homme&lt;/a&gt;. Née à Istanbul dans une famille de la communauté grecque, elle étudie la philosophie à l’université d’Istanbul, où elle soutient son doctorat en 1965. En 1968, elle fonde le département de philosophie de l’université Hacettepe, à Ankara, qu’elle dirige jusqu’en 2005.&lt;/p&gt; &lt;p&gt;Spécialiste de l’éthique, elle étudie la nature des valeurs et défend l’idée qu’une connaissance éthique est possible : on peut connaître, et pas seulement ressentir, la valeur de l’être humain et ce qu’exige le respect de sa dignité. Les droits de l’homme ne sont pas pour elle de simples conventions juridiques, mais des exigences éthiques qui découlent de cette valeur, et qui doivent guider les lois et les politiques. Elle insiste sur l’importance de l’éducation aux droits de l’homme et sur la responsabilité des philosophes dans la vie publique.&lt;/p&gt; &lt;p&gt;Elle crée à Hacettepe un centre de recherche sur la philosophie des droits de l’homme, préside en Turquie le Haut Conseil consultatif des droits de l’homme et occupe une chaire de philosophie de l’UNESCO. Présidente de la Société turque de philosophie, puis de la Fédération internationale des sociétés de philosophie de 1998 à 2003 et de l’Institut international de philosophie, elle a beaucoup œuvré au dialogue entre les philosophies du monde. Elle meurt à Istanbul le 2 octobre 2026, deux jours avant ses quatre-vingt-dix ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Gajo_Petrovi%C4%87" title=" Wikipedia (en)"&gt;Gajo PETROVIĆ&lt;/a&gt; est un philosophe croate, principal fondateur de l’école Praxis, le grand courant du marxisme humaniste yougoslave. Né à Karlovac, il étudie la philosophie à Zagreb, puis, en 1946-1948, en Union soviétique, où il découvre l’étouffement de la pensée sous Staline. Dès 1949, sa critique d’un dirigeant de la ligne officielle lui vaut d’être exclu du Parti communiste. Réintégré à l’université, il y enseigne la logique et la philosophie jusqu’à sa retraite.&lt;/p&gt; &lt;p&gt;Il fonde en 1964 avec d’autres philosophes de Zagreb la revue &lt;em&gt;Praxis&lt;/em&gt;, publiée jusqu’en 1974 et connue dans le monde entier, ainsi que l’école d’été de Korčula, qui réunit dans une île de l’Adriatique des penseurs de l’Est et de l’Ouest, d’&lt;a href="https://fr.wikipedia.org/wiki/Ernst_Bloch" title=" Wikipedia"&gt;Ernst Bloch&lt;/a&gt; à &lt;a href="https://fr.wikipedia.org/wiki/Herbert_Marcuse" title=" Wikipedia"&gt;Herbert Marcuse&lt;/a&gt; et Jürgen Habermas. Il préside aussi l’Association yougoslave de philosophie. Contre le marxisme dogmatique des partis, il revient aux écrits du jeune Marx : l’homme est un être de « praxis », c’est-à-dire d’activité libre et créatrice, qui se fait lui-même en transformant le monde.&lt;/p&gt; &lt;p&gt;Pour Petrović, la philosophie doit être une « critique impitoyable de tout ce qui existe », y compris du socialisme réel et de ses bureaucraties. En 1968, il soutient ouvertement les manifestations étudiantes, ce qui lui vaut une nouvelle exclusion du parti, et la revue est contrainte de cesser de paraître en 1974. Ses livres, comme &lt;em&gt;Marx au milieu du XXe siècle&lt;/em&gt; (1967), ont été traduits dans de nombreuses langues. Il meurt à Zagreb en 1993, à soixante-six ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kucuradi-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/petrovic-mini.webp</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turque</t>
+          <t xml:space="preserve">Croate</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; metaphysique</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Marxisme ; Humanisme</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe turque, penseuse des valeurs et de la philosophie des droits de l’homme.</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">philosophe croate, fondateur de la revue Praxis, penseur d’un marxisme humaniste et critique.</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7444,51 +7462,56 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1">
-        <v>1864</v>
+        <v>1936</v>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936</t>
+          <t xml:space="preserve">2026</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864 – 1936</t>
+          <t xml:space="preserve">1936 – 2026</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel de UNAMUNO</t>
+          <t xml:space="preserve">Ioanna KUÇURADI</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Miguel_de_Unamuno" title=" Wikipedia"&gt;Miguel de UNAMUNO&lt;/a&gt; est un écrivain et philosophe espagnol, figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9n%C3%A9ration_de_1898" title=" Wikipedia"&gt;génération de 1898&lt;/a&gt;, qui s’interroge sur l’âme de l’Espagne après la perte de ses dernières colonies. Né à Bilbao, professeur de grec puis recteur de l’université de Salamanque à partir de 1900, il écrit des romans, des poèmes, du théâtre et des essais. Ses critiques contre la monarchie et la dictature de Primo de Rivera lui valent d’être exilé en 1924 aux Canaries, puis il vit à Paris et à Hendaye jusqu’en 1930. Dans &lt;em&gt;Vie de Don Quichotte et de Sancho&lt;/em&gt; (1905), il fait du chevalier errant un héros de la foi contre le bon sens.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Sentiment_tragique_de_la_vie" title=" Wikipedia"&gt;&lt;em&gt;Le Sentiment tragique de la vie&lt;/em&gt;&lt;/a&gt; (1913), il part de « l’homme de chair et d’os », qui veut ne pas mourir. La raison lui dit que rien ne survit à la mort ; le cœur réclame l’immortalité. Unamuno refuse de trancher : la vie authentique consiste à vivre ce combat sans le résoudre, dans une foi qui doute. Lecteur passionné de Kierkegaard, il annonce l’existentialisme. Dans &lt;em&gt;L’Agonie du christianisme&lt;/em&gt; (1925), « agonie » est prise au sens grec de lutte. Dans son roman &lt;em&gt;Brouillard&lt;/em&gt; (1914), le héros vient discuter de son sort avec l’auteur lui-même.&lt;/p&gt; &lt;p&gt;Le 12 octobre 1936, au début de la guerre civile, il affronte publiquement dans l’université de Salamanque le général franquiste Millán Astray, qui vient de crier « Vive la mort ! », et lui oppose, selon le récit devenu célèbre : « Vous vaincrez, mais vous ne convaincrez pas. » Destitué et assigné à résidence, il meurt le 31 décembre 1936. Il reste l’une des grandes voix de la conscience européenne face au fanatisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C4%B0oanna_Ku%C3%A7uradi" title=" Wikipedia"&gt;Ioanna KUÇURADI&lt;/a&gt; est une philosophe turque d’origine grecque, l’une des grandes figures internationales de la philosophie des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_l%27homme" title=" Wikipedia"&gt;droits de l’homme&lt;/a&gt;. Née à Istanbul dans une famille de la communauté grecque, elle étudie la philosophie à l’université d’Istanbul, où elle soutient son doctorat en 1965. En 1968, elle fonde le département de philosophie de l’université Hacettepe, à Ankara, qu’elle dirige jusqu’en 2005.&lt;/p&gt; &lt;p&gt;Spécialiste de l’éthique, elle étudie la nature des valeurs et défend l’idée qu’une connaissance éthique est possible : on peut connaître, et pas seulement ressentir, la valeur de l’être humain et ce qu’exige le respect de sa dignité. Les droits de l’homme ne sont pas pour elle de simples conventions juridiques, mais des exigences éthiques qui découlent de cette valeur, et qui doivent guider les lois et les politiques. Elle insiste sur l’importance de l’éducation aux droits de l’homme et sur la responsabilité des philosophes dans la vie publique.&lt;/p&gt; &lt;p&gt;Elle crée à Hacettepe un centre de recherche sur la philosophie des droits de l’homme, préside en Turquie le Haut Conseil consultatif des droits de l’homme et occupe une chaire de philosophie de l’UNESCO. Présidente de la Société turque de philosophie, puis de la Fédération internationale des sociétés de philosophie de 1998 à 2003 et de l’Institut international de philosophie, elle a beaucoup œuvré au dialogue entre les philosophies du monde. Elle meurt à Istanbul le 2 octobre 2026, deux jours avant ses quatre-vingt-dix ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/unamuno-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kucuradi-mini.webp</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espagnole</t>
+          <t xml:space="preserve">Turque</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Existentialisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain et philosophe espagnol, auteur du Sentiment tragique de la vie, penseur de l’angoisse et de la foi.</t>
+          <t xml:space="preserve">philosophe turque, penseuse des valeurs et de la philosophie des droits de l’homme.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7497,61 +7520,56 @@
         </is>
       </c>
       <c r="P96">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1">
-        <v>1903</v>
+        <v>1864</v>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994</t>
+          <t xml:space="preserve">1936</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903 – 1994</t>
+          <t xml:space="preserve">1864 – 1936</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yeshayahou LEIBOWITZ</t>
+          <t xml:space="preserve">Miguel de UNAMUNO</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yeshayahou_Leibowitz" title=" Wikipedia"&gt;Yeshayahou LEIBOWITZ&lt;/a&gt; est un scientifique, philosophe et moraliste israélien, l’un des intellectuels les plus marquants et les plus controversés de son pays. Né à Riga dans une famille juive orthodoxe, il étudie la chimie et la philosophie à Berlin, puis la médecine à Bâle. Installé en 1934 en Palestine, il enseigne pendant près de soixante ans la chimie, la biochimie, la neurophysiologie et la philosophie à l’Université hébraïque de Jérusalem, et dirige l’&lt;a href="https://fr.wikipedia.org/wiki/Encyclop%C3%A9die_h%C3%A9bra%C3%AFque" title=" Wikipedia"&gt;Encyclopédie hébraïque&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Juif pratiquant rigoureux, il défend une conception austère de la foi. Le judaïsme n’est pas pour lui une sagesse, une morale ou une identité nationale, mais le service de Dieu par l’accomplissement des commandements, pour lui-même et sans rien attendre en retour : la religion n’est pas là pour satisfaire les besoins de l’homme. Il refuse donc d’attribuer une valeur religieuse à l’État, à la terre ou à l’histoire, et réclame la séparation de la religion et de l’État, qui selon lui corrompt la religion en la mettant au service de la politique.&lt;/p&gt; &lt;p&gt;Dès la guerre de 1967, il met en garde contre l’occupation des territoires palestiniens, qui détruirait selon lui la société israélienne elle-même, et appelle les soldats à refuser de servir dans les territoires. Ses critiques, parfois formulées en termes d’une extrême dureté, provoquent de vives polémiques. Lorsque le prix Israël lui est attribué, peu avant sa mort, le Premier ministre Yitzhak Rabin menace de boycotter la cérémonie, et Leibowitz renonce au prix. Il meurt à Jérusalem en 1994.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Miguel_de_Unamuno" title=" Wikipedia"&gt;Miguel de UNAMUNO&lt;/a&gt; est un écrivain et philosophe espagnol, figure majeure de la &lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9n%C3%A9ration_de_1898" title=" Wikipedia"&gt;génération de 1898&lt;/a&gt;, qui s’interroge sur l’âme de l’Espagne après la perte de ses dernières colonies. Né à Bilbao, professeur de grec puis recteur de l’université de Salamanque à partir de 1900, il écrit des romans, des poèmes, du théâtre et des essais. Ses critiques contre la monarchie et la dictature de Primo de Rivera lui valent d’être exilé en 1924 aux Canaries, puis il vit à Paris et à Hendaye jusqu’en 1930. Dans &lt;em&gt;Vie de Don Quichotte et de Sancho&lt;/em&gt; (1905), il fait du chevalier errant un héros de la foi contre le bon sens.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Sentiment_tragique_de_la_vie" title=" Wikipedia"&gt;&lt;em&gt;Le Sentiment tragique de la vie&lt;/em&gt;&lt;/a&gt; (1913), il part de « l’homme de chair et d’os », qui veut ne pas mourir. La raison lui dit que rien ne survit à la mort ; le cœur réclame l’immortalité. Unamuno refuse de trancher : la vie authentique consiste à vivre ce combat sans le résoudre, dans une foi qui doute. Lecteur passionné de Kierkegaard, il annonce l’existentialisme. Dans &lt;em&gt;L’Agonie du christianisme&lt;/em&gt; (1925), « agonie » est prise au sens grec de lutte. Dans son roman &lt;em&gt;Brouillard&lt;/em&gt; (1914), le héros vient discuter de son sort avec l’auteur lui-même.&lt;/p&gt; &lt;p&gt;Le 12 octobre 1936, au début de la guerre civile, il affronte publiquement dans l’université de Salamanque le général franquiste Millán Astray, qui vient de crier « Vive la mort ! », et lui oppose, selon le récit devenu célèbre : « Vous vaincrez, mais vous ne convaincrez pas. » Destitué et assigné à résidence, il meurt le 31 décembre 1936. Il reste l’une des grandes voix de la conscience européenne face au fanatisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/leibowitz-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/unamuno-mini.webp</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israélienne</t>
+          <t xml:space="preserve">Espagnole</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monothéisme</t>
+          <t xml:space="preserve">Existentialisme</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scientifique et philosophe israélien, penseur d’une foi sans illusions, critique de l’occupation.</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">écrivain et philosophe espagnol, auteur du Sentiment tragique de la vie, penseur de l’angoisse et de la foi.</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7560,56 +7578,61 @@
         </is>
       </c>
       <c r="P97">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1">
-        <v>1923</v>
+        <v>1903</v>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020</t>
+          <t xml:space="preserve">1994</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1923 – 2020</t>
+          <t xml:space="preserve">1903 – 1994</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eduardo LOURENÇO</t>
+          <t xml:space="preserve">Yeshayahou LEIBOWITZ</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eduardo_Louren%C3%A7o" title=" Wikipedia"&gt;Eduardo LOURENÇO&lt;/a&gt; est un essayiste, philosophe et critique portugais, l’un des grands intellectuels européens du XXe siècle. Né dans un village de la Beira, près de la frontière espagnole, il étudie l’histoire et la philosophie à l’université de Coimbra. Son premier livre, &lt;em&gt;Hétérodoxie&lt;/em&gt; (1949), revendique le droit de penser librement, contre les orthodoxies religieuses et politiques, dans le Portugal de la dictature de Salazar.&lt;/p&gt; &lt;p&gt;Il enseigne ensuite en Allemagne, à Hambourg et Heidelberg, puis au Brésil, avant de s’installer en France en 1960, à Grenoble puis à Nice, où il passe l’essentiel de sa carrière. De ce long exil, il observe son pays avec distance et tendresse. Dans &lt;em&gt;Le Labyrinthe de la saudade&lt;/em&gt; (1978), il analyse la « mythologie » que les Portugais se font d’eux-mêmes : un peuple qui, après avoir dominé un empire, oscille entre le sentiment d’être exceptionnel et celui d’être insignifiant, et se réfugie dans la &lt;a href="https://fr.wikipedia.org/wiki/Saudade" title=" Wikipedia"&gt;&lt;em&gt;saudade&lt;/em&gt;&lt;/a&gt;, cette nostalgie de ce qui n’est plus ou n’a jamais été.&lt;/p&gt; &lt;p&gt;Grand lecteur de Fernando Pessoa, dont il est l’un des meilleurs interprètes, et de toute la littérature portugaise depuis Camões, il réfléchit aussi à l’Europe, à la place de la culture dans un monde dominé par la technique, et au sens de la fin des empires coloniaux. Conseiller culturel à Rome, administrateur de la Fondation Gulbenkian à Lisbonne, il reçoit le prix Pessoa en 1996. Considéré comme un sage par ses compatriotes, il meurt à Lisbonne en 2020, à quatre-vingt-dix-sept ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yeshayahou_Leibowitz" title=" Wikipedia"&gt;Yeshayahou LEIBOWITZ&lt;/a&gt; est un scientifique, philosophe et moraliste israélien, l’un des intellectuels les plus marquants et les plus controversés de son pays. Né à Riga dans une famille juive orthodoxe, il étudie la chimie et la philosophie à Berlin, puis la médecine à Bâle. Installé en 1934 en Palestine, il enseigne pendant près de soixante ans la chimie, la biochimie, la neurophysiologie et la philosophie à l’Université hébraïque de Jérusalem, et dirige l’&lt;a href="https://fr.wikipedia.org/wiki/Encyclop%C3%A9die_h%C3%A9bra%C3%AFque" title=" Wikipedia"&gt;Encyclopédie hébraïque&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Juif pratiquant rigoureux, il défend une conception austère de la foi. Le judaïsme n’est pas pour lui une sagesse, une morale ou une identité nationale, mais le service de Dieu par l’accomplissement des commandements, pour lui-même et sans rien attendre en retour : la religion n’est pas là pour satisfaire les besoins de l’homme. Il refuse donc d’attribuer une valeur religieuse à l’État, à la terre ou à l’histoire, et réclame la séparation de la religion et de l’État, qui selon lui corrompt la religion en la mettant au service de la politique.&lt;/p&gt; &lt;p&gt;Dès la guerre de 1967, il met en garde contre l’occupation des territoires palestiniens, qui détruirait selon lui la société israélienne elle-même, et appelle les soldats à refuser de servir dans les territoires. Ses critiques, parfois formulées en termes d’une extrême dureté, provoquent de vives polémiques. Lorsque le prix Israël lui est attribué, peu avant sa mort, le Premier ministre Yitzhak Rabin menace de boycotter la cérémonie, et Leibowitz renonce au prix. Il meurt à Jérusalem en 1994.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/lourenco-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/leibowitz-mini.webp</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portugaise</t>
+          <t xml:space="preserve">Israélienne</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Existentialisme</t>
+          <t xml:space="preserve">Monothéisme</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">essayiste et philosophe portugais, penseur de l’identité portugaise et de la saudade.</t>
+          <t xml:space="preserve">scientifique et philosophe israélien, penseur d’une foi sans illusions, critique de l’occupation.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7623,51 +7646,51 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1">
-        <v>1883</v>
+        <v>1923</v>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">2020</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1883 – 1957</t>
+          <t xml:space="preserve">1923 – 2020</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Níkos KAZANTZÁKIS</t>
+          <t xml:space="preserve">Eduardo LOURENÇO</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%ADkos_Kazantz%C3%A1kis" title=" Wikipedia"&gt;Níkos KAZANTZÁKIS&lt;/a&gt; est un écrivain et penseur grec, l’un des grands auteurs européens du XXe siècle. Né à Héraklion, en Crète, alors encore sous domination ottomane, il étudie le droit à Athènes puis la philosophie à Paris, où il suit les cours d’&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson" title=" Wikipedia"&gt;Henri Bergson&lt;/a&gt;. Il traduit Nietzsche, Bergson et Dante en grec, voyage dans toute l’Europe, en Russie, au Japon et en Chine, et passe sa vie à chercher une réponse aux grandes questions, à travers le christianisme, le bouddhisme, le nationalisme puis le communisme, sans jamais s’arrêter à aucune.&lt;/p&gt; &lt;p&gt;Dans son court traité &lt;em&gt;Ascèse&lt;/em&gt; (1927), il expose sa philosophie : le monde est traversé par un élan vital qui lutte pour se libérer de la matière et s’élever, et l’homme doit collaborer à cet effort, sans espoir de récompense ni certitude de salut. « Je n’espère rien. Je ne crains rien. Je suis libre » : cette phrase, gravée sur sa tombe à Héraklion, résume l’idéal d’un homme qui accepte l’angoisse et le combat comme le cœur même de la vie.&lt;/p&gt; &lt;p&gt;Ses romans ont rendu cette pensée célèbre dans le monde entier : &lt;a href="https://fr.wikipedia.org/wiki/Alexis_Zorba" title=" Wikipedia"&gt;&lt;em&gt;Alexis Zorba&lt;/em&gt;&lt;/a&gt; (1946) oppose un intellectuel timide à un homme qui vit pleinement chaque instant, et &lt;em&gt;La Dernière Tentation du Christ&lt;/em&gt; (1955) montre un Christ déchiré entre l’esprit et la chair, ce qui lui vaut d’être condamné par les Églises orthodoxe et catholique. Il compose aussi une immense &lt;em&gt;Odyssée&lt;/em&gt; de 33 333 vers, qui prolonge le poème d’Homère. Il meurt en Allemagne en 1957, après avoir manqué de peu le prix Nobel de littérature.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eduardo_Louren%C3%A7o" title=" Wikipedia"&gt;Eduardo LOURENÇO&lt;/a&gt; est un essayiste, philosophe et critique portugais, l’un des grands intellectuels européens du XXe siècle. Né dans un village de la Beira, près de la frontière espagnole, il étudie l’histoire et la philosophie à l’université de Coimbra. Son premier livre, &lt;em&gt;Hétérodoxie&lt;/em&gt; (1949), revendique le droit de penser librement, contre les orthodoxies religieuses et politiques, dans le Portugal de la dictature de Salazar.&lt;/p&gt; &lt;p&gt;Il enseigne ensuite en Allemagne, à Hambourg et Heidelberg, puis au Brésil, avant de s’installer en France en 1960, à Grenoble puis à Nice, où il passe l’essentiel de sa carrière. De ce long exil, il observe son pays avec distance et tendresse. Dans &lt;em&gt;Le Labyrinthe de la saudade&lt;/em&gt; (1978), il analyse la « mythologie » que les Portugais se font d’eux-mêmes : un peuple qui, après avoir dominé un empire, oscille entre le sentiment d’être exceptionnel et celui d’être insignifiant, et se réfugie dans la &lt;a href="https://fr.wikipedia.org/wiki/Saudade" title=" Wikipedia"&gt;&lt;em&gt;saudade&lt;/em&gt;&lt;/a&gt;, cette nostalgie de ce qui n’est plus ou n’a jamais été.&lt;/p&gt; &lt;p&gt;Grand lecteur de Fernando Pessoa, dont il est l’un des meilleurs interprètes, et de toute la littérature portugaise depuis Camões, il réfléchit aussi à l’Europe, à la place de la culture dans un monde dominé par la technique, et au sens de la fin des empires coloniaux. Conseiller culturel à Rome, administrateur de la Fondation Gulbenkian à Lisbonne, il reçoit le prix Pessoa en 1996. Considéré comme un sage par ses compatriotes, il meurt à Lisbonne en 2020, à quatre-vingt-dix-sept ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kazantzakis-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lourenco-mini.webp</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grecque</t>
+          <t xml:space="preserve">Portugaise</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitalisme ; Mysticisme</t>
+          <t xml:space="preserve">Humanisme ; Existentialisme</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain et penseur grec, auteur d’Alexis Zorba et d’Ascèse, chercheur inquiet de la liberté et du sens.</t>
+          <t xml:space="preserve">essayiste et philosophe portugais, penseur de l’identité portugaise et de la saudade.</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7681,51 +7704,51 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1">
-        <v>1893</v>
+        <v>1883</v>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893 – 1970</t>
+          <t xml:space="preserve">1883 – 1957</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roman INGARDEN</t>
+          <t xml:space="preserve">Níkos KAZANTZÁKIS</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roman_Ingarden" title=" Wikipedia"&gt;Roman INGARDEN&lt;/a&gt; est un philosophe polonais, l’un des principaux représentants de la phénoménologie et le fondateur de l’esthétique phénoménologique. Né à Cracovie, il étudie à Göttingen auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Husserl" title=" Wikipedia"&gt;Edmund Husserl&lt;/a&gt;, sous la direction duquel il soutient en 1918 une thèse sur Bergson. Il y rencontre &lt;a href="https://fr.wikipedia.org/wiki/Edith_Stein" title=" Wikipedia"&gt;Edith Stein&lt;/a&gt;, avec qui il entretient pendant des années une correspondance et une amitié intellectuelle. Enseignant longtemps dans des lycées, il n’obtient une chaire à l’université de Lwów que dans les années 1930.&lt;/p&gt; &lt;p&gt;Fidèle à la méthode de Husserl, il refuse pourtant le tournant de son maître vers l’idéalisme, qui fait dépendre le monde de la conscience. Dans &lt;em&gt;La Controverse sur l’existence du monde&lt;/em&gt;, il défend une phénoménologie réaliste : le monde existe indépendamment de nous, et la philosophie doit décrire avec précision les différents modes d’être des choses. Il s’intéresse particulièrement aux objets « purement intentionnels », qui n’existent que par la conscience qui les vise.&lt;/p&gt; &lt;p&gt;L’œuvre d’art en est l’exemple : dans &lt;em&gt;L’Œuvre d’art littéraire&lt;/em&gt; (1931), il montre qu’un roman est composé de plusieurs couches, les sons des mots, leurs significations, les objets représentés et les aspects sous lesquels ils apparaissent. Il comporte aussi des « lieux d’indétermination » que le lecteur doit remplir par son imagination. Écarté de l’enseignement pendant plusieurs années par le régime communiste, qui lui reproche son « idéalisme », il continue d’écrire, notamment sur la responsabilité morale, qu’il enracine dans la structure même de l’être humain. Il meurt à Cracovie en 1970.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%ADkos_Kazantz%C3%A1kis" title=" Wikipedia"&gt;Níkos KAZANTZÁKIS&lt;/a&gt; est un écrivain et penseur grec, l’un des grands auteurs européens du XXe siècle. Né à Héraklion, en Crète, alors encore sous domination ottomane, il étudie le droit à Athènes puis la philosophie à Paris, où il suit les cours d’&lt;a href="https://fr.wikipedia.org/wiki/Henri_Bergson" title=" Wikipedia"&gt;Henri Bergson&lt;/a&gt;. Il traduit Nietzsche, Bergson et Dante en grec, voyage dans toute l’Europe, en Russie, au Japon et en Chine, et passe sa vie à chercher une réponse aux grandes questions, à travers le christianisme, le bouddhisme, le nationalisme puis le communisme, sans jamais s’arrêter à aucune.&lt;/p&gt; &lt;p&gt;Dans son court traité &lt;em&gt;Ascèse&lt;/em&gt; (1927), il expose sa philosophie : le monde est traversé par un élan vital qui lutte pour se libérer de la matière et s’élever, et l’homme doit collaborer à cet effort, sans espoir de récompense ni certitude de salut. « Je n’espère rien. Je ne crains rien. Je suis libre » : cette phrase, gravée sur sa tombe à Héraklion, résume l’idéal d’un homme qui accepte l’angoisse et le combat comme le cœur même de la vie.&lt;/p&gt; &lt;p&gt;Ses romans ont rendu cette pensée célèbre dans le monde entier : &lt;a href="https://fr.wikipedia.org/wiki/Alexis_Zorba" title=" Wikipedia"&gt;&lt;em&gt;Alexis Zorba&lt;/em&gt;&lt;/a&gt; (1946) oppose un intellectuel timide à un homme qui vit pleinement chaque instant, et &lt;em&gt;La Dernière Tentation du Christ&lt;/em&gt; (1955) montre un Christ déchiré entre l’esprit et la chair, ce qui lui vaut d’être condamné par les Églises orthodoxe et catholique. Il compose aussi une immense &lt;em&gt;Odyssée&lt;/em&gt; de 33 333 vers, qui prolonge le poème d’Homère. Il meurt en Allemagne en 1957, après avoir manqué de peu le prix Nobel de littérature.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ingarden-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kazantzakis-mini.webp</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polonaise</t>
+          <t xml:space="preserve">Grecque</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; metaphysique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie ; Réalisme ; Ontologie</t>
+          <t xml:space="preserve">Vitalisme ; Mysticisme</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe polonais, élève de Husserl, phénoménologue réaliste et grand théoricien de l’œuvre d’art.</t>
+          <t xml:space="preserve">écrivain et penseur grec, auteur d’Alexis Zorba et d’Ascèse, chercheur inquiet de la liberté et du sens.</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7739,51 +7762,51 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1">
-        <v>1907</v>
+        <v>1893</v>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1977</t>
+          <t xml:space="preserve">1893 – 1970</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan PATOČKA</t>
+          <t xml:space="preserve">Roman INGARDEN</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Pato%C4%8Dka" title=" Wikipedia"&gt;Jan PATOČKA&lt;/a&gt; est le plus grand philosophe tchèque du XXe siècle. Né à Turnov, il étudie à Prague, à Paris et à Fribourg-en-Brisgau, où il est l’un des derniers élèves d’Edmund Husserl et suit aussi les cours de Heidegger. Il consacre sa thèse d’habilitation au « monde naturel », le monde de l’expérience quotidienne, que les sciences tendent à faire oublier. Mais l’occupation nazie, puis le régime communiste, l’écartent presque constamment de l’université, et il doit enseigner dans des séminaires privés, chez lui ou chez ses élèves.&lt;/p&gt; &lt;p&gt;Pour Patočka, l’Europe est née d’une idée grecque : le « soin de l’âme », formulé par &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt;. Il s’agit de vivre dans la vérité et de s’interroger sans cesse sur le sens de son existence, plutôt que de se contenter d’une vie confortable et sans questions. Dans ses &lt;em&gt;Essais hérétiques sur la philosophie de l’histoire&lt;/em&gt; (1975), il décrit l’histoire comme ce moment où l’homme ose vivre sans certitude, dans une existence « ébranlée », et propose la « solidarité des ébranlés » : ceux qui ont compris la fragilité du sens peuvent s’unir contre la violence et le mensonge.&lt;/p&gt; &lt;p&gt;En 1977, il devient l’un des trois porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, qui réclame au régime le respect des droits de l’homme. Interrogé pendant des heures par la police, il meurt d’une hémorragie cérébrale le 13 mars 1977. Grand spécialiste de Comenius, dont il a édité les œuvres, il a formé dans la clandestinité toute une génération. Ses élèves et ses proches, comme Václav Havel, ont fait vivre sa pensée.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roman_Ingarden" title=" Wikipedia"&gt;Roman INGARDEN&lt;/a&gt; est un philosophe polonais, l’un des principaux représentants de la phénoménologie et le fondateur de l’esthétique phénoménologique. Né à Cracovie, il étudie à Göttingen auprès d’&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Husserl" title=" Wikipedia"&gt;Edmund Husserl&lt;/a&gt;, sous la direction duquel il soutient en 1918 une thèse sur Bergson. Il y rencontre &lt;a href="https://fr.wikipedia.org/wiki/Edith_Stein" title=" Wikipedia"&gt;Edith Stein&lt;/a&gt;, avec qui il entretient pendant des années une correspondance et une amitié intellectuelle. Enseignant longtemps dans des lycées, il n’obtient une chaire à l’université de Lwów que dans les années 1930.&lt;/p&gt; &lt;p&gt;Fidèle à la méthode de Husserl, il refuse pourtant le tournant de son maître vers l’idéalisme, qui fait dépendre le monde de la conscience. Dans &lt;em&gt;La Controverse sur l’existence du monde&lt;/em&gt;, il défend une phénoménologie réaliste : le monde existe indépendamment de nous, et la philosophie doit décrire avec précision les différents modes d’être des choses. Il s’intéresse particulièrement aux objets « purement intentionnels », qui n’existent que par la conscience qui les vise.&lt;/p&gt; &lt;p&gt;L’œuvre d’art en est l’exemple : dans &lt;em&gt;L’Œuvre d’art littéraire&lt;/em&gt; (1931), il montre qu’un roman est composé de plusieurs couches, les sons des mots, leurs significations, les objets représentés et les aspects sous lesquels ils apparaissent. Il comporte aussi des « lieux d’indétermination » que le lecteur doit remplir par son imagination. Écarté de l’enseignement pendant plusieurs années par le régime communiste, qui lui reproche son « idéalisme », il continue d’écrire, notamment sur la responsabilité morale, qu’il enracine dans la structure même de l’être humain. Il meurt à Cracovie en 1970.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/patocka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ingarden-mini.webp</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tchèque</t>
+          <t xml:space="preserve">Polonaise</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; politique</t>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie</t>
+          <t xml:space="preserve">Phénoménologie ; Réalisme ; Ontologie</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe tchèque, phénoménologue, penseur du « soin de l’âme » et porte-parole de la Charte 77.</t>
+          <t xml:space="preserve">philosophe polonais, élève de Husserl, phénoménologue réaliste et grand théoricien de l’œuvre d’art.</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7801,47 +7824,47 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986</t>
+          <t xml:space="preserve">1977</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907 – 1986</t>
+          <t xml:space="preserve">1907 – 1977</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mircea ELIADE</t>
+          <t xml:space="preserve">Jan PATOČKA</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mircea_Eliade" title=" Wikipedia"&gt;Mircea ELIADE&lt;/a&gt; est un historien des religions, philosophe et romancier roumain, l’un des fondateurs de l’histoire moderne des religions. Né à Bucarest, il part à vingt et un ans pour l’Inde, où il étudie le sanskrit et le yoga à Calcutta, puis séjourne dans un ermitage de l’Himalaya. Revenu en Roumanie, il devient une figure brillante de la jeune génération. Mais dans les années 1930, il soutient publiquement la &lt;a href="https://fr.wikipedia.org/wiki/Garde_de_fer" title=" Wikipedia"&gt;Garde de fer&lt;/a&gt;, mouvement fasciste et antisémite, un engagement qui reste la part sombre de sa biographie.&lt;/p&gt; &lt;p&gt;Après la guerre, il s’installe à Paris, puis enseigne à partir de 1957 à l’université de Chicago. Dans &lt;em&gt;Le Sacré et le Profane&lt;/em&gt; (1957), il montre que l’homme religieux vit dans un monde où certains lieux, certains temps et certains objets sont chargés d’une puissance qui les distingue de l’ordinaire : une « hiérophanie », manifestation du &lt;a href="https://fr.wikipedia.org/wiki/Sacr%C3%A9" title=" Wikipedia"&gt;sacré&lt;/a&gt;. Le temple, la fête ou le rite rejoignent le « centre du monde » et le temps des origines.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Mythe de l’éternel retour&lt;/em&gt; (1949), il explique que les sociétés traditionnelles cherchent à abolir le temps historique en répétant sans cesse les gestes exemplaires des dieux et des ancêtres, alors que le monde moderne vit dans une histoire irréversible, source d’angoisse. Il voit dans les mythes, les symboles et les rêves une manière universelle de donner sens au monde. Il consacre aussi un grand livre au &lt;a href="https://fr.wikipedia.org/wiki/Yoga" title=" Wikipedia"&gt;yoga&lt;/a&gt;, fruit de son séjour en Inde. Romancier, il écrit enfin une grande &lt;em&gt;Histoire des croyances et des idées religieuses&lt;/em&gt;. Il meurt à Chicago en 1986.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Pato%C4%8Dka" title=" Wikipedia"&gt;Jan PATOČKA&lt;/a&gt; est le plus grand philosophe tchèque du XXe siècle. Né à Turnov, il étudie à Prague, à Paris et à Fribourg-en-Brisgau, où il est l’un des derniers élèves d’Edmund Husserl et suit aussi les cours de Heidegger. Il consacre sa thèse d’habilitation au « monde naturel », le monde de l’expérience quotidienne, que les sciences tendent à faire oublier. Mais l’occupation nazie, puis le régime communiste, l’écartent presque constamment de l’université, et il doit enseigner dans des séminaires privés, chez lui ou chez ses élèves.&lt;/p&gt; &lt;p&gt;Pour Patočka, l’Europe est née d’une idée grecque : le « soin de l’âme », formulé par &lt;a href="https://fr.wikipedia.org/wiki/Platon" title=" Wikipedia"&gt;Platon&lt;/a&gt;. Il s’agit de vivre dans la vérité et de s’interroger sans cesse sur le sens de son existence, plutôt que de se contenter d’une vie confortable et sans questions. Dans ses &lt;em&gt;Essais hérétiques sur la philosophie de l’histoire&lt;/em&gt; (1975), il décrit l’histoire comme ce moment où l’homme ose vivre sans certitude, dans une existence « ébranlée », et propose la « solidarité des ébranlés » : ceux qui ont compris la fragilité du sens peuvent s’unir contre la violence et le mensonge.&lt;/p&gt; &lt;p&gt;En 1977, il devient l’un des trois porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, qui réclame au régime le respect des droits de l’homme. Interrogé pendant des heures par la police, il meurt d’une hémorragie cérébrale le 13 mars 1977. Grand spécialiste de Comenius, dont il a édité les œuvres, il a formé dans la clandestinité toute une génération. Ses élèves et ses proches, comme Václav Havel, ont fait vivre sa pensée.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/eliade-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/patocka-mini.webp</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roumaine</t>
+          <t xml:space="preserve">Tchèque</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">metaphysique ; politique</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herméneutique ; Chamanisme</t>
+          <t xml:space="preserve">Phénoménologie</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien des religions roumain, penseur du sacré, du mythe et de l’éternel retour.</t>
+          <t xml:space="preserve">philosophe tchèque, phénoménologue, penseur du « soin de l’âme » et porte-parole de la Charte 77.</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7855,51 +7878,51 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1">
-        <v>1927</v>
+        <v>1907</v>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">1986</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1927 – 2009</t>
+          <t xml:space="preserve">1907 – 1986</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leszek KOŁAKOWSKI</t>
+          <t xml:space="preserve">Mircea ELIADE</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leszek_Ko%C5%82akowski" title=" Wikipedia"&gt;Leszek KOŁAKOWSKI&lt;/a&gt; est un philosophe et historien des idées polonais. Né à Radom, il adhère jeune au Parti communiste et devient, au début des années 1950, un philosophe marxiste en vue, auteur d’une thèse sur &lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza" title=" Wikipedia"&gt;Spinoza&lt;/a&gt;. Mais après la mort de Staline, il dénonce le dogmatisme du parti et devient l’une des voix du « révisionnisme » : il défend un marxisme humaniste, attaché à la liberté de pensée. Professeur à l’université de Varsovie, il est exclu du parti en 1966, puis chassé de son poste en 1968.&lt;/p&gt; &lt;p&gt;Il s’exile alors en Occident et enseigne à Oxford, où il passe le reste de sa vie. Son œuvre majeure, &lt;em&gt;Les Principaux Courants du marxisme&lt;/em&gt; (1976-1978), retrace en trois volumes l’histoire de cette pensée, de ses origines à son déclin. Il y soutient que le stalinisme n’était pas une trahison du marxisme mais l’une de ses conséquences possibles : la promesse d’une humanité parfaitement unifiée et réconciliée conduit, quand on veut la réaliser par la force, à la tyrannie.&lt;/p&gt; &lt;p&gt;Penseur de la religion, il s’intéresse aussi aux mystiques et aux « chrétiens sans Église » du XVIIe siècle, et défend l’idée que les questions religieuses, sur le mal, la mort ou le sens, ne disparaissent pas avec la modernité. Il soutient le syndicat &lt;a href="https://fr.wikipedia.org/wiki/Solidarno%C5%9B%C4%87" title=" Wikipedia"&gt;Solidarność&lt;/a&gt; dans les années 1980. Esprit ironique et sceptique, il se méfie de toutes les promesses de salut politique. Il reçoit en 2003 le prix Kluge, l’une des plus hautes distinctions en sciences humaines. Il meurt à Oxford en 2009, à quatre-vingt-un ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mircea_Eliade" title=" Wikipedia"&gt;Mircea ELIADE&lt;/a&gt; est un historien des religions, philosophe et romancier roumain, l’un des fondateurs de l’histoire moderne des religions. Né à Bucarest, il part à vingt et un ans pour l’Inde, où il étudie le sanskrit et le yoga à Calcutta, puis séjourne dans un ermitage de l’Himalaya. Revenu en Roumanie, il devient une figure brillante de la jeune génération. Mais dans les années 1930, il soutient publiquement la &lt;a href="https://fr.wikipedia.org/wiki/Garde_de_fer" title=" Wikipedia"&gt;Garde de fer&lt;/a&gt;, mouvement fasciste et antisémite, un engagement qui reste la part sombre de sa biographie.&lt;/p&gt; &lt;p&gt;Après la guerre, il s’installe à Paris, puis enseigne à partir de 1957 à l’université de Chicago. Dans &lt;em&gt;Le Sacré et le Profane&lt;/em&gt; (1957), il montre que l’homme religieux vit dans un monde où certains lieux, certains temps et certains objets sont chargés d’une puissance qui les distingue de l’ordinaire : une « hiérophanie », manifestation du &lt;a href="https://fr.wikipedia.org/wiki/Sacr%C3%A9" title=" Wikipedia"&gt;sacré&lt;/a&gt;. Le temple, la fête ou le rite rejoignent le « centre du monde » et le temps des origines.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Mythe de l’éternel retour&lt;/em&gt; (1949), il explique que les sociétés traditionnelles cherchent à abolir le temps historique en répétant sans cesse les gestes exemplaires des dieux et des ancêtres, alors que le monde moderne vit dans une histoire irréversible, source d’angoisse. Il voit dans les mythes, les symboles et les rêves une manière universelle de donner sens au monde. Il consacre aussi un grand livre au &lt;a href="https://fr.wikipedia.org/wiki/Yoga" title=" Wikipedia"&gt;yoga&lt;/a&gt;, fruit de son séjour en Inde. Romancier, il écrit enfin une grande &lt;em&gt;Histoire des croyances et des idées religieuses&lt;/em&gt;. Il meurt à Chicago en 1986.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kolakowski-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eliade-mini.webp</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polonaise</t>
+          <t xml:space="preserve">Roumaine</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; spiritualite</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Herméneutique ; Chamanisme</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe polonais, marxiste devenu critique du communisme, auteur des Principaux courants du marxisme.</t>
+          <t xml:space="preserve">historien des religions roumain, penseur du sacré, du mythe et de l’éternel retour.</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7913,51 +7936,51 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1">
-        <v>1936</v>
+        <v>1927</v>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1936 – 2011</t>
+          <t xml:space="preserve">1927 – 2009</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav HAVEL</t>
+          <t xml:space="preserve">Leszek KOŁAKOWSKI</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A1clav_Havel" title=" Wikipedia"&gt;Václav HAVEL&lt;/a&gt; est un dramaturge, essayiste et homme d’État tchèque, l’une des grandes figures de la dissidence contre le communisme. Né à Prague dans une famille bourgeoise, il est écarté des études supérieures par le régime à cause de son origine. Il travaille au théâtre, où ses pièces absurdes et satiriques, comme &lt;em&gt;La Fête en plein air&lt;/em&gt; (1963), se moquent du langage creux de la bureaucratie. Après l’écrasement du &lt;a href="https://fr.wikipedia.org/wiki/Printemps_de_Prague" title=" Wikipedia"&gt;Printemps de Prague&lt;/a&gt; en 1968, ses œuvres sont interdites.&lt;/p&gt; &lt;p&gt;En 1977, il est l’un des fondateurs et porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, avec Jan Patočka, dont il se veut l’héritier. Dans &lt;em&gt;Le Pouvoir des sans-pouvoir&lt;/em&gt; (1978), il prend l’exemple d’un marchand de légumes qui place dans sa vitrine l’affiche « Prolétaires de tous les pays, unissez-vous ! » sans y croire, simplement pour être tranquille. Le régime ne tient que grâce à ces petits mensonges consentis par chacun. Refuser d’y participer, « vivre dans la vérité », est donc un acte politique : c’est le pouvoir de ceux qui n’en ont pas.&lt;/p&gt; &lt;p&gt;Emprisonné à plusieurs reprises, au total près de cinq ans, il écrit à sa femme des lettres publiées sous le titre &lt;em&gt;Lettres à Olga&lt;/em&gt;, méditation sur la responsabilité et l’espérance. Il devient en 1989 le chef de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_de_Velours" title=" Wikipedia"&gt;révolution de Velours&lt;/a&gt;, qui renverse pacifiquement le régime. Il est élu président de la Tchécoslovaquie, puis de la République tchèque jusqu’en 2003, en défendant une politique fondée sur la conscience et la responsabilité morale. Il meurt en 2011, à soixante-quinze ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leszek_Ko%C5%82akowski" title=" Wikipedia"&gt;Leszek KOŁAKOWSKI&lt;/a&gt; est un philosophe et historien des idées polonais. Né à Radom, il adhère jeune au Parti communiste et devient, au début des années 1950, un philosophe marxiste en vue, auteur d’une thèse sur &lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza" title=" Wikipedia"&gt;Spinoza&lt;/a&gt;. Mais après la mort de Staline, il dénonce le dogmatisme du parti et devient l’une des voix du « révisionnisme » : il défend un marxisme humaniste, attaché à la liberté de pensée. Professeur à l’université de Varsovie, il est exclu du parti en 1966, puis chassé de son poste en 1968.&lt;/p&gt; &lt;p&gt;Il s’exile alors en Occident et enseigne à Oxford, où il passe le reste de sa vie. Son œuvre majeure, &lt;em&gt;Les Principaux Courants du marxisme&lt;/em&gt; (1976-1978), retrace en trois volumes l’histoire de cette pensée, de ses origines à son déclin. Il y soutient que le stalinisme n’était pas une trahison du marxisme mais l’une de ses conséquences possibles : la promesse d’une humanité parfaitement unifiée et réconciliée conduit, quand on veut la réaliser par la force, à la tyrannie.&lt;/p&gt; &lt;p&gt;Penseur de la religion, il s’intéresse aussi aux mystiques et aux « chrétiens sans Église » du XVIIe siècle, et défend l’idée que les questions religieuses, sur le mal, la mort ou le sens, ne disparaissent pas avec la modernité. Il soutient le syndicat &lt;a href="https://fr.wikipedia.org/wiki/Solidarno%C5%9B%C4%87" title=" Wikipedia"&gt;Solidarność&lt;/a&gt; dans les années 1980. Esprit ironique et sceptique, il se méfie de toutes les promesses de salut politique. Il reçoit en 2003 le prix Kluge, l’une des plus hautes distinctions en sciences humaines. Il meurt à Oxford en 2009, à quatre-vingt-un ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/havel-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kolakowski-mini.webp</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tchèque</t>
+          <t xml:space="preserve">Polonaise</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">politique ; spiritualite</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Existentialisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dramaturge, dissident et président tchèque, penseur de la « vie dans la vérité » face au totalitarisme.</t>
+          <t xml:space="preserve">philosophe polonais, marxiste devenu critique du communisme, auteur des Principaux courants du marxisme.</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7971,51 +7994,51 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1">
-        <v>1866</v>
+        <v>1936</v>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952</t>
+          <t xml:space="preserve">2011</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866 – 1952</t>
+          <t xml:space="preserve">1936 – 2011</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Benedetto CROCE</t>
+          <t xml:space="preserve">Václav HAVEL</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Benedetto_Croce" title=" Wikipedia"&gt;Benedetto CROCE&lt;/a&gt; est un philosophe, historien et homme politique italien, la grande figure intellectuelle de l’Italie de la première moitié du XXe siècle. Né dans les Abruzzes dans une famille aisée, il perd ses parents et sa sœur dans un tremblement de terre en 1883, dont il réchappe lui-même blessé. Installé à Naples, il fonde en 1903 la revue &lt;em&gt;La Critica&lt;/em&gt;, qu’il dirige pendant plus de quarante ans, et développe une « philosophie de l’esprit » héritière de Hegel et de Vico.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Esthétique&lt;/em&gt; (1902), il définit l’art comme « intuition-expression » : l’artiste ne copie pas la réalité, il donne forme à une intuition singulière, et l’œuvre n’existe vraiment que dans cette expression. L’art est ainsi une forme de connaissance à part entière, distincte de la connaissance logique. Pour Croce, toute histoire est « histoire contemporaine », parce qu’elle répond aux questions du présent, et l’histoire humaine est au fond l’histoire de la liberté qui se conquiert.&lt;/p&gt; &lt;p&gt;D’abord ministre de l’Instruction publique, il rompt avec le &lt;a href="https://fr.wikipedia.org/wiki/Fascisme" title=" Wikipedia"&gt;fascisme&lt;/a&gt; et rédige en 1925 le &lt;em&gt;Manifeste des intellectuels antifascistes&lt;/em&gt;, en réponse à celui de Giovanni Gentile. Pendant tout le régime de Mussolini, il reste une voix libre, tolérée mais surveillée. Après la chute du fascisme, il refonde le Parti libéral italien et devient sénateur de la République. Il meurt à Naples en 1952. Son influence a été immense en Italie, jusque chez ses adversaires comme Antonio Gramsci. Sa longue amitié avec &lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile" title=" Wikipedia"&gt;Giovanni Gentile&lt;/a&gt;, son ancien collaborateur, s’était brisée sur la question du fascisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A1clav_Havel" title=" Wikipedia"&gt;Václav HAVEL&lt;/a&gt; est un dramaturge, essayiste et homme d’État tchèque, l’une des grandes figures de la dissidence contre le communisme. Né à Prague dans une famille bourgeoise, il est écarté des études supérieures par le régime à cause de son origine. Il travaille au théâtre, où ses pièces absurdes et satiriques, comme &lt;em&gt;La Fête en plein air&lt;/em&gt; (1963), se moquent du langage creux de la bureaucratie. Après l’écrasement du &lt;a href="https://fr.wikipedia.org/wiki/Printemps_de_Prague" title=" Wikipedia"&gt;Printemps de Prague&lt;/a&gt; en 1968, ses œuvres sont interdites.&lt;/p&gt; &lt;p&gt;En 1977, il est l’un des fondateurs et porte-parole de la &lt;a href="https://fr.wikipedia.org/wiki/Charte_77" title=" Wikipedia"&gt;Charte 77&lt;/a&gt;, avec Jan Patočka, dont il se veut l’héritier. Dans &lt;em&gt;Le Pouvoir des sans-pouvoir&lt;/em&gt; (1978), il prend l’exemple d’un marchand de légumes qui place dans sa vitrine l’affiche « Prolétaires de tous les pays, unissez-vous ! » sans y croire, simplement pour être tranquille. Le régime ne tient que grâce à ces petits mensonges consentis par chacun. Refuser d’y participer, « vivre dans la vérité », est donc un acte politique : c’est le pouvoir de ceux qui n’en ont pas.&lt;/p&gt; &lt;p&gt;Emprisonné à plusieurs reprises, au total près de cinq ans, il écrit à sa femme des lettres publiées sous le titre &lt;em&gt;Lettres à Olga&lt;/em&gt;, méditation sur la responsabilité et l’espérance. Il devient en 1989 le chef de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_de_Velours" title=" Wikipedia"&gt;révolution de Velours&lt;/a&gt;, qui renverse pacifiquement le régime. Il est élu président de la Tchécoslovaquie, puis de la République tchèque jusqu’en 2003, en défendant une politique fondée sur la conscience et la responsabilité morale. Il meurt en 2011, à soixante-quinze ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/croce-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/havel-mini.webp</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Italienne</t>
+          <t xml:space="preserve">Tchèque</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idéalisme ; Libéralisme</t>
+          <t xml:space="preserve">Humanisme ; Existentialisme</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe italien, penseur de l’esthétique comme intuition et de l’histoire comme histoire de la liberté.</t>
+          <t xml:space="preserve">dramaturge, dissident et président tchèque, penseur de la « vie dans la vérité » face au totalitarisme.</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8029,51 +8052,51 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1">
-        <v>1900</v>
+        <v>1866</v>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976</t>
+          <t xml:space="preserve">1952</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900 – 1976</t>
+          <t xml:space="preserve">1866 – 1952</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilbert RYLE</t>
+          <t xml:space="preserve">Benedetto CROCE</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_Ryle" title=" Wikipedia"&gt;Gilbert RYLE&lt;/a&gt; est un philosophe britannique, l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_du_langage_ordinaire" title=" Wikipedia"&gt;philosophie du langage ordinaire&lt;/a&gt; qui domine Oxford au milieu du XXe siècle. Né à Brighton, il étudie et enseigne toute sa vie à Oxford, à part la Seconde Guerre mondiale, qu’il passe dans le renseignement. Il dirige pendant près de vingt-cinq ans la grande revue philosophique &lt;em&gt;Mind&lt;/em&gt; et forme toute une génération de philosophes.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;La Notion d’esprit&lt;/em&gt; (1949) s’attaque à ce qu’il appelle avec ironie le « mythe de Descartes », ou le « dogme du fantôme dans la machine » : l’idée que l’être humain serait composé d’un corps mécanique et d’un esprit invisible qui le piloterait de l’intérieur. Selon Ryle, cette conception repose sur une « erreur de catégorie ». C’est comme un visiteur qui, après avoir vu les collèges, les bibliothèques et les laboratoires d’Oxford, demanderait : « Mais où est l’université ? » L’université n’est pas un bâtiment de plus, c’est la manière dont tout cela est organisé.&lt;/p&gt; &lt;p&gt;De même, l’esprit n’est pas une chose cachée derrière nos actes : dire de quelqu’un qu’il est intelligent, c’est dire comment il agit et comment il agirait dans diverses situations. Ryle distingue aussi « savoir que », connaître des faits, et « savoir comment », posséder un savoir-faire. Ses analyses ont profondément influencé la philosophie de l’esprit, même si beaucoup jugent aujourd’hui son approche trop proche du béhaviorisme. Il a aussi consacré un livre à Platon, &lt;em&gt;Plato’s Progress&lt;/em&gt; (1966). Il meurt en 1976.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Benedetto_Croce" title=" Wikipedia"&gt;Benedetto CROCE&lt;/a&gt; est un philosophe, historien et homme politique italien, la grande figure intellectuelle de l’Italie de la première moitié du XXe siècle. Né dans les Abruzzes dans une famille aisée, il perd ses parents et sa sœur dans un tremblement de terre en 1883, dont il réchappe lui-même blessé. Installé à Naples, il fonde en 1903 la revue &lt;em&gt;La Critica&lt;/em&gt;, qu’il dirige pendant plus de quarante ans, et développe une « philosophie de l’esprit » héritière de Hegel et de Vico.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Esthétique&lt;/em&gt; (1902), il définit l’art comme « intuition-expression » : l’artiste ne copie pas la réalité, il donne forme à une intuition singulière, et l’œuvre n’existe vraiment que dans cette expression. L’art est ainsi une forme de connaissance à part entière, distincte de la connaissance logique. Pour Croce, toute histoire est « histoire contemporaine », parce qu’elle répond aux questions du présent, et l’histoire humaine est au fond l’histoire de la liberté qui se conquiert.&lt;/p&gt; &lt;p&gt;D’abord ministre de l’Instruction publique, il rompt avec le &lt;a href="https://fr.wikipedia.org/wiki/Fascisme" title=" Wikipedia"&gt;fascisme&lt;/a&gt; et rédige en 1925 le &lt;em&gt;Manifeste des intellectuels antifascistes&lt;/em&gt;, en réponse à celui de Giovanni Gentile. Pendant tout le régime de Mussolini, il reste une voix libre, tolérée mais surveillée. Après la chute du fascisme, il refonde le Parti libéral italien et devient sénateur de la République. Il meurt à Naples en 1952. Son influence a été immense en Italie, jusque chez ses adversaires comme Antonio Gramsci. Sa longue amitié avec &lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Gentile" title=" Wikipedia"&gt;Giovanni Gentile&lt;/a&gt;, son ancien collaborateur, s’était brisée sur la question du fascisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ryle-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/croce-mini.webp</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Italienne</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">langage ; epistemologie</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique ; Béhaviorisme</t>
+          <t xml:space="preserve">Idéalisme ; Libéralisme</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe britannique d’Oxford, critique du « fantôme dans la machine » cartésien.</t>
+          <t xml:space="preserve">philosophe italien, penseur de l’esthétique comme intuition et de l’histoire comme histoire de la liberté.</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8087,31 +8110,31 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1">
-        <v>1919</v>
+        <v>1900</v>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">1976</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919 – 2006</t>
+          <t xml:space="preserve">1900 – 1976</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter STRAWSON</t>
+          <t xml:space="preserve">Gilbert RYLE</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Peter_Frederick_Strawson" title=" Wikipedia"&gt;Peter STRAWSON&lt;/a&gt; est un philosophe britannique de l’école d’Oxford, qui a renouvelé la métaphysique au sein de la philosophie analytique. Né à Londres, il étudie à Oxford, où il enseigne ensuite pendant toute sa carrière, jusqu’à occuper la chaire de métaphysique. Il se fait connaître en 1950 par un article célèbre, « De l’acte de référence », où il critique la théorie des descriptions de &lt;a href="https://fr.wikipedia.org/wiki/Bertrand_Russell" title=" Wikipedia"&gt;Bertrand Russell&lt;/a&gt;. Il est anobli en 1977 et devient Sir Peter Strawson.&lt;/p&gt; &lt;p&gt;Pour Russell, la phrase « L’actuel roi de France est chauve » est simplement fausse, puisqu’il n’y a pas de roi de France. Strawson répond que ce ne sont pas les phrases mais les personnes qui, en les utilisant, font référence ou affirment quelque chose : ici, la question de la vérité ne se pose même pas, car la phrase présuppose l’existence d’un roi. Il défend ainsi une analyse du langage tel qu’on l’utilise réellement, contre la seule logique formelle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Individus&lt;/em&gt; (1959), il propose une « métaphysique descriptive » : au lieu d’inventer une image nouvelle du monde, elle décrit la structure de pensée que nous partageons tous, où les corps et les personnes sont les éléments de base. Dans &lt;em&gt;Les Limites du sens&lt;/em&gt; (1966), il relit &lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant" title=" Wikipedia"&gt;Kant&lt;/a&gt; dans cet esprit. Dans « Liberté et ressentiment » (1962), il montre que nos réactions morales, comme la gratitude ou l’indignation, font partie de notre nature et ne dépendent pas de la question du déterminisme. Il meurt à Londres en 2006 ; son fils Galen Strawson est lui aussi philosophe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_Ryle" title=" Wikipedia"&gt;Gilbert RYLE&lt;/a&gt; est un philosophe britannique, l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_du_langage_ordinaire" title=" Wikipedia"&gt;philosophie du langage ordinaire&lt;/a&gt; qui domine Oxford au milieu du XXe siècle. Né à Brighton, il étudie et enseigne toute sa vie à Oxford, à part la Seconde Guerre mondiale, qu’il passe dans le renseignement. Il dirige pendant près de vingt-cinq ans la grande revue philosophique &lt;em&gt;Mind&lt;/em&gt; et forme toute une génération de philosophes.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;La Notion d’esprit&lt;/em&gt; (1949) s’attaque à ce qu’il appelle avec ironie le « mythe de Descartes », ou le « dogme du fantôme dans la machine » : l’idée que l’être humain serait composé d’un corps mécanique et d’un esprit invisible qui le piloterait de l’intérieur. Selon Ryle, cette conception repose sur une « erreur de catégorie ». C’est comme un visiteur qui, après avoir vu les collèges, les bibliothèques et les laboratoires d’Oxford, demanderait : « Mais où est l’université ? » L’université n’est pas un bâtiment de plus, c’est la manière dont tout cela est organisé.&lt;/p&gt; &lt;p&gt;De même, l’esprit n’est pas une chose cachée derrière nos actes : dire de quelqu’un qu’il est intelligent, c’est dire comment il agit et comment il agirait dans diverses situations. Ryle distingue aussi « savoir que », connaître des faits, et « savoir comment », posséder un savoir-faire. Ses analyses ont profondément influencé la philosophie de l’esprit, même si beaucoup jugent aujourd’hui son approche trop proche du béhaviorisme. Il a aussi consacré un livre à Platon, &lt;em&gt;Plato’s Progress&lt;/em&gt; (1966). Il meurt en 1976.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/strawson-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ryle-mini.webp</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8121,17 +8144,17 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; langage</t>
+          <t xml:space="preserve">langage ; epistemologie</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytique</t>
+          <t xml:space="preserve">Analytique ; Béhaviorisme</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe britannique d’Oxford, fondateur d’une « métaphysique descriptive » des cadres de notre pensée.</t>
+          <t xml:space="preserve">philosophe britannique d’Oxford, critique du « fantôme dans la machine » cartésien.</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8145,56 +8168,51 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974</t>
+          <t xml:space="preserve">2006</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1974</t>
+          <t xml:space="preserve">1919 – 2006</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imre LAKATOS</t>
+          <t xml:space="preserve">Peter STRAWSON</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Imre_Lakatos" title=" Wikipedia"&gt;Imre LAKATOS&lt;/a&gt; est un philosophe des mathématiques et des sciences d’origine hongroise. Né à Debrecen dans une famille juive, il échappe à la Shoah, où meurent sa mère et sa grand-mère, en changeant de nom ; il prend celui de Lakatos. Militant communiste après la guerre, il est pourtant emprisonné pendant trois ans sous le régime stalinien. Après l’insurrection de Budapest en 1956, il s’enfuit en Angleterre, où il étudie à Cambridge, puis enseigne à la London School of Economics, auprès de &lt;a href="https://fr.wikipedia.org/wiki/Karl_Popper" title=" Wikipedia"&gt;Karl Popper&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Preuves et réfutations&lt;/em&gt;, il montre, sous la forme d’un dialogue entre un professeur et ses élèves, que les mathématiques ne progressent pas par une simple accumulation de vérités démontrées, mais par une succession de conjectures, de contre-exemples et de corrections des définitions. Même les mathématiques ont une histoire faite d’essais et d’erreurs.&lt;/p&gt; &lt;p&gt;En philosophie des sciences, il cherche une voie entre Popper, pour qui une théorie doit être abandonnée dès qu’elle est réfutée, et Thomas Kuhn, qui décrit les révolutions scientifiques comme des changements presque irrationnels de paradigme. Selon Lakatos, les scientifiques travaillent dans des « &lt;a href="https://fr.wikipedia.org/wiki/Programme_de_recherche" title=" Wikipedia"&gt;programmes de recherche&lt;/a&gt; » : un noyau dur de principes que l’on protège, entouré d’hypothèses que l’on ajuste. Un programme est « progressif » s’il prédit des faits nouveaux, « dégénérescent » s’il ne fait que se défendre. Son séminaire de la London School of Economics attire les meilleurs philosophes des sciences, et son débat avec son ami et adversaire Paul Feyerabend est resté célèbre. Il meurt subitement à Londres en 1974, à cinquante et un ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Peter_Frederick_Strawson" title=" Wikipedia"&gt;Peter STRAWSON&lt;/a&gt; est un philosophe britannique de l’école d’Oxford, qui a renouvelé la métaphysique au sein de la philosophie analytique. Né à Londres, il étudie à Oxford, où il enseigne ensuite pendant toute sa carrière, jusqu’à occuper la chaire de métaphysique. Il se fait connaître en 1950 par un article célèbre, « De l’acte de référence », où il critique la théorie des descriptions de &lt;a href="https://fr.wikipedia.org/wiki/Bertrand_Russell" title=" Wikipedia"&gt;Bertrand Russell&lt;/a&gt;. Il est anobli en 1977 et devient Sir Peter Strawson.&lt;/p&gt; &lt;p&gt;Pour Russell, la phrase « L’actuel roi de France est chauve » est simplement fausse, puisqu’il n’y a pas de roi de France. Strawson répond que ce ne sont pas les phrases mais les personnes qui, en les utilisant, font référence ou affirment quelque chose : ici, la question de la vérité ne se pose même pas, car la phrase présuppose l’existence d’un roi. Il défend ainsi une analyse du langage tel qu’on l’utilise réellement, contre la seule logique formelle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Individus&lt;/em&gt; (1959), il propose une « métaphysique descriptive » : au lieu d’inventer une image nouvelle du monde, elle décrit la structure de pensée que nous partageons tous, où les corps et les personnes sont les éléments de base. Dans &lt;em&gt;Les Limites du sens&lt;/em&gt; (1966), il relit &lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant" title=" Wikipedia"&gt;Kant&lt;/a&gt; dans cet esprit. Dans « Liberté et ressentiment » (1962), il montre que nos réactions morales, comme la gratitude ou l’indignation, font partie de notre nature et ne dépendent pas de la question du déterminisme. Il meurt à Londres en 2006 ; son fils Galen Strawson est lui aussi philosophe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/lakatos-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/strawson-mini.webp</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hongroise</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; logique</t>
+          <t xml:space="preserve">metaphysique ; langage</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falsificationnisme ; Rationalisme</t>
+          <t xml:space="preserve">Analytique</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe des sciences hongrois, penseur des « programmes de recherche » et de la logique de la découverte mathématique.</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">philosophe britannique d’Oxford, fondateur d’une « métaphysique descriptive » des cadres de notre pensée.</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8208,51 +8226,56 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994</t>
+          <t xml:space="preserve">1974</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924 – 1994</t>
+          <t xml:space="preserve">1922 – 1974</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul FEYERABEND</t>
+          <t xml:space="preserve">Imre LAKATOS</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Feyerabend" title=" Wikipedia"&gt;Paul FEYERABEND&lt;/a&gt; est un philosophe des sciences autrichien, l’un des plus provocateurs du XXe siècle. Né à Vienne, il est grièvement blessé pendant la Seconde Guerre mondiale, alors qu’il sert dans l’armée allemande, et en garde un handicap toute sa vie. Il étudie la physique, l’histoire et le théâtre, puis la philosophie auprès de Karl Popper à Londres. Il enseigne ensuite à Bristol, puis pendant de longues années à Berkeley, en Californie, et à Zurich.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Contre_la_m%C3%A9thode" title=" Wikipedia"&gt;&lt;em&gt;Contre la méthode&lt;/em&gt;&lt;/a&gt; (1975), il soutient qu’il n’existe pas de méthode scientifique unique et universelle. L’étude de l’histoire des sciences, et notamment de Galilée, montre que les grands savants ont souvent progressé en violant les règles qu’on prétend leur imposer : en défendant des idées contre les faits établis, en usant de propagande et de rhétorique. D’où sa formule provocante : en matière de méthode, « tout est bon » (&lt;em&gt;anything goes&lt;/em&gt;). Il appelle cette position un « anarchisme épistémologique ».&lt;/p&gt; &lt;p&gt;Feyerabend ne rejette pas la science, mais son statut de vérité officielle. Dans une société libre, dit-il, la science devrait être séparée de l’État comme l’Église l’a été, et les citoyens devraient pouvoir juger eux-mêmes des savoirs, y compris des médecines traditionnelles ou des savoirs non occidentaux. Ses positions ont suscité de vives polémiques. Avec son ami Imre Lakatos, il projetait d’écrire un livre à deux voix, « pour et contre la méthode ». Son autobiographie, &lt;em&gt;Tuer le temps&lt;/em&gt;, paraît après sa mort, survenue en Suisse en 1994.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Imre_Lakatos" title=" Wikipedia"&gt;Imre LAKATOS&lt;/a&gt; est un philosophe des mathématiques et des sciences d’origine hongroise. Né à Debrecen dans une famille juive, il échappe à la Shoah, où meurent sa mère et sa grand-mère, en changeant de nom ; il prend celui de Lakatos. Militant communiste après la guerre, il est pourtant emprisonné pendant trois ans sous le régime stalinien. Après l’insurrection de Budapest en 1956, il s’enfuit en Angleterre, où il étudie à Cambridge, puis enseigne à la London School of Economics, auprès de &lt;a href="https://fr.wikipedia.org/wiki/Karl_Popper" title=" Wikipedia"&gt;Karl Popper&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Preuves et réfutations&lt;/em&gt;, il montre, sous la forme d’un dialogue entre un professeur et ses élèves, que les mathématiques ne progressent pas par une simple accumulation de vérités démontrées, mais par une succession de conjectures, de contre-exemples et de corrections des définitions. Même les mathématiques ont une histoire faite d’essais et d’erreurs.&lt;/p&gt; &lt;p&gt;En philosophie des sciences, il cherche une voie entre Popper, pour qui une théorie doit être abandonnée dès qu’elle est réfutée, et Thomas Kuhn, qui décrit les révolutions scientifiques comme des changements presque irrationnels de paradigme. Selon Lakatos, les scientifiques travaillent dans des « &lt;a href="https://fr.wikipedia.org/wiki/Programme_de_recherche" title=" Wikipedia"&gt;programmes de recherche&lt;/a&gt; » : un noyau dur de principes que l’on protège, entouré d’hypothèses que l’on ajuste. Un programme est « progressif » s’il prédit des faits nouveaux, « dégénérescent » s’il ne fait que se défendre. Son séminaire de la London School of Economics attire les meilleurs philosophes des sciences, et son débat avec son ami et adversaire Paul Feyerabend est resté célèbre. Il meurt subitement à Londres en 1974, à cinquante et un ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/feyerabend-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lakatos-mini.webp</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autrichienne</t>
+          <t xml:space="preserve">Hongroise</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie</t>
+          <t xml:space="preserve">epistemologie ; logique</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relativisme</t>
+          <t xml:space="preserve">Falsificationnisme ; Rationalisme</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe des sciences autrichien, auteur de Contre la méthode, défenseur d’un « anarchisme épistémologique ».</t>
+          <t xml:space="preserve">philosophe des sciences hongrois, penseur des « programmes de recherche » et de la logique de la découverte mathématique.</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8266,51 +8289,51 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025</t>
+          <t xml:space="preserve">1994</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929 – 2025</t>
+          <t xml:space="preserve">1924 – 1994</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alasdair MACINTYRE</t>
+          <t xml:space="preserve">Paul FEYERABEND</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alasdair_MacIntyre" title=" Wikipedia"&gt;Alasdair MACINTYRE&lt;/a&gt; est un philosophe écossais, l’un des penseurs de la morale les plus influents de la fin du XXe siècle. Né à Glasgow en 1929, il est d’abord marxiste et proche de la nouvelle gauche britannique, avant de s’éloigner du marxisme. Il s’installe aux États-Unis en 1970 et enseigne dans plusieurs universités, notamment à l’université Notre-Dame, dans l’Indiana. Converti au catholicisme dans les années 1980, il se rattache à la tradition d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt; et de Thomas d’Aquin.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Après la vertu&lt;/em&gt; (1981) part d’un constat : les débats moraux d’aujourd’hui, sur la guerre, l’avortement ou la justice, sont interminables, car chacun utilise des fragments de traditions anciennes dont on a perdu le cadre commun. Les Lumières ont voulu fonder la morale sur la seule raison individuelle ; cet échec a conduit à l’« émotivisme », l’idée que les jugements moraux ne sont que l’expression de préférences personnelles.&lt;/p&gt; &lt;p&gt;Contre cette impasse, MacIntyre propose de revenir à l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89thique_de_la_vertu" title=" Wikipedia"&gt;éthique des vertus&lt;/a&gt; : la vie bonne se comprend comme un récit unifié, inscrit dans des « pratiques » partagées, comme un métier ou un art, et dans une tradition vivante, au sein d’une communauté. Les vertus sont les qualités qui nous permettent d’atteindre les biens propres à ces pratiques. &lt;em&gt;Après la vertu&lt;/em&gt; se termine par un appel à construire des communautés locales où les vertus puissent survivre, en attendant « un autre saint Benoît ». Il prolonge cette réflexion dans &lt;em&gt;Quelle justice ? Quelle rationalité ?&lt;/em&gt; (1988). Il meurt dans l’Indiana en mai 2025, à quatre-vingt-seize ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Feyerabend" title=" Wikipedia"&gt;Paul FEYERABEND&lt;/a&gt; est un philosophe des sciences autrichien, l’un des plus provocateurs du XXe siècle. Né à Vienne, il est grièvement blessé pendant la Seconde Guerre mondiale, alors qu’il sert dans l’armée allemande, et en garde un handicap toute sa vie. Il étudie la physique, l’histoire et le théâtre, puis la philosophie auprès de Karl Popper à Londres. Il enseigne ensuite à Bristol, puis pendant de longues années à Berkeley, en Californie, et à Zurich.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Contre_la_m%C3%A9thode" title=" Wikipedia"&gt;&lt;em&gt;Contre la méthode&lt;/em&gt;&lt;/a&gt; (1975), il soutient qu’il n’existe pas de méthode scientifique unique et universelle. L’étude de l’histoire des sciences, et notamment de Galilée, montre que les grands savants ont souvent progressé en violant les règles qu’on prétend leur imposer : en défendant des idées contre les faits établis, en usant de propagande et de rhétorique. D’où sa formule provocante : en matière de méthode, « tout est bon » (&lt;em&gt;anything goes&lt;/em&gt;). Il appelle cette position un « anarchisme épistémologique ».&lt;/p&gt; &lt;p&gt;Feyerabend ne rejette pas la science, mais son statut de vérité officielle. Dans une société libre, dit-il, la science devrait être séparée de l’État comme l’Église l’a été, et les citoyens devraient pouvoir juger eux-mêmes des savoirs, y compris des médecines traditionnelles ou des savoirs non occidentaux. Ses positions ont suscité de vives polémiques. Avec son ami Imre Lakatos, il projetait d’écrire un livre à deux voix, « pour et contre la méthode ». Son autobiographie, &lt;em&gt;Tuer le temps&lt;/em&gt;, paraît après sa mort, survenue en Suisse en 1994.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/macintyre-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/feyerabend-mini.webp</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Autrichienne</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">epistemologie</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Éthique de la vertu ; Communautarisme</t>
+          <t xml:space="preserve">Relativisme</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe écossais, auteur d’Après la vertu, grand rénovateur de l’éthique aristotélicienne des vertus.</t>
+          <t xml:space="preserve">philosophe des sciences autrichien, auteur de Contre la méthode, défenseur d’un « anarchisme épistémologique ».</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8324,51 +8347,51 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016</t>
+          <t xml:space="preserve">2025</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1932 – 2016</t>
+          <t xml:space="preserve">1929 – 2025</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umberto ECO</t>
+          <t xml:space="preserve">Alasdair MACINTYRE</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Umberto_Eco" title=" Wikipedia"&gt;Umberto ECO&lt;/a&gt; est un philosophe, sémioticien et romancier italien, l’un des intellectuels les plus célèbres de son temps. Né à Alexandrie, dans le Piémont, il consacre sa thèse à l’esthétique de &lt;a href="https://fr.wikipedia.org/wiki/Thomas_d%27Aquin" title=" Wikipedia"&gt;Thomas d’Aquin&lt;/a&gt; et devient un grand connaisseur du Moyen Âge. Il travaille d’abord à la télévision italienne, puis enseigne à l’université de Bologne, où il occupe la première chaire de &lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9miotique" title=" Wikipedia"&gt;sémiotique&lt;/a&gt; en Italie, la science des signes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Œuvre ouverte&lt;/em&gt; (1962), il montre que les œuvres d’art modernes, de Joyce à la musique contemporaine, ne délivrent pas un message unique : elles laissent au lecteur ou à l’auditeur une part de liberté pour construire leur sens. Mais dans &lt;em&gt;Les Limites de l’interprétation&lt;/em&gt; (1990), il met en garde contre l’excès inverse : un texte autorise de nombreuses lectures, mais pas n’importe lesquelles. Il étudie aussi la culture de masse, la publicité, les bandes dessinées et les romans populaires avec le même sérieux que les classiques.&lt;/p&gt; &lt;p&gt;Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/Le_Nom_de_la_rose_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Le Nom de la rose&lt;/em&gt;&lt;/a&gt; (1980), enquête policière dans une abbaye du XIVe siècle, est un succès mondial ; il y met en scène la peur du rire et le pouvoir des livres. Il publie ensuite d’autres romans et de nombreux essais. Dans un texte célèbre, il décrit aussi les traits de ce qu’il appelle le « fascisme éternel », toujours prêt à renaître. Il écrit aussi sur &lt;em&gt;La Recherche de la langue parfaite&lt;/em&gt; (1994) dans la culture européenne. Grand bibliophile, il possédait une bibliothèque de plusieurs dizaines de milliers de volumes. Il meurt à Milan en 2016.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alasdair_MacIntyre" title=" Wikipedia"&gt;Alasdair MACINTYRE&lt;/a&gt; est un philosophe écossais, l’un des penseurs de la morale les plus influents de la fin du XXe siècle. Né à Glasgow en 1929, il est d’abord marxiste et proche de la nouvelle gauche britannique, avant de s’éloigner du marxisme. Il s’installe aux États-Unis en 1970 et enseigne dans plusieurs universités, notamment à l’université Notre-Dame, dans l’Indiana. Converti au catholicisme dans les années 1980, il se rattache à la tradition d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt; et de Thomas d’Aquin.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Après la vertu&lt;/em&gt; (1981) part d’un constat : les débats moraux d’aujourd’hui, sur la guerre, l’avortement ou la justice, sont interminables, car chacun utilise des fragments de traditions anciennes dont on a perdu le cadre commun. Les Lumières ont voulu fonder la morale sur la seule raison individuelle ; cet échec a conduit à l’« émotivisme », l’idée que les jugements moraux ne sont que l’expression de préférences personnelles.&lt;/p&gt; &lt;p&gt;Contre cette impasse, MacIntyre propose de revenir à l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89thique_de_la_vertu" title=" Wikipedia"&gt;éthique des vertus&lt;/a&gt; : la vie bonne se comprend comme un récit unifié, inscrit dans des « pratiques » partagées, comme un métier ou un art, et dans une tradition vivante, au sein d’une communauté. Les vertus sont les qualités qui nous permettent d’atteindre les biens propres à ces pratiques. &lt;em&gt;Après la vertu&lt;/em&gt; se termine par un appel à construire des communautés locales où les vertus puissent survivre, en attendant « un autre saint Benoît ». Il prolonge cette réflexion dans &lt;em&gt;Quelle justice ? Quelle rationalité ?&lt;/em&gt; (1988). Il meurt dans l’Indiana en mai 2025, à quatre-vingt-seize ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/eco-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/macintyre-mini.webp</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Italienne</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; langage</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structuralisme ; Herméneutique</t>
+          <t xml:space="preserve">Éthique de la vertu ; Communautarisme</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sémioticien, philosophe et romancier italien, auteur de L’Œuvre ouverte et du Nom de la rose.</t>
+          <t xml:space="preserve">philosophe écossais, auteur d’Après la vertu, grand rénovateur de l’éthique aristotélicienne des vertus.</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8382,31 +8405,31 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023</t>
+          <t xml:space="preserve">2016</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1933 – 2023</t>
+          <t xml:space="preserve">1932 – 2016</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antonio NEGRI</t>
+          <t xml:space="preserve">Umberto ECO</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Toni_Negri" title=" Wikipedia"&gt;Antonio NEGRI&lt;/a&gt; (dit Toni Negri) est un philosophe italien, figure majeure de la pensée marxiste radicale de la fin du XXe siècle. Né à Padoue, professeur de philosophie politique dans l’université de cette ville, il est dans les années 1960 et 1970 l’un des animateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;, un courant qui part des luttes concrètes des ouvriers d’usine plutôt que des directives des partis, puis du mouvement de l’Autonomie ouvrière.&lt;/p&gt; &lt;p&gt;En 1979, il est arrêté et accusé d’être le cerveau des Brigades rouges, accusation dont il est finalement lavé, mais il est condamné pour d’autres faits liés à la violence politique de ces années. Élu député en 1983, il profite de son immunité pour s’exiler en France, où il enseigne pendant quatorze ans, notamment à l’université Paris-VIII et au Collège international de philosophie, et se rapproche de Deleuze et de Guattari. Il rentre en Italie en 1997 pour purger sa peine. Parallèlement, il écrit sur Spinoza, dont il fait le penseur d’une puissance collective et créatrice.&lt;/p&gt; &lt;p&gt;Avec le philosophe américain Michael Hardt, il publie en 2000 &lt;em&gt;Empire&lt;/em&gt;, qui décrit la mondialisation comme une nouvelle forme de souveraineté sans centre ni frontières, réseau des États, des firmes et des institutions internationales. Face à elle se dresse la « multitude », l’ensemble des singularités qui produisent la richesse commune et peuvent s’organiser sans chef. Ce livre devient une référence du mouvement altermondialiste ; ils le prolongent dans &lt;em&gt;Multitude&lt;/em&gt; (2004) et &lt;em&gt;Commonwealth&lt;/em&gt; (2009). Il meurt à Villejuif, près de Paris, en 2023, à quatre-vingt-dix ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Umberto_Eco" title=" Wikipedia"&gt;Umberto ECO&lt;/a&gt; est un philosophe, sémioticien et romancier italien, l’un des intellectuels les plus célèbres de son temps. Né à Alexandrie, dans le Piémont, il consacre sa thèse à l’esthétique de &lt;a href="https://fr.wikipedia.org/wiki/Thomas_d%27Aquin" title=" Wikipedia"&gt;Thomas d’Aquin&lt;/a&gt; et devient un grand connaisseur du Moyen Âge. Il travaille d’abord à la télévision italienne, puis enseigne à l’université de Bologne, où il occupe la première chaire de &lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9miotique" title=" Wikipedia"&gt;sémiotique&lt;/a&gt; en Italie, la science des signes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Œuvre ouverte&lt;/em&gt; (1962), il montre que les œuvres d’art modernes, de Joyce à la musique contemporaine, ne délivrent pas un message unique : elles laissent au lecteur ou à l’auditeur une part de liberté pour construire leur sens. Mais dans &lt;em&gt;Les Limites de l’interprétation&lt;/em&gt; (1990), il met en garde contre l’excès inverse : un texte autorise de nombreuses lectures, mais pas n’importe lesquelles. Il étudie aussi la culture de masse, la publicité, les bandes dessinées et les romans populaires avec le même sérieux que les classiques.&lt;/p&gt; &lt;p&gt;Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/Le_Nom_de_la_rose_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Le Nom de la rose&lt;/em&gt;&lt;/a&gt; (1980), enquête policière dans une abbaye du XIVe siècle, est un succès mondial ; il y met en scène la peur du rire et le pouvoir des livres. Il publie ensuite d’autres romans et de nombreux essais. Dans un texte célèbre, il décrit aussi les traits de ce qu’il appelle le « fascisme éternel », toujours prêt à renaître. Il écrit aussi sur &lt;em&gt;La Recherche de la langue parfaite&lt;/em&gt; (1994) dans la culture européenne. Grand bibliophile, il possédait une bibliothèque de plusieurs dizaines de milliers de volumes. Il meurt à Milan en 2016.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/negri-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/eco-mini.webp</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -8416,17 +8439,17 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique</t>
+          <t xml:space="preserve">esthetique ; langage</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme ; Opéraïsme</t>
+          <t xml:space="preserve">Structuralisme ; Herméneutique</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe italien de l’opéraïsme, coauteur d’Empire, penseur de la « multitude ».</t>
+          <t xml:space="preserve">sémioticien, philosophe et romancier italien, auteur de L’Œuvre ouverte et du Nom de la rose.</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8440,7 +8463,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
@@ -8449,22 +8472,22 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931 – 2023</t>
+          <t xml:space="preserve">1933 – 2023</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mario TRONTI</t>
+          <t xml:space="preserve">Antonio NEGRI</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mario_Tronti" title=" Wikipedia"&gt;Mario TRONTI&lt;/a&gt; est un philosophe et homme politique italien, l’un des fondateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;. Né à Rome en 1931, il milite dans les années 1950 au Parti communiste italien et se forme à la philosophie auprès de Galvano Della Volpe, un marxiste qui s’opposait à la lecture humaniste de Gramsci. En 1961, il participe avec Raniero Panzieri à la fondation de la revue &lt;em&gt;Quaderni rossi&lt;/em&gt;, puis fonde en 1964 sa propre revue, &lt;em&gt;Classe operaia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Ouvriers et capital&lt;/em&gt; (1966) est le texte fondateur du courant. Il y propose une « révolution copernicienne » dans le marxisme : on a toujours pensé que le capital menait le jeu et que les ouvriers réagissaient ; il faut renverser la perspective et voir que ce sont les luttes ouvrières qui obligent le capital à se transformer, à innover, à mécaniser, à se réorganiser. La classe ouvrière n’est pas un simple rouage du système, mais la force active de l’histoire. Son but n’est pas d’être reconnue comme force de travail, mais de refuser le travail salarié lui-même. Ces idées inspirent la « nouvelle gauche » italienne et les grèves de l’« automne chaud » de 1969.&lt;/p&gt; &lt;p&gt;Pourtant, Tronti fait le choix inverse de ses camarades : il revient au Parti communiste, et défend dans les années 1970 l’« autonomie du politique », la nécessité pour les ouvriers de conquérir les institutions plutôt que de les fuir. Professeur de philosophie politique à l’université de Sienne pendant trente ans, il est deux fois sénateur. Il revient sur cette histoire dans &lt;em&gt;Nous, opéraïstes&lt;/em&gt; (2009). Il meurt en 2023, à quatre-vingt-douze ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Toni_Negri" title=" Wikipedia"&gt;Antonio NEGRI&lt;/a&gt; (dit Toni Negri) est un philosophe italien, figure majeure de la pensée marxiste radicale de la fin du XXe siècle. Né à Padoue, professeur de philosophie politique dans l’université de cette ville, il est dans les années 1960 et 1970 l’un des animateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;, un courant qui part des luttes concrètes des ouvriers d’usine plutôt que des directives des partis, puis du mouvement de l’Autonomie ouvrière.&lt;/p&gt; &lt;p&gt;En 1979, il est arrêté et accusé d’être le cerveau des Brigades rouges, accusation dont il est finalement lavé, mais il est condamné pour d’autres faits liés à la violence politique de ces années. Élu député en 1983, il profite de son immunité pour s’exiler en France, où il enseigne pendant quatorze ans, notamment à l’université Paris-VIII et au Collège international de philosophie, et se rapproche de Deleuze et de Guattari. Il rentre en Italie en 1997 pour purger sa peine. Parallèlement, il écrit sur Spinoza, dont il fait le penseur d’une puissance collective et créatrice.&lt;/p&gt; &lt;p&gt;Avec le philosophe américain Michael Hardt, il publie en 2000 &lt;em&gt;Empire&lt;/em&gt;, qui décrit la mondialisation comme une nouvelle forme de souveraineté sans centre ni frontières, réseau des États, des firmes et des institutions internationales. Face à elle se dresse la « multitude », l’ensemble des singularités qui produisent la richesse commune et peuvent s’organiser sans chef. Ce livre devient une référence du mouvement altermondialiste ; ils le prolongent dans &lt;em&gt;Multitude&lt;/em&gt; (2004) et &lt;em&gt;Commonwealth&lt;/em&gt; (2009). Il meurt à Villejuif, près de Paris, en 2023, à quatre-vingt-dix ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tronti-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/negri-mini.webp</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -8479,12 +8502,12 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opéraïsme ; Marxisme</t>
+          <t xml:space="preserve">Marxisme ; Opéraïsme</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe italien, fondateur de l’opéraïsme, penseur de la « révolution copernicienne » des luttes ouvrières.</t>
+          <t xml:space="preserve">philosophe italien de l’opéraïsme, coauteur d’Empire, penseur de la « multitude ».</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8492,40 +8515,42 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P113"/>
+      <c r="P113">
+        <v>2</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1">
-        <v>1903</v>
+        <v>1931</v>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983</t>
+          <t xml:space="preserve">2023</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903 – 1983</t>
+          <t xml:space="preserve">1931 – 2023</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joan ROBINSON</t>
+          <t xml:space="preserve">Mario TRONTI</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joan_Robinson" title=" Wikipedia"&gt;Joan ROBINSON&lt;/a&gt; est une économiste britannique, l’une des grandes figures de l’école de Cambridge et du &lt;a href="https://fr.wikipedia.org/wiki/Keyn%C3%A9sianisme" title=" Wikipedia"&gt;keynésianisme&lt;/a&gt;. Née en 1903 dans une famille de la bonne société anglaise, elle étudie l’économie à Cambridge, où elle fera toute sa carrière. En 1933, son &lt;em&gt;Économie de la concurrence imparfaite&lt;/em&gt; montre que la plupart des marchés ne ressemblent pas au modèle de la concurrence parfaite : des entreprises en situation de monopole ou d’oligopole fixent leurs prix, et l’acheteur unique d’un travail, qu’elle appelle « monopsone », peut imposer de bas salaires.&lt;/p&gt; &lt;p&gt;Au début des années 1930, elle appartient au « Cirque », le petit groupe de jeunes économistes qui discute avec &lt;a href="https://fr.wikipedia.org/wiki/John_Maynard_Keynes" title=" Wikipedia"&gt;Keynes&lt;/a&gt; les idées de sa future &lt;em&gt;Théorie générale&lt;/em&gt; (1936). Elle devient ensuite l’une de ses interprètes les plus radicales : pour elle, l’économie se déroule dans un temps historique et incertain, où les crises et le chômage ne sont pas des accidents, mais des traits du capitalisme. Avec Piero Sraffa et Nicholas Kaldor, elle fonde ce qu’on appellera le post-keynésianisme, et dans &lt;em&gt;L’Accumulation du capital&lt;/em&gt; (1956) elle étudie la croissance et la répartition des revenus entre salaires et profits.&lt;/p&gt; &lt;p&gt;Dans les années 1950 et 1960, elle mène la « controverse des deux Cambridge » contre Paul Samuelson et Robert Solow, du Cambridge américain : elle conteste qu’on puisse mesurer le « capital » comme une quantité simple, ce qui ébranle la théorie dominante de la répartition. Samuelson finit par lui donner raison sur le plan logique. Grande voyageuse, elle admire un temps la Chine de Mao et la Corée du Nord, ce qui lui est reproché. Souvent citée pour le prix Nobel, elle ne l’a jamais reçu. Elle meurt à Cambridge en 1983.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mario_Tronti" title=" Wikipedia"&gt;Mario TRONTI&lt;/a&gt; est un philosophe et homme politique italien, l’un des fondateurs de l’&lt;a href="https://fr.wikipedia.org/wiki/Op%C3%A9ra%C3%AFsme" title=" Wikipedia"&gt;opéraïsme&lt;/a&gt;. Né à Rome en 1931, il milite dans les années 1950 au Parti communiste italien et se forme à la philosophie auprès de Galvano Della Volpe, un marxiste qui s’opposait à la lecture humaniste de Gramsci. En 1961, il participe avec Raniero Panzieri à la fondation de la revue &lt;em&gt;Quaderni rossi&lt;/em&gt;, puis fonde en 1964 sa propre revue, &lt;em&gt;Classe operaia&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Ouvriers et capital&lt;/em&gt; (1966) est le texte fondateur du courant. Il y propose une « révolution copernicienne » dans le marxisme : on a toujours pensé que le capital menait le jeu et que les ouvriers réagissaient ; il faut renverser la perspective et voir que ce sont les luttes ouvrières qui obligent le capital à se transformer, à innover, à mécaniser, à se réorganiser. La classe ouvrière n’est pas un simple rouage du système, mais la force active de l’histoire. Son but n’est pas d’être reconnue comme force de travail, mais de refuser le travail salarié lui-même. Ces idées inspirent la « nouvelle gauche » italienne et les grèves de l’« automne chaud » de 1969.&lt;/p&gt; &lt;p&gt;Pourtant, Tronti fait le choix inverse de ses camarades : il revient au Parti communiste, et défend dans les années 1970 l’« autonomie du politique », la nécessité pour les ouvriers de conquérir les institutions plutôt que de les fuir. Professeur de philosophie politique à l’université de Sienne pendant trente ans, il est deux fois sénateur. Il revient sur cette histoire dans &lt;em&gt;Nous, opéraïstes&lt;/em&gt; (2009). Il meurt en 2023, à quatre-vingt-douze ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/robinson-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tronti-mini.webp</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Italienne</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8535,17 +8560,12 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keynésianisme</t>
+          <t xml:space="preserve">Opéraïsme ; Marxisme</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">économiste britannique de Cambridge, proche de Keynes et figure du post-keynésianisme.</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">philosophe italien, fondateur de l’opéraïsme, penseur de la « révolution copernicienne » des luttes ouvrières.</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8557,31 +8577,31 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1">
-        <v>1887</v>
+        <v>1903</v>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975</t>
+          <t xml:space="preserve">1983</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887 – 1975</t>
+          <t xml:space="preserve">1903 – 1983</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julian HUXLEY</t>
+          <t xml:space="preserve">Joan ROBINSON</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julian_Huxley" title=" Wikipedia"&gt;Julian HUXLEY&lt;/a&gt; est un biologiste, écrivain et humaniste britannique, petit-fils de Thomas Huxley, le défenseur de Darwin, et frère du romancier Aldous Huxley. Spécialiste du comportement animal, il étudie les parades nuptiales des oiseaux et contribue à fonder l’éthologie. Son livre &lt;em&gt;Evolution : The Modern Synthesis&lt;/em&gt; (1942) donne son nom à la « synthèse moderne », qui réunit la théorie de Darwin et la génétique.&lt;/p&gt; &lt;p&gt;Grand vulgarisateur, il est en 1946 le premier directeur général de l’UNESCO, à laquelle il veut donner pour philosophie un « humanisme scientifique » mondial ; il participe aussi, en 1961, à la fondation du WWF. Dans un essai de 1957, il forge le mot &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;« transhumanisme »&lt;/a&gt; : l’espèce humaine, devenue consciente de l’évolution, peut se dépasser elle-même, « en restant homme, mais en se transcendant », en réalisant de nouvelles possibilités de sa nature grâce à la science. Pour lui, l’évolution est désormais entre nos mains et doit être conduite de façon consciente et responsable.&lt;/p&gt; &lt;p&gt;Cette confiance dans la maîtrise de l’évolution a sa face sombre. Huxley a longtemps défendu l’eugénisme, l’amélioration de l’espèce par le contrôle de la reproduction, et présida la Société britannique d’eugénisme de 1959 à 1962, même s’il dénonça les théories raciales des nazis dès les années 1930. Il meurt à Londres en 1975. Le mouvement transhumaniste de la fin du XXe siècle reprendra son mot, en l’appliquant aux technologies de l’amélioration humaine.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joan_Robinson" title=" Wikipedia"&gt;Joan ROBINSON&lt;/a&gt; est une économiste britannique, l’une des grandes figures de l’école de Cambridge et du &lt;a href="https://fr.wikipedia.org/wiki/Keyn%C3%A9sianisme" title=" Wikipedia"&gt;keynésianisme&lt;/a&gt;. Née en 1903 dans une famille de la bonne société anglaise, elle étudie l’économie à Cambridge, où elle fera toute sa carrière. En 1933, son &lt;em&gt;Économie de la concurrence imparfaite&lt;/em&gt; montre que la plupart des marchés ne ressemblent pas au modèle de la concurrence parfaite : des entreprises en situation de monopole ou d’oligopole fixent leurs prix, et l’acheteur unique d’un travail, qu’elle appelle « monopsone », peut imposer de bas salaires.&lt;/p&gt; &lt;p&gt;Au début des années 1930, elle appartient au « Cirque », le petit groupe de jeunes économistes qui discute avec &lt;a href="https://fr.wikipedia.org/wiki/John_Maynard_Keynes" title=" Wikipedia"&gt;Keynes&lt;/a&gt; les idées de sa future &lt;em&gt;Théorie générale&lt;/em&gt; (1936). Elle devient ensuite l’une de ses interprètes les plus radicales : pour elle, l’économie se déroule dans un temps historique et incertain, où les crises et le chômage ne sont pas des accidents, mais des traits du capitalisme. Avec Piero Sraffa et Nicholas Kaldor, elle fonde ce qu’on appellera le post-keynésianisme, et dans &lt;em&gt;L’Accumulation du capital&lt;/em&gt; (1956) elle étudie la croissance et la répartition des revenus entre salaires et profits.&lt;/p&gt; &lt;p&gt;Dans les années 1950 et 1960, elle mène la « controverse des deux Cambridge » contre Paul Samuelson et Robert Solow, du Cambridge américain : elle conteste qu’on puisse mesurer le « capital » comme une quantité simple, ce qui ébranle la théorie dominante de la répartition. Samuelson finit par lui donner raison sur le plan logique. Grande voyageuse, elle admire un temps la Chine de Mao et la Corée du Nord, ce qui lui est reproché. Souvent citée pour le prix Nobel, elle ne l’a jamais reçu. Elle meurt à Cambridge en 1983.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/julianhuxley-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/robinson-mini.webp</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -8591,17 +8611,22 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; epistemologie</t>
+          <t xml:space="preserve">politique</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transhumanisme</t>
+          <t xml:space="preserve">Keynésianisme</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">biologiste britannique, premier directeur de l’UNESCO, inventeur du mot « transhumanisme ».</t>
+          <t xml:space="preserve">économiste britannique de Cambridge, proche de Keynes et figure du post-keynésianisme.</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8613,51 +8638,51 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1">
-        <v>1801</v>
+        <v>1887</v>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1975</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801 – 1852</t>
+          <t xml:space="preserve">1887 – 1975</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vincenzo GIOBERTI</t>
+          <t xml:space="preserve">Julian HUXLEY</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincenzo_Gioberti" title=" Wikipedia"&gt;Vincenzo GIOBERTI&lt;/a&gt; est un philosophe, prêtre et homme politique italien. Né à Turin en 1801, ordonné prêtre en 1825, il devient chapelain de la cour du roi de Sardaigne. Soupçonné de sympathies républicaines, il est arrêté en 1833 et contraint à l’exil : il vit à Paris, puis à Bruxelles, où il enseigne et écrit la plus grande partie de son œuvre.&lt;/p&gt; &lt;p&gt;Il est le principal représentant de l’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;. Contre la philosophie moderne, qui part depuis Descartes du sujet et de ses idées, il veut partir de l’être lui-même : l’esprit humain a une intuition directe de Dieu, l’Être absolu, et c’est dans cette lumière qu’il connaît toutes choses. Sa « formule idéale » résume tout le réel : « L’Être crée l’existant. » Il en tire une critique vigoureuse de Descartes et de son contemporain Antonio Rosmini, qu’il accuse de psychologisme. Plusieurs thèses ontologistes seront condamnées par le Saint-Office en 1861, après sa mort.&lt;/p&gt; &lt;p&gt;En 1843, son livre &lt;em&gt;De la primauté morale et civile des Italiens&lt;/em&gt; connaît un immense succès. Il y défend le « néo-guelfisme » : l’Italie, divisée, doit s’unir en une confédération d’États présidée par le pape. Ce programme fait de lui l’un des inspirateurs du &lt;a href="https://fr.wikipedia.org/wiki/Risorgimento" title=" Wikipedia"&gt;Risorgimento&lt;/a&gt;. Revenu triomphalement à Turin en 1848, il est président de la Chambre, puis chef du gouvernement du royaume de Sardaigne en 1848-1849. Désavoué, il repart pour Paris, où il meurt en 1852.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julian_Huxley" title=" Wikipedia"&gt;Julian HUXLEY&lt;/a&gt; est un biologiste, écrivain et humaniste britannique, petit-fils de Thomas Huxley, le défenseur de Darwin, et frère du romancier Aldous Huxley. Spécialiste du comportement animal, il étudie les parades nuptiales des oiseaux et contribue à fonder l’éthologie. Son livre &lt;em&gt;Evolution : The Modern Synthesis&lt;/em&gt; (1942) donne son nom à la « synthèse moderne », qui réunit la théorie de Darwin et la génétique.&lt;/p&gt; &lt;p&gt;Grand vulgarisateur, il est en 1946 le premier directeur général de l’UNESCO, à laquelle il veut donner pour philosophie un « humanisme scientifique » mondial ; il participe aussi, en 1961, à la fondation du WWF. Dans un essai de 1957, il forge le mot &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;« transhumanisme »&lt;/a&gt; : l’espèce humaine, devenue consciente de l’évolution, peut se dépasser elle-même, « en restant homme, mais en se transcendant », en réalisant de nouvelles possibilités de sa nature grâce à la science. Pour lui, l’évolution est désormais entre nos mains et doit être conduite de façon consciente et responsable.&lt;/p&gt; &lt;p&gt;Cette confiance dans la maîtrise de l’évolution a sa face sombre. Huxley a longtemps défendu l’eugénisme, l’amélioration de l’espèce par le contrôle de la reproduction, et présida la Société britannique d’eugénisme de 1959 à 1962, même s’il dénonça les théories raciales des nazis dès les années 1930. Il meurt à Londres en 1975. Le mouvement transhumaniste de la fin du XXe siècle reprendra son mot, en l’appliquant aux technologies de l’amélioration humaine.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gioberti-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/julianhuxley-mini.webp</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Italienne</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; politique</t>
+          <t xml:space="preserve">ethique ; epistemologie</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontologisme</t>
+          <t xml:space="preserve">Transhumanisme</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et homme politique italien, théoricien de l’ontologisme et du Risorgimento.</t>
+          <t xml:space="preserve">biologiste britannique, premier directeur de l’UNESCO, inventeur du mot « transhumanisme ».</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8669,31 +8694,31 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1797 – 1855</t>
+          <t xml:space="preserve">1801 – 1852</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antonio ROSMINI</t>
+          <t xml:space="preserve">Vincenzo GIOBERTI</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Rosmini" title=" Wikipedia"&gt;Antonio ROSMINI&lt;/a&gt; est un prêtre et philosophe italien, l’un des grands penseurs catholiques du XIXe siècle. Né en 1797 à Rovereto, dans le Trentin, alors autrichien, dans une famille noble, il étudie à Padoue et devient prêtre en 1821. En 1828, il fonde l’Institut de la Charité, dont les membres, les rosminiens, se consacrent à l’enseignement et aux œuvres de charité. Ami du romancier Alessandro Manzoni, il veut réconcilier la foi catholique avec la philosophie moderne.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Nouvel essai sur l’origine des idées&lt;/em&gt; (1830), il cherche ce qui rend possible la connaissance. Contre les empiristes, pour qui tout vient des sens, et contre Kant, qui multiplie les formes a priori, il soutient qu’une seule idée est innée : l’idée de l’être, indéterminée, que l’esprit intuitionne avant toute expérience et qui lui permet de juger que les choses existent. Sa philosophie du droit fait de la personne le fondement de tout : la personne humaine est « le droit subsistant », qu’aucun État ne peut absorber ni sacrifier. Il est ainsi regardé comme un précurseur du &lt;a href="https://fr.wikipedia.org/wiki/Personnalisme" title=" Wikipedia"&gt;personnalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;En 1848, ses &lt;em&gt;Cinq plaies de la sainte Église&lt;/em&gt; dénoncent la coupure entre le clergé et le peuple, et sa &lt;em&gt;Constitution selon la justice sociale&lt;/em&gt; imagine une Italie fédérale et libérale ; les deux livres sont mis à l’Index en 1849. Rosmini se soumet et se retire à Stresa, au bord du lac Majeur, où il meurt en 1855. En 1887, Rome condamne quarante thèses tirées de ses œuvres ; il est réhabilité en 2001 et béatifié en 2007.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincenzo_Gioberti" title=" Wikipedia"&gt;Vincenzo GIOBERTI&lt;/a&gt; est un philosophe, prêtre et homme politique italien. Né à Turin en 1801, ordonné prêtre en 1825, il devient chapelain de la cour du roi de Sardaigne. Soupçonné de sympathies républicaines, il est arrêté en 1833 et contraint à l’exil : il vit à Paris, puis à Bruxelles, où il enseigne et écrit la plus grande partie de son œuvre.&lt;/p&gt; &lt;p&gt;Il est le principal représentant de l’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;. Contre la philosophie moderne, qui part depuis Descartes du sujet et de ses idées, il veut partir de l’être lui-même : l’esprit humain a une intuition directe de Dieu, l’Être absolu, et c’est dans cette lumière qu’il connaît toutes choses. Sa « formule idéale » résume tout le réel : « L’Être crée l’existant. » Il en tire une critique vigoureuse de Descartes et de son contemporain Antonio Rosmini, qu’il accuse de psychologisme. Plusieurs thèses ontologistes seront condamnées par le Saint-Office en 1861, après sa mort.&lt;/p&gt; &lt;p&gt;En 1843, son livre &lt;em&gt;De la primauté morale et civile des Italiens&lt;/em&gt; connaît un immense succès. Il y défend le « néo-guelfisme » : l’Italie, divisée, doit s’unir en une confédération d’États présidée par le pape. Ce programme fait de lui l’un des inspirateurs du &lt;a href="https://fr.wikipedia.org/wiki/Risorgimento" title=" Wikipedia"&gt;Risorgimento&lt;/a&gt;. Revenu triomphalement à Turin en 1848, il est président de la Chambre, puis chef du gouvernement du royaume de Sardaigne en 1848-1849. Désavoué, il repart pour Paris, où il meurt en 1852.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rosmini-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gioberti-mini.webp</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -8703,17 +8728,17 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; politique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; politique</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Personnalisme ; Spiritualisme</t>
+          <t xml:space="preserve">Ontologisme</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre et philosophe italien, penseur de l’idée de l’être et de la personne, pionnier de la justice sociale.</t>
+          <t xml:space="preserve">philosophe et homme politique italien, théoricien de l’ontologisme et du Risorgimento.</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -8721,57 +8746,55 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P117">
-        <v>2</v>
-      </c>
+      <c r="P117"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 – 1875</t>
+          <t xml:space="preserve">1797 – 1855</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casimir UBAGHS</t>
+          <t xml:space="preserve">Antonio ROSMINI</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Casimir_Ubaghs" title=" Wikipedia (en)"&gt;Casimir UBAGHS&lt;/a&gt; est un philosophe et théologien catholique néerlandais, chef de file de ce qu’on a appelé l’école « ontologico-traditionaliste » de Louvain. Né en 1800 à Berg en Terblijt, près de Valkenburg, dans le Limbourg néerlandais, fils d’un aubergiste, il enseigne d’abord la philosophie au séminaire de Rolduc. En 1834, il est appelé à l’université catholique de Louvain, en Belgique, où il devient doyen de la faculté de philosophie et lettres et enseigne la logique, la métaphysique et l’anthropologie pendant trente ans.&lt;/p&gt; &lt;p&gt;Sa doctrine unit deux courants de son temps. Le traditionalisme, venu de Bonald, affirme que la raison humaine ne peut découvrir seule les vérités morales et religieuses : elles ont été révélées à l’origine et nous sont transmises par la parole et l’enseignement. Mais Ubaghs ajoute que, une fois éveillée par cette instruction, la raison peut les comprendre et les démontrer. L’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;, celui de Malebranche et de Gioberti, soutient que l’esprit connaît les vérités éternelles en ayant une vision directe, quoique obscure, de Dieu lui-même. À partir de 1846, la &lt;em&gt;Revue catholique&lt;/em&gt; de Louvain diffuse ces idées, qui gagnent aussi des disciples en France.&lt;/p&gt; &lt;p&gt;Très vite, des adversaires dénoncent ces thèses comme contraires à la doctrine de l’Église, qui distingue nettement ce que la raison peut connaître par elle-même et ce que seule la foi apporte. La controverse fait rage de 1858 à 1861. En 1864, Rome censure une série de propositions tirées de ses ouvrages, et Ubaghs, qui se soumet, doit quitter l’enseignement. Il vit alors retiré à Louvain, où il meurt en 1875. Son école disparaît avec lui, mais elle prépare le retour au thomisme imposé à la fin du siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antonio_Rosmini" title=" Wikipedia"&gt;Antonio ROSMINI&lt;/a&gt; est un prêtre et philosophe italien, l’un des grands penseurs catholiques du XIXe siècle. Né en 1797 à Rovereto, dans le Trentin, alors autrichien, dans une famille noble, il étudie à Padoue et devient prêtre en 1821. En 1828, il fonde l’Institut de la Charité, dont les membres, les rosminiens, se consacrent à l’enseignement et aux œuvres de charité. Ami du romancier Alessandro Manzoni, il veut réconcilier la foi catholique avec la philosophie moderne.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Nouvel essai sur l’origine des idées&lt;/em&gt; (1830), il cherche ce qui rend possible la connaissance. Contre les empiristes, pour qui tout vient des sens, et contre Kant, qui multiplie les formes a priori, il soutient qu’une seule idée est innée : l’idée de l’être, indéterminée, que l’esprit intuitionne avant toute expérience et qui lui permet de juger que les choses existent. Sa philosophie du droit fait de la personne le fondement de tout : la personne humaine est « le droit subsistant », qu’aucun État ne peut absorber ni sacrifier. Il est ainsi regardé comme un précurseur du &lt;a href="https://fr.wikipedia.org/wiki/Personnalisme" title=" Wikipedia"&gt;personnalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;En 1848, ses &lt;em&gt;Cinq plaies de la sainte Église&lt;/em&gt; dénoncent la coupure entre le clergé et le peuple, et sa &lt;em&gt;Constitution selon la justice sociale&lt;/em&gt; imagine une Italie fédérale et libérale ; les deux livres sont mis à l’Index en 1849. Rosmini se soumet et se retire à Stresa, au bord du lac Majeur, où il meurt en 1855. En 1887, Rome condamne quarante thèses tirées de ses œuvres ; il est réhabilité en 2001 et béatifié en 2007.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ubaghs-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rosmini-mini.webp</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néerlandaise</t>
+          <t xml:space="preserve">Italienne</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; politique ; spiritualite</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ontologisme</t>
+          <t xml:space="preserve">Personnalisme ; Spiritualisme</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe et théologien néerlandais, chef de l’école ontologiste de Louvain.</t>
+          <t xml:space="preserve">prêtre et philosophe italien, penseur de l’idée de l’être et de la personne, pionnier de la justice sociale.</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -8779,55 +8802,57 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P118"/>
+      <c r="P118">
+        <v>2</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1">
-        <v>1809</v>
+        <v>1800</v>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882</t>
+          <t xml:space="preserve">1875</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809 – 1882</t>
+          <t xml:space="preserve">1800 – 1875</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charles DARWIN</t>
+          <t xml:space="preserve">Casimir UBAGHS</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Darwin" title=" Wikipedia"&gt;Charles DARWIN&lt;/a&gt; est un naturaliste britannique dont la théorie de l’évolution a bouleversé la science et la philosophie. Né en 1809 à Shrewsbury, petit-fils du médecin Erasmus Darwin, il abandonne la médecine puis des études de théologie pour l’histoire naturelle. De 1831 à 1836, il fait le tour du monde à bord du &lt;em&gt;Beagle&lt;/em&gt; : les fossiles d’Amérique du Sud et les espèces voisines d’une île à l’autre des Galápagos le convainquent que les espèces ne sont pas fixes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Origine des espèces&lt;/em&gt; (1859), il explique leur transformation par la « sélection naturelle » : dans chaque génération naissent des individus légèrement différents, et ceux dont les variations favorisent la survie et la reproduction transmettent davantage leurs traits. Sur des temps immenses, ce tri sans but suffit à produire la diversité et l’adaptation des êtres vivants. Il n’y a plus besoin d’un dessein divin pour expliquer l’ordre de la nature, ce qui ruine l’argument de William Paley et ouvre la voie au &lt;a href="https://fr.wikipedia.org/wiki/Naturalisme_%28philosophie%29" title=" Wikipedia"&gt;naturalisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Filiation de l’homme&lt;/em&gt; (1871), il inscrit l’être humain dans cette histoire : nos facultés morales viennent des instincts sociaux de nos ancêtres animaux, renforcés par la sympathie, le langage et l’habitude. Darwin lui-même se dit agnostique et reste prudent sur la religion. Sa théorie sera détournée, avec le darwinisme social de Spencer, pour justifier la concurrence et les inégalités, ce qu’il n’avait pas voulu, même s’il partageait certains préjugés de son temps. Il meurt en 1882 et repose à l’abbaye de Westminster.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Casimir_Ubaghs" title=" Wikipedia (en)"&gt;Casimir UBAGHS&lt;/a&gt; est un philosophe et théologien catholique néerlandais, chef de file de ce qu’on a appelé l’école « ontologico-traditionaliste » de Louvain. Né en 1800 à Berg en Terblijt, près de Valkenburg, dans le Limbourg néerlandais, fils d’un aubergiste, il enseigne d’abord la philosophie au séminaire de Rolduc. En 1834, il est appelé à l’université catholique de Louvain, en Belgique, où il devient doyen de la faculté de philosophie et lettres et enseigne la logique, la métaphysique et l’anthropologie pendant trente ans.&lt;/p&gt; &lt;p&gt;Sa doctrine unit deux courants de son temps. Le traditionalisme, venu de Bonald, affirme que la raison humaine ne peut découvrir seule les vérités morales et religieuses : elles ont été révélées à l’origine et nous sont transmises par la parole et l’enseignement. Mais Ubaghs ajoute que, une fois éveillée par cette instruction, la raison peut les comprendre et les démontrer. L’&lt;a href="https://fr.wikipedia.org/wiki/Ontologisme" title=" Wikipedia"&gt;ontologisme&lt;/a&gt;, celui de Malebranche et de Gioberti, soutient que l’esprit connaît les vérités éternelles en ayant une vision directe, quoique obscure, de Dieu lui-même. À partir de 1846, la &lt;em&gt;Revue catholique&lt;/em&gt; de Louvain diffuse ces idées, qui gagnent aussi des disciples en France.&lt;/p&gt; &lt;p&gt;Très vite, des adversaires dénoncent ces thèses comme contraires à la doctrine de l’Église, qui distingue nettement ce que la raison peut connaître par elle-même et ce que seule la foi apporte. La controverse fait rage de 1858 à 1861. En 1864, Rome censure une série de propositions tirées de ses ouvrages, et Ubaghs, qui se soumet, doit quitter l’enseignement. Il vit alors retiré à Louvain, où il meurt en 1875. Son école disparaît avec lui, mais elle prépare le retour au thomisme imposé à la fin du siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/darwin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ubaghs-mini.webp</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Néerlandaise</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturalisme</t>
+          <t xml:space="preserve">Ontologisme</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">naturaliste britannique, auteur de la théorie de l’évolution par la sélection naturelle.</t>
+          <t xml:space="preserve">philosophe et théologien néerlandais, chef de l’école ontologiste de Louvain.</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -8835,9 +8860,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P119">
-        <v>2</v>
-      </c>
+      <c r="P119"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1">
@@ -9374,79 +9397,79 @@
     <hyperlink ref="E10" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Giacomo_Leopardi&quot;  title=&quot; Wikipedia&quot;&gt;Giacomo LEOPARDI&lt;/a&gt;  était un poète &amp; philosophe italien souvent présenté comme l’un des plus profonds représentants du pessimisme moderne. À partir de 1819, il vit ce qu’il appelle une &quot;conversion philosophique&quot; : il quitte l’illusion d’un monde harmonieux pour la recherche du &quot;vrai&quot;, au prix d’une vision très sombre de la condition humaine. &lt;/p&gt; &lt;p&gt; Il i résume   &lt;a href=&quot;https://www.youtube.com/watch?v=2IQ7BUruaMk&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Giacomo Léopardi : Pensées par Ina Culture&quot;&gt;&quot;sa pensée &lt;/a&gt; par l’idée d’&quot;infelicità&quot;, un malheur constitutif de la condition humaine, et non pas seulement accidentel. Il se méfie de l’idée de progrès moral ou spirituel de l’h